--- a/Dziennik2024.xlsx
+++ b/Dziennik2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szybk\OneDrive\Pulpit\Studia\inzynierka\Inzynierka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36740C2-33FE-4583-841A-D9C59B04CB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A890AAD-5FF9-4B90-B715-01FD35BEA116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BF3D5F66-ACDF-49A3-8594-396AB682FC7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="210">
   <si>
     <t>Godzina</t>
   </si>
@@ -435,6 +435,237 @@
   </si>
   <si>
     <t>020*59,7E</t>
+  </si>
+  <si>
+    <t>55*49,2N</t>
+  </si>
+  <si>
+    <t>020*54,3E</t>
+  </si>
+  <si>
+    <t>F60</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>020*54,4E</t>
+  </si>
+  <si>
+    <t>56*06,7N</t>
+  </si>
+  <si>
+    <t>020*54,9E</t>
+  </si>
+  <si>
+    <t>56*16,4N</t>
+  </si>
+  <si>
+    <t>56*24,8N</t>
+  </si>
+  <si>
+    <t>020*54,6E</t>
+  </si>
+  <si>
+    <t>56*32,5N</t>
+  </si>
+  <si>
+    <t>020*56,0E</t>
+  </si>
+  <si>
+    <t>56*37,3N</t>
+  </si>
+  <si>
+    <t>020*55,6E</t>
+  </si>
+  <si>
+    <t>56*44,7N</t>
+  </si>
+  <si>
+    <t>020*53,9E</t>
+  </si>
+  <si>
+    <t>56*52,3N</t>
+  </si>
+  <si>
+    <t>020*53,5E</t>
+  </si>
+  <si>
+    <t>57*04,3N</t>
+  </si>
+  <si>
+    <t>020*56,7E</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>57*08,6N</t>
+  </si>
+  <si>
+    <t>57*16,2N</t>
+  </si>
+  <si>
+    <t>020*49,8E</t>
+  </si>
+  <si>
+    <t>57*23,5N</t>
+  </si>
+  <si>
+    <t>G87 + F60</t>
+  </si>
+  <si>
+    <t>57*39,7N</t>
+  </si>
+  <si>
+    <t>020*49,9E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G87 </t>
+  </si>
+  <si>
+    <t>WSW</t>
+  </si>
+  <si>
+    <t>57*32,3N</t>
+  </si>
+  <si>
+    <t>020*52,2E</t>
+  </si>
+  <si>
+    <t>57*47,7N</t>
+  </si>
+  <si>
+    <t>57*55,9N</t>
+  </si>
+  <si>
+    <t>58*04,1N</t>
+  </si>
+  <si>
+    <t>021*03,6E</t>
+  </si>
+  <si>
+    <t>58*11,9N</t>
+  </si>
+  <si>
+    <t>021*08,0E</t>
+  </si>
+  <si>
+    <t>58*19,7N</t>
+  </si>
+  <si>
+    <t>021*10,2E</t>
+  </si>
+  <si>
+    <t>58*26,7N</t>
+  </si>
+  <si>
+    <t>021*16,9E</t>
+  </si>
+  <si>
+    <t>58*35,6N</t>
+  </si>
+  <si>
+    <t>021*24,0E</t>
+  </si>
+  <si>
+    <t>58*41,9N</t>
+  </si>
+  <si>
+    <t>021*30,8E</t>
+  </si>
+  <si>
+    <t>58*48,6N</t>
+  </si>
+  <si>
+    <t>021*39,9E</t>
+  </si>
+  <si>
+    <t>58*56,6N</t>
+  </si>
+  <si>
+    <t>021*48,4E</t>
+  </si>
+  <si>
+    <t>59*08,3N</t>
+  </si>
+  <si>
+    <t>022*03,7E</t>
+  </si>
+  <si>
+    <t>59*01,5N</t>
+  </si>
+  <si>
+    <t>021*56,3E</t>
+  </si>
+  <si>
+    <t>59*13,6N</t>
+  </si>
+  <si>
+    <t>022*16,6E</t>
+  </si>
+  <si>
+    <t>59*18,2N</t>
+  </si>
+  <si>
+    <t>022*26,9E</t>
+  </si>
+  <si>
+    <t>59*21,5N</t>
+  </si>
+  <si>
+    <t>022*41,9E</t>
+  </si>
+  <si>
+    <t>59*22,9N</t>
+  </si>
+  <si>
+    <t>022*58,5E</t>
+  </si>
+  <si>
+    <t>59*24,7N</t>
+  </si>
+  <si>
+    <t>023*12,5E</t>
+  </si>
+  <si>
+    <t>59*27,0N</t>
+  </si>
+  <si>
+    <t>023*28,1E</t>
+  </si>
+  <si>
+    <t>59*28,9N</t>
+  </si>
+  <si>
+    <t>023*44,2E</t>
+  </si>
+  <si>
+    <t>59*30,9N</t>
+  </si>
+  <si>
+    <t>023*59,7E</t>
+  </si>
+  <si>
+    <t>59*32,8N</t>
+  </si>
+  <si>
+    <t>024*12,7E</t>
+  </si>
+  <si>
+    <t>SSW</t>
+  </si>
+  <si>
+    <t>59*31,7N</t>
+  </si>
+  <si>
+    <t>024*25,5E</t>
+  </si>
+  <si>
+    <t>59*31,6N</t>
+  </si>
+  <si>
+    <t>024*38,8E</t>
   </si>
 </sst>
 </file>
@@ -825,13 +1056,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2DB018-EC3F-4C8E-A36B-34F72611C81F}">
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
     <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -3468,6 +3700,1900 @@
       </c>
       <c r="P53">
         <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="B54" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>411.1</v>
+      </c>
+      <c r="F54" s="1">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H54" t="s">
+        <v>135</v>
+      </c>
+      <c r="I54" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54" t="s">
+        <v>136</v>
+      </c>
+      <c r="K54">
+        <v>7</v>
+      </c>
+      <c r="L54">
+        <v>4</v>
+      </c>
+      <c r="M54">
+        <v>3</v>
+      </c>
+      <c r="N54">
+        <v>7</v>
+      </c>
+      <c r="O54">
+        <v>1002</v>
+      </c>
+      <c r="P54">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="B55" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>420.2</v>
+      </c>
+      <c r="F55" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H55" t="s">
+        <v>135</v>
+      </c>
+      <c r="I55" t="s">
+        <v>26</v>
+      </c>
+      <c r="J55" t="s">
+        <v>136</v>
+      </c>
+      <c r="K55">
+        <v>6</v>
+      </c>
+      <c r="L55">
+        <v>3</v>
+      </c>
+      <c r="M55">
+        <v>3</v>
+      </c>
+      <c r="N55">
+        <v>7</v>
+      </c>
+      <c r="O55">
+        <v>1002</v>
+      </c>
+      <c r="P55">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="B56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" t="s">
+        <v>121</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>428.8</v>
+      </c>
+      <c r="F56" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H56" t="s">
+        <v>77</v>
+      </c>
+      <c r="I56" t="s">
+        <v>26</v>
+      </c>
+      <c r="J56" t="s">
+        <v>136</v>
+      </c>
+      <c r="K56">
+        <v>6</v>
+      </c>
+      <c r="L56">
+        <v>3</v>
+      </c>
+      <c r="M56">
+        <v>3</v>
+      </c>
+      <c r="N56">
+        <v>7</v>
+      </c>
+      <c r="O56">
+        <v>1002</v>
+      </c>
+      <c r="P56">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="B57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" t="s">
+        <v>139</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>438.7</v>
+      </c>
+      <c r="F57" s="1">
+        <v>9</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H57" t="s">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s">
+        <v>26</v>
+      </c>
+      <c r="J57" t="s">
+        <v>136</v>
+      </c>
+      <c r="K57">
+        <v>5</v>
+      </c>
+      <c r="L57">
+        <v>3</v>
+      </c>
+      <c r="M57">
+        <v>3</v>
+      </c>
+      <c r="N57">
+        <v>7</v>
+      </c>
+      <c r="O57">
+        <v>998</v>
+      </c>
+      <c r="P57">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="B58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" t="s">
+        <v>142</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <v>447.2</v>
+      </c>
+      <c r="F58" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H58" t="s">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s">
+        <v>26</v>
+      </c>
+      <c r="J58" t="s">
+        <v>136</v>
+      </c>
+      <c r="K58">
+        <v>5</v>
+      </c>
+      <c r="L58">
+        <v>3</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>7</v>
+      </c>
+      <c r="O58">
+        <v>997</v>
+      </c>
+      <c r="P58">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="B59" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>453.2</v>
+      </c>
+      <c r="F59" s="1">
+        <v>6</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H59" t="s">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s">
+        <v>26</v>
+      </c>
+      <c r="J59" t="s">
+        <v>136</v>
+      </c>
+      <c r="K59">
+        <v>5</v>
+      </c>
+      <c r="L59">
+        <v>3</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>5</v>
+      </c>
+      <c r="O59">
+        <v>1000</v>
+      </c>
+      <c r="P59">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>0.91666666666666796</v>
+      </c>
+      <c r="B60" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" t="s">
+        <v>146</v>
+      </c>
+      <c r="D60">
+        <v>350</v>
+      </c>
+      <c r="E60">
+        <v>460.2</v>
+      </c>
+      <c r="F60" s="1">
+        <v>7</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H60" t="s">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s">
+        <v>26</v>
+      </c>
+      <c r="J60" t="s">
+        <v>136</v>
+      </c>
+      <c r="K60">
+        <v>5</v>
+      </c>
+      <c r="L60">
+        <v>3</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>6</v>
+      </c>
+      <c r="O60">
+        <v>1000</v>
+      </c>
+      <c r="P60">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>0.95833333333333504</v>
+      </c>
+      <c r="B61" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" t="s">
+        <v>148</v>
+      </c>
+      <c r="D61">
+        <v>350</v>
+      </c>
+      <c r="E61">
+        <v>467.5</v>
+      </c>
+      <c r="F61" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H61" t="s">
+        <v>118</v>
+      </c>
+      <c r="I61" t="s">
+        <v>26</v>
+      </c>
+      <c r="J61" t="s">
+        <v>136</v>
+      </c>
+      <c r="K61">
+        <v>4</v>
+      </c>
+      <c r="L61">
+        <v>3</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>7</v>
+      </c>
+      <c r="O61">
+        <v>1000</v>
+      </c>
+      <c r="P61">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>1</v>
+      </c>
+      <c r="B62" t="s">
+        <v>149</v>
+      </c>
+      <c r="C62" t="s">
+        <v>150</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>475.7</v>
+      </c>
+      <c r="F62" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H62" t="s">
+        <v>118</v>
+      </c>
+      <c r="I62" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" t="s">
+        <v>136</v>
+      </c>
+      <c r="K62">
+        <v>5</v>
+      </c>
+      <c r="L62">
+        <v>3</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>7</v>
+      </c>
+      <c r="O62">
+        <v>999</v>
+      </c>
+      <c r="P62">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="B63" t="s">
+        <v>151</v>
+      </c>
+      <c r="C63" t="s">
+        <v>152</v>
+      </c>
+      <c r="D63">
+        <v>8</v>
+      </c>
+      <c r="E63">
+        <v>485.4</v>
+      </c>
+      <c r="F63" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H63" t="s">
+        <v>135</v>
+      </c>
+      <c r="I63" t="s">
+        <v>26</v>
+      </c>
+      <c r="J63" t="s">
+        <v>153</v>
+      </c>
+      <c r="K63">
+        <v>6</v>
+      </c>
+      <c r="L63">
+        <v>3</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>7</v>
+      </c>
+      <c r="O63">
+        <v>999</v>
+      </c>
+      <c r="P63">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>1.0833333333333399</v>
+      </c>
+      <c r="B64" t="s">
+        <v>154</v>
+      </c>
+      <c r="C64" t="s">
+        <v>148</v>
+      </c>
+      <c r="D64">
+        <v>344</v>
+      </c>
+      <c r="E64">
+        <v>493.1</v>
+      </c>
+      <c r="F64" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H64" t="s">
+        <v>135</v>
+      </c>
+      <c r="I64" t="s">
+        <v>26</v>
+      </c>
+      <c r="J64" t="s">
+        <v>153</v>
+      </c>
+      <c r="K64">
+        <v>6</v>
+      </c>
+      <c r="L64">
+        <v>3</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>7</v>
+      </c>
+      <c r="O64">
+        <v>999</v>
+      </c>
+      <c r="P64">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>1.12500000000001</v>
+      </c>
+      <c r="B65" t="s">
+        <v>155</v>
+      </c>
+      <c r="C65" t="s">
+        <v>156</v>
+      </c>
+      <c r="D65">
+        <v>345</v>
+      </c>
+      <c r="E65">
+        <v>501.1</v>
+      </c>
+      <c r="F65" s="1">
+        <v>8</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H65" t="s">
+        <v>135</v>
+      </c>
+      <c r="I65" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65" t="s">
+        <v>153</v>
+      </c>
+      <c r="K65">
+        <v>5</v>
+      </c>
+      <c r="L65">
+        <v>3</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>7</v>
+      </c>
+      <c r="O65">
+        <v>1000</v>
+      </c>
+      <c r="P65">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>1.1666666666666801</v>
+      </c>
+      <c r="B66" t="s">
+        <v>157</v>
+      </c>
+      <c r="C66" t="s">
+        <v>110</v>
+      </c>
+      <c r="D66">
+        <v>341</v>
+      </c>
+      <c r="E66">
+        <v>509.2</v>
+      </c>
+      <c r="F66" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H66" t="s">
+        <v>158</v>
+      </c>
+      <c r="I66" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66" t="s">
+        <v>153</v>
+      </c>
+      <c r="K66">
+        <v>5</v>
+      </c>
+      <c r="L66">
+        <v>3</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>7</v>
+      </c>
+      <c r="O66">
+        <v>999</v>
+      </c>
+      <c r="P66">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>1.2083333333333499</v>
+      </c>
+      <c r="B67" t="s">
+        <v>163</v>
+      </c>
+      <c r="C67" t="s">
+        <v>160</v>
+      </c>
+      <c r="D67">
+        <v>10</v>
+      </c>
+      <c r="E67">
+        <v>518.6</v>
+      </c>
+      <c r="F67" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H67" t="s">
+        <v>161</v>
+      </c>
+      <c r="I67" t="s">
+        <v>26</v>
+      </c>
+      <c r="J67" t="s">
+        <v>162</v>
+      </c>
+      <c r="K67">
+        <v>5</v>
+      </c>
+      <c r="L67">
+        <v>3</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>7</v>
+      </c>
+      <c r="O67">
+        <v>999</v>
+      </c>
+      <c r="P67">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>1.25000000000002</v>
+      </c>
+      <c r="B68" t="s">
+        <v>159</v>
+      </c>
+      <c r="C68" t="s">
+        <v>164</v>
+      </c>
+      <c r="D68">
+        <v>12</v>
+      </c>
+      <c r="E68">
+        <v>526.4</v>
+      </c>
+      <c r="F68" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H68" t="s">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s">
+        <v>26</v>
+      </c>
+      <c r="J68" t="s">
+        <v>49</v>
+      </c>
+      <c r="K68">
+        <v>5</v>
+      </c>
+      <c r="L68">
+        <v>3</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>7</v>
+      </c>
+      <c r="O68">
+        <v>998</v>
+      </c>
+      <c r="P68">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>1.2916666666666901</v>
+      </c>
+      <c r="B69" t="s">
+        <v>165</v>
+      </c>
+      <c r="C69" t="s">
+        <v>139</v>
+      </c>
+      <c r="D69">
+        <v>10</v>
+      </c>
+      <c r="E69">
+        <v>534.6</v>
+      </c>
+      <c r="F69" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H69" t="s">
+        <v>77</v>
+      </c>
+      <c r="I69" t="s">
+        <v>26</v>
+      </c>
+      <c r="J69" t="s">
+        <v>49</v>
+      </c>
+      <c r="K69">
+        <v>5</v>
+      </c>
+      <c r="L69">
+        <v>3</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>7</v>
+      </c>
+      <c r="O69">
+        <v>998</v>
+      </c>
+      <c r="P69">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>1.3333333333333599</v>
+      </c>
+      <c r="B70" t="s">
+        <v>166</v>
+      </c>
+      <c r="C70" t="s">
+        <v>130</v>
+      </c>
+      <c r="D70">
+        <v>10</v>
+      </c>
+      <c r="E70">
+        <v>543.29999999999995</v>
+      </c>
+      <c r="F70" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H70" t="s">
+        <v>77</v>
+      </c>
+      <c r="I70" t="s">
+        <v>26</v>
+      </c>
+      <c r="J70" t="s">
+        <v>49</v>
+      </c>
+      <c r="K70">
+        <v>5</v>
+      </c>
+      <c r="L70">
+        <v>4</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>7</v>
+      </c>
+      <c r="O70">
+        <v>998</v>
+      </c>
+      <c r="P70">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>1.37500000000003</v>
+      </c>
+      <c r="B71" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" t="s">
+        <v>168</v>
+      </c>
+      <c r="D71">
+        <v>20</v>
+      </c>
+      <c r="E71">
+        <v>551.79999999999995</v>
+      </c>
+      <c r="F71" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H71" t="s">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s">
+        <v>26</v>
+      </c>
+      <c r="J71" t="s">
+        <v>49</v>
+      </c>
+      <c r="K71">
+        <v>5</v>
+      </c>
+      <c r="L71">
+        <v>4</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>7</v>
+      </c>
+      <c r="O71">
+        <v>1000</v>
+      </c>
+      <c r="P71">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>1.4166666666667</v>
+      </c>
+      <c r="B72" t="s">
+        <v>169</v>
+      </c>
+      <c r="C72" t="s">
+        <v>170</v>
+      </c>
+      <c r="D72">
+        <v>15</v>
+      </c>
+      <c r="E72">
+        <v>560.4</v>
+      </c>
+      <c r="F72" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H72" t="s">
+        <v>77</v>
+      </c>
+      <c r="I72" t="s">
+        <v>26</v>
+      </c>
+      <c r="J72" t="s">
+        <v>27</v>
+      </c>
+      <c r="K72">
+        <v>5</v>
+      </c>
+      <c r="L72">
+        <v>4</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>7</v>
+      </c>
+      <c r="O72">
+        <v>1000</v>
+      </c>
+      <c r="P72">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>1.4583333333333699</v>
+      </c>
+      <c r="B73" t="s">
+        <v>171</v>
+      </c>
+      <c r="C73" t="s">
+        <v>172</v>
+      </c>
+      <c r="D73">
+        <v>10</v>
+      </c>
+      <c r="E73">
+        <v>568.20000000000005</v>
+      </c>
+      <c r="F73" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H73" t="s">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s">
+        <v>26</v>
+      </c>
+      <c r="J73" t="s">
+        <v>27</v>
+      </c>
+      <c r="K73">
+        <v>5</v>
+      </c>
+      <c r="L73">
+        <v>4</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>7</v>
+      </c>
+      <c r="O73">
+        <v>1001</v>
+      </c>
+      <c r="P73">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>1.50000000000004</v>
+      </c>
+      <c r="B74" t="s">
+        <v>173</v>
+      </c>
+      <c r="C74" t="s">
+        <v>174</v>
+      </c>
+      <c r="D74">
+        <v>43</v>
+      </c>
+      <c r="E74">
+        <v>576.5</v>
+      </c>
+      <c r="F74" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H74" t="s">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s">
+        <v>26</v>
+      </c>
+      <c r="J74" t="s">
+        <v>27</v>
+      </c>
+      <c r="K74">
+        <v>5</v>
+      </c>
+      <c r="L74">
+        <v>4</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>7</v>
+      </c>
+      <c r="O74">
+        <v>1001</v>
+      </c>
+      <c r="P74">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>1.54166666666671</v>
+      </c>
+      <c r="B75" t="s">
+        <v>175</v>
+      </c>
+      <c r="C75" t="s">
+        <v>176</v>
+      </c>
+      <c r="D75">
+        <v>16</v>
+      </c>
+      <c r="E75">
+        <v>586.1</v>
+      </c>
+      <c r="F75" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H75" t="s">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s">
+        <v>26</v>
+      </c>
+      <c r="J75" t="s">
+        <v>49</v>
+      </c>
+      <c r="K75">
+        <v>5</v>
+      </c>
+      <c r="L75">
+        <v>4</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>7</v>
+      </c>
+      <c r="O75">
+        <v>1001</v>
+      </c>
+      <c r="P75">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>1.5833333333333801</v>
+      </c>
+      <c r="B76" t="s">
+        <v>177</v>
+      </c>
+      <c r="C76" t="s">
+        <v>178</v>
+      </c>
+      <c r="D76">
+        <v>30</v>
+      </c>
+      <c r="E76">
+        <v>594.20000000000005</v>
+      </c>
+      <c r="F76" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H76" t="s">
+        <v>77</v>
+      </c>
+      <c r="I76" t="s">
+        <v>26</v>
+      </c>
+      <c r="J76" t="s">
+        <v>49</v>
+      </c>
+      <c r="K76">
+        <v>5</v>
+      </c>
+      <c r="L76">
+        <v>4</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>7</v>
+      </c>
+      <c r="O76">
+        <v>1002</v>
+      </c>
+      <c r="P76">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>1.62500000000005</v>
+      </c>
+      <c r="B77" t="s">
+        <v>179</v>
+      </c>
+      <c r="C77" t="s">
+        <v>180</v>
+      </c>
+      <c r="D77">
+        <v>30</v>
+      </c>
+      <c r="E77">
+        <v>602.1</v>
+      </c>
+      <c r="F77" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H77" t="s">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J77" t="s">
+        <v>49</v>
+      </c>
+      <c r="K77">
+        <v>5</v>
+      </c>
+      <c r="L77">
+        <v>4</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>7</v>
+      </c>
+      <c r="O77">
+        <v>1002</v>
+      </c>
+      <c r="P77">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>1.66666666666672</v>
+      </c>
+      <c r="B78" t="s">
+        <v>181</v>
+      </c>
+      <c r="C78" t="s">
+        <v>182</v>
+      </c>
+      <c r="D78">
+        <v>25</v>
+      </c>
+      <c r="E78">
+        <v>612.70000000000005</v>
+      </c>
+      <c r="F78" s="1">
+        <v>10.3</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H78" t="s">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s">
+        <v>26</v>
+      </c>
+      <c r="J78" t="s">
+        <v>49</v>
+      </c>
+      <c r="K78">
+        <v>5</v>
+      </c>
+      <c r="L78">
+        <v>4</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>7</v>
+      </c>
+      <c r="O78">
+        <v>1002</v>
+      </c>
+      <c r="P78">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>1.7083333333333901</v>
+      </c>
+      <c r="B79" t="s">
+        <v>185</v>
+      </c>
+      <c r="C79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D79">
+        <v>25</v>
+      </c>
+      <c r="E79">
+        <v>620</v>
+      </c>
+      <c r="F79" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H79" t="s">
+        <v>77</v>
+      </c>
+      <c r="I79" t="s">
+        <v>26</v>
+      </c>
+      <c r="J79" t="s">
+        <v>49</v>
+      </c>
+      <c r="K79">
+        <v>5</v>
+      </c>
+      <c r="L79">
+        <v>4</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>7</v>
+      </c>
+      <c r="O79">
+        <v>1002</v>
+      </c>
+      <c r="P79">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>1.75000000000006</v>
+      </c>
+      <c r="B80" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" t="s">
+        <v>184</v>
+      </c>
+      <c r="D80">
+        <v>54</v>
+      </c>
+      <c r="E80">
+        <v>626.1</v>
+      </c>
+      <c r="F80" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H80" t="s">
+        <v>118</v>
+      </c>
+      <c r="I80" t="s">
+        <v>26</v>
+      </c>
+      <c r="J80" t="s">
+        <v>153</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+      <c r="L80">
+        <v>3</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80">
+        <v>7</v>
+      </c>
+      <c r="O80">
+        <v>1000</v>
+      </c>
+      <c r="P80">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>1.79166666666673</v>
+      </c>
+      <c r="B81" t="s">
+        <v>187</v>
+      </c>
+      <c r="C81" t="s">
+        <v>188</v>
+      </c>
+      <c r="D81">
+        <v>54</v>
+      </c>
+      <c r="E81">
+        <v>634.6</v>
+      </c>
+      <c r="F81" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H81" t="s">
+        <v>118</v>
+      </c>
+      <c r="I81" t="s">
+        <v>26</v>
+      </c>
+      <c r="J81" t="s">
+        <v>162</v>
+      </c>
+      <c r="K81">
+        <v>2</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>7</v>
+      </c>
+      <c r="O81">
+        <v>1000</v>
+      </c>
+      <c r="P81">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>1.8333333333334001</v>
+      </c>
+      <c r="B82" t="s">
+        <v>189</v>
+      </c>
+      <c r="C82" t="s">
+        <v>190</v>
+      </c>
+      <c r="D82">
+        <v>54</v>
+      </c>
+      <c r="E82">
+        <v>641.70000000000005</v>
+      </c>
+      <c r="F82" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H82" t="s">
+        <v>118</v>
+      </c>
+      <c r="I82" t="s">
+        <v>26</v>
+      </c>
+      <c r="J82" t="s">
+        <v>162</v>
+      </c>
+      <c r="K82">
+        <v>2</v>
+      </c>
+      <c r="L82">
+        <v>2</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>7</v>
+      </c>
+      <c r="O82">
+        <v>1000</v>
+      </c>
+      <c r="P82">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>1.8750000000000699</v>
+      </c>
+      <c r="B83" t="s">
+        <v>191</v>
+      </c>
+      <c r="C83" t="s">
+        <v>192</v>
+      </c>
+      <c r="D83">
+        <v>80</v>
+      </c>
+      <c r="E83">
+        <v>650.4</v>
+      </c>
+      <c r="F83" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H83" t="s">
+        <v>118</v>
+      </c>
+      <c r="I83" t="s">
+        <v>26</v>
+      </c>
+      <c r="J83" t="s">
+        <v>153</v>
+      </c>
+      <c r="K83">
+        <v>4</v>
+      </c>
+      <c r="L83">
+        <v>3</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>7</v>
+      </c>
+      <c r="O83">
+        <v>1001</v>
+      </c>
+      <c r="P83">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>1.91666666666674</v>
+      </c>
+      <c r="B84" t="s">
+        <v>193</v>
+      </c>
+      <c r="C84" t="s">
+        <v>194</v>
+      </c>
+      <c r="D84">
+        <v>80</v>
+      </c>
+      <c r="E84">
+        <v>659.6</v>
+      </c>
+      <c r="F84" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H84" t="s">
+        <v>118</v>
+      </c>
+      <c r="I84" t="s">
+        <v>26</v>
+      </c>
+      <c r="J84" t="s">
+        <v>153</v>
+      </c>
+      <c r="K84">
+        <v>4</v>
+      </c>
+      <c r="L84">
+        <v>3</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>7</v>
+      </c>
+      <c r="O84">
+        <v>1001</v>
+      </c>
+      <c r="P84">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>1.9583333333334101</v>
+      </c>
+      <c r="B85" t="s">
+        <v>195</v>
+      </c>
+      <c r="C85" t="s">
+        <v>196</v>
+      </c>
+      <c r="D85">
+        <v>80</v>
+      </c>
+      <c r="E85">
+        <v>666.6</v>
+      </c>
+      <c r="F85" s="1">
+        <v>7</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H85" t="s">
+        <v>118</v>
+      </c>
+      <c r="I85" t="s">
+        <v>26</v>
+      </c>
+      <c r="J85" t="s">
+        <v>153</v>
+      </c>
+      <c r="K85">
+        <v>4</v>
+      </c>
+      <c r="L85">
+        <v>3</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>7</v>
+      </c>
+      <c r="O85">
+        <v>1001</v>
+      </c>
+      <c r="P85">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>2.0000000000000799</v>
+      </c>
+      <c r="B86" t="s">
+        <v>197</v>
+      </c>
+      <c r="C86" t="s">
+        <v>198</v>
+      </c>
+      <c r="D86">
+        <v>73</v>
+      </c>
+      <c r="E86">
+        <v>674.9</v>
+      </c>
+      <c r="F86" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H86" t="s">
+        <v>118</v>
+      </c>
+      <c r="I86" t="s">
+        <v>26</v>
+      </c>
+      <c r="J86" t="s">
+        <v>153</v>
+      </c>
+      <c r="K86">
+        <v>4</v>
+      </c>
+      <c r="L86">
+        <v>3</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>7</v>
+      </c>
+      <c r="O86">
+        <v>1001</v>
+      </c>
+      <c r="P86">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>2.04166666666675</v>
+      </c>
+      <c r="B87" t="s">
+        <v>199</v>
+      </c>
+      <c r="C87" t="s">
+        <v>200</v>
+      </c>
+      <c r="D87">
+        <v>71</v>
+      </c>
+      <c r="E87">
+        <v>683.4</v>
+      </c>
+      <c r="F87" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H87" t="s">
+        <v>118</v>
+      </c>
+      <c r="I87" t="s">
+        <v>26</v>
+      </c>
+      <c r="J87" t="s">
+        <v>162</v>
+      </c>
+      <c r="K87">
+        <v>6</v>
+      </c>
+      <c r="L87">
+        <v>3</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87">
+        <v>7</v>
+      </c>
+      <c r="O87">
+        <v>1001</v>
+      </c>
+      <c r="P87">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>2.0833333333334201</v>
+      </c>
+      <c r="B88" t="s">
+        <v>201</v>
+      </c>
+      <c r="C88" t="s">
+        <v>202</v>
+      </c>
+      <c r="D88">
+        <v>70</v>
+      </c>
+      <c r="E88">
+        <v>691.7</v>
+      </c>
+      <c r="F88" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H88" t="s">
+        <v>118</v>
+      </c>
+      <c r="I88" t="s">
+        <v>26</v>
+      </c>
+      <c r="J88" t="s">
+        <v>162</v>
+      </c>
+      <c r="K88">
+        <v>6</v>
+      </c>
+      <c r="L88">
+        <v>3</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>7</v>
+      </c>
+      <c r="O88">
+        <v>1001</v>
+      </c>
+      <c r="P88">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>2.1250000000000902</v>
+      </c>
+      <c r="B89" t="s">
+        <v>203</v>
+      </c>
+      <c r="C89" t="s">
+        <v>204</v>
+      </c>
+      <c r="D89">
+        <v>70</v>
+      </c>
+      <c r="E89">
+        <v>699.5</v>
+      </c>
+      <c r="F89" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H89" t="s">
+        <v>118</v>
+      </c>
+      <c r="I89" t="s">
+        <v>26</v>
+      </c>
+      <c r="J89" t="s">
+        <v>205</v>
+      </c>
+      <c r="K89">
+        <v>5</v>
+      </c>
+      <c r="L89">
+        <v>3</v>
+      </c>
+      <c r="M89">
+        <v>2</v>
+      </c>
+      <c r="N89">
+        <v>7</v>
+      </c>
+      <c r="O89">
+        <v>1001</v>
+      </c>
+      <c r="P89">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>2.1666666666667602</v>
+      </c>
+      <c r="B90" t="s">
+        <v>206</v>
+      </c>
+      <c r="C90" t="s">
+        <v>207</v>
+      </c>
+      <c r="D90">
+        <v>100</v>
+      </c>
+      <c r="E90">
+        <v>705.3</v>
+      </c>
+      <c r="F90" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I90" t="s">
+        <v>26</v>
+      </c>
+      <c r="J90" t="s">
+        <v>205</v>
+      </c>
+      <c r="K90">
+        <v>5</v>
+      </c>
+      <c r="L90">
+        <v>3</v>
+      </c>
+      <c r="M90">
+        <v>2</v>
+      </c>
+      <c r="N90">
+        <v>7</v>
+      </c>
+      <c r="O90">
+        <v>1001</v>
+      </c>
+      <c r="P90">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>2.2083333333334298</v>
+      </c>
+      <c r="B91" t="s">
+        <v>208</v>
+      </c>
+      <c r="C91" t="s">
+        <v>209</v>
+      </c>
+      <c r="D91">
+        <v>340</v>
+      </c>
+      <c r="E91">
+        <v>710.5</v>
+      </c>
+      <c r="F91" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I91" t="s">
+        <v>26</v>
+      </c>
+      <c r="J91" t="s">
+        <v>205</v>
+      </c>
+      <c r="K91">
+        <v>4</v>
+      </c>
+      <c r="L91">
+        <v>2</v>
+      </c>
+      <c r="M91">
+        <v>2</v>
+      </c>
+      <c r="N91">
+        <v>7</v>
+      </c>
+      <c r="O91">
+        <v>1001</v>
+      </c>
+      <c r="P91">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Dziennik2024.xlsx
+++ b/Dziennik2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szybk\OneDrive\Pulpit\Studia\inzynierka\Inzynierka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A890AAD-5FF9-4B90-B715-01FD35BEA116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F0F61B-DC6B-489A-A45B-DC434A142A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BF3D5F66-ACDF-49A3-8594-396AB682FC7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="484">
   <si>
     <t>Godzina</t>
   </si>
@@ -666,6 +666,828 @@
   </si>
   <si>
     <t>024*38,8E</t>
+  </si>
+  <si>
+    <t>024*55,4E</t>
+  </si>
+  <si>
+    <t>024*49,6E</t>
+  </si>
+  <si>
+    <t>024*42,9E</t>
+  </si>
+  <si>
+    <t>024*36,7E</t>
+  </si>
+  <si>
+    <t>59*37,9N</t>
+  </si>
+  <si>
+    <t>59*45,6N</t>
+  </si>
+  <si>
+    <t>59*53,2N</t>
+  </si>
+  <si>
+    <t>59*59,7N</t>
+  </si>
+  <si>
+    <t>60*04,3N</t>
+  </si>
+  <si>
+    <t>025*03,1E</t>
+  </si>
+  <si>
+    <t>59*59,2N</t>
+  </si>
+  <si>
+    <t>025*12,9E</t>
+  </si>
+  <si>
+    <t>59*54,4N</t>
+  </si>
+  <si>
+    <t>025*24,0E</t>
+  </si>
+  <si>
+    <t>59*50,1N</t>
+  </si>
+  <si>
+    <t>025*33,9E</t>
+  </si>
+  <si>
+    <t>59*45,4N</t>
+  </si>
+  <si>
+    <t>025*42,9E</t>
+  </si>
+  <si>
+    <t>59*41,2N</t>
+  </si>
+  <si>
+    <t>025*49,8E</t>
+  </si>
+  <si>
+    <t>59*38,7N</t>
+  </si>
+  <si>
+    <t>025*54,9E</t>
+  </si>
+  <si>
+    <t>59*39,7N</t>
+  </si>
+  <si>
+    <t>025*52,9E</t>
+  </si>
+  <si>
+    <t>59*42,0N</t>
+  </si>
+  <si>
+    <t>025*43,3E</t>
+  </si>
+  <si>
+    <t>59*38,8N</t>
+  </si>
+  <si>
+    <t>025*38,2E</t>
+  </si>
+  <si>
+    <t>G100</t>
+  </si>
+  <si>
+    <t>59*36,7N</t>
+  </si>
+  <si>
+    <t>025*36,6E</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>59*39,8N</t>
+  </si>
+  <si>
+    <t>025*25,5E</t>
+  </si>
+  <si>
+    <t>59*40,0N</t>
+  </si>
+  <si>
+    <t>025*15,7E</t>
+  </si>
+  <si>
+    <t>025*04,4E</t>
+  </si>
+  <si>
+    <t>ESE</t>
+  </si>
+  <si>
+    <t>59*38,5N</t>
+  </si>
+  <si>
+    <t>024*53,1E</t>
+  </si>
+  <si>
+    <t>59*34,9N</t>
+  </si>
+  <si>
+    <t>024*43,1E</t>
+  </si>
+  <si>
+    <t>59*28,8N</t>
+  </si>
+  <si>
+    <t>024*44,8E</t>
+  </si>
+  <si>
+    <t>59*27,8N</t>
+  </si>
+  <si>
+    <t>024*12,1E</t>
+  </si>
+  <si>
+    <t>024*07,8E</t>
+  </si>
+  <si>
+    <t>59*26,1N</t>
+  </si>
+  <si>
+    <t>024*03,8E</t>
+  </si>
+  <si>
+    <t>59*24,0N</t>
+  </si>
+  <si>
+    <t>024*00,1E</t>
+  </si>
+  <si>
+    <t>59*24,8N</t>
+  </si>
+  <si>
+    <t>023*59,2E</t>
+  </si>
+  <si>
+    <t>N NW</t>
+  </si>
+  <si>
+    <t>023*59,4E</t>
+  </si>
+  <si>
+    <t>59*26,6N</t>
+  </si>
+  <si>
+    <t>023*55,4E</t>
+  </si>
+  <si>
+    <t>59*27,5N</t>
+  </si>
+  <si>
+    <t>023*45,5E</t>
+  </si>
+  <si>
+    <t>023*35,4E</t>
+  </si>
+  <si>
+    <t>59*29,2N</t>
+  </si>
+  <si>
+    <t>023*23,4E</t>
+  </si>
+  <si>
+    <t>023*12,4E</t>
+  </si>
+  <si>
+    <t>59*27,1N</t>
+  </si>
+  <si>
+    <t>022*57,9E</t>
+  </si>
+  <si>
+    <t>59*26,7N</t>
+  </si>
+  <si>
+    <t>022*49,0E</t>
+  </si>
+  <si>
+    <t>59*21,1N</t>
+  </si>
+  <si>
+    <t>022*48,0E</t>
+  </si>
+  <si>
+    <t>59*18,0N</t>
+  </si>
+  <si>
+    <t>022*45,4E</t>
+  </si>
+  <si>
+    <t>59*18,1N</t>
+  </si>
+  <si>
+    <t>022*34,1E</t>
+  </si>
+  <si>
+    <t>59*18,9N</t>
+  </si>
+  <si>
+    <t>022*21,7E</t>
+  </si>
+  <si>
+    <t>59*20,1N</t>
+  </si>
+  <si>
+    <t>022*08,4E</t>
+  </si>
+  <si>
+    <t>59*20,9N</t>
+  </si>
+  <si>
+    <t>021*56,4E</t>
+  </si>
+  <si>
+    <t>021*40,6E</t>
+  </si>
+  <si>
+    <t>59*20,6N</t>
+  </si>
+  <si>
+    <t>021*33,4E</t>
+  </si>
+  <si>
+    <t>59*19,4N</t>
+  </si>
+  <si>
+    <t>021*22,9E</t>
+  </si>
+  <si>
+    <t>59*17,9N</t>
+  </si>
+  <si>
+    <t>021*10,9E</t>
+  </si>
+  <si>
+    <t>59*16,1N</t>
+  </si>
+  <si>
+    <t>020*57,4E</t>
+  </si>
+  <si>
+    <t>59*15,1N</t>
+  </si>
+  <si>
+    <t>SSE</t>
+  </si>
+  <si>
+    <t>59*12,3N</t>
+  </si>
+  <si>
+    <t>020*37,2E</t>
+  </si>
+  <si>
+    <t>59*09,9N</t>
+  </si>
+  <si>
+    <t>020*25,6E</t>
+  </si>
+  <si>
+    <t>59*09,1N</t>
+  </si>
+  <si>
+    <t>020*14,9E</t>
+  </si>
+  <si>
+    <t>020*25,1E</t>
+  </si>
+  <si>
+    <t>59*18,6N</t>
+  </si>
+  <si>
+    <t>020*32,6E</t>
+  </si>
+  <si>
+    <t>59*22,8N</t>
+  </si>
+  <si>
+    <t>020*41,5E</t>
+  </si>
+  <si>
+    <t>59*29,0N</t>
+  </si>
+  <si>
+    <t>020*47,1E</t>
+  </si>
+  <si>
+    <t>59*27,3N</t>
+  </si>
+  <si>
+    <t>020*50,7E</t>
+  </si>
+  <si>
+    <t>59*32,1N</t>
+  </si>
+  <si>
+    <t>021*00,8E</t>
+  </si>
+  <si>
+    <t>59*38,0N</t>
+  </si>
+  <si>
+    <t>021*12,4E</t>
+  </si>
+  <si>
+    <t>59*43,6N</t>
+  </si>
+  <si>
+    <t>021*21,7E</t>
+  </si>
+  <si>
+    <t>59*54,7N</t>
+  </si>
+  <si>
+    <t>021*31,1E</t>
+  </si>
+  <si>
+    <t>60*05,0N</t>
+  </si>
+  <si>
+    <t>21*11,5E</t>
+  </si>
+  <si>
+    <t>60*05,1N</t>
+  </si>
+  <si>
+    <t>21*04,2E</t>
+  </si>
+  <si>
+    <t>60*04,1N</t>
+  </si>
+  <si>
+    <t>20*56,6E</t>
+  </si>
+  <si>
+    <t>60*00,8N</t>
+  </si>
+  <si>
+    <t>19*50,4E</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>59*57,0N</t>
+  </si>
+  <si>
+    <t>19*42,1E</t>
+  </si>
+  <si>
+    <t>59*53,7N</t>
+  </si>
+  <si>
+    <t>19*31,3E</t>
+  </si>
+  <si>
+    <t>59*50,6N</t>
+  </si>
+  <si>
+    <t>19*33,4E</t>
+  </si>
+  <si>
+    <t>59*56,8N</t>
+  </si>
+  <si>
+    <t>19*40,8E</t>
+  </si>
+  <si>
+    <t>59*42,8N</t>
+  </si>
+  <si>
+    <t>19*51,3E</t>
+  </si>
+  <si>
+    <t>59*37,2N</t>
+  </si>
+  <si>
+    <t>20*00,9E</t>
+  </si>
+  <si>
+    <t>59*32,6N</t>
+  </si>
+  <si>
+    <t>20*05,4E</t>
+  </si>
+  <si>
+    <t>59*29,7N</t>
+  </si>
+  <si>
+    <t>19*55,6E</t>
+  </si>
+  <si>
+    <t>59*29,5N</t>
+  </si>
+  <si>
+    <t>19*49,0E</t>
+  </si>
+  <si>
+    <t>59*26,2N</t>
+  </si>
+  <si>
+    <t>19*47,5E</t>
+  </si>
+  <si>
+    <t>59*24,2N</t>
+  </si>
+  <si>
+    <t>19*45,3E</t>
+  </si>
+  <si>
+    <t>19*47,0E</t>
+  </si>
+  <si>
+    <t>19*39,9E</t>
+  </si>
+  <si>
+    <t>59*12,7N</t>
+  </si>
+  <si>
+    <t>19*33,7E</t>
+  </si>
+  <si>
+    <t>59*05,6N</t>
+  </si>
+  <si>
+    <t>19*28,0E</t>
+  </si>
+  <si>
+    <t>58*59,4N</t>
+  </si>
+  <si>
+    <t>19*23,8E</t>
+  </si>
+  <si>
+    <t>58*55,1N</t>
+  </si>
+  <si>
+    <t>19*21,2E</t>
+  </si>
+  <si>
+    <t>58*43,8N</t>
+  </si>
+  <si>
+    <t>19*14,5E</t>
+  </si>
+  <si>
+    <t>19*18,5E</t>
+  </si>
+  <si>
+    <t>58*49,8N</t>
+  </si>
+  <si>
+    <t>58*38,0N</t>
+  </si>
+  <si>
+    <t>19*09,1E</t>
+  </si>
+  <si>
+    <t>58*30,4N</t>
+  </si>
+  <si>
+    <t>19*04,1E</t>
+  </si>
+  <si>
+    <t>58*26,0N</t>
+  </si>
+  <si>
+    <t>19*00,2E</t>
+  </si>
+  <si>
+    <t>58*19,8N</t>
+  </si>
+  <si>
+    <t>18*52,3E</t>
+  </si>
+  <si>
+    <t>58*13,0N</t>
+  </si>
+  <si>
+    <t>18*45,3E</t>
+  </si>
+  <si>
+    <t>58*06,7N</t>
+  </si>
+  <si>
+    <t>18*31,1E</t>
+  </si>
+  <si>
+    <t>57*59,9N</t>
+  </si>
+  <si>
+    <t>18*28,3E</t>
+  </si>
+  <si>
+    <t>57*53,6N</t>
+  </si>
+  <si>
+    <t>18*06,1E</t>
+  </si>
+  <si>
+    <t>57*47,6N</t>
+  </si>
+  <si>
+    <t>18*18,1E</t>
+  </si>
+  <si>
+    <t>17*54,8E</t>
+  </si>
+  <si>
+    <t>57*40,3N</t>
+  </si>
+  <si>
+    <t>57*33,9N</t>
+  </si>
+  <si>
+    <t>17*44,6E</t>
+  </si>
+  <si>
+    <t>57*25,5N</t>
+  </si>
+  <si>
+    <t>17*34,6E</t>
+  </si>
+  <si>
+    <t>57*18,2N</t>
+  </si>
+  <si>
+    <t>17*30,7E</t>
+  </si>
+  <si>
+    <t>57*09,4N</t>
+  </si>
+  <si>
+    <t>17*25,7E</t>
+  </si>
+  <si>
+    <t>57*00,5N</t>
+  </si>
+  <si>
+    <t>17*21,0E</t>
+  </si>
+  <si>
+    <t>56*52,5N</t>
+  </si>
+  <si>
+    <t>17*15,9E</t>
+  </si>
+  <si>
+    <t>56*44,8N</t>
+  </si>
+  <si>
+    <t>56*36,8N</t>
+  </si>
+  <si>
+    <t>17*00,7E</t>
+  </si>
+  <si>
+    <t>17*07,7E</t>
+  </si>
+  <si>
+    <t>16*52,6E</t>
+  </si>
+  <si>
+    <t>56*20,5N</t>
+  </si>
+  <si>
+    <t>16*45,3E</t>
+  </si>
+  <si>
+    <t>56*13,9N</t>
+  </si>
+  <si>
+    <t>16*39,2E</t>
+  </si>
+  <si>
+    <t>56*07,9N</t>
+  </si>
+  <si>
+    <t>16*33,1E</t>
+  </si>
+  <si>
+    <t>56*01,6N</t>
+  </si>
+  <si>
+    <t>16*28,7E</t>
+  </si>
+  <si>
+    <t>55*53,6N</t>
+  </si>
+  <si>
+    <t>16*13,2E</t>
+  </si>
+  <si>
+    <t>16*23,7E</t>
+  </si>
+  <si>
+    <t>55*45,4N</t>
+  </si>
+  <si>
+    <t>16*18,5E</t>
+  </si>
+  <si>
+    <t>55*34,8N</t>
+  </si>
+  <si>
+    <t>55*28,7N</t>
+  </si>
+  <si>
+    <t>16*07,5E</t>
+  </si>
+  <si>
+    <t>55*21,1N</t>
+  </si>
+  <si>
+    <t>16*02,6E</t>
+  </si>
+  <si>
+    <t>55*13,4N</t>
+  </si>
+  <si>
+    <t>54*57,8N</t>
+  </si>
+  <si>
+    <t>15*56,8E</t>
+  </si>
+  <si>
+    <t>55*05,6N</t>
+  </si>
+  <si>
+    <t>15*46,6E</t>
+  </si>
+  <si>
+    <t>15*05,1E</t>
+  </si>
+  <si>
+    <t>54*49,8N</t>
+  </si>
+  <si>
+    <t>15*38,6E</t>
+  </si>
+  <si>
+    <t>54*44,9N</t>
+  </si>
+  <si>
+    <t>15*32,1E</t>
+  </si>
+  <si>
+    <t>54*36,5N</t>
+  </si>
+  <si>
+    <t>15*23,2E</t>
+  </si>
+  <si>
+    <t>54*32,9N</t>
+  </si>
+  <si>
+    <t>15*15,3E</t>
+  </si>
+  <si>
+    <t>54*25,5N</t>
+  </si>
+  <si>
+    <t>15*04,8E</t>
+  </si>
+  <si>
+    <t>54*20,5N</t>
+  </si>
+  <si>
+    <t>54*12,4N</t>
+  </si>
+  <si>
+    <t>14*57,8E</t>
+  </si>
+  <si>
+    <t>14*46,7E</t>
+  </si>
+  <si>
+    <t>54*09,6N</t>
+  </si>
+  <si>
+    <t>14*40,6E</t>
+  </si>
+  <si>
+    <t>54*06,1N</t>
+  </si>
+  <si>
+    <t>14*31,2E</t>
+  </si>
+  <si>
+    <t>54*02,1N</t>
+  </si>
+  <si>
+    <t>14*24,2E</t>
+  </si>
+  <si>
+    <t>53*58,4N</t>
+  </si>
+  <si>
+    <t>14*17,8E</t>
+  </si>
+  <si>
+    <t>54*02,3N</t>
+  </si>
+  <si>
+    <t>14*21,8E</t>
+  </si>
+  <si>
+    <t>54*04,4N</t>
+  </si>
+  <si>
+    <t>14*24,8E</t>
+  </si>
+  <si>
+    <t>54*05,8N</t>
+  </si>
+  <si>
+    <t>14*25,3E</t>
+  </si>
+  <si>
+    <t>54*07,7N</t>
+  </si>
+  <si>
+    <t>14*25,8E</t>
+  </si>
+  <si>
+    <t>54*10,1N</t>
+  </si>
+  <si>
+    <t>14*26,0E</t>
+  </si>
+  <si>
+    <t>54*15,0N</t>
+  </si>
+  <si>
+    <t>14*25,0E</t>
+  </si>
+  <si>
+    <t>54*17,2N</t>
+  </si>
+  <si>
+    <t>54*21,1N</t>
+  </si>
+  <si>
+    <t>54*24,8N</t>
+  </si>
+  <si>
+    <t>14*27,5E</t>
+  </si>
+  <si>
+    <t>54*27,5N</t>
+  </si>
+  <si>
+    <t>14*33,6E</t>
+  </si>
+  <si>
+    <t>54*35,1N</t>
+  </si>
+  <si>
+    <t>14*30,8E</t>
+  </si>
+  <si>
+    <t>54*40,1N</t>
+  </si>
+  <si>
+    <t>14*30,6E</t>
+  </si>
+  <si>
+    <t>54*44,4N</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>54*52,5N</t>
+  </si>
+  <si>
+    <t>14*27,1E</t>
+  </si>
+  <si>
+    <t>54*57,1N</t>
+  </si>
+  <si>
+    <t>14*32,5E</t>
+  </si>
+  <si>
+    <t>14*48,2E</t>
+  </si>
+  <si>
+    <t>SWS</t>
+  </si>
+  <si>
+    <t>54*58,1N</t>
+  </si>
+  <si>
+    <t>15*02,0E</t>
+  </si>
+  <si>
+    <t>G`</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2DB018-EC3F-4C8E-A36B-34F72611C81F}">
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:P231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -5524,6 +6346,9 @@
       <c r="G90" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="H90" t="s">
+        <v>26</v>
+      </c>
       <c r="I90" t="s">
         <v>26</v>
       </c>
@@ -5571,6 +6396,9 @@
       <c r="G91" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="H91" t="s">
+        <v>26</v>
+      </c>
       <c r="I91" t="s">
         <v>26</v>
       </c>
@@ -5594,6 +6422,7006 @@
       </c>
       <c r="P91">
         <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="B92" t="s">
+        <v>214</v>
+      </c>
+      <c r="C92" t="s">
+        <v>213</v>
+      </c>
+      <c r="D92">
+        <v>30</v>
+      </c>
+      <c r="E92">
+        <v>718.8</v>
+      </c>
+      <c r="F92" s="1">
+        <v>7</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H92" t="s">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s">
+        <v>26</v>
+      </c>
+      <c r="J92" t="s">
+        <v>162</v>
+      </c>
+      <c r="K92">
+        <v>3</v>
+      </c>
+      <c r="L92">
+        <v>2</v>
+      </c>
+      <c r="M92">
+        <v>3</v>
+      </c>
+      <c r="N92">
+        <v>7</v>
+      </c>
+      <c r="O92">
+        <v>1000</v>
+      </c>
+      <c r="P92">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="B93" t="s">
+        <v>215</v>
+      </c>
+      <c r="C93" t="s">
+        <v>212</v>
+      </c>
+      <c r="D93">
+        <v>20</v>
+      </c>
+      <c r="E93">
+        <v>727.2</v>
+      </c>
+      <c r="F93" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H93" t="s">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s">
+        <v>26</v>
+      </c>
+      <c r="J93" t="s">
+        <v>49</v>
+      </c>
+      <c r="K93">
+        <v>4</v>
+      </c>
+      <c r="L93">
+        <v>3</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>8</v>
+      </c>
+      <c r="O93">
+        <v>999</v>
+      </c>
+      <c r="P93">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="B94" t="s">
+        <v>216</v>
+      </c>
+      <c r="C94" t="s">
+        <v>211</v>
+      </c>
+      <c r="D94">
+        <v>18</v>
+      </c>
+      <c r="E94">
+        <v>736.3</v>
+      </c>
+      <c r="F94" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H94" t="s">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s">
+        <v>26</v>
+      </c>
+      <c r="J94" t="s">
+        <v>49</v>
+      </c>
+      <c r="K94">
+        <v>4</v>
+      </c>
+      <c r="L94">
+        <v>3</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>8</v>
+      </c>
+      <c r="O94">
+        <v>999</v>
+      </c>
+      <c r="P94">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="B95" t="s">
+        <v>217</v>
+      </c>
+      <c r="C95" t="s">
+        <v>210</v>
+      </c>
+      <c r="D95">
+        <v>23</v>
+      </c>
+      <c r="E95">
+        <v>742.9</v>
+      </c>
+      <c r="F95" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H95" t="s">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s">
+        <v>26</v>
+      </c>
+      <c r="J95" t="s">
+        <v>162</v>
+      </c>
+      <c r="K95">
+        <v>4</v>
+      </c>
+      <c r="L95">
+        <v>3</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>8</v>
+      </c>
+      <c r="O95">
+        <v>999</v>
+      </c>
+      <c r="P95">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="B96" t="s">
+        <v>218</v>
+      </c>
+      <c r="C96" t="s">
+        <v>219</v>
+      </c>
+      <c r="D96">
+        <v>145</v>
+      </c>
+      <c r="E96">
+        <v>763</v>
+      </c>
+      <c r="F96" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H96" t="s">
+        <v>135</v>
+      </c>
+      <c r="I96" t="s">
+        <v>26</v>
+      </c>
+      <c r="J96" t="s">
+        <v>153</v>
+      </c>
+      <c r="K96">
+        <v>4</v>
+      </c>
+      <c r="L96">
+        <v>3</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>8</v>
+      </c>
+      <c r="O96">
+        <v>1014</v>
+      </c>
+      <c r="P96">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="B97" t="s">
+        <v>220</v>
+      </c>
+      <c r="C97" t="s">
+        <v>221</v>
+      </c>
+      <c r="D97">
+        <v>134</v>
+      </c>
+      <c r="E97">
+        <v>770.2</v>
+      </c>
+      <c r="F97" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H97" t="s">
+        <v>135</v>
+      </c>
+      <c r="I97" t="s">
+        <v>26</v>
+      </c>
+      <c r="J97" t="s">
+        <v>153</v>
+      </c>
+      <c r="K97">
+        <v>4</v>
+      </c>
+      <c r="L97">
+        <v>3</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>8</v>
+      </c>
+      <c r="O97">
+        <v>1014</v>
+      </c>
+      <c r="P97">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="B98" t="s">
+        <v>222</v>
+      </c>
+      <c r="C98" t="s">
+        <v>223</v>
+      </c>
+      <c r="D98">
+        <v>140</v>
+      </c>
+      <c r="E98">
+        <v>777.6</v>
+      </c>
+      <c r="F98" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H98" t="s">
+        <v>135</v>
+      </c>
+      <c r="I98" t="s">
+        <v>26</v>
+      </c>
+      <c r="J98" t="s">
+        <v>153</v>
+      </c>
+      <c r="K98">
+        <v>5</v>
+      </c>
+      <c r="L98">
+        <v>3</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>8</v>
+      </c>
+      <c r="O98">
+        <v>1016</v>
+      </c>
+      <c r="P98">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="B99" t="s">
+        <v>224</v>
+      </c>
+      <c r="C99" t="s">
+        <v>225</v>
+      </c>
+      <c r="D99">
+        <v>140</v>
+      </c>
+      <c r="E99">
+        <v>784.3</v>
+      </c>
+      <c r="F99" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H99" t="s">
+        <v>135</v>
+      </c>
+      <c r="I99" t="s">
+        <v>26</v>
+      </c>
+      <c r="J99" t="s">
+        <v>153</v>
+      </c>
+      <c r="K99">
+        <v>3</v>
+      </c>
+      <c r="L99">
+        <v>3</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>8</v>
+      </c>
+      <c r="O99">
+        <v>1016</v>
+      </c>
+      <c r="P99">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="B100" t="s">
+        <v>226</v>
+      </c>
+      <c r="C100" t="s">
+        <v>227</v>
+      </c>
+      <c r="D100">
+        <v>140</v>
+      </c>
+      <c r="E100">
+        <v>790.9</v>
+      </c>
+      <c r="F100" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H100" t="s">
+        <v>135</v>
+      </c>
+      <c r="I100" t="s">
+        <v>26</v>
+      </c>
+      <c r="J100" t="s">
+        <v>162</v>
+      </c>
+      <c r="K100">
+        <v>3</v>
+      </c>
+      <c r="L100">
+        <v>3</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>8</v>
+      </c>
+      <c r="O100">
+        <v>1016</v>
+      </c>
+      <c r="P100">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>0.500000000000001</v>
+      </c>
+      <c r="B101" t="s">
+        <v>228</v>
+      </c>
+      <c r="C101" t="s">
+        <v>229</v>
+      </c>
+      <c r="D101">
+        <v>140</v>
+      </c>
+      <c r="E101">
+        <v>796.5</v>
+      </c>
+      <c r="F101" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H101" t="s">
+        <v>135</v>
+      </c>
+      <c r="I101" t="s">
+        <v>26</v>
+      </c>
+      <c r="J101" t="s">
+        <v>27</v>
+      </c>
+      <c r="K101">
+        <v>3</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101">
+        <v>8</v>
+      </c>
+      <c r="O101">
+        <v>1016</v>
+      </c>
+      <c r="P101">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>0.54166666666666796</v>
+      </c>
+      <c r="B102" t="s">
+        <v>230</v>
+      </c>
+      <c r="C102" t="s">
+        <v>231</v>
+      </c>
+      <c r="D102">
+        <v>148</v>
+      </c>
+      <c r="E102">
+        <v>800.1</v>
+      </c>
+      <c r="F102" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H102" t="s">
+        <v>135</v>
+      </c>
+      <c r="I102" t="s">
+        <v>26</v>
+      </c>
+      <c r="J102" t="s">
+        <v>99</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102">
+        <v>8</v>
+      </c>
+      <c r="O102">
+        <v>1012</v>
+      </c>
+      <c r="P102">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="B103" t="s">
+        <v>232</v>
+      </c>
+      <c r="C103" t="s">
+        <v>233</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>807.2</v>
+      </c>
+      <c r="F103" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H103" t="s">
+        <v>135</v>
+      </c>
+      <c r="I103" t="s">
+        <v>26</v>
+      </c>
+      <c r="J103" t="s">
+        <v>99</v>
+      </c>
+      <c r="K103">
+        <v>2</v>
+      </c>
+      <c r="L103">
+        <v>2</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103">
+        <v>8</v>
+      </c>
+      <c r="O103">
+        <v>1025</v>
+      </c>
+      <c r="P103">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="B104" t="s">
+        <v>234</v>
+      </c>
+      <c r="C104" t="s">
+        <v>235</v>
+      </c>
+      <c r="D104">
+        <v>270</v>
+      </c>
+      <c r="E104">
+        <v>813.3</v>
+      </c>
+      <c r="F104" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H104" t="s">
+        <v>26</v>
+      </c>
+      <c r="I104">
+        <v>1700</v>
+      </c>
+      <c r="J104" t="s">
+        <v>102</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>8</v>
+      </c>
+      <c r="O104">
+        <v>1025</v>
+      </c>
+      <c r="P104">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="B105" t="s">
+        <v>236</v>
+      </c>
+      <c r="C105" t="s">
+        <v>237</v>
+      </c>
+      <c r="D105">
+        <v>185</v>
+      </c>
+      <c r="E105">
+        <v>818.6</v>
+      </c>
+      <c r="F105" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H105" t="s">
+        <v>238</v>
+      </c>
+      <c r="I105">
+        <v>1200</v>
+      </c>
+      <c r="J105" t="s">
+        <v>102</v>
+      </c>
+      <c r="K105">
+        <v>2</v>
+      </c>
+      <c r="L105">
+        <v>2</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>8</v>
+      </c>
+      <c r="O105">
+        <v>1025</v>
+      </c>
+      <c r="P105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="B106" t="s">
+        <v>239</v>
+      </c>
+      <c r="C106" t="s">
+        <v>240</v>
+      </c>
+      <c r="D106">
+        <v>320</v>
+      </c>
+      <c r="E106">
+        <v>824.4</v>
+      </c>
+      <c r="F106" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H106" t="s">
+        <v>238</v>
+      </c>
+      <c r="I106" t="s">
+        <v>26</v>
+      </c>
+      <c r="J106" t="s">
+        <v>241</v>
+      </c>
+      <c r="K106">
+        <v>4</v>
+      </c>
+      <c r="L106">
+        <v>2</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106">
+        <v>8</v>
+      </c>
+      <c r="O106">
+        <v>1022</v>
+      </c>
+      <c r="P106">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="B107" t="s">
+        <v>242</v>
+      </c>
+      <c r="C107" t="s">
+        <v>243</v>
+      </c>
+      <c r="D107">
+        <v>281</v>
+      </c>
+      <c r="E107">
+        <v>830.1</v>
+      </c>
+      <c r="F107" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H107" t="s">
+        <v>238</v>
+      </c>
+      <c r="I107" t="s">
+        <v>26</v>
+      </c>
+      <c r="J107" t="s">
+        <v>241</v>
+      </c>
+      <c r="K107">
+        <v>4</v>
+      </c>
+      <c r="L107">
+        <v>2</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>8</v>
+      </c>
+      <c r="O107">
+        <v>1022</v>
+      </c>
+      <c r="P107">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="B108" t="s">
+        <v>244</v>
+      </c>
+      <c r="C108" t="s">
+        <v>245</v>
+      </c>
+      <c r="D108">
+        <v>267</v>
+      </c>
+      <c r="E108">
+        <v>836.2</v>
+      </c>
+      <c r="F108" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H108" t="s">
+        <v>238</v>
+      </c>
+      <c r="I108" t="s">
+        <v>26</v>
+      </c>
+      <c r="J108" t="s">
+        <v>241</v>
+      </c>
+      <c r="K108">
+        <v>4</v>
+      </c>
+      <c r="L108">
+        <v>2</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>8</v>
+      </c>
+      <c r="O108">
+        <v>1022</v>
+      </c>
+      <c r="P108">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>0.95833333333333404</v>
+      </c>
+      <c r="B109" t="s">
+        <v>242</v>
+      </c>
+      <c r="C109" t="s">
+        <v>246</v>
+      </c>
+      <c r="D109">
+        <v>265</v>
+      </c>
+      <c r="E109">
+        <v>842</v>
+      </c>
+      <c r="F109" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H109" t="s">
+        <v>238</v>
+      </c>
+      <c r="I109" t="s">
+        <v>26</v>
+      </c>
+      <c r="J109" t="s">
+        <v>247</v>
+      </c>
+      <c r="K109">
+        <v>4</v>
+      </c>
+      <c r="L109">
+        <v>2</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>8</v>
+      </c>
+      <c r="O109">
+        <v>1021</v>
+      </c>
+      <c r="P109">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>1</v>
+      </c>
+      <c r="B110" t="s">
+        <v>248</v>
+      </c>
+      <c r="C110" t="s">
+        <v>249</v>
+      </c>
+      <c r="D110">
+        <v>250</v>
+      </c>
+      <c r="E110">
+        <v>848.1</v>
+      </c>
+      <c r="F110" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H110" t="s">
+        <v>238</v>
+      </c>
+      <c r="I110" t="s">
+        <v>26</v>
+      </c>
+      <c r="J110" t="s">
+        <v>247</v>
+      </c>
+      <c r="K110">
+        <v>4</v>
+      </c>
+      <c r="L110">
+        <v>3</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>8</v>
+      </c>
+      <c r="O110">
+        <v>1021</v>
+      </c>
+      <c r="P110">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="B111" t="s">
+        <v>250</v>
+      </c>
+      <c r="C111" t="s">
+        <v>251</v>
+      </c>
+      <c r="D111">
+        <v>166</v>
+      </c>
+      <c r="E111">
+        <v>855.3</v>
+      </c>
+      <c r="F111" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" t="s">
+        <v>135</v>
+      </c>
+      <c r="I111" t="s">
+        <v>26</v>
+      </c>
+      <c r="J111" t="s">
+        <v>241</v>
+      </c>
+      <c r="K111">
+        <v>4</v>
+      </c>
+      <c r="L111">
+        <v>2</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>8</v>
+      </c>
+      <c r="O111">
+        <v>1020</v>
+      </c>
+      <c r="P111">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>1.0833333333333399</v>
+      </c>
+      <c r="B112" t="s">
+        <v>252</v>
+      </c>
+      <c r="C112" t="s">
+        <v>253</v>
+      </c>
+      <c r="D112">
+        <v>177</v>
+      </c>
+      <c r="E112">
+        <v>861.4</v>
+      </c>
+      <c r="F112" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H112" t="s">
+        <v>135</v>
+      </c>
+      <c r="I112" t="s">
+        <v>26</v>
+      </c>
+      <c r="J112" t="s">
+        <v>247</v>
+      </c>
+      <c r="K112">
+        <v>4</v>
+      </c>
+      <c r="L112">
+        <v>2</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>8</v>
+      </c>
+      <c r="O112">
+        <v>1020</v>
+      </c>
+      <c r="P112">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="B113" t="s">
+        <v>252</v>
+      </c>
+      <c r="C113" t="s">
+        <v>255</v>
+      </c>
+      <c r="D113">
+        <v>260</v>
+      </c>
+      <c r="E113">
+        <v>928.2</v>
+      </c>
+      <c r="F113" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H113" t="s">
+        <v>238</v>
+      </c>
+      <c r="I113" t="s">
+        <v>26</v>
+      </c>
+      <c r="J113" t="s">
+        <v>118</v>
+      </c>
+      <c r="K113">
+        <v>3</v>
+      </c>
+      <c r="L113">
+        <v>2</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>7</v>
+      </c>
+      <c r="O113">
+        <v>1012</v>
+      </c>
+      <c r="P113">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>1.7916666666666701</v>
+      </c>
+      <c r="B114" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" t="s">
+        <v>256</v>
+      </c>
+      <c r="D114">
+        <v>220</v>
+      </c>
+      <c r="E114">
+        <v>930.8</v>
+      </c>
+      <c r="F114" s="1">
+        <v>4</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H114" t="s">
+        <v>238</v>
+      </c>
+      <c r="I114" t="s">
+        <v>26</v>
+      </c>
+      <c r="J114" t="s">
+        <v>27</v>
+      </c>
+      <c r="K114">
+        <v>3</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>7</v>
+      </c>
+      <c r="O114">
+        <v>1012</v>
+      </c>
+      <c r="P114">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>1.8333333333333399</v>
+      </c>
+      <c r="B115" t="s">
+        <v>257</v>
+      </c>
+      <c r="C115" t="s">
+        <v>258</v>
+      </c>
+      <c r="D115">
+        <v>235</v>
+      </c>
+      <c r="E115">
+        <v>933.5</v>
+      </c>
+      <c r="F115" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H115" t="s">
+        <v>238</v>
+      </c>
+      <c r="I115" t="s">
+        <v>26</v>
+      </c>
+      <c r="J115" t="s">
+        <v>27</v>
+      </c>
+      <c r="K115">
+        <v>2</v>
+      </c>
+      <c r="L115">
+        <v>2</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>7</v>
+      </c>
+      <c r="O115">
+        <v>1012</v>
+      </c>
+      <c r="P115">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>1.87500000000001</v>
+      </c>
+      <c r="B116" t="s">
+        <v>261</v>
+      </c>
+      <c r="C116" t="s">
+        <v>260</v>
+      </c>
+      <c r="D116">
+        <v>235</v>
+      </c>
+      <c r="E116">
+        <v>935.8</v>
+      </c>
+      <c r="F116" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H116" t="s">
+        <v>238</v>
+      </c>
+      <c r="I116" t="s">
+        <v>26</v>
+      </c>
+      <c r="J116" t="s">
+        <v>102</v>
+      </c>
+      <c r="K116">
+        <v>2</v>
+      </c>
+      <c r="L116">
+        <v>2</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>7</v>
+      </c>
+      <c r="O116">
+        <v>1011</v>
+      </c>
+      <c r="P116">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>1.9166666666666801</v>
+      </c>
+      <c r="B117" t="s">
+        <v>259</v>
+      </c>
+      <c r="C117" t="s">
+        <v>262</v>
+      </c>
+      <c r="D117">
+        <v>231</v>
+      </c>
+      <c r="E117">
+        <v>936.5</v>
+      </c>
+      <c r="F117" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H117" t="s">
+        <v>238</v>
+      </c>
+      <c r="I117" t="s">
+        <v>26</v>
+      </c>
+      <c r="J117" t="s">
+        <v>263</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>3</v>
+      </c>
+      <c r="N117">
+        <v>8</v>
+      </c>
+      <c r="O117">
+        <v>1011</v>
+      </c>
+      <c r="P117">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>1.9583333333333499</v>
+      </c>
+      <c r="B118" t="s">
+        <v>259</v>
+      </c>
+      <c r="C118" t="s">
+        <v>264</v>
+      </c>
+      <c r="D118">
+        <v>231</v>
+      </c>
+      <c r="E118">
+        <v>936.5</v>
+      </c>
+      <c r="F118" s="1">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H118" t="s">
+        <v>238</v>
+      </c>
+      <c r="I118" t="s">
+        <v>26</v>
+      </c>
+      <c r="J118" t="s">
+        <v>263</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>3</v>
+      </c>
+      <c r="N118">
+        <v>8</v>
+      </c>
+      <c r="O118">
+        <v>1011</v>
+      </c>
+      <c r="P118">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>2.00000000000002</v>
+      </c>
+      <c r="B119" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119" t="s">
+        <v>266</v>
+      </c>
+      <c r="D119">
+        <v>300</v>
+      </c>
+      <c r="E119">
+        <v>939.1</v>
+      </c>
+      <c r="F119" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H119" t="s">
+        <v>238</v>
+      </c>
+      <c r="I119" t="s">
+        <v>26</v>
+      </c>
+      <c r="J119" t="s">
+        <v>153</v>
+      </c>
+      <c r="K119">
+        <v>4</v>
+      </c>
+      <c r="L119">
+        <v>2</v>
+      </c>
+      <c r="M119">
+        <v>3</v>
+      </c>
+      <c r="N119">
+        <v>8</v>
+      </c>
+      <c r="O119">
+        <v>1011</v>
+      </c>
+      <c r="P119">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>2.0416666666666901</v>
+      </c>
+      <c r="B120" t="s">
+        <v>267</v>
+      </c>
+      <c r="C120" t="s">
+        <v>268</v>
+      </c>
+      <c r="D120">
+        <v>275</v>
+      </c>
+      <c r="E120">
+        <v>944.7</v>
+      </c>
+      <c r="F120" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H120" t="s">
+        <v>238</v>
+      </c>
+      <c r="I120" t="s">
+        <v>26</v>
+      </c>
+      <c r="J120" t="s">
+        <v>205</v>
+      </c>
+      <c r="K120">
+        <v>4</v>
+      </c>
+      <c r="L120">
+        <v>2</v>
+      </c>
+      <c r="M120">
+        <v>3</v>
+      </c>
+      <c r="N120">
+        <v>8</v>
+      </c>
+      <c r="O120">
+        <v>1011</v>
+      </c>
+      <c r="P120">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>2.0833333333333601</v>
+      </c>
+      <c r="B121" t="s">
+        <v>199</v>
+      </c>
+      <c r="C121" t="s">
+        <v>269</v>
+      </c>
+      <c r="D121">
+        <v>290</v>
+      </c>
+      <c r="E121">
+        <v>950</v>
+      </c>
+      <c r="F121" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H121" t="s">
+        <v>238</v>
+      </c>
+      <c r="I121" t="s">
+        <v>26</v>
+      </c>
+      <c r="J121" t="s">
+        <v>205</v>
+      </c>
+      <c r="K121">
+        <v>4</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>2</v>
+      </c>
+      <c r="N121">
+        <v>8</v>
+      </c>
+      <c r="O121">
+        <v>1011</v>
+      </c>
+      <c r="P121">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>2.1250000000000302</v>
+      </c>
+      <c r="B122" t="s">
+        <v>270</v>
+      </c>
+      <c r="C122" t="s">
+        <v>271</v>
+      </c>
+      <c r="D122">
+        <v>270</v>
+      </c>
+      <c r="E122">
+        <v>956.6</v>
+      </c>
+      <c r="F122" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H122" t="s">
+        <v>77</v>
+      </c>
+      <c r="I122" t="s">
+        <v>26</v>
+      </c>
+      <c r="J122" t="s">
+        <v>205</v>
+      </c>
+      <c r="K122">
+        <v>5</v>
+      </c>
+      <c r="L122">
+        <v>2</v>
+      </c>
+      <c r="M122">
+        <v>1</v>
+      </c>
+      <c r="N122">
+        <v>8</v>
+      </c>
+      <c r="O122">
+        <v>1012</v>
+      </c>
+      <c r="P122">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>2.1666666666666998</v>
+      </c>
+      <c r="B123" t="s">
+        <v>199</v>
+      </c>
+      <c r="C123" t="s">
+        <v>272</v>
+      </c>
+      <c r="D123">
+        <v>270</v>
+      </c>
+      <c r="E123">
+        <v>962.4</v>
+      </c>
+      <c r="F123" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H123" t="s">
+        <v>238</v>
+      </c>
+      <c r="I123" t="s">
+        <v>26</v>
+      </c>
+      <c r="J123" t="s">
+        <v>205</v>
+      </c>
+      <c r="K123">
+        <v>5</v>
+      </c>
+      <c r="L123">
+        <v>2</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+      <c r="N123">
+        <v>8</v>
+      </c>
+      <c r="O123">
+        <v>1013</v>
+      </c>
+      <c r="P123">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="B124" t="s">
+        <v>273</v>
+      </c>
+      <c r="C124" t="s">
+        <v>274</v>
+      </c>
+      <c r="D124">
+        <v>270</v>
+      </c>
+      <c r="E124">
+        <v>970</v>
+      </c>
+      <c r="F124" s="1">
+        <v>4</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H124" t="s">
+        <v>238</v>
+      </c>
+      <c r="I124" t="s">
+        <v>26</v>
+      </c>
+      <c r="J124" t="s">
+        <v>205</v>
+      </c>
+      <c r="K124">
+        <v>4</v>
+      </c>
+      <c r="L124">
+        <v>3</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>8</v>
+      </c>
+      <c r="O124">
+        <v>1012</v>
+      </c>
+      <c r="P124">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>2.2916666666666701</v>
+      </c>
+      <c r="B125" t="s">
+        <v>275</v>
+      </c>
+      <c r="C125" t="s">
+        <v>276</v>
+      </c>
+      <c r="D125">
+        <v>270</v>
+      </c>
+      <c r="E125">
+        <v>974.6</v>
+      </c>
+      <c r="F125" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H125" t="s">
+        <v>238</v>
+      </c>
+      <c r="I125" t="s">
+        <v>26</v>
+      </c>
+      <c r="J125" t="s">
+        <v>205</v>
+      </c>
+      <c r="K125">
+        <v>4</v>
+      </c>
+      <c r="L125">
+        <v>3</v>
+      </c>
+      <c r="M125">
+        <v>2</v>
+      </c>
+      <c r="N125">
+        <v>8</v>
+      </c>
+      <c r="O125">
+        <v>1012</v>
+      </c>
+      <c r="P125">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>2.3333333333333401</v>
+      </c>
+      <c r="B126" t="s">
+        <v>277</v>
+      </c>
+      <c r="C126" t="s">
+        <v>278</v>
+      </c>
+      <c r="D126">
+        <v>170</v>
+      </c>
+      <c r="E126">
+        <v>970.7</v>
+      </c>
+      <c r="F126" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H126" t="s">
+        <v>238</v>
+      </c>
+      <c r="I126" t="s">
+        <v>26</v>
+      </c>
+      <c r="J126" t="s">
+        <v>205</v>
+      </c>
+      <c r="K126">
+        <v>5</v>
+      </c>
+      <c r="L126">
+        <v>3</v>
+      </c>
+      <c r="M126">
+        <v>3</v>
+      </c>
+      <c r="N126">
+        <v>8</v>
+      </c>
+      <c r="O126">
+        <v>1012</v>
+      </c>
+      <c r="P126">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>2.3750000000000102</v>
+      </c>
+      <c r="B127" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" t="s">
+        <v>280</v>
+      </c>
+      <c r="D127">
+        <v>265</v>
+      </c>
+      <c r="E127">
+        <v>986</v>
+      </c>
+      <c r="F127" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H127" t="s">
+        <v>238</v>
+      </c>
+      <c r="I127" t="s">
+        <v>26</v>
+      </c>
+      <c r="J127" t="s">
+        <v>205</v>
+      </c>
+      <c r="K127">
+        <v>5</v>
+      </c>
+      <c r="L127">
+        <v>3</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>8</v>
+      </c>
+      <c r="O127">
+        <v>1012</v>
+      </c>
+      <c r="P127">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <v>2.4166666666666798</v>
+      </c>
+      <c r="B128" t="s">
+        <v>281</v>
+      </c>
+      <c r="C128" t="s">
+        <v>282</v>
+      </c>
+      <c r="D128">
+        <v>270</v>
+      </c>
+      <c r="E128">
+        <v>991.8</v>
+      </c>
+      <c r="F128" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H128" t="s">
+        <v>238</v>
+      </c>
+      <c r="I128" t="s">
+        <v>26</v>
+      </c>
+      <c r="J128" t="s">
+        <v>205</v>
+      </c>
+      <c r="K128">
+        <v>5</v>
+      </c>
+      <c r="L128">
+        <v>3</v>
+      </c>
+      <c r="M128">
+        <v>1</v>
+      </c>
+      <c r="N128">
+        <v>8</v>
+      </c>
+      <c r="O128">
+        <v>1012</v>
+      </c>
+      <c r="P128">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>2.4583333333333335</v>
+      </c>
+      <c r="B129" t="s">
+        <v>283</v>
+      </c>
+      <c r="C129" t="s">
+        <v>284</v>
+      </c>
+      <c r="D129">
+        <v>275</v>
+      </c>
+      <c r="E129">
+        <v>998.4</v>
+      </c>
+      <c r="F129" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H129" t="s">
+        <v>238</v>
+      </c>
+      <c r="I129" t="s">
+        <v>26</v>
+      </c>
+      <c r="J129" t="s">
+        <v>205</v>
+      </c>
+      <c r="K129">
+        <v>5</v>
+      </c>
+      <c r="L129">
+        <v>3</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>8</v>
+      </c>
+      <c r="O129">
+        <v>1012</v>
+      </c>
+      <c r="P129">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="B130" t="s">
+        <v>285</v>
+      </c>
+      <c r="C130" t="s">
+        <v>286</v>
+      </c>
+      <c r="D130">
+        <v>280</v>
+      </c>
+      <c r="E130">
+        <v>1005.3</v>
+      </c>
+      <c r="F130" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H130" t="s">
+        <v>238</v>
+      </c>
+      <c r="I130" t="s">
+        <v>26</v>
+      </c>
+      <c r="J130" t="s">
+        <v>205</v>
+      </c>
+      <c r="K130">
+        <v>5</v>
+      </c>
+      <c r="L130">
+        <v>3</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>8</v>
+      </c>
+      <c r="O130">
+        <v>1012</v>
+      </c>
+      <c r="P130">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <v>2.5416666666666701</v>
+      </c>
+      <c r="B131" t="s">
+        <v>287</v>
+      </c>
+      <c r="C131" t="s">
+        <v>288</v>
+      </c>
+      <c r="D131">
+        <v>275</v>
+      </c>
+      <c r="E131">
+        <v>1011.5</v>
+      </c>
+      <c r="F131" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H131" t="s">
+        <v>238</v>
+      </c>
+      <c r="I131" t="s">
+        <v>26</v>
+      </c>
+      <c r="J131" t="s">
+        <v>205</v>
+      </c>
+      <c r="K131">
+        <v>4</v>
+      </c>
+      <c r="L131">
+        <v>3</v>
+      </c>
+      <c r="M131">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>8</v>
+      </c>
+      <c r="O131">
+        <v>1012</v>
+      </c>
+      <c r="P131">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>2.5833333333333401</v>
+      </c>
+      <c r="B132" t="s">
+        <v>277</v>
+      </c>
+      <c r="C132" t="s">
+        <v>289</v>
+      </c>
+      <c r="D132">
+        <v>265</v>
+      </c>
+      <c r="E132">
+        <v>1016.6</v>
+      </c>
+      <c r="F132" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H132" t="s">
+        <v>238</v>
+      </c>
+      <c r="I132" t="s">
+        <v>26</v>
+      </c>
+      <c r="J132" t="s">
+        <v>205</v>
+      </c>
+      <c r="K132">
+        <v>4</v>
+      </c>
+      <c r="L132">
+        <v>3</v>
+      </c>
+      <c r="M132">
+        <v>2</v>
+      </c>
+      <c r="N132">
+        <v>8</v>
+      </c>
+      <c r="O132">
+        <v>1012</v>
+      </c>
+      <c r="P132">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>2.6250000000000102</v>
+      </c>
+      <c r="B133" t="s">
+        <v>290</v>
+      </c>
+      <c r="C133" t="s">
+        <v>291</v>
+      </c>
+      <c r="D133">
+        <v>255</v>
+      </c>
+      <c r="E133">
+        <v>1023.6</v>
+      </c>
+      <c r="F133" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H133" t="s">
+        <v>238</v>
+      </c>
+      <c r="I133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J133" t="s">
+        <v>205</v>
+      </c>
+      <c r="K133">
+        <v>4</v>
+      </c>
+      <c r="L133">
+        <v>3</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+      <c r="N133">
+        <v>8</v>
+      </c>
+      <c r="O133">
+        <v>1013</v>
+      </c>
+      <c r="P133">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>2.6666666666666798</v>
+      </c>
+      <c r="B134" t="s">
+        <v>292</v>
+      </c>
+      <c r="C134" t="s">
+        <v>293</v>
+      </c>
+      <c r="D134">
+        <v>250</v>
+      </c>
+      <c r="E134">
+        <v>1029.2</v>
+      </c>
+      <c r="F134" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H134" t="s">
+        <v>238</v>
+      </c>
+      <c r="I134" t="s">
+        <v>26</v>
+      </c>
+      <c r="J134" t="s">
+        <v>205</v>
+      </c>
+      <c r="K134">
+        <v>4</v>
+      </c>
+      <c r="L134">
+        <v>3</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+      <c r="N134">
+        <v>8</v>
+      </c>
+      <c r="O134">
+        <v>1013</v>
+      </c>
+      <c r="P134">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>2.7083333333333499</v>
+      </c>
+      <c r="B135" t="s">
+        <v>294</v>
+      </c>
+      <c r="C135" t="s">
+        <v>295</v>
+      </c>
+      <c r="D135">
+        <v>260</v>
+      </c>
+      <c r="E135">
+        <v>1035.5999999999999</v>
+      </c>
+      <c r="F135" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H135" t="s">
+        <v>238</v>
+      </c>
+      <c r="I135" t="s">
+        <v>26</v>
+      </c>
+      <c r="J135" t="s">
+        <v>205</v>
+      </c>
+      <c r="K135">
+        <v>4</v>
+      </c>
+      <c r="L135">
+        <v>3</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>8</v>
+      </c>
+      <c r="O135">
+        <v>1013</v>
+      </c>
+      <c r="P135">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>2.75000000000002</v>
+      </c>
+      <c r="B136" t="s">
+        <v>296</v>
+      </c>
+      <c r="C136" t="s">
+        <v>297</v>
+      </c>
+      <c r="D136">
+        <v>250</v>
+      </c>
+      <c r="E136">
+        <v>1042.7</v>
+      </c>
+      <c r="F136" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H136" t="s">
+        <v>238</v>
+      </c>
+      <c r="I136" t="s">
+        <v>26</v>
+      </c>
+      <c r="J136" t="s">
+        <v>118</v>
+      </c>
+      <c r="K136">
+        <v>3</v>
+      </c>
+      <c r="L136">
+        <v>3</v>
+      </c>
+      <c r="M136">
+        <v>2</v>
+      </c>
+      <c r="N136">
+        <v>8</v>
+      </c>
+      <c r="O136">
+        <v>1013</v>
+      </c>
+      <c r="P136">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>2.7916666666666901</v>
+      </c>
+      <c r="B137" t="s">
+        <v>298</v>
+      </c>
+      <c r="C137" t="s">
+        <v>160</v>
+      </c>
+      <c r="D137">
+        <v>248</v>
+      </c>
+      <c r="E137">
+        <v>1046.5999999999999</v>
+      </c>
+      <c r="F137" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H137" t="s">
+        <v>238</v>
+      </c>
+      <c r="I137" t="s">
+        <v>26</v>
+      </c>
+      <c r="J137" t="s">
+        <v>299</v>
+      </c>
+      <c r="K137">
+        <v>3</v>
+      </c>
+      <c r="L137">
+        <v>2</v>
+      </c>
+      <c r="M137">
+        <v>2</v>
+      </c>
+      <c r="N137">
+        <v>8</v>
+      </c>
+      <c r="O137">
+        <v>1012</v>
+      </c>
+      <c r="P137">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>2.8333333333333601</v>
+      </c>
+      <c r="B138" t="s">
+        <v>300</v>
+      </c>
+      <c r="C138" t="s">
+        <v>301</v>
+      </c>
+      <c r="D138">
+        <v>250</v>
+      </c>
+      <c r="E138">
+        <v>1053.8</v>
+      </c>
+      <c r="F138" s="1">
+        <v>8</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H138" t="s">
+        <v>238</v>
+      </c>
+      <c r="I138" t="s">
+        <v>26</v>
+      </c>
+      <c r="J138" t="s">
+        <v>299</v>
+      </c>
+      <c r="K138">
+        <v>3</v>
+      </c>
+      <c r="L138">
+        <v>2</v>
+      </c>
+      <c r="M138">
+        <v>3</v>
+      </c>
+      <c r="N138">
+        <v>8</v>
+      </c>
+      <c r="O138">
+        <v>1012</v>
+      </c>
+      <c r="P138">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>2.8750000000000302</v>
+      </c>
+      <c r="B139" t="s">
+        <v>302</v>
+      </c>
+      <c r="C139" t="s">
+        <v>303</v>
+      </c>
+      <c r="D139">
+        <v>250</v>
+      </c>
+      <c r="E139">
+        <v>1060.2</v>
+      </c>
+      <c r="F139" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H139" t="s">
+        <v>238</v>
+      </c>
+      <c r="I139" t="s">
+        <v>26</v>
+      </c>
+      <c r="J139" t="s">
+        <v>299</v>
+      </c>
+      <c r="K139">
+        <v>4</v>
+      </c>
+      <c r="L139">
+        <v>2</v>
+      </c>
+      <c r="M139">
+        <v>3</v>
+      </c>
+      <c r="N139">
+        <v>8</v>
+      </c>
+      <c r="O139">
+        <v>1012</v>
+      </c>
+      <c r="P139">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>2.9166666666666998</v>
+      </c>
+      <c r="B140" t="s">
+        <v>304</v>
+      </c>
+      <c r="C140" t="s">
+        <v>305</v>
+      </c>
+      <c r="D140">
+        <v>35</v>
+      </c>
+      <c r="E140">
+        <v>1069.0999999999999</v>
+      </c>
+      <c r="F140" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H140" t="s">
+        <v>238</v>
+      </c>
+      <c r="I140" t="s">
+        <v>26</v>
+      </c>
+      <c r="J140" t="s">
+        <v>118</v>
+      </c>
+      <c r="K140">
+        <v>3</v>
+      </c>
+      <c r="L140">
+        <v>2</v>
+      </c>
+      <c r="M140">
+        <v>3</v>
+      </c>
+      <c r="N140">
+        <v>8</v>
+      </c>
+      <c r="O140">
+        <v>1012</v>
+      </c>
+      <c r="P140">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <v>2.9583333333333699</v>
+      </c>
+      <c r="B141" t="s">
+        <v>300</v>
+      </c>
+      <c r="C141" t="s">
+        <v>306</v>
+      </c>
+      <c r="D141">
+        <v>40</v>
+      </c>
+      <c r="E141">
+        <v>1075.5999999999999</v>
+      </c>
+      <c r="F141" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I141" t="s">
+        <v>26</v>
+      </c>
+      <c r="J141" t="s">
+        <v>205</v>
+      </c>
+      <c r="K141">
+        <v>3</v>
+      </c>
+      <c r="L141">
+        <v>2</v>
+      </c>
+      <c r="M141">
+        <v>3</v>
+      </c>
+      <c r="N141">
+        <v>7</v>
+      </c>
+      <c r="O141">
+        <v>1012</v>
+      </c>
+      <c r="P141">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>3.00000000000004</v>
+      </c>
+      <c r="B142" t="s">
+        <v>307</v>
+      </c>
+      <c r="C142" t="s">
+        <v>308</v>
+      </c>
+      <c r="D142">
+        <v>50</v>
+      </c>
+      <c r="E142">
+        <v>1082.4000000000001</v>
+      </c>
+      <c r="F142" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H142" t="s">
+        <v>118</v>
+      </c>
+      <c r="I142" t="s">
+        <v>26</v>
+      </c>
+      <c r="J142" t="s">
+        <v>205</v>
+      </c>
+      <c r="K142">
+        <v>3</v>
+      </c>
+      <c r="L142">
+        <v>2</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>7</v>
+      </c>
+      <c r="O142">
+        <v>1012</v>
+      </c>
+      <c r="P142">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>3.04166666666671</v>
+      </c>
+      <c r="B143" t="s">
+        <v>309</v>
+      </c>
+      <c r="C143" t="s">
+        <v>310</v>
+      </c>
+      <c r="D143">
+        <v>53</v>
+      </c>
+      <c r="E143">
+        <v>1088.5</v>
+      </c>
+      <c r="F143" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H143" t="s">
+        <v>118</v>
+      </c>
+      <c r="I143" t="s">
+        <v>26</v>
+      </c>
+      <c r="J143" t="s">
+        <v>205</v>
+      </c>
+      <c r="K143">
+        <v>3</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>7</v>
+      </c>
+      <c r="O143">
+        <v>1012</v>
+      </c>
+      <c r="P143">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>3.0833333333333801</v>
+      </c>
+      <c r="B144" t="s">
+        <v>311</v>
+      </c>
+      <c r="C144" t="s">
+        <v>312</v>
+      </c>
+      <c r="D144">
+        <v>60</v>
+      </c>
+      <c r="E144">
+        <v>1092.2</v>
+      </c>
+      <c r="F144" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H144" t="s">
+        <v>118</v>
+      </c>
+      <c r="I144" t="s">
+        <v>26</v>
+      </c>
+      <c r="J144" t="s">
+        <v>205</v>
+      </c>
+      <c r="K144">
+        <v>1</v>
+      </c>
+      <c r="L144">
+        <v>1</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>7</v>
+      </c>
+      <c r="O144">
+        <v>1012</v>
+      </c>
+      <c r="P144">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>3.1250000000000502</v>
+      </c>
+      <c r="B145" t="s">
+        <v>313</v>
+      </c>
+      <c r="C145" t="s">
+        <v>314</v>
+      </c>
+      <c r="D145">
+        <v>47</v>
+      </c>
+      <c r="E145">
+        <v>1095.4000000000001</v>
+      </c>
+      <c r="F145" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H145" t="s">
+        <v>238</v>
+      </c>
+      <c r="I145" t="s">
+        <v>26</v>
+      </c>
+      <c r="J145" t="s">
+        <v>247</v>
+      </c>
+      <c r="K145">
+        <v>3</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>7</v>
+      </c>
+      <c r="O145">
+        <v>1012</v>
+      </c>
+      <c r="P145">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>3.1666666666667198</v>
+      </c>
+      <c r="B146" t="s">
+        <v>315</v>
+      </c>
+      <c r="C146" t="s">
+        <v>316</v>
+      </c>
+      <c r="D146">
+        <v>50</v>
+      </c>
+      <c r="E146">
+        <v>1102.4000000000001</v>
+      </c>
+      <c r="F146" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H146" t="s">
+        <v>238</v>
+      </c>
+      <c r="I146" t="s">
+        <v>26</v>
+      </c>
+      <c r="J146" t="s">
+        <v>136</v>
+      </c>
+      <c r="K146">
+        <v>4</v>
+      </c>
+      <c r="L146">
+        <v>1</v>
+      </c>
+      <c r="M146">
+        <v>4</v>
+      </c>
+      <c r="N146">
+        <v>7</v>
+      </c>
+      <c r="O146">
+        <v>1013</v>
+      </c>
+      <c r="P146">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>3.2083333333333899</v>
+      </c>
+      <c r="B147" t="s">
+        <v>317</v>
+      </c>
+      <c r="C147" t="s">
+        <v>318</v>
+      </c>
+      <c r="D147">
+        <v>53</v>
+      </c>
+      <c r="E147">
+        <v>1110.8</v>
+      </c>
+      <c r="F147" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H147" t="s">
+        <v>238</v>
+      </c>
+      <c r="I147" t="s">
+        <v>26</v>
+      </c>
+      <c r="J147" t="s">
+        <v>299</v>
+      </c>
+      <c r="K147">
+        <v>4</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <v>3</v>
+      </c>
+      <c r="N147">
+        <v>7</v>
+      </c>
+      <c r="O147">
+        <v>1013</v>
+      </c>
+      <c r="P147">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>3.25000000000006</v>
+      </c>
+      <c r="B148" t="s">
+        <v>319</v>
+      </c>
+      <c r="C148" t="s">
+        <v>320</v>
+      </c>
+      <c r="D148">
+        <v>356</v>
+      </c>
+      <c r="E148">
+        <v>1119</v>
+      </c>
+      <c r="F148" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H148" t="s">
+        <v>238</v>
+      </c>
+      <c r="I148" t="s">
+        <v>26</v>
+      </c>
+      <c r="J148" t="s">
+        <v>299</v>
+      </c>
+      <c r="K148">
+        <v>4</v>
+      </c>
+      <c r="L148">
+        <v>1</v>
+      </c>
+      <c r="M148">
+        <v>3</v>
+      </c>
+      <c r="N148">
+        <v>8</v>
+      </c>
+      <c r="O148">
+        <v>1013</v>
+      </c>
+      <c r="P148">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>3.2916666666666665</v>
+      </c>
+      <c r="B149" t="s">
+        <v>321</v>
+      </c>
+      <c r="C149" t="s">
+        <v>322</v>
+      </c>
+      <c r="D149">
+        <v>29</v>
+      </c>
+      <c r="E149">
+        <v>1132.7</v>
+      </c>
+      <c r="F149" s="1">
+        <v>5</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H149" t="s">
+        <v>77</v>
+      </c>
+      <c r="I149" t="s">
+        <v>26</v>
+      </c>
+      <c r="J149" t="s">
+        <v>241</v>
+      </c>
+      <c r="K149">
+        <v>5</v>
+      </c>
+      <c r="L149">
+        <v>2</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>6</v>
+      </c>
+      <c r="O149">
+        <v>1005</v>
+      </c>
+      <c r="P149">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="B150" t="s">
+        <v>323</v>
+      </c>
+      <c r="C150" t="s">
+        <v>324</v>
+      </c>
+      <c r="D150">
+        <v>255</v>
+      </c>
+      <c r="E150">
+        <v>1235.9000000000001</v>
+      </c>
+      <c r="F150" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H150" t="s">
+        <v>77</v>
+      </c>
+      <c r="I150" t="s">
+        <v>26</v>
+      </c>
+      <c r="J150" t="s">
+        <v>205</v>
+      </c>
+      <c r="K150">
+        <v>2</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <v>1</v>
+      </c>
+      <c r="N150">
+        <v>8</v>
+      </c>
+      <c r="O150">
+        <v>1007</v>
+      </c>
+      <c r="P150">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="B151" t="s">
+        <v>325</v>
+      </c>
+      <c r="C151" t="s">
+        <v>326</v>
+      </c>
+      <c r="D151">
+        <v>267</v>
+      </c>
+      <c r="E151">
+        <v>1239.4000000000001</v>
+      </c>
+      <c r="F151" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H151" t="s">
+        <v>77</v>
+      </c>
+      <c r="I151" t="s">
+        <v>26</v>
+      </c>
+      <c r="J151" t="s">
+        <v>247</v>
+      </c>
+      <c r="K151">
+        <v>2</v>
+      </c>
+      <c r="L151">
+        <v>1</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>7</v>
+      </c>
+      <c r="O151">
+        <v>1007</v>
+      </c>
+      <c r="P151">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="B152" t="s">
+        <v>327</v>
+      </c>
+      <c r="C152" t="s">
+        <v>328</v>
+      </c>
+      <c r="D152">
+        <v>265</v>
+      </c>
+      <c r="E152">
+        <v>1242.9000000000001</v>
+      </c>
+      <c r="F152" s="1">
+        <v>4</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H152" t="s">
+        <v>77</v>
+      </c>
+      <c r="I152" t="s">
+        <v>26</v>
+      </c>
+      <c r="J152" t="s">
+        <v>136</v>
+      </c>
+      <c r="K152">
+        <v>3</v>
+      </c>
+      <c r="L152">
+        <v>2</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+      <c r="N152">
+        <v>7</v>
+      </c>
+      <c r="O152">
+        <v>1007</v>
+      </c>
+      <c r="P152">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="B153" t="s">
+        <v>329</v>
+      </c>
+      <c r="C153" t="s">
+        <v>330</v>
+      </c>
+      <c r="D153">
+        <v>225</v>
+      </c>
+      <c r="E153">
+        <v>1293</v>
+      </c>
+      <c r="F153" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H153" t="s">
+        <v>135</v>
+      </c>
+      <c r="I153" t="s">
+        <v>26</v>
+      </c>
+      <c r="J153" t="s">
+        <v>299</v>
+      </c>
+      <c r="K153">
+        <v>5</v>
+      </c>
+      <c r="L153">
+        <v>2</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>7</v>
+      </c>
+      <c r="O153">
+        <v>1007</v>
+      </c>
+      <c r="P153">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="B154" t="s">
+        <v>332</v>
+      </c>
+      <c r="C154" t="s">
+        <v>333</v>
+      </c>
+      <c r="D154">
+        <v>226</v>
+      </c>
+      <c r="E154">
+        <v>1398.7</v>
+      </c>
+      <c r="F154" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H154" t="s">
+        <v>135</v>
+      </c>
+      <c r="I154" t="s">
+        <v>26</v>
+      </c>
+      <c r="J154" t="s">
+        <v>299</v>
+      </c>
+      <c r="K154">
+        <v>5</v>
+      </c>
+      <c r="L154">
+        <v>2</v>
+      </c>
+      <c r="M154">
+        <v>2</v>
+      </c>
+      <c r="N154">
+        <v>8</v>
+      </c>
+      <c r="O154">
+        <v>1007</v>
+      </c>
+      <c r="P154">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="B155" t="s">
+        <v>334</v>
+      </c>
+      <c r="C155" t="s">
+        <v>335</v>
+      </c>
+      <c r="D155">
+        <v>241</v>
+      </c>
+      <c r="E155">
+        <v>1305.4100000000001</v>
+      </c>
+      <c r="F155" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H155" t="s">
+        <v>135</v>
+      </c>
+      <c r="I155" t="s">
+        <v>26</v>
+      </c>
+      <c r="J155" t="s">
+        <v>299</v>
+      </c>
+      <c r="K155">
+        <v>5</v>
+      </c>
+      <c r="L155">
+        <v>3</v>
+      </c>
+      <c r="M155">
+        <v>2</v>
+      </c>
+      <c r="N155">
+        <v>8</v>
+      </c>
+      <c r="O155">
+        <v>1007</v>
+      </c>
+      <c r="P155">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>0.83333333333333404</v>
+      </c>
+      <c r="B156" t="s">
+        <v>336</v>
+      </c>
+      <c r="C156" t="s">
+        <v>337</v>
+      </c>
+      <c r="D156">
+        <v>139</v>
+      </c>
+      <c r="E156">
+        <v>1310.4000000000001</v>
+      </c>
+      <c r="F156" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H156" t="s">
+        <v>135</v>
+      </c>
+      <c r="I156" t="s">
+        <v>26</v>
+      </c>
+      <c r="J156" t="s">
+        <v>118</v>
+      </c>
+      <c r="K156">
+        <v>5</v>
+      </c>
+      <c r="L156">
+        <v>3</v>
+      </c>
+      <c r="M156">
+        <v>2</v>
+      </c>
+      <c r="N156">
+        <v>8</v>
+      </c>
+      <c r="O156">
+        <v>1007</v>
+      </c>
+      <c r="P156">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="B157" t="s">
+        <v>338</v>
+      </c>
+      <c r="C157" t="s">
+        <v>339</v>
+      </c>
+      <c r="D157">
+        <v>125</v>
+      </c>
+      <c r="E157">
+        <v>1315.7</v>
+      </c>
+      <c r="F157" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H157" t="s">
+        <v>135</v>
+      </c>
+      <c r="I157" t="s">
+        <v>26</v>
+      </c>
+      <c r="J157" t="s">
+        <v>205</v>
+      </c>
+      <c r="K157">
+        <v>5</v>
+      </c>
+      <c r="L157">
+        <v>3</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+      <c r="N157">
+        <v>8</v>
+      </c>
+      <c r="O157">
+        <v>1007</v>
+      </c>
+      <c r="P157">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>0.91666666666666796</v>
+      </c>
+      <c r="B158" t="s">
+        <v>340</v>
+      </c>
+      <c r="C158" t="s">
+        <v>341</v>
+      </c>
+      <c r="D158">
+        <v>128</v>
+      </c>
+      <c r="E158">
+        <v>1322.3</v>
+      </c>
+      <c r="F158" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H158" t="s">
+        <v>135</v>
+      </c>
+      <c r="I158" t="s">
+        <v>26</v>
+      </c>
+      <c r="J158" t="s">
+        <v>205</v>
+      </c>
+      <c r="K158">
+        <v>5</v>
+      </c>
+      <c r="L158">
+        <v>3</v>
+      </c>
+      <c r="M158">
+        <v>1</v>
+      </c>
+      <c r="N158">
+        <v>8</v>
+      </c>
+      <c r="O158">
+        <v>1007</v>
+      </c>
+      <c r="P158">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>0.95833333333333504</v>
+      </c>
+      <c r="B159" t="s">
+        <v>342</v>
+      </c>
+      <c r="C159" t="s">
+        <v>343</v>
+      </c>
+      <c r="D159">
+        <v>160</v>
+      </c>
+      <c r="E159">
+        <v>1329.9</v>
+      </c>
+      <c r="F159" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H159" t="s">
+        <v>135</v>
+      </c>
+      <c r="I159" t="s">
+        <v>26</v>
+      </c>
+      <c r="J159" t="s">
+        <v>205</v>
+      </c>
+      <c r="K159">
+        <v>5</v>
+      </c>
+      <c r="L159">
+        <v>3</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>8</v>
+      </c>
+      <c r="O159">
+        <v>1007</v>
+      </c>
+      <c r="P159">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>1</v>
+      </c>
+      <c r="B160" t="s">
+        <v>344</v>
+      </c>
+      <c r="C160" t="s">
+        <v>345</v>
+      </c>
+      <c r="D160">
+        <v>160</v>
+      </c>
+      <c r="E160">
+        <v>1351.1</v>
+      </c>
+      <c r="F160" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H160" t="s">
+        <v>135</v>
+      </c>
+      <c r="I160" t="s">
+        <v>26</v>
+      </c>
+      <c r="J160" t="s">
+        <v>205</v>
+      </c>
+      <c r="K160">
+        <v>5</v>
+      </c>
+      <c r="L160">
+        <v>3</v>
+      </c>
+      <c r="M160">
+        <v>1</v>
+      </c>
+      <c r="N160">
+        <v>8</v>
+      </c>
+      <c r="O160">
+        <v>1007</v>
+      </c>
+      <c r="P160">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2">
+        <v>1.0833333333333333</v>
+      </c>
+      <c r="B161" t="s">
+        <v>346</v>
+      </c>
+      <c r="C161" t="s">
+        <v>347</v>
+      </c>
+      <c r="D161">
+        <v>280</v>
+      </c>
+      <c r="E161">
+        <v>1346</v>
+      </c>
+      <c r="F161" s="1">
+        <v>5</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H161" t="s">
+        <v>135</v>
+      </c>
+      <c r="I161" t="s">
+        <v>26</v>
+      </c>
+      <c r="J161" t="s">
+        <v>153</v>
+      </c>
+      <c r="K161">
+        <v>4</v>
+      </c>
+      <c r="L161">
+        <v>3</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>7</v>
+      </c>
+      <c r="O161">
+        <v>1007</v>
+      </c>
+      <c r="P161">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <v>1.125</v>
+      </c>
+      <c r="B162" t="s">
+        <v>348</v>
+      </c>
+      <c r="C162" t="s">
+        <v>349</v>
+      </c>
+      <c r="D162">
+        <v>225</v>
+      </c>
+      <c r="E162">
+        <v>1350</v>
+      </c>
+      <c r="F162" s="1">
+        <v>4</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H162" t="s">
+        <v>135</v>
+      </c>
+      <c r="I162" t="s">
+        <v>26</v>
+      </c>
+      <c r="J162" t="s">
+        <v>27</v>
+      </c>
+      <c r="K162">
+        <v>3</v>
+      </c>
+      <c r="L162">
+        <v>3</v>
+      </c>
+      <c r="M162">
+        <v>2</v>
+      </c>
+      <c r="N162">
+        <v>7</v>
+      </c>
+      <c r="O162">
+        <v>1007</v>
+      </c>
+      <c r="P162">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="B163" t="s">
+        <v>350</v>
+      </c>
+      <c r="C163" t="s">
+        <v>351</v>
+      </c>
+      <c r="D163">
+        <v>220</v>
+      </c>
+      <c r="E163">
+        <v>1354.2</v>
+      </c>
+      <c r="F163" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H163" t="s">
+        <v>135</v>
+      </c>
+      <c r="I163" t="s">
+        <v>26</v>
+      </c>
+      <c r="J163" t="s">
+        <v>49</v>
+      </c>
+      <c r="K163">
+        <v>3</v>
+      </c>
+      <c r="L163">
+        <v>3</v>
+      </c>
+      <c r="M163">
+        <v>2</v>
+      </c>
+      <c r="N163">
+        <v>7</v>
+      </c>
+      <c r="O163">
+        <v>1007</v>
+      </c>
+      <c r="P163">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
+        <v>1.2083333333333333</v>
+      </c>
+      <c r="B164" t="s">
+        <v>352</v>
+      </c>
+      <c r="C164" t="s">
+        <v>353</v>
+      </c>
+      <c r="D164">
+        <v>150</v>
+      </c>
+      <c r="E164">
+        <v>1356.5</v>
+      </c>
+      <c r="F164" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H164" t="s">
+        <v>26</v>
+      </c>
+      <c r="I164" t="s">
+        <v>26</v>
+      </c>
+      <c r="J164" t="s">
+        <v>49</v>
+      </c>
+      <c r="K164">
+        <v>3</v>
+      </c>
+      <c r="L164">
+        <v>3</v>
+      </c>
+      <c r="M164">
+        <v>2</v>
+      </c>
+      <c r="N164">
+        <v>7</v>
+      </c>
+      <c r="O164">
+        <v>1007</v>
+      </c>
+      <c r="P164">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="B165" t="s">
+        <v>195</v>
+      </c>
+      <c r="C165" t="s">
+        <v>354</v>
+      </c>
+      <c r="D165">
+        <v>175</v>
+      </c>
+      <c r="E165">
+        <v>1360.5</v>
+      </c>
+      <c r="F165" s="1">
+        <v>4</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H165" t="s">
+        <v>238</v>
+      </c>
+      <c r="I165" t="s">
+        <v>26</v>
+      </c>
+      <c r="J165" t="s">
+        <v>49</v>
+      </c>
+      <c r="K165">
+        <v>3</v>
+      </c>
+      <c r="L165">
+        <v>2</v>
+      </c>
+      <c r="M165">
+        <v>2</v>
+      </c>
+      <c r="N165">
+        <v>7</v>
+      </c>
+      <c r="O165">
+        <v>1007</v>
+      </c>
+      <c r="P165">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <v>1.2916666666666701</v>
+      </c>
+      <c r="B166" t="s">
+        <v>189</v>
+      </c>
+      <c r="C166" t="s">
+        <v>355</v>
+      </c>
+      <c r="D166">
+        <v>210</v>
+      </c>
+      <c r="E166">
+        <v>1368.1</v>
+      </c>
+      <c r="F166" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H166" t="s">
+        <v>238</v>
+      </c>
+      <c r="I166" t="s">
+        <v>26</v>
+      </c>
+      <c r="J166" t="s">
+        <v>27</v>
+      </c>
+      <c r="K166">
+        <v>4</v>
+      </c>
+      <c r="L166">
+        <v>2</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>8</v>
+      </c>
+      <c r="O166">
+        <v>1007</v>
+      </c>
+      <c r="P166">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2">
+        <v>1.3333333333333399</v>
+      </c>
+      <c r="B167" t="s">
+        <v>356</v>
+      </c>
+      <c r="C167" t="s">
+        <v>357</v>
+      </c>
+      <c r="D167">
+        <v>206</v>
+      </c>
+      <c r="E167">
+        <v>1374.5</v>
+      </c>
+      <c r="F167" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H167" t="s">
+        <v>238</v>
+      </c>
+      <c r="I167" t="s">
+        <v>26</v>
+      </c>
+      <c r="J167" t="s">
+        <v>27</v>
+      </c>
+      <c r="K167">
+        <v>4</v>
+      </c>
+      <c r="L167">
+        <v>2</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>8</v>
+      </c>
+      <c r="O167">
+        <v>1007</v>
+      </c>
+      <c r="P167">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <v>1.375</v>
+      </c>
+      <c r="B168" t="s">
+        <v>358</v>
+      </c>
+      <c r="C168" t="s">
+        <v>359</v>
+      </c>
+      <c r="D168">
+        <v>200</v>
+      </c>
+      <c r="E168">
+        <v>1382.3</v>
+      </c>
+      <c r="F168" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H168" t="s">
+        <v>238</v>
+      </c>
+      <c r="I168" t="s">
+        <v>26</v>
+      </c>
+      <c r="J168" t="s">
+        <v>27</v>
+      </c>
+      <c r="K168">
+        <v>4</v>
+      </c>
+      <c r="L168">
+        <v>2</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>8</v>
+      </c>
+      <c r="O168">
+        <v>1007</v>
+      </c>
+      <c r="P168">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <v>1.4166666666666701</v>
+      </c>
+      <c r="B169" t="s">
+        <v>360</v>
+      </c>
+      <c r="C169" t="s">
+        <v>361</v>
+      </c>
+      <c r="D169">
+        <v>200</v>
+      </c>
+      <c r="E169">
+        <v>1388.8</v>
+      </c>
+      <c r="F169" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H169" t="s">
+        <v>238</v>
+      </c>
+      <c r="I169" t="s">
+        <v>26</v>
+      </c>
+      <c r="J169" t="s">
+        <v>27</v>
+      </c>
+      <c r="K169">
+        <v>4</v>
+      </c>
+      <c r="L169">
+        <v>2</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>8</v>
+      </c>
+      <c r="O169">
+        <v>1007</v>
+      </c>
+      <c r="P169">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
+        <v>1.4583333333333399</v>
+      </c>
+      <c r="B170" t="s">
+        <v>362</v>
+      </c>
+      <c r="C170" t="s">
+        <v>363</v>
+      </c>
+      <c r="D170">
+        <v>163</v>
+      </c>
+      <c r="E170">
+        <v>1393.6</v>
+      </c>
+      <c r="F170" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H170" t="s">
+        <v>238</v>
+      </c>
+      <c r="I170" t="s">
+        <v>26</v>
+      </c>
+      <c r="J170" t="s">
+        <v>27</v>
+      </c>
+      <c r="K170">
+        <v>3</v>
+      </c>
+      <c r="L170">
+        <v>2</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>8</v>
+      </c>
+      <c r="O170">
+        <v>1007</v>
+      </c>
+      <c r="P170">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2">
+        <v>1.50000000000001</v>
+      </c>
+      <c r="B171" t="s">
+        <v>367</v>
+      </c>
+      <c r="C171" t="s">
+        <v>366</v>
+      </c>
+      <c r="D171">
+        <v>190</v>
+      </c>
+      <c r="E171">
+        <v>1399.1</v>
+      </c>
+      <c r="F171" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H171" t="s">
+        <v>238</v>
+      </c>
+      <c r="I171" t="s">
+        <v>26</v>
+      </c>
+      <c r="J171" t="s">
+        <v>27</v>
+      </c>
+      <c r="K171">
+        <v>3</v>
+      </c>
+      <c r="L171">
+        <v>2</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171">
+        <v>7</v>
+      </c>
+      <c r="O171">
+        <v>1007</v>
+      </c>
+      <c r="P171">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>1.5416666666666801</v>
+      </c>
+      <c r="B172" t="s">
+        <v>364</v>
+      </c>
+      <c r="C172" t="s">
+        <v>365</v>
+      </c>
+      <c r="D172">
+        <v>190</v>
+      </c>
+      <c r="E172">
+        <v>1405</v>
+      </c>
+      <c r="F172" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H172" t="s">
+        <v>238</v>
+      </c>
+      <c r="I172" t="s">
+        <v>26</v>
+      </c>
+      <c r="J172" t="s">
+        <v>27</v>
+      </c>
+      <c r="K172">
+        <v>4</v>
+      </c>
+      <c r="L172">
+        <v>2</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>7</v>
+      </c>
+      <c r="O172">
+        <v>1008</v>
+      </c>
+      <c r="P172">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2">
+        <v>1.5833333333333499</v>
+      </c>
+      <c r="B173" t="s">
+        <v>368</v>
+      </c>
+      <c r="C173" t="s">
+        <v>369</v>
+      </c>
+      <c r="D173">
+        <v>210</v>
+      </c>
+      <c r="E173">
+        <v>1412</v>
+      </c>
+      <c r="F173" s="1">
+        <v>7</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H173" t="s">
+        <v>238</v>
+      </c>
+      <c r="I173" t="s">
+        <v>26</v>
+      </c>
+      <c r="J173" t="s">
+        <v>27</v>
+      </c>
+      <c r="K173">
+        <v>4</v>
+      </c>
+      <c r="L173">
+        <v>2</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>7</v>
+      </c>
+      <c r="O173">
+        <v>1008</v>
+      </c>
+      <c r="P173">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
+        <v>1.62500000000002</v>
+      </c>
+      <c r="B174" t="s">
+        <v>370</v>
+      </c>
+      <c r="C174" t="s">
+        <v>371</v>
+      </c>
+      <c r="D174">
+        <v>205</v>
+      </c>
+      <c r="E174">
+        <v>1419</v>
+      </c>
+      <c r="F174" s="1">
+        <v>7</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H174" t="s">
+        <v>238</v>
+      </c>
+      <c r="I174" t="s">
+        <v>26</v>
+      </c>
+      <c r="J174" t="s">
+        <v>27</v>
+      </c>
+      <c r="K174">
+        <v>4</v>
+      </c>
+      <c r="L174">
+        <v>2</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174">
+        <v>7</v>
+      </c>
+      <c r="O174">
+        <v>1008</v>
+      </c>
+      <c r="P174">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="2">
+        <v>1.6666666666666901</v>
+      </c>
+      <c r="B175" t="s">
+        <v>372</v>
+      </c>
+      <c r="C175" t="s">
+        <v>373</v>
+      </c>
+      <c r="D175">
+        <v>200</v>
+      </c>
+      <c r="E175">
+        <v>1425</v>
+      </c>
+      <c r="F175" s="1">
+        <v>6</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H175" t="s">
+        <v>238</v>
+      </c>
+      <c r="I175" t="s">
+        <v>26</v>
+      </c>
+      <c r="J175" t="s">
+        <v>27</v>
+      </c>
+      <c r="K175">
+        <v>4</v>
+      </c>
+      <c r="L175">
+        <v>2</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>7</v>
+      </c>
+      <c r="O175">
+        <v>1008</v>
+      </c>
+      <c r="P175">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <v>1.7083333333333599</v>
+      </c>
+      <c r="B176" t="s">
+        <v>374</v>
+      </c>
+      <c r="C176" t="s">
+        <v>375</v>
+      </c>
+      <c r="D176">
+        <v>206</v>
+      </c>
+      <c r="E176">
+        <v>1432.9</v>
+      </c>
+      <c r="F176" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H176" t="s">
+        <v>238</v>
+      </c>
+      <c r="I176" t="s">
+        <v>26</v>
+      </c>
+      <c r="J176" t="s">
+        <v>27</v>
+      </c>
+      <c r="K176">
+        <v>5</v>
+      </c>
+      <c r="L176">
+        <v>3</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>7</v>
+      </c>
+      <c r="O176">
+        <v>1008</v>
+      </c>
+      <c r="P176">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="2">
+        <v>1.75000000000003</v>
+      </c>
+      <c r="B177" t="s">
+        <v>376</v>
+      </c>
+      <c r="C177" t="s">
+        <v>377</v>
+      </c>
+      <c r="D177">
+        <v>200</v>
+      </c>
+      <c r="E177">
+        <v>1440.8</v>
+      </c>
+      <c r="F177" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H177" t="s">
+        <v>238</v>
+      </c>
+      <c r="I177" t="s">
+        <v>26</v>
+      </c>
+      <c r="J177" t="s">
+        <v>27</v>
+      </c>
+      <c r="K177">
+        <v>4</v>
+      </c>
+      <c r="L177">
+        <v>3</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>7</v>
+      </c>
+      <c r="O177">
+        <v>1008</v>
+      </c>
+      <c r="P177">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="2">
+        <v>1.7916666666666665</v>
+      </c>
+      <c r="B178" t="s">
+        <v>378</v>
+      </c>
+      <c r="C178" t="s">
+        <v>379</v>
+      </c>
+      <c r="D178">
+        <v>212</v>
+      </c>
+      <c r="E178">
+        <v>1448.6</v>
+      </c>
+      <c r="F178" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H178" t="s">
+        <v>238</v>
+      </c>
+      <c r="I178" t="s">
+        <v>26</v>
+      </c>
+      <c r="J178" t="s">
+        <v>27</v>
+      </c>
+      <c r="K178">
+        <v>6</v>
+      </c>
+      <c r="L178">
+        <v>3</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>7</v>
+      </c>
+      <c r="O178">
+        <v>1008</v>
+      </c>
+      <c r="P178">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="2">
+        <v>1.8333333333333299</v>
+      </c>
+      <c r="B179" t="s">
+        <v>380</v>
+      </c>
+      <c r="C179" t="s">
+        <v>381</v>
+      </c>
+      <c r="D179">
+        <v>214</v>
+      </c>
+      <c r="E179">
+        <v>1457.1</v>
+      </c>
+      <c r="F179" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H179" t="s">
+        <v>238</v>
+      </c>
+      <c r="I179" t="s">
+        <v>26</v>
+      </c>
+      <c r="J179" t="s">
+        <v>99</v>
+      </c>
+      <c r="K179">
+        <v>5</v>
+      </c>
+      <c r="L179">
+        <v>3</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>7</v>
+      </c>
+      <c r="O179">
+        <v>1008</v>
+      </c>
+      <c r="P179">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="2">
+        <v>1.875</v>
+      </c>
+      <c r="B180" t="s">
+        <v>382</v>
+      </c>
+      <c r="C180" t="s">
+        <v>385</v>
+      </c>
+      <c r="D180">
+        <v>202</v>
+      </c>
+      <c r="E180">
+        <v>1465.3</v>
+      </c>
+      <c r="F180" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H180" t="s">
+        <v>135</v>
+      </c>
+      <c r="I180" t="s">
+        <v>26</v>
+      </c>
+      <c r="J180" t="s">
+        <v>99</v>
+      </c>
+      <c r="K180">
+        <v>5</v>
+      </c>
+      <c r="L180">
+        <v>3</v>
+      </c>
+      <c r="M180">
+        <v>3</v>
+      </c>
+      <c r="N180">
+        <v>7</v>
+      </c>
+      <c r="O180">
+        <v>1008</v>
+      </c>
+      <c r="P180">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="2">
+        <v>1.9166666666666701</v>
+      </c>
+      <c r="B181" t="s">
+        <v>384</v>
+      </c>
+      <c r="C181" t="s">
+        <v>383</v>
+      </c>
+      <c r="D181">
+        <v>220</v>
+      </c>
+      <c r="E181">
+        <v>1474.3</v>
+      </c>
+      <c r="F181" s="1">
+        <v>9</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H181" t="s">
+        <v>135</v>
+      </c>
+      <c r="I181" t="s">
+        <v>26</v>
+      </c>
+      <c r="J181" t="s">
+        <v>99</v>
+      </c>
+      <c r="K181">
+        <v>5</v>
+      </c>
+      <c r="L181">
+        <v>3</v>
+      </c>
+      <c r="M181">
+        <v>3</v>
+      </c>
+      <c r="N181">
+        <v>7</v>
+      </c>
+      <c r="O181">
+        <v>1008</v>
+      </c>
+      <c r="P181">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="2">
+        <v>1.9583333333333399</v>
+      </c>
+      <c r="B182" t="s">
+        <v>387</v>
+      </c>
+      <c r="C182" t="s">
+        <v>386</v>
+      </c>
+      <c r="D182">
+        <v>220</v>
+      </c>
+      <c r="E182">
+        <v>1483.9</v>
+      </c>
+      <c r="F182" s="1">
+        <v>9</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H182" t="s">
+        <v>135</v>
+      </c>
+      <c r="I182" t="s">
+        <v>26</v>
+      </c>
+      <c r="J182" t="s">
+        <v>99</v>
+      </c>
+      <c r="K182">
+        <v>6</v>
+      </c>
+      <c r="L182">
+        <v>4</v>
+      </c>
+      <c r="M182">
+        <v>2</v>
+      </c>
+      <c r="N182">
+        <v>7</v>
+      </c>
+      <c r="O182">
+        <v>1011</v>
+      </c>
+      <c r="P182">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="2">
+        <v>2.0000000000000102</v>
+      </c>
+      <c r="B183" t="s">
+        <v>388</v>
+      </c>
+      <c r="C183" t="s">
+        <v>389</v>
+      </c>
+      <c r="D183">
+        <v>220</v>
+      </c>
+      <c r="E183">
+        <v>1492.8</v>
+      </c>
+      <c r="F183" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H183" t="s">
+        <v>135</v>
+      </c>
+      <c r="I183" t="s">
+        <v>26</v>
+      </c>
+      <c r="J183" t="s">
+        <v>99</v>
+      </c>
+      <c r="K183">
+        <v>6</v>
+      </c>
+      <c r="L183">
+        <v>4</v>
+      </c>
+      <c r="M183">
+        <v>2</v>
+      </c>
+      <c r="N183">
+        <v>7</v>
+      </c>
+      <c r="O183">
+        <v>1011</v>
+      </c>
+      <c r="P183">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <v>2.0416666666666798</v>
+      </c>
+      <c r="B184" t="s">
+        <v>390</v>
+      </c>
+      <c r="C184" t="s">
+        <v>391</v>
+      </c>
+      <c r="D184">
+        <v>195</v>
+      </c>
+      <c r="E184">
+        <v>1502.8</v>
+      </c>
+      <c r="F184" s="1">
+        <v>10</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H184" t="s">
+        <v>135</v>
+      </c>
+      <c r="I184" t="s">
+        <v>26</v>
+      </c>
+      <c r="J184" t="s">
+        <v>99</v>
+      </c>
+      <c r="K184">
+        <v>4</v>
+      </c>
+      <c r="L184">
+        <v>3</v>
+      </c>
+      <c r="M184">
+        <v>2</v>
+      </c>
+      <c r="N184">
+        <v>8</v>
+      </c>
+      <c r="O184">
+        <v>1009</v>
+      </c>
+      <c r="P184">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="2">
+        <v>2.0833333333333499</v>
+      </c>
+      <c r="B185" t="s">
+        <v>392</v>
+      </c>
+      <c r="C185" t="s">
+        <v>393</v>
+      </c>
+      <c r="D185">
+        <v>195</v>
+      </c>
+      <c r="E185">
+        <v>1510.2</v>
+      </c>
+      <c r="F185" s="1">
+        <v>8</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H185" t="s">
+        <v>77</v>
+      </c>
+      <c r="I185" t="s">
+        <v>26</v>
+      </c>
+      <c r="J185" t="s">
+        <v>102</v>
+      </c>
+      <c r="K185">
+        <v>5</v>
+      </c>
+      <c r="L185">
+        <v>4</v>
+      </c>
+      <c r="M185">
+        <v>3</v>
+      </c>
+      <c r="N185">
+        <v>8</v>
+      </c>
+      <c r="O185">
+        <v>1009</v>
+      </c>
+      <c r="P185">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <v>2.12500000000002</v>
+      </c>
+      <c r="B186" t="s">
+        <v>394</v>
+      </c>
+      <c r="C186" t="s">
+        <v>395</v>
+      </c>
+      <c r="D186">
+        <v>200</v>
+      </c>
+      <c r="E186">
+        <v>1520.2</v>
+      </c>
+      <c r="F186" s="1">
+        <v>10</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H186" t="s">
+        <v>77</v>
+      </c>
+      <c r="I186" t="s">
+        <v>26</v>
+      </c>
+      <c r="J186" t="s">
+        <v>102</v>
+      </c>
+      <c r="K186">
+        <v>4</v>
+      </c>
+      <c r="L186">
+        <v>4</v>
+      </c>
+      <c r="M186">
+        <v>1</v>
+      </c>
+      <c r="N186">
+        <v>8</v>
+      </c>
+      <c r="O186">
+        <v>1009</v>
+      </c>
+      <c r="P186">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="2">
+        <v>2.1666666666666901</v>
+      </c>
+      <c r="B187" t="s">
+        <v>396</v>
+      </c>
+      <c r="C187" t="s">
+        <v>397</v>
+      </c>
+      <c r="D187">
+        <v>160</v>
+      </c>
+      <c r="E187">
+        <v>1530.4</v>
+      </c>
+      <c r="F187" s="1">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H187" t="s">
+        <v>77</v>
+      </c>
+      <c r="I187" t="s">
+        <v>26</v>
+      </c>
+      <c r="J187" t="s">
+        <v>102</v>
+      </c>
+      <c r="K187">
+        <v>5</v>
+      </c>
+      <c r="L187">
+        <v>4</v>
+      </c>
+      <c r="M187">
+        <v>1</v>
+      </c>
+      <c r="N187">
+        <v>8</v>
+      </c>
+      <c r="O187">
+        <v>1009</v>
+      </c>
+      <c r="P187">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="2">
+        <v>2.2083333333333335</v>
+      </c>
+      <c r="B188" t="s">
+        <v>398</v>
+      </c>
+      <c r="C188" t="s">
+        <v>399</v>
+      </c>
+      <c r="D188">
+        <v>198</v>
+      </c>
+      <c r="E188">
+        <v>1538.5</v>
+      </c>
+      <c r="F188" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H188" t="s">
+        <v>77</v>
+      </c>
+      <c r="I188" t="s">
+        <v>26</v>
+      </c>
+      <c r="J188" t="s">
+        <v>102</v>
+      </c>
+      <c r="K188">
+        <v>6</v>
+      </c>
+      <c r="L188">
+        <v>4</v>
+      </c>
+      <c r="M188">
+        <v>1</v>
+      </c>
+      <c r="N188">
+        <v>8</v>
+      </c>
+      <c r="O188">
+        <v>1009</v>
+      </c>
+      <c r="P188">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="B189" t="s">
+        <v>400</v>
+      </c>
+      <c r="C189" t="s">
+        <v>403</v>
+      </c>
+      <c r="D189">
+        <v>209</v>
+      </c>
+      <c r="E189">
+        <v>1547.5</v>
+      </c>
+      <c r="F189" s="1">
+        <v>9</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H189" t="s">
+        <v>77</v>
+      </c>
+      <c r="I189" t="s">
+        <v>26</v>
+      </c>
+      <c r="J189" t="s">
+        <v>102</v>
+      </c>
+      <c r="K189">
+        <v>6</v>
+      </c>
+      <c r="L189">
+        <v>4</v>
+      </c>
+      <c r="M189">
+        <v>1</v>
+      </c>
+      <c r="N189">
+        <v>8</v>
+      </c>
+      <c r="O189">
+        <v>1009</v>
+      </c>
+      <c r="P189">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="2">
+        <v>2.2916666666666701</v>
+      </c>
+      <c r="B190" t="s">
+        <v>401</v>
+      </c>
+      <c r="C190" t="s">
+        <v>402</v>
+      </c>
+      <c r="D190">
+        <v>206</v>
+      </c>
+      <c r="E190">
+        <v>1556.6</v>
+      </c>
+      <c r="F190" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H190" t="s">
+        <v>77</v>
+      </c>
+      <c r="I190" t="s">
+        <v>26</v>
+      </c>
+      <c r="J190" t="s">
+        <v>102</v>
+      </c>
+      <c r="K190">
+        <v>5</v>
+      </c>
+      <c r="L190">
+        <v>3</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>8</v>
+      </c>
+      <c r="O190">
+        <v>1009</v>
+      </c>
+      <c r="P190">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="2">
+        <v>2.3333333333333401</v>
+      </c>
+      <c r="B191" t="s">
+        <v>107</v>
+      </c>
+      <c r="C191" t="s">
+        <v>404</v>
+      </c>
+      <c r="D191">
+        <v>208</v>
+      </c>
+      <c r="E191">
+        <v>1565.9</v>
+      </c>
+      <c r="F191" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H191" t="s">
+        <v>77</v>
+      </c>
+      <c r="I191" t="s">
+        <v>26</v>
+      </c>
+      <c r="J191" t="s">
+        <v>99</v>
+      </c>
+      <c r="K191">
+        <v>5</v>
+      </c>
+      <c r="L191">
+        <v>2</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>8</v>
+      </c>
+      <c r="O191">
+        <v>1011</v>
+      </c>
+      <c r="P191">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="2">
+        <v>2.3750000000000102</v>
+      </c>
+      <c r="B192" t="s">
+        <v>405</v>
+      </c>
+      <c r="C192" t="s">
+        <v>406</v>
+      </c>
+      <c r="D192">
+        <v>220</v>
+      </c>
+      <c r="E192">
+        <v>1575.2</v>
+      </c>
+      <c r="F192" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H192" t="s">
+        <v>77</v>
+      </c>
+      <c r="I192" t="s">
+        <v>26</v>
+      </c>
+      <c r="J192" t="s">
+        <v>102</v>
+      </c>
+      <c r="K192">
+        <v>5</v>
+      </c>
+      <c r="L192">
+        <v>2</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>8</v>
+      </c>
+      <c r="O192">
+        <v>1011</v>
+      </c>
+      <c r="P192">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="2">
+        <v>2.4166666666666798</v>
+      </c>
+      <c r="B193" t="s">
+        <v>407</v>
+      </c>
+      <c r="C193" t="s">
+        <v>408</v>
+      </c>
+      <c r="D193">
+        <v>210</v>
+      </c>
+      <c r="E193">
+        <v>1582.6</v>
+      </c>
+      <c r="F193" s="1">
+        <v>7</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H193" t="s">
+        <v>77</v>
+      </c>
+      <c r="I193" t="s">
+        <v>26</v>
+      </c>
+      <c r="J193" t="s">
+        <v>102</v>
+      </c>
+      <c r="K193">
+        <v>4</v>
+      </c>
+      <c r="L193">
+        <v>2</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>8</v>
+      </c>
+      <c r="O193">
+        <v>1011</v>
+      </c>
+      <c r="P193">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="2">
+        <v>2.4583333333333499</v>
+      </c>
+      <c r="B194" t="s">
+        <v>409</v>
+      </c>
+      <c r="C194" t="s">
+        <v>410</v>
+      </c>
+      <c r="D194">
+        <v>210</v>
+      </c>
+      <c r="E194">
+        <v>1589.7</v>
+      </c>
+      <c r="F194" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H194" t="s">
+        <v>238</v>
+      </c>
+      <c r="I194" t="s">
+        <v>26</v>
+      </c>
+      <c r="J194" t="s">
+        <v>102</v>
+      </c>
+      <c r="K194">
+        <v>4</v>
+      </c>
+      <c r="L194">
+        <v>2</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>8</v>
+      </c>
+      <c r="O194">
+        <v>1010</v>
+      </c>
+      <c r="P194">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="2">
+        <v>2.50000000000002</v>
+      </c>
+      <c r="B195" t="s">
+        <v>411</v>
+      </c>
+      <c r="C195" t="s">
+        <v>412</v>
+      </c>
+      <c r="D195">
+        <v>200</v>
+      </c>
+      <c r="E195">
+        <v>1596.6</v>
+      </c>
+      <c r="F195" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H195" t="s">
+        <v>238</v>
+      </c>
+      <c r="I195" t="s">
+        <v>26</v>
+      </c>
+      <c r="J195" t="s">
+        <v>49</v>
+      </c>
+      <c r="K195">
+        <v>4</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>8</v>
+      </c>
+      <c r="O195">
+        <v>1010</v>
+      </c>
+      <c r="P195">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="2">
+        <v>2.5416666666666901</v>
+      </c>
+      <c r="B196" t="s">
+        <v>413</v>
+      </c>
+      <c r="C196" t="s">
+        <v>415</v>
+      </c>
+      <c r="D196">
+        <v>200</v>
+      </c>
+      <c r="E196">
+        <v>1605</v>
+      </c>
+      <c r="F196" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H196" t="s">
+        <v>238</v>
+      </c>
+      <c r="I196" t="s">
+        <v>26</v>
+      </c>
+      <c r="J196" t="s">
+        <v>27</v>
+      </c>
+      <c r="K196">
+        <v>6</v>
+      </c>
+      <c r="L196">
+        <v>3</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+      <c r="N196">
+        <v>8</v>
+      </c>
+      <c r="O196">
+        <v>1012</v>
+      </c>
+      <c r="P196">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="2">
+        <v>2.5833333333333601</v>
+      </c>
+      <c r="B197" t="s">
+        <v>416</v>
+      </c>
+      <c r="C197" t="s">
+        <v>417</v>
+      </c>
+      <c r="D197">
+        <v>200</v>
+      </c>
+      <c r="E197">
+        <v>1613.8</v>
+      </c>
+      <c r="F197" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H197" t="s">
+        <v>238</v>
+      </c>
+      <c r="I197" t="s">
+        <v>26</v>
+      </c>
+      <c r="J197" t="s">
+        <v>49</v>
+      </c>
+      <c r="K197">
+        <v>5</v>
+      </c>
+      <c r="L197">
+        <v>4</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="N197">
+        <v>8</v>
+      </c>
+      <c r="O197">
+        <v>1013</v>
+      </c>
+      <c r="P197">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="2">
+        <v>2.6250000000000302</v>
+      </c>
+      <c r="B198" t="s">
+        <v>418</v>
+      </c>
+      <c r="C198" t="s">
+        <v>414</v>
+      </c>
+      <c r="D198">
+        <v>200</v>
+      </c>
+      <c r="E198">
+        <v>1622.9</v>
+      </c>
+      <c r="F198" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H198" t="s">
+        <v>238</v>
+      </c>
+      <c r="I198" t="s">
+        <v>26</v>
+      </c>
+      <c r="J198" t="s">
+        <v>49</v>
+      </c>
+      <c r="K198">
+        <v>5</v>
+      </c>
+      <c r="L198">
+        <v>4</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>8</v>
+      </c>
+      <c r="O198">
+        <v>1014</v>
+      </c>
+      <c r="P198">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="2">
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="B199" t="s">
+        <v>419</v>
+      </c>
+      <c r="C199" t="s">
+        <v>420</v>
+      </c>
+      <c r="D199">
+        <v>200</v>
+      </c>
+      <c r="E199">
+        <v>1632.1</v>
+      </c>
+      <c r="F199" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H199" t="s">
+        <v>238</v>
+      </c>
+      <c r="I199" t="s">
+        <v>26</v>
+      </c>
+      <c r="J199" t="s">
+        <v>49</v>
+      </c>
+      <c r="K199">
+        <v>5</v>
+      </c>
+      <c r="L199">
+        <v>4</v>
+      </c>
+      <c r="M199">
+        <v>1</v>
+      </c>
+      <c r="N199">
+        <v>8</v>
+      </c>
+      <c r="O199">
+        <v>1014</v>
+      </c>
+      <c r="P199">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <v>2.7083333333333299</v>
+      </c>
+      <c r="B200" t="s">
+        <v>421</v>
+      </c>
+      <c r="C200" t="s">
+        <v>422</v>
+      </c>
+      <c r="D200">
+        <v>200</v>
+      </c>
+      <c r="E200">
+        <v>1640.3</v>
+      </c>
+      <c r="F200" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H200" t="s">
+        <v>238</v>
+      </c>
+      <c r="I200" t="s">
+        <v>26</v>
+      </c>
+      <c r="J200" t="s">
+        <v>49</v>
+      </c>
+      <c r="K200">
+        <v>6</v>
+      </c>
+      <c r="L200">
+        <v>4</v>
+      </c>
+      <c r="M200">
+        <v>1</v>
+      </c>
+      <c r="N200">
+        <v>8</v>
+      </c>
+      <c r="O200">
+        <v>1014</v>
+      </c>
+      <c r="P200">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="B201" t="s">
+        <v>423</v>
+      </c>
+      <c r="C201" t="s">
+        <v>425</v>
+      </c>
+      <c r="D201">
+        <v>200</v>
+      </c>
+      <c r="E201">
+        <v>1648.9</v>
+      </c>
+      <c r="F201" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H201" t="s">
+        <v>238</v>
+      </c>
+      <c r="I201" t="s">
+        <v>26</v>
+      </c>
+      <c r="J201" t="s">
+        <v>27</v>
+      </c>
+      <c r="K201">
+        <v>5</v>
+      </c>
+      <c r="L201">
+        <v>4</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201">
+        <v>8</v>
+      </c>
+      <c r="O201">
+        <v>1014</v>
+      </c>
+      <c r="P201">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="2">
+        <v>2.7916666666666701</v>
+      </c>
+      <c r="B202" t="s">
+        <v>426</v>
+      </c>
+      <c r="C202" t="s">
+        <v>428</v>
+      </c>
+      <c r="D202">
+        <v>200</v>
+      </c>
+      <c r="E202">
+        <v>1657.4</v>
+      </c>
+      <c r="F202" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H202" t="s">
+        <v>238</v>
+      </c>
+      <c r="I202" t="s">
+        <v>26</v>
+      </c>
+      <c r="J202" t="s">
+        <v>27</v>
+      </c>
+      <c r="K202">
+        <v>5</v>
+      </c>
+      <c r="L202">
+        <v>4</v>
+      </c>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>8</v>
+      </c>
+      <c r="O202">
+        <v>1015</v>
+      </c>
+      <c r="P202">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="2">
+        <v>2.8333333333333401</v>
+      </c>
+      <c r="B203" t="s">
+        <v>424</v>
+      </c>
+      <c r="C203" t="s">
+        <v>427</v>
+      </c>
+      <c r="D203">
+        <v>200</v>
+      </c>
+      <c r="E203">
+        <v>1665.4</v>
+      </c>
+      <c r="F203" s="1">
+        <v>8</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H203" t="s">
+        <v>238</v>
+      </c>
+      <c r="I203" t="s">
+        <v>26</v>
+      </c>
+      <c r="J203" t="s">
+        <v>27</v>
+      </c>
+      <c r="K203">
+        <v>5</v>
+      </c>
+      <c r="L203">
+        <v>4</v>
+      </c>
+      <c r="M203">
+        <v>1</v>
+      </c>
+      <c r="N203">
+        <v>8</v>
+      </c>
+      <c r="O203">
+        <v>1015</v>
+      </c>
+      <c r="P203">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="2">
+        <v>2.8750000000000102</v>
+      </c>
+      <c r="B204" t="s">
+        <v>429</v>
+      </c>
+      <c r="C204" t="s">
+        <v>430</v>
+      </c>
+      <c r="D204">
+        <v>210</v>
+      </c>
+      <c r="E204">
+        <v>1675.4</v>
+      </c>
+      <c r="F204" s="1">
+        <v>8</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H204" t="s">
+        <v>77</v>
+      </c>
+      <c r="I204" t="s">
+        <v>26</v>
+      </c>
+      <c r="J204" t="s">
+        <v>27</v>
+      </c>
+      <c r="K204">
+        <v>5</v>
+      </c>
+      <c r="L204">
+        <v>4</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>8</v>
+      </c>
+      <c r="O204">
+        <v>1014</v>
+      </c>
+      <c r="P204">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="2">
+        <v>2.9166666666666798</v>
+      </c>
+      <c r="B205" t="s">
+        <v>431</v>
+      </c>
+      <c r="C205" t="s">
+        <v>432</v>
+      </c>
+      <c r="D205">
+        <v>225</v>
+      </c>
+      <c r="E205">
+        <v>1681.6</v>
+      </c>
+      <c r="F205" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H205" t="s">
+        <v>77</v>
+      </c>
+      <c r="I205" t="s">
+        <v>26</v>
+      </c>
+      <c r="J205" t="s">
+        <v>27</v>
+      </c>
+      <c r="K205">
+        <v>5</v>
+      </c>
+      <c r="L205">
+        <v>4</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>8</v>
+      </c>
+      <c r="O205">
+        <v>1014</v>
+      </c>
+      <c r="P205">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <v>2.9583333333333499</v>
+      </c>
+      <c r="B206" t="s">
+        <v>433</v>
+      </c>
+      <c r="C206" t="s">
+        <v>434</v>
+      </c>
+      <c r="D206">
+        <v>220</v>
+      </c>
+      <c r="E206">
+        <v>1689.9</v>
+      </c>
+      <c r="F206" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H206" t="s">
+        <v>77</v>
+      </c>
+      <c r="I206" t="s">
+        <v>26</v>
+      </c>
+      <c r="J206" t="s">
+        <v>27</v>
+      </c>
+      <c r="K206">
+        <v>5</v>
+      </c>
+      <c r="L206">
+        <v>4</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>8</v>
+      </c>
+      <c r="O206">
+        <v>1014</v>
+      </c>
+      <c r="P206">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="2">
+        <v>3.00000000000002</v>
+      </c>
+      <c r="B207" t="s">
+        <v>435</v>
+      </c>
+      <c r="C207" t="s">
+        <v>436</v>
+      </c>
+      <c r="D207">
+        <v>215</v>
+      </c>
+      <c r="E207">
+        <v>1697.3</v>
+      </c>
+      <c r="F207" s="1">
+        <v>8</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H207" t="s">
+        <v>77</v>
+      </c>
+      <c r="I207" t="s">
+        <v>26</v>
+      </c>
+      <c r="J207" t="s">
+        <v>27</v>
+      </c>
+      <c r="K207">
+        <v>4</v>
+      </c>
+      <c r="L207">
+        <v>4</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>8</v>
+      </c>
+      <c r="O207">
+        <v>1015</v>
+      </c>
+      <c r="P207">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="2">
+        <v>3.0416666666666901</v>
+      </c>
+      <c r="B208" t="s">
+        <v>437</v>
+      </c>
+      <c r="C208" t="s">
+        <v>438</v>
+      </c>
+      <c r="D208">
+        <v>220</v>
+      </c>
+      <c r="E208">
+        <v>1706.2</v>
+      </c>
+      <c r="F208" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H208" t="s">
+        <v>77</v>
+      </c>
+      <c r="I208" t="s">
+        <v>26</v>
+      </c>
+      <c r="J208" t="s">
+        <v>27</v>
+      </c>
+      <c r="K208">
+        <v>4</v>
+      </c>
+      <c r="L208">
+        <v>3</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>8</v>
+      </c>
+      <c r="O208">
+        <v>1015</v>
+      </c>
+      <c r="P208">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="2">
+        <v>3.0833333333333601</v>
+      </c>
+      <c r="B209" t="s">
+        <v>439</v>
+      </c>
+      <c r="C209" t="s">
+        <v>441</v>
+      </c>
+      <c r="D209">
+        <v>220</v>
+      </c>
+      <c r="E209">
+        <v>1713.5</v>
+      </c>
+      <c r="F209" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H209" t="s">
+        <v>77</v>
+      </c>
+      <c r="I209" t="s">
+        <v>26</v>
+      </c>
+      <c r="J209" t="s">
+        <v>27</v>
+      </c>
+      <c r="K209">
+        <v>4</v>
+      </c>
+      <c r="L209">
+        <v>3</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>8</v>
+      </c>
+      <c r="O209">
+        <v>1016</v>
+      </c>
+      <c r="P209">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="2">
+        <v>3.1250000000000302</v>
+      </c>
+      <c r="B210" t="s">
+        <v>440</v>
+      </c>
+      <c r="C210" t="s">
+        <v>442</v>
+      </c>
+      <c r="D210">
+        <v>217</v>
+      </c>
+      <c r="E210">
+        <v>1723.9</v>
+      </c>
+      <c r="F210" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H210" t="s">
+        <v>77</v>
+      </c>
+      <c r="I210" t="s">
+        <v>26</v>
+      </c>
+      <c r="J210" t="s">
+        <v>27</v>
+      </c>
+      <c r="K210">
+        <v>4</v>
+      </c>
+      <c r="L210">
+        <v>3</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>8</v>
+      </c>
+      <c r="O210">
+        <v>1016</v>
+      </c>
+      <c r="P210">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="2">
+        <v>3.1666666666666998</v>
+      </c>
+      <c r="B211" t="s">
+        <v>443</v>
+      </c>
+      <c r="C211" t="s">
+        <v>444</v>
+      </c>
+      <c r="D211">
+        <v>232</v>
+      </c>
+      <c r="E211">
+        <v>1728.9</v>
+      </c>
+      <c r="F211" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H211" t="s">
+        <v>77</v>
+      </c>
+      <c r="I211" t="s">
+        <v>26</v>
+      </c>
+      <c r="J211" t="s">
+        <v>27</v>
+      </c>
+      <c r="K211">
+        <v>4</v>
+      </c>
+      <c r="L211">
+        <v>3</v>
+      </c>
+      <c r="M211">
+        <v>1</v>
+      </c>
+      <c r="N211">
+        <v>8</v>
+      </c>
+      <c r="O211">
+        <v>1016</v>
+      </c>
+      <c r="P211">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="2">
+        <v>3.2083333333333699</v>
+      </c>
+      <c r="B212" t="s">
+        <v>445</v>
+      </c>
+      <c r="C212" t="s">
+        <v>446</v>
+      </c>
+      <c r="D212">
+        <v>233</v>
+      </c>
+      <c r="E212">
+        <v>1734.9</v>
+      </c>
+      <c r="F212" s="1">
+        <v>6</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H212" t="s">
+        <v>77</v>
+      </c>
+      <c r="I212" t="s">
+        <v>26</v>
+      </c>
+      <c r="J212" t="s">
+        <v>27</v>
+      </c>
+      <c r="K212">
+        <v>4</v>
+      </c>
+      <c r="L212">
+        <v>3</v>
+      </c>
+      <c r="M212">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>8</v>
+      </c>
+      <c r="O212">
+        <v>1018</v>
+      </c>
+      <c r="P212">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="2">
+        <v>3.25000000000004</v>
+      </c>
+      <c r="B213" t="s">
+        <v>447</v>
+      </c>
+      <c r="C213" t="s">
+        <v>448</v>
+      </c>
+      <c r="D213">
+        <v>224</v>
+      </c>
+      <c r="E213">
+        <v>1740.9</v>
+      </c>
+      <c r="F213" s="1">
+        <v>6</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H213" t="s">
+        <v>77</v>
+      </c>
+      <c r="I213" t="s">
+        <v>26</v>
+      </c>
+      <c r="J213" t="s">
+        <v>27</v>
+      </c>
+      <c r="K213">
+        <v>4</v>
+      </c>
+      <c r="L213">
+        <v>3</v>
+      </c>
+      <c r="M213">
+        <v>1</v>
+      </c>
+      <c r="N213">
+        <v>8</v>
+      </c>
+      <c r="O213">
+        <v>1018</v>
+      </c>
+      <c r="P213">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="2">
+        <v>3.875</v>
+      </c>
+      <c r="B214" t="s">
+        <v>449</v>
+      </c>
+      <c r="C214" t="s">
+        <v>450</v>
+      </c>
+      <c r="D214">
+        <v>28</v>
+      </c>
+      <c r="E214">
+        <v>41.5</v>
+      </c>
+      <c r="F214" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H214" t="s">
+        <v>135</v>
+      </c>
+      <c r="I214" t="s">
+        <v>26</v>
+      </c>
+      <c r="J214" t="s">
+        <v>102</v>
+      </c>
+      <c r="K214">
+        <v>3</v>
+      </c>
+      <c r="L214">
+        <v>2</v>
+      </c>
+      <c r="M214">
+        <v>2</v>
+      </c>
+      <c r="N214">
+        <v>7</v>
+      </c>
+      <c r="O214">
+        <v>1010</v>
+      </c>
+      <c r="P214">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="2">
+        <v>3.9166666666666701</v>
+      </c>
+      <c r="B215" t="s">
+        <v>451</v>
+      </c>
+      <c r="C215" t="s">
+        <v>452</v>
+      </c>
+      <c r="D215">
+        <v>30</v>
+      </c>
+      <c r="E215">
+        <v>45.1</v>
+      </c>
+      <c r="F215" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H215" t="s">
+        <v>135</v>
+      </c>
+      <c r="I215" t="s">
+        <v>26</v>
+      </c>
+      <c r="J215" t="s">
+        <v>102</v>
+      </c>
+      <c r="K215">
+        <v>3</v>
+      </c>
+      <c r="L215">
+        <v>2</v>
+      </c>
+      <c r="M215">
+        <v>2</v>
+      </c>
+      <c r="N215">
+        <v>7</v>
+      </c>
+      <c r="O215">
+        <v>1010</v>
+      </c>
+      <c r="P215">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="2">
+        <v>3.9583333333333401</v>
+      </c>
+      <c r="B216" t="s">
+        <v>453</v>
+      </c>
+      <c r="C216" t="s">
+        <v>454</v>
+      </c>
+      <c r="D216">
+        <v>15</v>
+      </c>
+      <c r="E216">
+        <v>48.9</v>
+      </c>
+      <c r="F216" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H216" t="s">
+        <v>135</v>
+      </c>
+      <c r="I216" t="s">
+        <v>26</v>
+      </c>
+      <c r="J216" t="s">
+        <v>102</v>
+      </c>
+      <c r="K216">
+        <v>2</v>
+      </c>
+      <c r="L216">
+        <v>2</v>
+      </c>
+      <c r="M216">
+        <v>2</v>
+      </c>
+      <c r="N216">
+        <v>7</v>
+      </c>
+      <c r="O216">
+        <v>1010</v>
+      </c>
+      <c r="P216">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="2">
+        <v>4.0000000000000098</v>
+      </c>
+      <c r="B217" t="s">
+        <v>455</v>
+      </c>
+      <c r="C217" t="s">
+        <v>456</v>
+      </c>
+      <c r="D217">
+        <v>5</v>
+      </c>
+      <c r="E217">
+        <v>50.2</v>
+      </c>
+      <c r="F217" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H217" t="s">
+        <v>135</v>
+      </c>
+      <c r="I217" t="s">
+        <v>26</v>
+      </c>
+      <c r="J217" t="s">
+        <v>102</v>
+      </c>
+      <c r="K217">
+        <v>2</v>
+      </c>
+      <c r="L217">
+        <v>2</v>
+      </c>
+      <c r="M217">
+        <v>2</v>
+      </c>
+      <c r="N217">
+        <v>7</v>
+      </c>
+      <c r="O217">
+        <v>1010</v>
+      </c>
+      <c r="P217">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
+        <v>4.0416666666666803</v>
+      </c>
+      <c r="B218" t="s">
+        <v>457</v>
+      </c>
+      <c r="C218" t="s">
+        <v>458</v>
+      </c>
+      <c r="D218">
+        <v>15</v>
+      </c>
+      <c r="E218">
+        <v>52.2</v>
+      </c>
+      <c r="F218" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H218" t="s">
+        <v>135</v>
+      </c>
+      <c r="I218" t="s">
+        <v>26</v>
+      </c>
+      <c r="J218" t="s">
+        <v>153</v>
+      </c>
+      <c r="K218">
+        <v>2</v>
+      </c>
+      <c r="L218">
+        <v>2</v>
+      </c>
+      <c r="M218">
+        <v>0</v>
+      </c>
+      <c r="N218">
+        <v>7</v>
+      </c>
+      <c r="O218">
+        <v>1010</v>
+      </c>
+      <c r="P218">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="2">
+        <v>4.0833333333333499</v>
+      </c>
+      <c r="B219" t="s">
+        <v>459</v>
+      </c>
+      <c r="C219" t="s">
+        <v>460</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>54.9</v>
+      </c>
+      <c r="F219" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H219" t="s">
+        <v>135</v>
+      </c>
+      <c r="I219" t="s">
+        <v>26</v>
+      </c>
+      <c r="J219" t="s">
+        <v>153</v>
+      </c>
+      <c r="K219">
+        <v>3</v>
+      </c>
+      <c r="L219">
+        <v>2</v>
+      </c>
+      <c r="M219">
+        <v>1</v>
+      </c>
+      <c r="N219">
+        <v>7</v>
+      </c>
+      <c r="O219">
+        <v>1010</v>
+      </c>
+      <c r="P219">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="2">
+        <v>4.1250000000000204</v>
+      </c>
+      <c r="B220" t="s">
+        <v>461</v>
+      </c>
+      <c r="C220" t="s">
+        <v>462</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>59.9</v>
+      </c>
+      <c r="F220" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H220" t="s">
+        <v>135</v>
+      </c>
+      <c r="I220" t="s">
+        <v>26</v>
+      </c>
+      <c r="J220" t="s">
+        <v>153</v>
+      </c>
+      <c r="K220">
+        <v>2</v>
+      </c>
+      <c r="L220">
+        <v>2</v>
+      </c>
+      <c r="M220">
+        <v>4</v>
+      </c>
+      <c r="N220">
+        <v>7</v>
+      </c>
+      <c r="O220">
+        <v>1010</v>
+      </c>
+      <c r="P220">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="2">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="B221" t="s">
+        <v>463</v>
+      </c>
+      <c r="C221" t="s">
+        <v>462</v>
+      </c>
+      <c r="D221">
+        <v>358</v>
+      </c>
+      <c r="E221">
+        <v>62</v>
+      </c>
+      <c r="F221" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H221" t="s">
+        <v>135</v>
+      </c>
+      <c r="I221" t="s">
+        <v>26</v>
+      </c>
+      <c r="J221" t="s">
+        <v>205</v>
+      </c>
+      <c r="K221">
+        <v>2</v>
+      </c>
+      <c r="L221">
+        <v>2</v>
+      </c>
+      <c r="M221">
+        <v>1</v>
+      </c>
+      <c r="N221">
+        <v>8</v>
+      </c>
+      <c r="O221">
+        <v>1010</v>
+      </c>
+      <c r="P221">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="2">
+        <v>4.2083333333333304</v>
+      </c>
+      <c r="B222" t="s">
+        <v>464</v>
+      </c>
+      <c r="C222" t="s">
+        <v>460</v>
+      </c>
+      <c r="D222">
+        <v>10</v>
+      </c>
+      <c r="E222">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="F222" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H222" t="s">
+        <v>135</v>
+      </c>
+      <c r="I222" t="s">
+        <v>26</v>
+      </c>
+      <c r="J222" t="s">
+        <v>205</v>
+      </c>
+      <c r="K222">
+        <v>2</v>
+      </c>
+      <c r="L222">
+        <v>2</v>
+      </c>
+      <c r="M222">
+        <v>2</v>
+      </c>
+      <c r="N222">
+        <v>8</v>
+      </c>
+      <c r="O222">
+        <v>1010</v>
+      </c>
+      <c r="P222">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="2">
+        <v>4.25</v>
+      </c>
+      <c r="B223" t="s">
+        <v>465</v>
+      </c>
+      <c r="C223" t="s">
+        <v>466</v>
+      </c>
+      <c r="D223">
+        <v>10</v>
+      </c>
+      <c r="E223">
+        <v>70</v>
+      </c>
+      <c r="F223" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H223" t="s">
+        <v>135</v>
+      </c>
+      <c r="I223" t="s">
+        <v>26</v>
+      </c>
+      <c r="J223" t="s">
+        <v>205</v>
+      </c>
+      <c r="K223">
+        <v>2</v>
+      </c>
+      <c r="L223">
+        <v>2</v>
+      </c>
+      <c r="M223">
+        <v>2</v>
+      </c>
+      <c r="N223">
+        <v>8</v>
+      </c>
+      <c r="O223">
+        <v>1010</v>
+      </c>
+      <c r="P223">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="2">
+        <v>4.2916666666666696</v>
+      </c>
+      <c r="B224" t="s">
+        <v>467</v>
+      </c>
+      <c r="C224" t="s">
+        <v>468</v>
+      </c>
+      <c r="D224">
+        <v>10</v>
+      </c>
+      <c r="E224">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="F224" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H224" t="s">
+        <v>135</v>
+      </c>
+      <c r="I224" t="s">
+        <v>26</v>
+      </c>
+      <c r="J224" t="s">
+        <v>205</v>
+      </c>
+      <c r="K224">
+        <v>2</v>
+      </c>
+      <c r="L224">
+        <v>2</v>
+      </c>
+      <c r="M224">
+        <v>2</v>
+      </c>
+      <c r="N224">
+        <v>8</v>
+      </c>
+      <c r="O224">
+        <v>1010</v>
+      </c>
+      <c r="P224">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="2">
+        <v>4.3333333333333401</v>
+      </c>
+      <c r="B225" t="s">
+        <v>469</v>
+      </c>
+      <c r="C225" t="s">
+        <v>470</v>
+      </c>
+      <c r="D225">
+        <v>350</v>
+      </c>
+      <c r="E225">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="F225" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="G225" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H225" t="s">
+        <v>135</v>
+      </c>
+      <c r="I225" t="s">
+        <v>26</v>
+      </c>
+      <c r="J225" t="s">
+        <v>205</v>
+      </c>
+      <c r="K225">
+        <v>3</v>
+      </c>
+      <c r="L225">
+        <v>2</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="N225">
+        <v>8</v>
+      </c>
+      <c r="O225">
+        <v>1010</v>
+      </c>
+      <c r="P225">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="2">
+        <v>4.3750000000000098</v>
+      </c>
+      <c r="B226" t="s">
+        <v>471</v>
+      </c>
+      <c r="C226" t="s">
+        <v>472</v>
+      </c>
+      <c r="D226">
+        <v>356</v>
+      </c>
+      <c r="E226">
+        <v>85.9</v>
+      </c>
+      <c r="F226" s="1">
+        <v>5</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H226" t="s">
+        <v>135</v>
+      </c>
+      <c r="I226" t="s">
+        <v>26</v>
+      </c>
+      <c r="J226" t="s">
+        <v>118</v>
+      </c>
+      <c r="K226">
+        <v>3</v>
+      </c>
+      <c r="L226">
+        <v>2</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>7</v>
+      </c>
+      <c r="O226">
+        <v>1010</v>
+      </c>
+      <c r="P226">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="2">
+        <v>4.4166666666666803</v>
+      </c>
+      <c r="B227" t="s">
+        <v>473</v>
+      </c>
+      <c r="C227" t="s">
+        <v>472</v>
+      </c>
+      <c r="D227">
+        <v>350</v>
+      </c>
+      <c r="E227">
+        <v>90</v>
+      </c>
+      <c r="F227" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H227" t="s">
+        <v>135</v>
+      </c>
+      <c r="I227" t="s">
+        <v>26</v>
+      </c>
+      <c r="J227" t="s">
+        <v>474</v>
+      </c>
+      <c r="K227">
+        <v>3</v>
+      </c>
+      <c r="L227">
+        <v>2</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
+      </c>
+      <c r="N227">
+        <v>8</v>
+      </c>
+      <c r="O227">
+        <v>1010</v>
+      </c>
+      <c r="P227">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="2">
+        <v>4.4583333333333499</v>
+      </c>
+      <c r="B228" t="s">
+        <v>475</v>
+      </c>
+      <c r="C228" t="s">
+        <v>476</v>
+      </c>
+      <c r="D228">
+        <v>350</v>
+      </c>
+      <c r="E228">
+        <v>98.5</v>
+      </c>
+      <c r="F228" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H228" t="s">
+        <v>135</v>
+      </c>
+      <c r="I228" t="s">
+        <v>26</v>
+      </c>
+      <c r="J228" t="s">
+        <v>162</v>
+      </c>
+      <c r="K228">
+        <v>4</v>
+      </c>
+      <c r="L228">
+        <v>2</v>
+      </c>
+      <c r="M228">
+        <v>3</v>
+      </c>
+      <c r="N228">
+        <v>7</v>
+      </c>
+      <c r="O228">
+        <v>1010</v>
+      </c>
+      <c r="P228">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="2">
+        <v>4.5000000000000204</v>
+      </c>
+      <c r="B229" t="s">
+        <v>477</v>
+      </c>
+      <c r="C229" t="s">
+        <v>478</v>
+      </c>
+      <c r="D229">
+        <v>90</v>
+      </c>
+      <c r="E229">
+        <v>110.4</v>
+      </c>
+      <c r="F229" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H229" t="s">
+        <v>135</v>
+      </c>
+      <c r="I229" t="s">
+        <v>26</v>
+      </c>
+      <c r="J229" t="s">
+        <v>162</v>
+      </c>
+      <c r="K229">
+        <v>5</v>
+      </c>
+      <c r="L229">
+        <v>4</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
+      </c>
+      <c r="N229">
+        <v>7</v>
+      </c>
+      <c r="O229">
+        <v>1010</v>
+      </c>
+      <c r="P229">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <v>4.5416666666666901</v>
+      </c>
+      <c r="B230" t="s">
+        <v>424</v>
+      </c>
+      <c r="C230" t="s">
+        <v>479</v>
+      </c>
+      <c r="D230">
+        <v>85</v>
+      </c>
+      <c r="E230">
+        <v>119.4</v>
+      </c>
+      <c r="F230" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H230" t="s">
+        <v>135</v>
+      </c>
+      <c r="I230" t="s">
+        <v>26</v>
+      </c>
+      <c r="J230" t="s">
+        <v>480</v>
+      </c>
+      <c r="K230">
+        <v>6</v>
+      </c>
+      <c r="L230">
+        <v>4</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>7</v>
+      </c>
+      <c r="O230">
+        <v>1009</v>
+      </c>
+      <c r="P230">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <v>4.5833333333333597</v>
+      </c>
+      <c r="B231" t="s">
+        <v>481</v>
+      </c>
+      <c r="C231" t="s">
+        <v>482</v>
+      </c>
+      <c r="D231">
+        <v>80</v>
+      </c>
+      <c r="E231">
+        <v>123.3</v>
+      </c>
+      <c r="F231" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="H231" t="s">
+        <v>135</v>
+      </c>
+      <c r="I231" t="s">
+        <v>26</v>
+      </c>
+      <c r="J231" t="s">
+        <v>480</v>
+      </c>
+      <c r="K231">
+        <v>6</v>
+      </c>
+      <c r="L231">
+        <v>5</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>7</v>
+      </c>
+      <c r="O231">
+        <v>1009</v>
+      </c>
+      <c r="P231">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Dziennik2024.xlsx
+++ b/Dziennik2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szybk\OneDrive\Pulpit\Studia\inzynierka\Inzynierka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F0F61B-DC6B-489A-A45B-DC434A142A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6689546E-6037-4469-BF08-6CB0B4BB2F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BF3D5F66-ACDF-49A3-8594-396AB682FC7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="668">
   <si>
     <t>Godzina</t>
   </si>
@@ -1487,7 +1487,559 @@
     <t>15*02,0E</t>
   </si>
   <si>
-    <t>G`</t>
+    <t>55*06,6N</t>
+  </si>
+  <si>
+    <t>15*10,6E</t>
+  </si>
+  <si>
+    <t>F30</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>55*12,3N</t>
+  </si>
+  <si>
+    <t>55*20,4N</t>
+  </si>
+  <si>
+    <t>15*08,8E</t>
+  </si>
+  <si>
+    <t>15*08,2E</t>
+  </si>
+  <si>
+    <t>55*27,2N</t>
+  </si>
+  <si>
+    <t>15*13,9E</t>
+  </si>
+  <si>
+    <t>55*34,9N</t>
+  </si>
+  <si>
+    <t>15*18,2E</t>
+  </si>
+  <si>
+    <t>55*41,8N</t>
+  </si>
+  <si>
+    <t>15*22,1E</t>
+  </si>
+  <si>
+    <t>15*26,3E</t>
+  </si>
+  <si>
+    <t>55*56,3N</t>
+  </si>
+  <si>
+    <t>15*30,3E</t>
+  </si>
+  <si>
+    <t>56*03,7N</t>
+  </si>
+  <si>
+    <t>15*33,7E</t>
+  </si>
+  <si>
+    <t>56*04,1N</t>
+  </si>
+  <si>
+    <t>15*33,0E</t>
+  </si>
+  <si>
+    <t>56*01,3N</t>
+  </si>
+  <si>
+    <t>15*29,0E</t>
+  </si>
+  <si>
+    <t>55*55,7N</t>
+  </si>
+  <si>
+    <t>15*21,6E</t>
+  </si>
+  <si>
+    <t>55*50,9N</t>
+  </si>
+  <si>
+    <t>15*16,7E</t>
+  </si>
+  <si>
+    <t>55*45,5N</t>
+  </si>
+  <si>
+    <t>15*12,1E</t>
+  </si>
+  <si>
+    <t>55*38,9N</t>
+  </si>
+  <si>
+    <t>15*06,6E</t>
+  </si>
+  <si>
+    <t>55*32,9N</t>
+  </si>
+  <si>
+    <t>15*01,7E</t>
+  </si>
+  <si>
+    <t>55*27,7N</t>
+  </si>
+  <si>
+    <t>14*57,2E</t>
+  </si>
+  <si>
+    <t>55*23,3N</t>
+  </si>
+  <si>
+    <t>14*54,1E</t>
+  </si>
+  <si>
+    <t>55*18,1N</t>
+  </si>
+  <si>
+    <t>14*49,9E</t>
+  </si>
+  <si>
+    <t>14*46,4E</t>
+  </si>
+  <si>
+    <t>55*15,7N</t>
+  </si>
+  <si>
+    <t>14*42,1E</t>
+  </si>
+  <si>
+    <t>55*12,5N</t>
+  </si>
+  <si>
+    <t>14*38,6E</t>
+  </si>
+  <si>
+    <t>55*10,9N</t>
+  </si>
+  <si>
+    <t>14*37,9E</t>
+  </si>
+  <si>
+    <t>55*05,3N</t>
+  </si>
+  <si>
+    <t>14*33,0E</t>
+  </si>
+  <si>
+    <t>14*27,6E</t>
+  </si>
+  <si>
+    <t>54*59,1N</t>
+  </si>
+  <si>
+    <t>ENE</t>
+  </si>
+  <si>
+    <t>54*53,1N</t>
+  </si>
+  <si>
+    <t>14*22,4E</t>
+  </si>
+  <si>
+    <t>54*46,6N</t>
+  </si>
+  <si>
+    <t>14*15,5E</t>
+  </si>
+  <si>
+    <t>54*41,1N</t>
+  </si>
+  <si>
+    <t>14*04,4E</t>
+  </si>
+  <si>
+    <t>13*55,2E</t>
+  </si>
+  <si>
+    <t>54*36,1N</t>
+  </si>
+  <si>
+    <t>54*31,5N</t>
+  </si>
+  <si>
+    <t>13*44,5E</t>
+  </si>
+  <si>
+    <t>54*29,3N</t>
+  </si>
+  <si>
+    <t>13*42,3E</t>
+  </si>
+  <si>
+    <t>54*27,2N</t>
+  </si>
+  <si>
+    <t>13*48,1E</t>
+  </si>
+  <si>
+    <t>54*26,8N</t>
+  </si>
+  <si>
+    <t>13*57,3E</t>
+  </si>
+  <si>
+    <t>54*25,9N</t>
+  </si>
+  <si>
+    <t>14*01,9E</t>
+  </si>
+  <si>
+    <t>54*25,0N</t>
+  </si>
+  <si>
+    <t>14*07,8E</t>
+  </si>
+  <si>
+    <t>54*23,1N</t>
+  </si>
+  <si>
+    <t>54*23,9N</t>
+  </si>
+  <si>
+    <t>14*14,2E</t>
+  </si>
+  <si>
+    <t>14*18,2E</t>
+  </si>
+  <si>
+    <t>54*22,6N</t>
+  </si>
+  <si>
+    <t>14*21,5E</t>
+  </si>
+  <si>
+    <t>54*22,4N</t>
+  </si>
+  <si>
+    <t>14*25,2E</t>
+  </si>
+  <si>
+    <t>54*22,2N</t>
+  </si>
+  <si>
+    <t>14*27,0E</t>
+  </si>
+  <si>
+    <t>54*21,8N</t>
+  </si>
+  <si>
+    <t>14*29,1E</t>
+  </si>
+  <si>
+    <t>54*21,6N</t>
+  </si>
+  <si>
+    <t>14*29,8E</t>
+  </si>
+  <si>
+    <t>54*20,9N</t>
+  </si>
+  <si>
+    <t>14*33,3E</t>
+  </si>
+  <si>
+    <t>54*19,6N</t>
+  </si>
+  <si>
+    <t>14*39,0E</t>
+  </si>
+  <si>
+    <t>54*18,3N</t>
+  </si>
+  <si>
+    <t>14*47,2E</t>
+  </si>
+  <si>
+    <t>54*17,0N</t>
+  </si>
+  <si>
+    <t>14*55,0E</t>
+  </si>
+  <si>
+    <t>54*16,1N</t>
+  </si>
+  <si>
+    <t>15*01,8E</t>
+  </si>
+  <si>
+    <t>54*14,8N</t>
+  </si>
+  <si>
+    <t>15*10,4E</t>
+  </si>
+  <si>
+    <t>54*13,8N</t>
+  </si>
+  <si>
+    <t>15*17,9E</t>
+  </si>
+  <si>
+    <t>54*11,6N</t>
+  </si>
+  <si>
+    <t>15*26,4E</t>
+  </si>
+  <si>
+    <t>54*12,1N</t>
+  </si>
+  <si>
+    <t>15*29,8E</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>54*13,2N</t>
+  </si>
+  <si>
+    <t>15*27,6E</t>
+  </si>
+  <si>
+    <t>NNE</t>
+  </si>
+  <si>
+    <t>54*14,6N</t>
+  </si>
+  <si>
+    <t>15*11,4E</t>
+  </si>
+  <si>
+    <t>54*20,8N</t>
+  </si>
+  <si>
+    <t>15*01,4E</t>
+  </si>
+  <si>
+    <t>54*15,5N</t>
+  </si>
+  <si>
+    <t>14*56,5E</t>
+  </si>
+  <si>
+    <t>54*17,5N</t>
+  </si>
+  <si>
+    <t>14*46,5E</t>
+  </si>
+  <si>
+    <t>54*18,5N</t>
+  </si>
+  <si>
+    <t>14*35,8E</t>
+  </si>
+  <si>
+    <t>54*18,7N</t>
+  </si>
+  <si>
+    <t>54*19,2N</t>
+  </si>
+  <si>
+    <t>14*16,4E</t>
+  </si>
+  <si>
+    <t>14*06,2E</t>
+  </si>
+  <si>
+    <t>13*56,0E</t>
+  </si>
+  <si>
+    <t>13*50,3E</t>
+  </si>
+  <si>
+    <t>54*27,6N</t>
+  </si>
+  <si>
+    <t>13*53,3E</t>
+  </si>
+  <si>
+    <t>54*30,7N</t>
+  </si>
+  <si>
+    <t>54*29,1N</t>
+  </si>
+  <si>
+    <t>13*43,6E</t>
+  </si>
+  <si>
+    <t>54*29,5N</t>
+  </si>
+  <si>
+    <t>13*37,9E</t>
+  </si>
+  <si>
+    <t>54*34,5N</t>
+  </si>
+  <si>
+    <t>13*41,6E</t>
+  </si>
+  <si>
+    <t>54*37,8N</t>
+  </si>
+  <si>
+    <t>13*38,7E</t>
+  </si>
+  <si>
+    <t>54*43,2N</t>
+  </si>
+  <si>
+    <t>13*33,6E</t>
+  </si>
+  <si>
+    <t>54*48,9N</t>
+  </si>
+  <si>
+    <t>13*29,0E</t>
+  </si>
+  <si>
+    <t>54*54,8N</t>
+  </si>
+  <si>
+    <t>13*22,0E</t>
+  </si>
+  <si>
+    <t>54*59,4N</t>
+  </si>
+  <si>
+    <t>13*16,2E</t>
+  </si>
+  <si>
+    <t>55*03,1N</t>
+  </si>
+  <si>
+    <t>13*09,7E</t>
+  </si>
+  <si>
+    <t>55*06,2N</t>
+  </si>
+  <si>
+    <t>13*03,1E</t>
+  </si>
+  <si>
+    <t>55*08,9N</t>
+  </si>
+  <si>
+    <t>12*56,9E</t>
+  </si>
+  <si>
+    <t>55*11,8N</t>
+  </si>
+  <si>
+    <t>12*51,2E</t>
+  </si>
+  <si>
+    <t>55*15,0N</t>
+  </si>
+  <si>
+    <t>12*44,4E</t>
+  </si>
+  <si>
+    <t>55*20,9N</t>
+  </si>
+  <si>
+    <t>12*42,1E</t>
+  </si>
+  <si>
+    <t>55*29,2N</t>
+  </si>
+  <si>
+    <t>12*43,0E</t>
+  </si>
+  <si>
+    <t>55*29,7N</t>
+  </si>
+  <si>
+    <t>12*42,9E</t>
+  </si>
+  <si>
+    <t>55*20,5N</t>
+  </si>
+  <si>
+    <t>55*14,4N</t>
+  </si>
+  <si>
+    <t>12*46,3E</t>
+  </si>
+  <si>
+    <t>55*09,4N</t>
+  </si>
+  <si>
+    <t>12*55,7E</t>
+  </si>
+  <si>
+    <t>55*04,4N</t>
+  </si>
+  <si>
+    <t>13*06,1E</t>
+  </si>
+  <si>
+    <t>55*00,7N</t>
+  </si>
+  <si>
+    <t>13*15,1E</t>
+  </si>
+  <si>
+    <t>54*55,8N</t>
+  </si>
+  <si>
+    <t>13*20,0E</t>
+  </si>
+  <si>
+    <t>54*50,8N</t>
+  </si>
+  <si>
+    <t>13*25,5E</t>
+  </si>
+  <si>
+    <t>54*45,9N</t>
+  </si>
+  <si>
+    <t>13*31,6E</t>
+  </si>
+  <si>
+    <t>54*40,3N</t>
+  </si>
+  <si>
+    <t>54*33,0N</t>
+  </si>
+  <si>
+    <t>13*45,1E</t>
+  </si>
+  <si>
+    <t>54*27,0N</t>
+  </si>
+  <si>
+    <t>54*19,3N</t>
+  </si>
+  <si>
+    <t>13*56,5E</t>
+  </si>
+  <si>
+    <t>54*12,7N</t>
+  </si>
+  <si>
+    <t>54*04,8N</t>
+  </si>
+  <si>
+    <t>14*01,7E</t>
+  </si>
+  <si>
+    <t>14*08,5E</t>
+  </si>
+  <si>
+    <t>54*01,4N</t>
+  </si>
+  <si>
+    <t>14*11,8E</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2DB018-EC3F-4C8E-A36B-34F72611C81F}">
-  <dimension ref="A1:P231"/>
+  <dimension ref="A1:P328"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -13394,7 +13946,7 @@
         <v>3.9</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>483</v>
+        <v>331</v>
       </c>
       <c r="H231" t="s">
         <v>135</v>
@@ -13422,6 +13974,4856 @@
       </c>
       <c r="P231">
         <v>21</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" s="2">
+        <v>4.916666666666667</v>
+      </c>
+      <c r="B232" t="s">
+        <v>483</v>
+      </c>
+      <c r="C232" t="s">
+        <v>484</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>137.30000000000001</v>
+      </c>
+      <c r="F232" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H232" t="s">
+        <v>485</v>
+      </c>
+      <c r="I232" t="s">
+        <v>26</v>
+      </c>
+      <c r="J232" t="s">
+        <v>49</v>
+      </c>
+      <c r="K232">
+        <v>4</v>
+      </c>
+      <c r="L232">
+        <v>2</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>8</v>
+      </c>
+      <c r="O232">
+        <v>1009</v>
+      </c>
+      <c r="P232">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" s="2">
+        <v>4.9583333333333304</v>
+      </c>
+      <c r="B233" t="s">
+        <v>487</v>
+      </c>
+      <c r="C233" t="s">
+        <v>489</v>
+      </c>
+      <c r="D233">
+        <v>340</v>
+      </c>
+      <c r="E233">
+        <v>142.1</v>
+      </c>
+      <c r="F233" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G233" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H233" t="s">
+        <v>485</v>
+      </c>
+      <c r="I233" t="s">
+        <v>26</v>
+      </c>
+      <c r="J233" t="s">
+        <v>49</v>
+      </c>
+      <c r="K233">
+        <v>5</v>
+      </c>
+      <c r="L233">
+        <v>4</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>8</v>
+      </c>
+      <c r="O233">
+        <v>1012</v>
+      </c>
+      <c r="P233">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <v>5</v>
+      </c>
+      <c r="B234" t="s">
+        <v>488</v>
+      </c>
+      <c r="C234" t="s">
+        <v>490</v>
+      </c>
+      <c r="D234">
+        <v>20</v>
+      </c>
+      <c r="E234">
+        <v>151</v>
+      </c>
+      <c r="F234" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H234" t="s">
+        <v>485</v>
+      </c>
+      <c r="I234" t="s">
+        <v>26</v>
+      </c>
+      <c r="J234" t="s">
+        <v>49</v>
+      </c>
+      <c r="K234">
+        <v>6</v>
+      </c>
+      <c r="L234">
+        <v>5</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>8</v>
+      </c>
+      <c r="O234">
+        <v>1012</v>
+      </c>
+      <c r="P234">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <v>5.0416666666666696</v>
+      </c>
+      <c r="B235" t="s">
+        <v>491</v>
+      </c>
+      <c r="C235" t="s">
+        <v>492</v>
+      </c>
+      <c r="D235">
+        <v>26</v>
+      </c>
+      <c r="E235">
+        <v>158.80000000000001</v>
+      </c>
+      <c r="F235" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G235" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H235" t="s">
+        <v>485</v>
+      </c>
+      <c r="I235" t="s">
+        <v>26</v>
+      </c>
+      <c r="J235" t="s">
+        <v>49</v>
+      </c>
+      <c r="K235">
+        <v>7</v>
+      </c>
+      <c r="L235">
+        <v>5</v>
+      </c>
+      <c r="M235">
+        <v>0</v>
+      </c>
+      <c r="N235">
+        <v>8</v>
+      </c>
+      <c r="O235">
+        <v>1012</v>
+      </c>
+      <c r="P235">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <v>5.0833333333333401</v>
+      </c>
+      <c r="B236" t="s">
+        <v>493</v>
+      </c>
+      <c r="C236" t="s">
+        <v>494</v>
+      </c>
+      <c r="D236">
+        <v>15</v>
+      </c>
+      <c r="E236">
+        <v>167.4</v>
+      </c>
+      <c r="F236" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="G236" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H236" t="s">
+        <v>485</v>
+      </c>
+      <c r="I236" t="s">
+        <v>26</v>
+      </c>
+      <c r="J236" t="s">
+        <v>49</v>
+      </c>
+      <c r="K236">
+        <v>7</v>
+      </c>
+      <c r="L236">
+        <v>5</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>8</v>
+      </c>
+      <c r="O236">
+        <v>1012</v>
+      </c>
+      <c r="P236">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="2">
+        <v>5.1250000000000098</v>
+      </c>
+      <c r="B237" t="s">
+        <v>495</v>
+      </c>
+      <c r="C237" t="s">
+        <v>496</v>
+      </c>
+      <c r="D237">
+        <v>20</v>
+      </c>
+      <c r="E237">
+        <v>174.6</v>
+      </c>
+      <c r="F237" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G237" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H237" t="s">
+        <v>485</v>
+      </c>
+      <c r="I237" t="s">
+        <v>26</v>
+      </c>
+      <c r="J237" t="s">
+        <v>49</v>
+      </c>
+      <c r="K237">
+        <v>6</v>
+      </c>
+      <c r="L237">
+        <v>5</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>8</v>
+      </c>
+      <c r="O237">
+        <v>1012</v>
+      </c>
+      <c r="P237">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <v>5.1666666666666803</v>
+      </c>
+      <c r="B238" t="s">
+        <v>133</v>
+      </c>
+      <c r="C238" t="s">
+        <v>497</v>
+      </c>
+      <c r="D238">
+        <v>15</v>
+      </c>
+      <c r="E238">
+        <v>182.6</v>
+      </c>
+      <c r="F238" s="1">
+        <v>8</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H238" t="s">
+        <v>485</v>
+      </c>
+      <c r="I238" t="s">
+        <v>26</v>
+      </c>
+      <c r="J238" t="s">
+        <v>49</v>
+      </c>
+      <c r="K238">
+        <v>5</v>
+      </c>
+      <c r="L238">
+        <v>4</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+      <c r="N238">
+        <v>8</v>
+      </c>
+      <c r="O238">
+        <v>1012</v>
+      </c>
+      <c r="P238">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <v>5.2083333333333499</v>
+      </c>
+      <c r="B239" t="s">
+        <v>498</v>
+      </c>
+      <c r="C239" t="s">
+        <v>499</v>
+      </c>
+      <c r="D239">
+        <v>15</v>
+      </c>
+      <c r="E239">
+        <v>190</v>
+      </c>
+      <c r="F239" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H239" t="s">
+        <v>485</v>
+      </c>
+      <c r="I239" t="s">
+        <v>26</v>
+      </c>
+      <c r="J239" t="s">
+        <v>49</v>
+      </c>
+      <c r="K239">
+        <v>6</v>
+      </c>
+      <c r="L239">
+        <v>4</v>
+      </c>
+      <c r="M239">
+        <v>2</v>
+      </c>
+      <c r="N239">
+        <v>8</v>
+      </c>
+      <c r="O239">
+        <v>1012</v>
+      </c>
+      <c r="P239">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <v>5.2500000000000204</v>
+      </c>
+      <c r="B240" t="s">
+        <v>500</v>
+      </c>
+      <c r="C240" t="s">
+        <v>501</v>
+      </c>
+      <c r="D240">
+        <v>7</v>
+      </c>
+      <c r="E240">
+        <v>197.5</v>
+      </c>
+      <c r="F240" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H240" t="s">
+        <v>485</v>
+      </c>
+      <c r="I240" t="s">
+        <v>26</v>
+      </c>
+      <c r="J240" t="s">
+        <v>49</v>
+      </c>
+      <c r="K240">
+        <v>6</v>
+      </c>
+      <c r="L240">
+        <v>4</v>
+      </c>
+      <c r="M240">
+        <v>2</v>
+      </c>
+      <c r="N240">
+        <v>8</v>
+      </c>
+      <c r="O240">
+        <v>1012</v>
+      </c>
+      <c r="P240">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="2">
+        <v>5.25</v>
+      </c>
+      <c r="B241" t="s">
+        <v>502</v>
+      </c>
+      <c r="C241" t="s">
+        <v>503</v>
+      </c>
+      <c r="D241">
+        <v>115</v>
+      </c>
+      <c r="E241">
+        <v>212.6</v>
+      </c>
+      <c r="F241" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H241" t="s">
+        <v>25</v>
+      </c>
+      <c r="I241" t="s">
+        <v>26</v>
+      </c>
+      <c r="J241" t="s">
+        <v>27</v>
+      </c>
+      <c r="K241">
+        <v>5</v>
+      </c>
+      <c r="L241">
+        <v>2</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>8</v>
+      </c>
+      <c r="O241">
+        <v>1014</v>
+      </c>
+      <c r="P241">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <v>5.2916666666666696</v>
+      </c>
+      <c r="B242" t="s">
+        <v>504</v>
+      </c>
+      <c r="C242" t="s">
+        <v>505</v>
+      </c>
+      <c r="D242">
+        <v>220</v>
+      </c>
+      <c r="E242">
+        <v>216.1</v>
+      </c>
+      <c r="F242" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H242" t="s">
+        <v>135</v>
+      </c>
+      <c r="I242" t="s">
+        <v>26</v>
+      </c>
+      <c r="J242" t="s">
+        <v>27</v>
+      </c>
+      <c r="K242">
+        <v>5</v>
+      </c>
+      <c r="L242">
+        <v>2</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>8</v>
+      </c>
+      <c r="O242">
+        <v>1014</v>
+      </c>
+      <c r="P242">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <v>5.3333333333333401</v>
+      </c>
+      <c r="B243" t="s">
+        <v>506</v>
+      </c>
+      <c r="C243" t="s">
+        <v>507</v>
+      </c>
+      <c r="D243">
+        <v>215</v>
+      </c>
+      <c r="E243">
+        <v>223.2</v>
+      </c>
+      <c r="F243" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H243" t="s">
+        <v>135</v>
+      </c>
+      <c r="I243" t="s">
+        <v>26</v>
+      </c>
+      <c r="J243" t="s">
+        <v>27</v>
+      </c>
+      <c r="K243">
+        <v>5</v>
+      </c>
+      <c r="L243">
+        <v>2</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
+      </c>
+      <c r="N243">
+        <v>8</v>
+      </c>
+      <c r="O243">
+        <v>1014</v>
+      </c>
+      <c r="P243">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
+        <v>5.3750000000000098</v>
+      </c>
+      <c r="B244" t="s">
+        <v>508</v>
+      </c>
+      <c r="C244" t="s">
+        <v>509</v>
+      </c>
+      <c r="D244">
+        <v>206</v>
+      </c>
+      <c r="E244">
+        <v>228.6</v>
+      </c>
+      <c r="F244" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="G244" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H244" t="s">
+        <v>135</v>
+      </c>
+      <c r="I244" t="s">
+        <v>26</v>
+      </c>
+      <c r="J244" t="s">
+        <v>27</v>
+      </c>
+      <c r="K244">
+        <v>5</v>
+      </c>
+      <c r="L244">
+        <v>2</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
+      </c>
+      <c r="N244">
+        <v>8</v>
+      </c>
+      <c r="O244">
+        <v>1014</v>
+      </c>
+      <c r="P244">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="2">
+        <v>5.4166666666666803</v>
+      </c>
+      <c r="B245" t="s">
+        <v>510</v>
+      </c>
+      <c r="C245" t="s">
+        <v>511</v>
+      </c>
+      <c r="D245">
+        <v>205</v>
+      </c>
+      <c r="E245">
+        <v>234.6</v>
+      </c>
+      <c r="F245" s="1">
+        <v>6</v>
+      </c>
+      <c r="G245" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H245" t="s">
+        <v>135</v>
+      </c>
+      <c r="I245" t="s">
+        <v>26</v>
+      </c>
+      <c r="J245" t="s">
+        <v>49</v>
+      </c>
+      <c r="K245">
+        <v>4</v>
+      </c>
+      <c r="L245">
+        <v>2</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>8</v>
+      </c>
+      <c r="O245">
+        <v>1014</v>
+      </c>
+      <c r="P245">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="2">
+        <v>5.4583333333333499</v>
+      </c>
+      <c r="B246" t="s">
+        <v>512</v>
+      </c>
+      <c r="C246" t="s">
+        <v>513</v>
+      </c>
+      <c r="D246">
+        <v>205</v>
+      </c>
+      <c r="E246">
+        <v>242</v>
+      </c>
+      <c r="F246" s="1">
+        <v>8</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H246" t="s">
+        <v>135</v>
+      </c>
+      <c r="I246" t="s">
+        <v>26</v>
+      </c>
+      <c r="J246" t="s">
+        <v>49</v>
+      </c>
+      <c r="K246">
+        <v>5</v>
+      </c>
+      <c r="L246">
+        <v>2</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>8</v>
+      </c>
+      <c r="O246">
+        <v>1014</v>
+      </c>
+      <c r="P246">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="2">
+        <v>5.5000000000000204</v>
+      </c>
+      <c r="B247" t="s">
+        <v>514</v>
+      </c>
+      <c r="C247" t="s">
+        <v>515</v>
+      </c>
+      <c r="D247">
+        <v>210</v>
+      </c>
+      <c r="E247">
+        <v>248.7</v>
+      </c>
+      <c r="F247" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H247" t="s">
+        <v>135</v>
+      </c>
+      <c r="I247" t="s">
+        <v>26</v>
+      </c>
+      <c r="J247" t="s">
+        <v>27</v>
+      </c>
+      <c r="K247">
+        <v>4</v>
+      </c>
+      <c r="L247">
+        <v>2</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>8</v>
+      </c>
+      <c r="O247">
+        <v>1014</v>
+      </c>
+      <c r="P247">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="2">
+        <v>5.5416666666666901</v>
+      </c>
+      <c r="B248" t="s">
+        <v>516</v>
+      </c>
+      <c r="C248" t="s">
+        <v>517</v>
+      </c>
+      <c r="D248">
+        <v>205</v>
+      </c>
+      <c r="E248">
+        <v>253.2</v>
+      </c>
+      <c r="F248" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G248" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H248" t="s">
+        <v>135</v>
+      </c>
+      <c r="I248" t="s">
+        <v>26</v>
+      </c>
+      <c r="J248" t="s">
+        <v>27</v>
+      </c>
+      <c r="K248">
+        <v>4</v>
+      </c>
+      <c r="L248">
+        <v>2</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>8</v>
+      </c>
+      <c r="O248">
+        <v>1014</v>
+      </c>
+      <c r="P248">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="2">
+        <v>5.5833333333333597</v>
+      </c>
+      <c r="B249" t="s">
+        <v>518</v>
+      </c>
+      <c r="C249" t="s">
+        <v>519</v>
+      </c>
+      <c r="D249">
+        <v>203</v>
+      </c>
+      <c r="E249">
+        <v>258.10000000000002</v>
+      </c>
+      <c r="F249" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G249" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H249" t="s">
+        <v>135</v>
+      </c>
+      <c r="I249" t="s">
+        <v>26</v>
+      </c>
+      <c r="J249" t="s">
+        <v>27</v>
+      </c>
+      <c r="K249">
+        <v>4</v>
+      </c>
+      <c r="L249">
+        <v>2</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>8</v>
+      </c>
+      <c r="O249">
+        <v>1014</v>
+      </c>
+      <c r="P249">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="2">
+        <v>5.6250000000000302</v>
+      </c>
+      <c r="B250" t="s">
+        <v>520</v>
+      </c>
+      <c r="C250" t="s">
+        <v>521</v>
+      </c>
+      <c r="D250">
+        <v>210</v>
+      </c>
+      <c r="E250">
+        <v>265.10000000000002</v>
+      </c>
+      <c r="F250" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G250" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H250" t="s">
+        <v>135</v>
+      </c>
+      <c r="I250" t="s">
+        <v>26</v>
+      </c>
+      <c r="J250" t="s">
+        <v>27</v>
+      </c>
+      <c r="K250">
+        <v>4</v>
+      </c>
+      <c r="L250">
+        <v>2</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>8</v>
+      </c>
+      <c r="O250">
+        <v>1014</v>
+      </c>
+      <c r="P250">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="B251" t="s">
+        <v>520</v>
+      </c>
+      <c r="C251" t="s">
+        <v>522</v>
+      </c>
+      <c r="D251">
+        <v>257</v>
+      </c>
+      <c r="E251">
+        <v>269.5</v>
+      </c>
+      <c r="F251" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H251" t="s">
+        <v>135</v>
+      </c>
+      <c r="I251" t="s">
+        <v>26</v>
+      </c>
+      <c r="J251" t="s">
+        <v>241</v>
+      </c>
+      <c r="K251">
+        <v>2</v>
+      </c>
+      <c r="L251">
+        <v>2</v>
+      </c>
+      <c r="M251">
+        <v>1</v>
+      </c>
+      <c r="N251">
+        <v>8</v>
+      </c>
+      <c r="O251">
+        <v>1013</v>
+      </c>
+      <c r="P251">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="2">
+        <v>5.5416666666666696</v>
+      </c>
+      <c r="B252" t="s">
+        <v>523</v>
+      </c>
+      <c r="C252" t="s">
+        <v>524</v>
+      </c>
+      <c r="D252">
+        <v>200</v>
+      </c>
+      <c r="E252">
+        <v>273</v>
+      </c>
+      <c r="F252" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G252" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H252" t="s">
+        <v>135</v>
+      </c>
+      <c r="I252" t="s">
+        <v>26</v>
+      </c>
+      <c r="J252" t="s">
+        <v>102</v>
+      </c>
+      <c r="K252">
+        <v>3</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>1</v>
+      </c>
+      <c r="N252">
+        <v>8</v>
+      </c>
+      <c r="O252">
+        <v>1013</v>
+      </c>
+      <c r="P252">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="2">
+        <v>5.5833333333333401</v>
+      </c>
+      <c r="B253" t="s">
+        <v>525</v>
+      </c>
+      <c r="C253" t="s">
+        <v>526</v>
+      </c>
+      <c r="D253">
+        <v>205</v>
+      </c>
+      <c r="E253">
+        <v>276.5</v>
+      </c>
+      <c r="F253" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G253" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H253" t="s">
+        <v>135</v>
+      </c>
+      <c r="I253" t="s">
+        <v>26</v>
+      </c>
+      <c r="J253" t="s">
+        <v>299</v>
+      </c>
+      <c r="K253">
+        <v>3</v>
+      </c>
+      <c r="L253">
+        <v>2</v>
+      </c>
+      <c r="M253">
+        <v>1</v>
+      </c>
+      <c r="N253">
+        <v>8</v>
+      </c>
+      <c r="O253">
+        <v>1014</v>
+      </c>
+      <c r="P253">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A254" s="2">
+        <v>5.6250000000000098</v>
+      </c>
+      <c r="B254" t="s">
+        <v>527</v>
+      </c>
+      <c r="C254" t="s">
+        <v>528</v>
+      </c>
+      <c r="D254">
+        <v>180</v>
+      </c>
+      <c r="E254">
+        <v>278.5</v>
+      </c>
+      <c r="F254" s="1">
+        <v>2</v>
+      </c>
+      <c r="G254" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H254" t="s">
+        <v>135</v>
+      </c>
+      <c r="I254" t="s">
+        <v>26</v>
+      </c>
+      <c r="J254" t="s">
+        <v>299</v>
+      </c>
+      <c r="K254">
+        <v>4</v>
+      </c>
+      <c r="L254">
+        <v>3</v>
+      </c>
+      <c r="M254">
+        <v>1</v>
+      </c>
+      <c r="N254">
+        <v>8</v>
+      </c>
+      <c r="O254">
+        <v>1014</v>
+      </c>
+      <c r="P254">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A255" s="2">
+        <v>5.6666666666666803</v>
+      </c>
+      <c r="B255" t="s">
+        <v>529</v>
+      </c>
+      <c r="C255" t="s">
+        <v>530</v>
+      </c>
+      <c r="D255">
+        <v>195</v>
+      </c>
+      <c r="E255">
+        <v>285</v>
+      </c>
+      <c r="F255" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H255" t="s">
+        <v>135</v>
+      </c>
+      <c r="I255" t="s">
+        <v>26</v>
+      </c>
+      <c r="J255" t="s">
+        <v>247</v>
+      </c>
+      <c r="K255">
+        <v>5</v>
+      </c>
+      <c r="L255">
+        <v>3</v>
+      </c>
+      <c r="M255">
+        <v>1</v>
+      </c>
+      <c r="N255">
+        <v>8</v>
+      </c>
+      <c r="O255">
+        <v>1014</v>
+      </c>
+      <c r="P255">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A256" s="2">
+        <v>5.7083333333333499</v>
+      </c>
+      <c r="B256" t="s">
+        <v>532</v>
+      </c>
+      <c r="C256" t="s">
+        <v>531</v>
+      </c>
+      <c r="D256">
+        <v>195</v>
+      </c>
+      <c r="E256">
+        <v>291.8</v>
+      </c>
+      <c r="F256" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H256" t="s">
+        <v>135</v>
+      </c>
+      <c r="I256" t="s">
+        <v>26</v>
+      </c>
+      <c r="J256" t="s">
+        <v>533</v>
+      </c>
+      <c r="K256">
+        <v>5</v>
+      </c>
+      <c r="L256">
+        <v>3</v>
+      </c>
+      <c r="M256">
+        <v>1</v>
+      </c>
+      <c r="N256">
+        <v>8</v>
+      </c>
+      <c r="O256">
+        <v>1014</v>
+      </c>
+      <c r="P256">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A257" s="2">
+        <v>5.7500000000000204</v>
+      </c>
+      <c r="B257" t="s">
+        <v>534</v>
+      </c>
+      <c r="C257" t="s">
+        <v>535</v>
+      </c>
+      <c r="D257">
+        <v>208</v>
+      </c>
+      <c r="E257">
+        <v>298.60000000000002</v>
+      </c>
+      <c r="F257" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G257" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H257" t="s">
+        <v>135</v>
+      </c>
+      <c r="I257" t="s">
+        <v>26</v>
+      </c>
+      <c r="J257" t="s">
+        <v>241</v>
+      </c>
+      <c r="K257">
+        <v>5</v>
+      </c>
+      <c r="L257">
+        <v>4</v>
+      </c>
+      <c r="M257">
+        <v>1</v>
+      </c>
+      <c r="N257">
+        <v>8</v>
+      </c>
+      <c r="O257">
+        <v>1014</v>
+      </c>
+      <c r="P257">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="2">
+        <v>5.7916666666666901</v>
+      </c>
+      <c r="B258" t="s">
+        <v>536</v>
+      </c>
+      <c r="C258" t="s">
+        <v>537</v>
+      </c>
+      <c r="D258">
+        <v>214</v>
+      </c>
+      <c r="E258">
+        <v>306.2</v>
+      </c>
+      <c r="F258" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G258" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H258" t="s">
+        <v>135</v>
+      </c>
+      <c r="I258" t="s">
+        <v>26</v>
+      </c>
+      <c r="J258" t="s">
+        <v>241</v>
+      </c>
+      <c r="K258">
+        <v>6</v>
+      </c>
+      <c r="L258">
+        <v>4</v>
+      </c>
+      <c r="M258">
+        <v>1</v>
+      </c>
+      <c r="N258">
+        <v>8</v>
+      </c>
+      <c r="O258">
+        <v>1014</v>
+      </c>
+      <c r="P258">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="2">
+        <v>5.8333333333333597</v>
+      </c>
+      <c r="B259" t="s">
+        <v>538</v>
+      </c>
+      <c r="C259" t="s">
+        <v>539</v>
+      </c>
+      <c r="D259">
+        <v>240</v>
+      </c>
+      <c r="E259">
+        <v>315.10000000000002</v>
+      </c>
+      <c r="F259" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="G259" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H259" t="s">
+        <v>135</v>
+      </c>
+      <c r="I259" t="s">
+        <v>26</v>
+      </c>
+      <c r="J259" t="s">
+        <v>241</v>
+      </c>
+      <c r="K259">
+        <v>6</v>
+      </c>
+      <c r="L259">
+        <v>4</v>
+      </c>
+      <c r="M259">
+        <v>1</v>
+      </c>
+      <c r="N259">
+        <v>8</v>
+      </c>
+      <c r="O259">
+        <v>1014</v>
+      </c>
+      <c r="P259">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="2">
+        <v>5.8750000000000302</v>
+      </c>
+      <c r="B260" t="s">
+        <v>541</v>
+      </c>
+      <c r="C260" t="s">
+        <v>540</v>
+      </c>
+      <c r="D260">
+        <v>220</v>
+      </c>
+      <c r="E260">
+        <v>322.60000000000002</v>
+      </c>
+      <c r="F260" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G260" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H260" t="s">
+        <v>135</v>
+      </c>
+      <c r="I260" t="s">
+        <v>26</v>
+      </c>
+      <c r="J260" t="s">
+        <v>241</v>
+      </c>
+      <c r="K260">
+        <v>5</v>
+      </c>
+      <c r="L260">
+        <v>4</v>
+      </c>
+      <c r="M260">
+        <v>1</v>
+      </c>
+      <c r="N260">
+        <v>8</v>
+      </c>
+      <c r="O260">
+        <v>1014</v>
+      </c>
+      <c r="P260">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="2">
+        <v>5.9166666666666998</v>
+      </c>
+      <c r="B261" t="s">
+        <v>542</v>
+      </c>
+      <c r="C261" t="s">
+        <v>543</v>
+      </c>
+      <c r="D261">
+        <v>240</v>
+      </c>
+      <c r="E261">
+        <v>330.5</v>
+      </c>
+      <c r="F261" s="1">
+        <v>8</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H261" t="s">
+        <v>135</v>
+      </c>
+      <c r="I261" t="s">
+        <v>26</v>
+      </c>
+      <c r="J261" t="s">
+        <v>241</v>
+      </c>
+      <c r="K261">
+        <v>5</v>
+      </c>
+      <c r="L261">
+        <v>4</v>
+      </c>
+      <c r="M261">
+        <v>1</v>
+      </c>
+      <c r="N261">
+        <v>8</v>
+      </c>
+      <c r="O261">
+        <v>1020</v>
+      </c>
+      <c r="P261">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="B262" t="s">
+        <v>544</v>
+      </c>
+      <c r="C262" t="s">
+        <v>545</v>
+      </c>
+      <c r="D262">
+        <v>100</v>
+      </c>
+      <c r="E262">
+        <v>338.8</v>
+      </c>
+      <c r="F262" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G262" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H262" t="s">
+        <v>135</v>
+      </c>
+      <c r="I262" t="s">
+        <v>26</v>
+      </c>
+      <c r="J262" t="s">
+        <v>118</v>
+      </c>
+      <c r="K262">
+        <v>2</v>
+      </c>
+      <c r="L262">
+        <v>2</v>
+      </c>
+      <c r="M262">
+        <v>2</v>
+      </c>
+      <c r="N262">
+        <v>7</v>
+      </c>
+      <c r="O262">
+        <v>1014</v>
+      </c>
+      <c r="P262">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A263" s="2">
+        <v>4.375</v>
+      </c>
+      <c r="B263" t="s">
+        <v>546</v>
+      </c>
+      <c r="C263" t="s">
+        <v>547</v>
+      </c>
+      <c r="D263">
+        <v>105</v>
+      </c>
+      <c r="E263">
+        <v>341.2</v>
+      </c>
+      <c r="F263" s="1">
+        <v>4</v>
+      </c>
+      <c r="G263" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H263" t="s">
+        <v>135</v>
+      </c>
+      <c r="I263" t="s">
+        <v>26</v>
+      </c>
+      <c r="J263" t="s">
+        <v>153</v>
+      </c>
+      <c r="K263">
+        <v>2</v>
+      </c>
+      <c r="L263">
+        <v>2</v>
+      </c>
+      <c r="M263">
+        <v>3</v>
+      </c>
+      <c r="N263">
+        <v>7</v>
+      </c>
+      <c r="O263">
+        <v>1014</v>
+      </c>
+      <c r="P263">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A264" s="2">
+        <v>4.416666666666667</v>
+      </c>
+      <c r="B264" t="s">
+        <v>548</v>
+      </c>
+      <c r="C264" t="s">
+        <v>549</v>
+      </c>
+      <c r="D264">
+        <v>115</v>
+      </c>
+      <c r="E264">
+        <v>348</v>
+      </c>
+      <c r="F264" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G264" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H264" t="s">
+        <v>135</v>
+      </c>
+      <c r="I264" t="s">
+        <v>26</v>
+      </c>
+      <c r="J264" t="s">
+        <v>153</v>
+      </c>
+      <c r="K264">
+        <v>2</v>
+      </c>
+      <c r="L264">
+        <v>2</v>
+      </c>
+      <c r="M264">
+        <v>0</v>
+      </c>
+      <c r="N264">
+        <v>7</v>
+      </c>
+      <c r="O264">
+        <v>1014</v>
+      </c>
+      <c r="P264">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A265" s="2">
+        <v>4.4583333333333304</v>
+      </c>
+      <c r="B265" t="s">
+        <v>550</v>
+      </c>
+      <c r="C265" t="s">
+        <v>551</v>
+      </c>
+      <c r="D265">
+        <v>105</v>
+      </c>
+      <c r="E265">
+        <v>350.9</v>
+      </c>
+      <c r="F265" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="G265" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H265" t="s">
+        <v>135</v>
+      </c>
+      <c r="I265" t="s">
+        <v>26</v>
+      </c>
+      <c r="J265" t="s">
+        <v>205</v>
+      </c>
+      <c r="K265">
+        <v>2</v>
+      </c>
+      <c r="L265">
+        <v>2</v>
+      </c>
+      <c r="M265">
+        <v>3</v>
+      </c>
+      <c r="N265">
+        <v>7</v>
+      </c>
+      <c r="O265">
+        <v>1014</v>
+      </c>
+      <c r="P265">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A266" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="B266" t="s">
+        <v>552</v>
+      </c>
+      <c r="C266" t="s">
+        <v>553</v>
+      </c>
+      <c r="D266">
+        <v>105</v>
+      </c>
+      <c r="E266">
+        <v>354.5</v>
+      </c>
+      <c r="F266" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G266" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H266" t="s">
+        <v>135</v>
+      </c>
+      <c r="I266" t="s">
+        <v>26</v>
+      </c>
+      <c r="J266" t="s">
+        <v>153</v>
+      </c>
+      <c r="K266">
+        <v>2</v>
+      </c>
+      <c r="L266">
+        <v>2</v>
+      </c>
+      <c r="M266">
+        <v>0</v>
+      </c>
+      <c r="N266">
+        <v>7</v>
+      </c>
+      <c r="O266">
+        <v>1014</v>
+      </c>
+      <c r="P266">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A267" s="2">
+        <v>4.5416666666666696</v>
+      </c>
+      <c r="B267" t="s">
+        <v>555</v>
+      </c>
+      <c r="C267" t="s">
+        <v>556</v>
+      </c>
+      <c r="D267">
+        <v>100</v>
+      </c>
+      <c r="E267">
+        <v>358.4</v>
+      </c>
+      <c r="F267" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="G267" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H267" t="s">
+        <v>135</v>
+      </c>
+      <c r="I267" t="s">
+        <v>26</v>
+      </c>
+      <c r="J267" t="s">
+        <v>162</v>
+      </c>
+      <c r="K267">
+        <v>2</v>
+      </c>
+      <c r="L267">
+        <v>2</v>
+      </c>
+      <c r="M267">
+        <v>2</v>
+      </c>
+      <c r="N267">
+        <v>7</v>
+      </c>
+      <c r="O267">
+        <v>1010</v>
+      </c>
+      <c r="P267">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A268" s="2">
+        <v>4.5833333333333401</v>
+      </c>
+      <c r="B268" t="s">
+        <v>554</v>
+      </c>
+      <c r="C268" t="s">
+        <v>557</v>
+      </c>
+      <c r="D268">
+        <v>108</v>
+      </c>
+      <c r="E268">
+        <v>360.9</v>
+      </c>
+      <c r="F268" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G268" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H268" t="s">
+        <v>135</v>
+      </c>
+      <c r="I268" t="s">
+        <v>26</v>
+      </c>
+      <c r="J268" t="s">
+        <v>162</v>
+      </c>
+      <c r="K268">
+        <v>2</v>
+      </c>
+      <c r="L268">
+        <v>2</v>
+      </c>
+      <c r="M268">
+        <v>2</v>
+      </c>
+      <c r="N268">
+        <v>7</v>
+      </c>
+      <c r="O268">
+        <v>1010</v>
+      </c>
+      <c r="P268">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A269" s="2">
+        <v>4.6250000000000098</v>
+      </c>
+      <c r="B269" t="s">
+        <v>558</v>
+      </c>
+      <c r="C269" t="s">
+        <v>559</v>
+      </c>
+      <c r="D269">
+        <v>100</v>
+      </c>
+      <c r="E269">
+        <v>362.8</v>
+      </c>
+      <c r="F269" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="G269" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H269" t="s">
+        <v>135</v>
+      </c>
+      <c r="I269" t="s">
+        <v>26</v>
+      </c>
+      <c r="J269" t="s">
+        <v>205</v>
+      </c>
+      <c r="K269">
+        <v>1</v>
+      </c>
+      <c r="L269">
+        <v>2</v>
+      </c>
+      <c r="M269">
+        <v>2</v>
+      </c>
+      <c r="N269">
+        <v>7</v>
+      </c>
+      <c r="O269">
+        <v>1008</v>
+      </c>
+      <c r="P269">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A270" s="2">
+        <v>4.6666666666666803</v>
+      </c>
+      <c r="B270" t="s">
+        <v>560</v>
+      </c>
+      <c r="C270" t="s">
+        <v>561</v>
+      </c>
+      <c r="D270">
+        <v>65</v>
+      </c>
+      <c r="E270">
+        <v>363.1</v>
+      </c>
+      <c r="F270" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="G270" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H270" t="s">
+        <v>135</v>
+      </c>
+      <c r="I270" t="s">
+        <v>26</v>
+      </c>
+      <c r="J270" t="s">
+        <v>205</v>
+      </c>
+      <c r="K270">
+        <v>1</v>
+      </c>
+      <c r="L270">
+        <v>2</v>
+      </c>
+      <c r="M270">
+        <v>1</v>
+      </c>
+      <c r="N270">
+        <v>8</v>
+      </c>
+      <c r="O270">
+        <v>1008</v>
+      </c>
+      <c r="P270">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A271" s="2">
+        <v>4.7083333333333499</v>
+      </c>
+      <c r="B271" t="s">
+        <v>560</v>
+      </c>
+      <c r="C271" t="s">
+        <v>561</v>
+      </c>
+      <c r="D271">
+        <v>65</v>
+      </c>
+      <c r="E271">
+        <v>364.8</v>
+      </c>
+      <c r="F271" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="G271" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H271" t="s">
+        <v>135</v>
+      </c>
+      <c r="I271" t="s">
+        <v>26</v>
+      </c>
+      <c r="J271" t="s">
+        <v>299</v>
+      </c>
+      <c r="K271">
+        <v>2</v>
+      </c>
+      <c r="L271">
+        <v>2</v>
+      </c>
+      <c r="M271">
+        <v>3</v>
+      </c>
+      <c r="N271">
+        <v>7</v>
+      </c>
+      <c r="O271">
+        <v>1008</v>
+      </c>
+      <c r="P271">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A272" s="2">
+        <v>4.7500000000000204</v>
+      </c>
+      <c r="B272" t="s">
+        <v>560</v>
+      </c>
+      <c r="C272" t="s">
+        <v>460</v>
+      </c>
+      <c r="D272">
+        <v>65</v>
+      </c>
+      <c r="E272">
+        <v>365.1</v>
+      </c>
+      <c r="F272" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="G272" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H272" t="s">
+        <v>135</v>
+      </c>
+      <c r="I272" t="s">
+        <v>26</v>
+      </c>
+      <c r="J272" t="s">
+        <v>162</v>
+      </c>
+      <c r="K272">
+        <v>1</v>
+      </c>
+      <c r="L272">
+        <v>2</v>
+      </c>
+      <c r="M272">
+        <v>3</v>
+      </c>
+      <c r="N272">
+        <v>7</v>
+      </c>
+      <c r="O272">
+        <v>1007</v>
+      </c>
+      <c r="P272">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A273" s="2">
+        <v>4.7916666666666901</v>
+      </c>
+      <c r="B273" t="s">
+        <v>562</v>
+      </c>
+      <c r="C273" t="s">
+        <v>563</v>
+      </c>
+      <c r="D273">
+        <v>120</v>
+      </c>
+      <c r="E273">
+        <v>365.5</v>
+      </c>
+      <c r="F273" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G273" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H273" t="s">
+        <v>135</v>
+      </c>
+      <c r="I273" t="s">
+        <v>26</v>
+      </c>
+      <c r="J273" t="s">
+        <v>27</v>
+      </c>
+      <c r="K273">
+        <v>1</v>
+      </c>
+      <c r="L273">
+        <v>1</v>
+      </c>
+      <c r="M273">
+        <v>2</v>
+      </c>
+      <c r="N273">
+        <v>7</v>
+      </c>
+      <c r="O273">
+        <v>1010</v>
+      </c>
+      <c r="P273">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A274" s="2">
+        <v>4.8333333333333597</v>
+      </c>
+      <c r="B274" t="s">
+        <v>564</v>
+      </c>
+      <c r="C274" t="s">
+        <v>565</v>
+      </c>
+      <c r="D274">
+        <v>120</v>
+      </c>
+      <c r="E274">
+        <v>366.6</v>
+      </c>
+      <c r="F274" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G274" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H274" t="s">
+        <v>135</v>
+      </c>
+      <c r="I274" t="s">
+        <v>26</v>
+      </c>
+      <c r="J274" t="s">
+        <v>27</v>
+      </c>
+      <c r="K274">
+        <v>1</v>
+      </c>
+      <c r="L274">
+        <v>1</v>
+      </c>
+      <c r="M274">
+        <v>2</v>
+      </c>
+      <c r="N274">
+        <v>7</v>
+      </c>
+      <c r="O274">
+        <v>1008</v>
+      </c>
+      <c r="P274">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A275" s="2">
+        <v>4.8750000000000302</v>
+      </c>
+      <c r="B275" t="s">
+        <v>566</v>
+      </c>
+      <c r="C275" t="s">
+        <v>567</v>
+      </c>
+      <c r="D275">
+        <v>80</v>
+      </c>
+      <c r="E275">
+        <v>367</v>
+      </c>
+      <c r="F275" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G275" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H275" t="s">
+        <v>135</v>
+      </c>
+      <c r="I275" t="s">
+        <v>26</v>
+      </c>
+      <c r="J275" t="s">
+        <v>27</v>
+      </c>
+      <c r="K275">
+        <v>1</v>
+      </c>
+      <c r="L275">
+        <v>1</v>
+      </c>
+      <c r="M275">
+        <v>2</v>
+      </c>
+      <c r="N275">
+        <v>7</v>
+      </c>
+      <c r="O275">
+        <v>1010</v>
+      </c>
+      <c r="P275">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A276" s="2">
+        <v>4.9166666666666998</v>
+      </c>
+      <c r="B276" t="s">
+        <v>568</v>
+      </c>
+      <c r="C276" t="s">
+        <v>569</v>
+      </c>
+      <c r="D276">
+        <v>105</v>
+      </c>
+      <c r="E276">
+        <v>369.2</v>
+      </c>
+      <c r="F276" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G276" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H276" t="s">
+        <v>135</v>
+      </c>
+      <c r="I276" t="s">
+        <v>26</v>
+      </c>
+      <c r="J276" t="s">
+        <v>153</v>
+      </c>
+      <c r="K276">
+        <v>2</v>
+      </c>
+      <c r="L276">
+        <v>1</v>
+      </c>
+      <c r="M276">
+        <v>3</v>
+      </c>
+      <c r="N276">
+        <v>7</v>
+      </c>
+      <c r="O276">
+        <v>1010</v>
+      </c>
+      <c r="P276">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A277" s="2">
+        <v>4.9583333333333703</v>
+      </c>
+      <c r="B277" t="s">
+        <v>570</v>
+      </c>
+      <c r="C277" t="s">
+        <v>571</v>
+      </c>
+      <c r="D277">
+        <v>105</v>
+      </c>
+      <c r="E277">
+        <v>372.8</v>
+      </c>
+      <c r="F277" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G277" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H277" t="s">
+        <v>135</v>
+      </c>
+      <c r="I277" t="s">
+        <v>26</v>
+      </c>
+      <c r="J277" t="s">
+        <v>205</v>
+      </c>
+      <c r="K277">
+        <v>3</v>
+      </c>
+      <c r="L277">
+        <v>1</v>
+      </c>
+      <c r="M277">
+        <v>3</v>
+      </c>
+      <c r="N277">
+        <v>7</v>
+      </c>
+      <c r="O277">
+        <v>1011</v>
+      </c>
+      <c r="P277">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A278" s="2">
+        <v>5.00000000000004</v>
+      </c>
+      <c r="B278" t="s">
+        <v>572</v>
+      </c>
+      <c r="C278" t="s">
+        <v>573</v>
+      </c>
+      <c r="D278">
+        <v>105</v>
+      </c>
+      <c r="E278">
+        <v>377.8</v>
+      </c>
+      <c r="F278" s="1">
+        <v>5</v>
+      </c>
+      <c r="G278" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H278" t="s">
+        <v>135</v>
+      </c>
+      <c r="I278" t="s">
+        <v>26</v>
+      </c>
+      <c r="J278" t="s">
+        <v>205</v>
+      </c>
+      <c r="K278">
+        <v>3</v>
+      </c>
+      <c r="L278">
+        <v>1</v>
+      </c>
+      <c r="M278">
+        <v>3</v>
+      </c>
+      <c r="N278">
+        <v>7</v>
+      </c>
+      <c r="O278">
+        <v>1012</v>
+      </c>
+      <c r="P278">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A279" s="2">
+        <v>5.0416666666667096</v>
+      </c>
+      <c r="B279" t="s">
+        <v>574</v>
+      </c>
+      <c r="C279" t="s">
+        <v>575</v>
+      </c>
+      <c r="D279">
+        <v>105</v>
+      </c>
+      <c r="E279">
+        <v>382.6</v>
+      </c>
+      <c r="F279" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="G279" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H279" t="s">
+        <v>135</v>
+      </c>
+      <c r="I279" t="s">
+        <v>26</v>
+      </c>
+      <c r="J279" t="s">
+        <v>153</v>
+      </c>
+      <c r="K279">
+        <v>3</v>
+      </c>
+      <c r="L279">
+        <v>2</v>
+      </c>
+      <c r="M279">
+        <v>0</v>
+      </c>
+      <c r="N279">
+        <v>7</v>
+      </c>
+      <c r="O279">
+        <v>1012</v>
+      </c>
+      <c r="P279">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A280" s="2">
+        <v>5.0833333333333801</v>
+      </c>
+      <c r="B280" t="s">
+        <v>576</v>
+      </c>
+      <c r="C280" t="s">
+        <v>577</v>
+      </c>
+      <c r="D280">
+        <v>105</v>
+      </c>
+      <c r="E280">
+        <v>386.7</v>
+      </c>
+      <c r="F280" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G280" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H280" t="s">
+        <v>135</v>
+      </c>
+      <c r="I280" t="s">
+        <v>26</v>
+      </c>
+      <c r="J280" t="s">
+        <v>153</v>
+      </c>
+      <c r="K280">
+        <v>3</v>
+      </c>
+      <c r="L280">
+        <v>2</v>
+      </c>
+      <c r="M280">
+        <v>0</v>
+      </c>
+      <c r="N280">
+        <v>7</v>
+      </c>
+      <c r="O280">
+        <v>1012</v>
+      </c>
+      <c r="P280">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A281" s="2">
+        <v>5.1250000000000497</v>
+      </c>
+      <c r="B281" t="s">
+        <v>578</v>
+      </c>
+      <c r="C281" t="s">
+        <v>579</v>
+      </c>
+      <c r="D281">
+        <v>105</v>
+      </c>
+      <c r="E281">
+        <v>392</v>
+      </c>
+      <c r="F281" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G281" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H281" t="s">
+        <v>135</v>
+      </c>
+      <c r="I281" t="s">
+        <v>26</v>
+      </c>
+      <c r="J281" t="s">
+        <v>153</v>
+      </c>
+      <c r="K281">
+        <v>3</v>
+      </c>
+      <c r="L281">
+        <v>2</v>
+      </c>
+      <c r="M281">
+        <v>0</v>
+      </c>
+      <c r="N281">
+        <v>7</v>
+      </c>
+      <c r="O281">
+        <v>1012</v>
+      </c>
+      <c r="P281">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A282" s="2">
+        <v>5.1666666666667203</v>
+      </c>
+      <c r="B282" t="s">
+        <v>580</v>
+      </c>
+      <c r="C282" t="s">
+        <v>581</v>
+      </c>
+      <c r="D282">
+        <v>105</v>
+      </c>
+      <c r="E282">
+        <v>396.3</v>
+      </c>
+      <c r="F282" s="1">
+        <v>4</v>
+      </c>
+      <c r="G282" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H282" t="s">
+        <v>135</v>
+      </c>
+      <c r="I282" t="s">
+        <v>26</v>
+      </c>
+      <c r="J282" t="s">
+        <v>153</v>
+      </c>
+      <c r="K282">
+        <v>3</v>
+      </c>
+      <c r="L282">
+        <v>2</v>
+      </c>
+      <c r="M282">
+        <v>0</v>
+      </c>
+      <c r="N282">
+        <v>7</v>
+      </c>
+      <c r="O282">
+        <v>1012</v>
+      </c>
+      <c r="P282">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A283" s="2">
+        <v>5.2083333333333899</v>
+      </c>
+      <c r="B283" t="s">
+        <v>582</v>
+      </c>
+      <c r="C283" t="s">
+        <v>583</v>
+      </c>
+      <c r="D283">
+        <v>105</v>
+      </c>
+      <c r="E283">
+        <v>401.6</v>
+      </c>
+      <c r="F283" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G283" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H283" t="s">
+        <v>135</v>
+      </c>
+      <c r="I283" t="s">
+        <v>26</v>
+      </c>
+      <c r="J283" t="s">
+        <v>153</v>
+      </c>
+      <c r="K283">
+        <v>3</v>
+      </c>
+      <c r="L283">
+        <v>2</v>
+      </c>
+      <c r="M283">
+        <v>3</v>
+      </c>
+      <c r="N283">
+        <v>7</v>
+      </c>
+      <c r="O283">
+        <v>1012</v>
+      </c>
+      <c r="P283">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A284" s="2">
+        <v>5.458333333333333</v>
+      </c>
+      <c r="B284" t="s">
+        <v>584</v>
+      </c>
+      <c r="C284" t="s">
+        <v>585</v>
+      </c>
+      <c r="D284">
+        <v>285</v>
+      </c>
+      <c r="E284">
+        <v>402.7</v>
+      </c>
+      <c r="F284" s="1">
+        <v>5</v>
+      </c>
+      <c r="G284" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H284" t="s">
+        <v>135</v>
+      </c>
+      <c r="I284" t="s">
+        <v>26</v>
+      </c>
+      <c r="J284" t="s">
+        <v>586</v>
+      </c>
+      <c r="K284">
+        <v>3</v>
+      </c>
+      <c r="L284">
+        <v>2</v>
+      </c>
+      <c r="M284">
+        <v>0</v>
+      </c>
+      <c r="N284">
+        <v>7</v>
+      </c>
+      <c r="O284">
+        <v>1008</v>
+      </c>
+      <c r="P284">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A285" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="B285" t="s">
+        <v>587</v>
+      </c>
+      <c r="C285" t="s">
+        <v>588</v>
+      </c>
+      <c r="D285">
+        <v>285</v>
+      </c>
+      <c r="E285">
+        <v>407.5</v>
+      </c>
+      <c r="F285" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="G285" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H285" t="s">
+        <v>135</v>
+      </c>
+      <c r="I285" t="s">
+        <v>26</v>
+      </c>
+      <c r="J285" t="s">
+        <v>589</v>
+      </c>
+      <c r="K285">
+        <v>3</v>
+      </c>
+      <c r="L285">
+        <v>2</v>
+      </c>
+      <c r="M285">
+        <v>0</v>
+      </c>
+      <c r="N285">
+        <v>7</v>
+      </c>
+      <c r="O285">
+        <v>1008</v>
+      </c>
+      <c r="P285">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A286" s="2">
+        <v>5.5416666666666696</v>
+      </c>
+      <c r="B286" t="s">
+        <v>590</v>
+      </c>
+      <c r="C286" t="s">
+        <v>591</v>
+      </c>
+      <c r="D286">
+        <v>285</v>
+      </c>
+      <c r="E286">
+        <v>414.2</v>
+      </c>
+      <c r="F286" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="G286" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H286" t="s">
+        <v>135</v>
+      </c>
+      <c r="I286" t="s">
+        <v>26</v>
+      </c>
+      <c r="J286" t="s">
+        <v>589</v>
+      </c>
+      <c r="K286">
+        <v>3</v>
+      </c>
+      <c r="L286">
+        <v>2</v>
+      </c>
+      <c r="M286">
+        <v>0</v>
+      </c>
+      <c r="N286">
+        <v>7</v>
+      </c>
+      <c r="O286">
+        <v>1008</v>
+      </c>
+      <c r="P286">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A287" s="2">
+        <v>5.5833333333333401</v>
+      </c>
+      <c r="B287" t="s">
+        <v>592</v>
+      </c>
+      <c r="C287" t="s">
+        <v>593</v>
+      </c>
+      <c r="D287">
+        <v>285</v>
+      </c>
+      <c r="E287">
+        <v>418</v>
+      </c>
+      <c r="F287" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="G287" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H287" t="s">
+        <v>135</v>
+      </c>
+      <c r="I287" t="s">
+        <v>26</v>
+      </c>
+      <c r="J287" t="s">
+        <v>586</v>
+      </c>
+      <c r="K287">
+        <v>3</v>
+      </c>
+      <c r="L287">
+        <v>2</v>
+      </c>
+      <c r="M287">
+        <v>0</v>
+      </c>
+      <c r="N287">
+        <v>8</v>
+      </c>
+      <c r="O287">
+        <v>1008</v>
+      </c>
+      <c r="P287">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A288" s="2">
+        <v>5.6250000000000098</v>
+      </c>
+      <c r="B288" t="s">
+        <v>594</v>
+      </c>
+      <c r="C288" t="s">
+        <v>595</v>
+      </c>
+      <c r="D288">
+        <v>285</v>
+      </c>
+      <c r="E288">
+        <v>423.2</v>
+      </c>
+      <c r="F288" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H288" t="s">
+        <v>135</v>
+      </c>
+      <c r="I288" t="s">
+        <v>26</v>
+      </c>
+      <c r="J288" t="s">
+        <v>115</v>
+      </c>
+      <c r="K288">
+        <v>2</v>
+      </c>
+      <c r="L288">
+        <v>2</v>
+      </c>
+      <c r="M288">
+        <v>0</v>
+      </c>
+      <c r="N288">
+        <v>8</v>
+      </c>
+      <c r="O288">
+        <v>1008</v>
+      </c>
+      <c r="P288">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A289" s="2">
+        <v>5.6666666666666803</v>
+      </c>
+      <c r="B289" t="s">
+        <v>596</v>
+      </c>
+      <c r="C289" t="s">
+        <v>597</v>
+      </c>
+      <c r="D289">
+        <v>280</v>
+      </c>
+      <c r="E289">
+        <v>429.2</v>
+      </c>
+      <c r="F289" s="1">
+        <v>4</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H289" t="s">
+        <v>135</v>
+      </c>
+      <c r="I289" t="s">
+        <v>26</v>
+      </c>
+      <c r="J289" t="s">
+        <v>99</v>
+      </c>
+      <c r="K289">
+        <v>4</v>
+      </c>
+      <c r="L289">
+        <v>3</v>
+      </c>
+      <c r="M289">
+        <v>0</v>
+      </c>
+      <c r="N289">
+        <v>8</v>
+      </c>
+      <c r="O289">
+        <v>1008</v>
+      </c>
+      <c r="P289">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A290" s="2">
+        <v>5.7083333333333499</v>
+      </c>
+      <c r="B290" t="s">
+        <v>598</v>
+      </c>
+      <c r="C290" t="s">
+        <v>599</v>
+      </c>
+      <c r="D290">
+        <v>281</v>
+      </c>
+      <c r="E290">
+        <v>437.9</v>
+      </c>
+      <c r="F290" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="G290" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H290" t="s">
+        <v>135</v>
+      </c>
+      <c r="I290" t="s">
+        <v>26</v>
+      </c>
+      <c r="J290" t="s">
+        <v>99</v>
+      </c>
+      <c r="K290">
+        <v>4</v>
+      </c>
+      <c r="L290">
+        <v>3</v>
+      </c>
+      <c r="M290">
+        <v>0</v>
+      </c>
+      <c r="N290">
+        <v>8</v>
+      </c>
+      <c r="O290">
+        <v>1008</v>
+      </c>
+      <c r="P290">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A291" s="2">
+        <v>5.7500000000000204</v>
+      </c>
+      <c r="B291" t="s">
+        <v>600</v>
+      </c>
+      <c r="C291" t="s">
+        <v>531</v>
+      </c>
+      <c r="D291">
+        <v>270</v>
+      </c>
+      <c r="E291">
+        <v>440.4</v>
+      </c>
+      <c r="F291" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G291" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H291" t="s">
+        <v>135</v>
+      </c>
+      <c r="I291" t="s">
+        <v>26</v>
+      </c>
+      <c r="J291" t="s">
+        <v>99</v>
+      </c>
+      <c r="K291">
+        <v>4</v>
+      </c>
+      <c r="L291">
+        <v>3</v>
+      </c>
+      <c r="M291">
+        <v>0</v>
+      </c>
+      <c r="N291">
+        <v>8</v>
+      </c>
+      <c r="O291">
+        <v>1008</v>
+      </c>
+      <c r="P291">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A292" s="2">
+        <v>5.7916666666666901</v>
+      </c>
+      <c r="B292" t="s">
+        <v>601</v>
+      </c>
+      <c r="C292" t="s">
+        <v>602</v>
+      </c>
+      <c r="D292">
+        <v>280</v>
+      </c>
+      <c r="E292">
+        <v>447.1</v>
+      </c>
+      <c r="F292" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="G292" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H292" t="s">
+        <v>135</v>
+      </c>
+      <c r="I292" t="s">
+        <v>26</v>
+      </c>
+      <c r="J292" t="s">
+        <v>99</v>
+      </c>
+      <c r="K292">
+        <v>4</v>
+      </c>
+      <c r="L292">
+        <v>3</v>
+      </c>
+      <c r="M292">
+        <v>0</v>
+      </c>
+      <c r="N292">
+        <v>8</v>
+      </c>
+      <c r="O292">
+        <v>1008</v>
+      </c>
+      <c r="P292">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A293" s="2">
+        <v>5.8333333333333597</v>
+      </c>
+      <c r="B293" t="s">
+        <v>439</v>
+      </c>
+      <c r="C293" t="s">
+        <v>603</v>
+      </c>
+      <c r="D293">
+        <v>285</v>
+      </c>
+      <c r="E293">
+        <v>453.3</v>
+      </c>
+      <c r="F293" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G293" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H293" t="s">
+        <v>135</v>
+      </c>
+      <c r="I293" t="s">
+        <v>26</v>
+      </c>
+      <c r="J293" t="s">
+        <v>99</v>
+      </c>
+      <c r="K293">
+        <v>4</v>
+      </c>
+      <c r="L293">
+        <v>3</v>
+      </c>
+      <c r="M293">
+        <v>0</v>
+      </c>
+      <c r="N293">
+        <v>8</v>
+      </c>
+      <c r="O293">
+        <v>1008</v>
+      </c>
+      <c r="P293">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A294" s="2">
+        <v>5.8750000000000302</v>
+      </c>
+      <c r="B294" t="s">
+        <v>464</v>
+      </c>
+      <c r="C294" t="s">
+        <v>604</v>
+      </c>
+      <c r="D294">
+        <v>288</v>
+      </c>
+      <c r="E294">
+        <v>458.3</v>
+      </c>
+      <c r="F294" s="1">
+        <v>5</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H294" t="s">
+        <v>135</v>
+      </c>
+      <c r="I294" t="s">
+        <v>26</v>
+      </c>
+      <c r="J294" t="s">
+        <v>102</v>
+      </c>
+      <c r="K294">
+        <v>4</v>
+      </c>
+      <c r="L294">
+        <v>3</v>
+      </c>
+      <c r="M294">
+        <v>0</v>
+      </c>
+      <c r="N294">
+        <v>8</v>
+      </c>
+      <c r="O294">
+        <v>1009</v>
+      </c>
+      <c r="P294">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A295" s="2">
+        <v>5.9166666666666998</v>
+      </c>
+      <c r="B295" t="s">
+        <v>566</v>
+      </c>
+      <c r="C295" t="s">
+        <v>605</v>
+      </c>
+      <c r="D295">
+        <v>358</v>
+      </c>
+      <c r="E295">
+        <v>464.3</v>
+      </c>
+      <c r="F295" s="1">
+        <v>6</v>
+      </c>
+      <c r="G295" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H295" t="s">
+        <v>135</v>
+      </c>
+      <c r="I295" t="s">
+        <v>26</v>
+      </c>
+      <c r="J295" t="s">
+        <v>27</v>
+      </c>
+      <c r="K295">
+        <v>4</v>
+      </c>
+      <c r="L295">
+        <v>3</v>
+      </c>
+      <c r="M295">
+        <v>0</v>
+      </c>
+      <c r="N295">
+        <v>8</v>
+      </c>
+      <c r="O295">
+        <v>1010</v>
+      </c>
+      <c r="P295">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A296" s="2">
+        <v>5.9583333333333703</v>
+      </c>
+      <c r="B296" t="s">
+        <v>606</v>
+      </c>
+      <c r="C296" t="s">
+        <v>607</v>
+      </c>
+      <c r="D296">
+        <v>15</v>
+      </c>
+      <c r="E296">
+        <v>470.7</v>
+      </c>
+      <c r="F296" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G296" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H296" t="s">
+        <v>135</v>
+      </c>
+      <c r="I296" t="s">
+        <v>26</v>
+      </c>
+      <c r="J296" t="s">
+        <v>27</v>
+      </c>
+      <c r="K296">
+        <v>4</v>
+      </c>
+      <c r="L296">
+        <v>3</v>
+      </c>
+      <c r="M296">
+        <v>3</v>
+      </c>
+      <c r="N296">
+        <v>8</v>
+      </c>
+      <c r="O296">
+        <v>1010</v>
+      </c>
+      <c r="P296">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A297" s="2">
+        <v>6.00000000000004</v>
+      </c>
+      <c r="B297" t="s">
+        <v>608</v>
+      </c>
+      <c r="C297" t="s">
+        <v>605</v>
+      </c>
+      <c r="D297">
+        <v>266</v>
+      </c>
+      <c r="E297">
+        <v>476.7</v>
+      </c>
+      <c r="F297" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H297" t="s">
+        <v>135</v>
+      </c>
+      <c r="I297" t="s">
+        <v>26</v>
+      </c>
+      <c r="J297" t="s">
+        <v>102</v>
+      </c>
+      <c r="K297">
+        <v>4</v>
+      </c>
+      <c r="L297">
+        <v>3</v>
+      </c>
+      <c r="M297">
+        <v>3</v>
+      </c>
+      <c r="N297">
+        <v>8</v>
+      </c>
+      <c r="O297">
+        <v>1010</v>
+      </c>
+      <c r="P297">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A298" s="2">
+        <v>6.0416666666667096</v>
+      </c>
+      <c r="B298" t="s">
+        <v>609</v>
+      </c>
+      <c r="C298" t="s">
+        <v>610</v>
+      </c>
+      <c r="D298">
+        <v>250</v>
+      </c>
+      <c r="E298">
+        <v>481.8</v>
+      </c>
+      <c r="F298" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="G298" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H298" t="s">
+        <v>135</v>
+      </c>
+      <c r="I298" t="s">
+        <v>26</v>
+      </c>
+      <c r="J298" t="s">
+        <v>27</v>
+      </c>
+      <c r="K298">
+        <v>3</v>
+      </c>
+      <c r="L298">
+        <v>2</v>
+      </c>
+      <c r="M298">
+        <v>0</v>
+      </c>
+      <c r="N298">
+        <v>7</v>
+      </c>
+      <c r="O298">
+        <v>1011</v>
+      </c>
+      <c r="P298">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A299" s="2">
+        <v>6.0833333333333801</v>
+      </c>
+      <c r="B299" t="s">
+        <v>611</v>
+      </c>
+      <c r="C299" t="s">
+        <v>612</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299">
+        <v>486</v>
+      </c>
+      <c r="F299" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G299" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H299" t="s">
+        <v>135</v>
+      </c>
+      <c r="I299">
+        <v>800</v>
+      </c>
+      <c r="J299" t="s">
+        <v>27</v>
+      </c>
+      <c r="K299">
+        <v>3</v>
+      </c>
+      <c r="L299">
+        <v>1</v>
+      </c>
+      <c r="M299">
+        <v>0</v>
+      </c>
+      <c r="N299">
+        <v>7</v>
+      </c>
+      <c r="O299">
+        <v>1011</v>
+      </c>
+      <c r="P299">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A300" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="B300" t="s">
+        <v>613</v>
+      </c>
+      <c r="C300" t="s">
+        <v>614</v>
+      </c>
+      <c r="D300">
+        <v>330</v>
+      </c>
+      <c r="E300">
+        <v>493.6</v>
+      </c>
+      <c r="F300" s="1">
+        <v>4</v>
+      </c>
+      <c r="G300" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H300" t="s">
+        <v>26</v>
+      </c>
+      <c r="I300">
+        <v>1100</v>
+      </c>
+      <c r="J300" t="s">
+        <v>118</v>
+      </c>
+      <c r="K300">
+        <v>3</v>
+      </c>
+      <c r="L300">
+        <v>1</v>
+      </c>
+      <c r="M300">
+        <v>2</v>
+      </c>
+      <c r="N300">
+        <v>8</v>
+      </c>
+      <c r="O300">
+        <v>1015</v>
+      </c>
+      <c r="P300">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A301" s="2">
+        <v>6.2916666666666696</v>
+      </c>
+      <c r="B301" t="s">
+        <v>615</v>
+      </c>
+      <c r="C301" t="s">
+        <v>616</v>
+      </c>
+      <c r="D301">
+        <v>333</v>
+      </c>
+      <c r="E301">
+        <v>497.5</v>
+      </c>
+      <c r="F301" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="G301" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H301" t="s">
+        <v>135</v>
+      </c>
+      <c r="I301" t="s">
+        <v>26</v>
+      </c>
+      <c r="J301" t="s">
+        <v>118</v>
+      </c>
+      <c r="K301">
+        <v>3</v>
+      </c>
+      <c r="L301">
+        <v>1</v>
+      </c>
+      <c r="M301">
+        <v>2</v>
+      </c>
+      <c r="N301">
+        <v>8</v>
+      </c>
+      <c r="O301">
+        <v>1015</v>
+      </c>
+      <c r="P301">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A302" s="2">
+        <v>6.3333333333333401</v>
+      </c>
+      <c r="B302" t="s">
+        <v>617</v>
+      </c>
+      <c r="C302" t="s">
+        <v>618</v>
+      </c>
+      <c r="D302">
+        <v>330</v>
+      </c>
+      <c r="E302">
+        <v>503.6</v>
+      </c>
+      <c r="F302" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G302" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H302" t="s">
+        <v>135</v>
+      </c>
+      <c r="I302" t="s">
+        <v>26</v>
+      </c>
+      <c r="J302" t="s">
+        <v>136</v>
+      </c>
+      <c r="K302">
+        <v>3</v>
+      </c>
+      <c r="L302">
+        <v>2</v>
+      </c>
+      <c r="M302">
+        <v>1</v>
+      </c>
+      <c r="N302">
+        <v>8</v>
+      </c>
+      <c r="O302">
+        <v>1015</v>
+      </c>
+      <c r="P302">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A303" s="2">
+        <v>6.3750000000000098</v>
+      </c>
+      <c r="B303" t="s">
+        <v>619</v>
+      </c>
+      <c r="C303" t="s">
+        <v>620</v>
+      </c>
+      <c r="D303">
+        <v>330</v>
+      </c>
+      <c r="E303">
+        <v>510.2</v>
+      </c>
+      <c r="F303" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G303" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H303" t="s">
+        <v>135</v>
+      </c>
+      <c r="I303" t="s">
+        <v>26</v>
+      </c>
+      <c r="J303" t="s">
+        <v>136</v>
+      </c>
+      <c r="K303">
+        <v>3</v>
+      </c>
+      <c r="L303">
+        <v>2</v>
+      </c>
+      <c r="M303">
+        <v>2</v>
+      </c>
+      <c r="N303">
+        <v>8</v>
+      </c>
+      <c r="O303">
+        <v>1010</v>
+      </c>
+      <c r="P303">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A304" s="2">
+        <v>6.4166666666666803</v>
+      </c>
+      <c r="B304" t="s">
+        <v>621</v>
+      </c>
+      <c r="C304" t="s">
+        <v>622</v>
+      </c>
+      <c r="D304">
+        <v>333</v>
+      </c>
+      <c r="E304">
+        <v>517.29999999999995</v>
+      </c>
+      <c r="F304" s="1">
+        <v>6</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H304" t="s">
+        <v>135</v>
+      </c>
+      <c r="I304" t="s">
+        <v>26</v>
+      </c>
+      <c r="J304" t="s">
+        <v>136</v>
+      </c>
+      <c r="K304">
+        <v>3</v>
+      </c>
+      <c r="L304">
+        <v>2</v>
+      </c>
+      <c r="M304">
+        <v>0</v>
+      </c>
+      <c r="N304">
+        <v>8</v>
+      </c>
+      <c r="O304">
+        <v>1010</v>
+      </c>
+      <c r="P304">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A305" s="2">
+        <v>6.4583333333333499</v>
+      </c>
+      <c r="B305" t="s">
+        <v>623</v>
+      </c>
+      <c r="C305" t="s">
+        <v>624</v>
+      </c>
+      <c r="D305">
+        <v>325</v>
+      </c>
+      <c r="E305">
+        <v>522.9</v>
+      </c>
+      <c r="F305" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G305" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H305" t="s">
+        <v>135</v>
+      </c>
+      <c r="I305" t="s">
+        <v>26</v>
+      </c>
+      <c r="J305" t="s">
+        <v>299</v>
+      </c>
+      <c r="K305">
+        <v>3</v>
+      </c>
+      <c r="L305">
+        <v>2</v>
+      </c>
+      <c r="M305">
+        <v>0</v>
+      </c>
+      <c r="N305">
+        <v>8</v>
+      </c>
+      <c r="O305">
+        <v>1013</v>
+      </c>
+      <c r="P305">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A306" s="2">
+        <v>6.5000000000000204</v>
+      </c>
+      <c r="B306" t="s">
+        <v>625</v>
+      </c>
+      <c r="C306" t="s">
+        <v>626</v>
+      </c>
+      <c r="D306">
+        <v>310</v>
+      </c>
+      <c r="E306">
+        <v>528.29999999999995</v>
+      </c>
+      <c r="F306" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="G306" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H306" t="s">
+        <v>135</v>
+      </c>
+      <c r="I306" t="s">
+        <v>26</v>
+      </c>
+      <c r="J306" t="s">
+        <v>118</v>
+      </c>
+      <c r="K306">
+        <v>3</v>
+      </c>
+      <c r="L306">
+        <v>2</v>
+      </c>
+      <c r="M306">
+        <v>0</v>
+      </c>
+      <c r="N306">
+        <v>8</v>
+      </c>
+      <c r="O306">
+        <v>1013</v>
+      </c>
+      <c r="P306">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A307" s="2">
+        <v>6.5416666666666901</v>
+      </c>
+      <c r="B307" t="s">
+        <v>627</v>
+      </c>
+      <c r="C307" t="s">
+        <v>628</v>
+      </c>
+      <c r="D307">
+        <v>310</v>
+      </c>
+      <c r="E307">
+        <v>533.20000000000005</v>
+      </c>
+      <c r="F307" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G307" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H307" t="s">
+        <v>135</v>
+      </c>
+      <c r="I307" t="s">
+        <v>26</v>
+      </c>
+      <c r="J307" t="s">
+        <v>118</v>
+      </c>
+      <c r="K307">
+        <v>3</v>
+      </c>
+      <c r="L307">
+        <v>2</v>
+      </c>
+      <c r="M307">
+        <v>0</v>
+      </c>
+      <c r="N307">
+        <v>8</v>
+      </c>
+      <c r="O307">
+        <v>1013</v>
+      </c>
+      <c r="P307">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A308" s="2">
+        <v>6.5833333333333597</v>
+      </c>
+      <c r="B308" t="s">
+        <v>629</v>
+      </c>
+      <c r="C308" t="s">
+        <v>630</v>
+      </c>
+      <c r="D308">
+        <v>310</v>
+      </c>
+      <c r="E308">
+        <v>537.79999999999995</v>
+      </c>
+      <c r="F308" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G308" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H308" t="s">
+        <v>135</v>
+      </c>
+      <c r="I308" t="s">
+        <v>26</v>
+      </c>
+      <c r="J308" t="s">
+        <v>136</v>
+      </c>
+      <c r="K308">
+        <v>2</v>
+      </c>
+      <c r="L308">
+        <v>2</v>
+      </c>
+      <c r="M308">
+        <v>0</v>
+      </c>
+      <c r="N308">
+        <v>8</v>
+      </c>
+      <c r="O308">
+        <v>1013</v>
+      </c>
+      <c r="P308">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A309" s="2">
+        <v>6.6250000000000302</v>
+      </c>
+      <c r="B309" t="s">
+        <v>631</v>
+      </c>
+      <c r="C309" t="s">
+        <v>632</v>
+      </c>
+      <c r="D309">
+        <v>310</v>
+      </c>
+      <c r="E309">
+        <v>542.1</v>
+      </c>
+      <c r="F309" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H309" t="s">
+        <v>135</v>
+      </c>
+      <c r="I309" t="s">
+        <v>26</v>
+      </c>
+      <c r="J309" t="s">
+        <v>136</v>
+      </c>
+      <c r="K309">
+        <v>2</v>
+      </c>
+      <c r="L309">
+        <v>2</v>
+      </c>
+      <c r="M309">
+        <v>0</v>
+      </c>
+      <c r="N309">
+        <v>8</v>
+      </c>
+      <c r="O309">
+        <v>1012</v>
+      </c>
+      <c r="P309">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A310" s="2">
+        <v>6.6666666666666998</v>
+      </c>
+      <c r="B310" t="s">
+        <v>633</v>
+      </c>
+      <c r="C310" t="s">
+        <v>634</v>
+      </c>
+      <c r="D310">
+        <v>307</v>
+      </c>
+      <c r="E310">
+        <v>547.20000000000005</v>
+      </c>
+      <c r="F310" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G310" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H310" t="s">
+        <v>77</v>
+      </c>
+      <c r="I310" t="s">
+        <v>26</v>
+      </c>
+      <c r="J310" t="s">
+        <v>136</v>
+      </c>
+      <c r="K310">
+        <v>3</v>
+      </c>
+      <c r="L310">
+        <v>2</v>
+      </c>
+      <c r="M310">
+        <v>1</v>
+      </c>
+      <c r="N310">
+        <v>8</v>
+      </c>
+      <c r="O310">
+        <v>1012</v>
+      </c>
+      <c r="P310">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A311" s="2">
+        <v>6.7083333333333703</v>
+      </c>
+      <c r="B311" t="s">
+        <v>635</v>
+      </c>
+      <c r="C311" t="s">
+        <v>636</v>
+      </c>
+      <c r="D311">
+        <v>310</v>
+      </c>
+      <c r="E311">
+        <v>554.20000000000005</v>
+      </c>
+      <c r="F311" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G311" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H311" t="s">
+        <v>77</v>
+      </c>
+      <c r="I311" t="s">
+        <v>26</v>
+      </c>
+      <c r="J311" t="s">
+        <v>136</v>
+      </c>
+      <c r="K311">
+        <v>5</v>
+      </c>
+      <c r="L311">
+        <v>2</v>
+      </c>
+      <c r="M311">
+        <v>2</v>
+      </c>
+      <c r="N311">
+        <v>8</v>
+      </c>
+      <c r="O311">
+        <v>1011</v>
+      </c>
+      <c r="P311">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A312" s="2">
+        <v>6.75000000000004</v>
+      </c>
+      <c r="B312" t="s">
+        <v>637</v>
+      </c>
+      <c r="C312" t="s">
+        <v>638</v>
+      </c>
+      <c r="D312">
+        <v>5</v>
+      </c>
+      <c r="E312">
+        <v>562.70000000000005</v>
+      </c>
+      <c r="F312" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G312" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H312" t="s">
+        <v>77</v>
+      </c>
+      <c r="I312" t="s">
+        <v>26</v>
+      </c>
+      <c r="J312" t="s">
+        <v>136</v>
+      </c>
+      <c r="K312">
+        <v>5</v>
+      </c>
+      <c r="L312">
+        <v>2</v>
+      </c>
+      <c r="M312">
+        <v>2</v>
+      </c>
+      <c r="N312">
+        <v>8</v>
+      </c>
+      <c r="O312">
+        <v>1011</v>
+      </c>
+      <c r="P312">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A313" s="2">
+        <v>6.958333333333333</v>
+      </c>
+      <c r="B313" t="s">
+        <v>639</v>
+      </c>
+      <c r="C313" t="s">
+        <v>640</v>
+      </c>
+      <c r="D313">
+        <v>170</v>
+      </c>
+      <c r="E313">
+        <v>598.79999999999995</v>
+      </c>
+      <c r="F313" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G313" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H313" t="s">
+        <v>25</v>
+      </c>
+      <c r="I313" t="s">
+        <v>26</v>
+      </c>
+      <c r="J313" t="s">
+        <v>153</v>
+      </c>
+      <c r="K313">
+        <v>5</v>
+      </c>
+      <c r="L313">
+        <v>4</v>
+      </c>
+      <c r="M313">
+        <v>1</v>
+      </c>
+      <c r="N313">
+        <v>8</v>
+      </c>
+      <c r="O313">
+        <v>1011</v>
+      </c>
+      <c r="P313">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A314" s="2">
+        <v>7</v>
+      </c>
+      <c r="B314" t="s">
+        <v>641</v>
+      </c>
+      <c r="C314" t="s">
+        <v>636</v>
+      </c>
+      <c r="D314">
+        <v>180</v>
+      </c>
+      <c r="E314">
+        <v>608.29999999999995</v>
+      </c>
+      <c r="F314" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="G314" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H314" t="s">
+        <v>25</v>
+      </c>
+      <c r="I314" t="s">
+        <v>26</v>
+      </c>
+      <c r="J314" t="s">
+        <v>49</v>
+      </c>
+      <c r="K314">
+        <v>5</v>
+      </c>
+      <c r="L314">
+        <v>3</v>
+      </c>
+      <c r="M314">
+        <v>0</v>
+      </c>
+      <c r="N314">
+        <v>7</v>
+      </c>
+      <c r="O314">
+        <v>1009</v>
+      </c>
+      <c r="P314">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A315" s="2">
+        <v>7.0416666666666696</v>
+      </c>
+      <c r="B315" t="s">
+        <v>642</v>
+      </c>
+      <c r="C315" t="s">
+        <v>643</v>
+      </c>
+      <c r="D315">
+        <v>134</v>
+      </c>
+      <c r="E315">
+        <v>615.5</v>
+      </c>
+      <c r="F315" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G315" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H315" t="s">
+        <v>25</v>
+      </c>
+      <c r="I315" t="s">
+        <v>26</v>
+      </c>
+      <c r="J315" t="s">
+        <v>49</v>
+      </c>
+      <c r="K315">
+        <v>6</v>
+      </c>
+      <c r="L315">
+        <v>4</v>
+      </c>
+      <c r="M315">
+        <v>3</v>
+      </c>
+      <c r="N315">
+        <v>8</v>
+      </c>
+      <c r="O315">
+        <v>1010</v>
+      </c>
+      <c r="P315">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A316" s="2">
+        <v>7.0833333333333401</v>
+      </c>
+      <c r="B316" t="s">
+        <v>644</v>
+      </c>
+      <c r="C316" t="s">
+        <v>645</v>
+      </c>
+      <c r="D316">
+        <v>130</v>
+      </c>
+      <c r="E316">
+        <v>622.79999999999995</v>
+      </c>
+      <c r="F316" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G316" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H316" t="s">
+        <v>25</v>
+      </c>
+      <c r="I316" t="s">
+        <v>26</v>
+      </c>
+      <c r="J316" t="s">
+        <v>49</v>
+      </c>
+      <c r="K316">
+        <v>7</v>
+      </c>
+      <c r="L316">
+        <v>4</v>
+      </c>
+      <c r="M316">
+        <v>3</v>
+      </c>
+      <c r="N316">
+        <v>8</v>
+      </c>
+      <c r="O316">
+        <v>1010</v>
+      </c>
+      <c r="P316">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A317" s="2">
+        <v>7.1250000000000098</v>
+      </c>
+      <c r="B317" t="s">
+        <v>646</v>
+      </c>
+      <c r="C317" t="s">
+        <v>647</v>
+      </c>
+      <c r="D317">
+        <v>123</v>
+      </c>
+      <c r="E317">
+        <v>630.70000000000005</v>
+      </c>
+      <c r="F317" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G317" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H317" t="s">
+        <v>25</v>
+      </c>
+      <c r="I317" t="s">
+        <v>26</v>
+      </c>
+      <c r="J317" t="s">
+        <v>49</v>
+      </c>
+      <c r="K317">
+        <v>5</v>
+      </c>
+      <c r="L317">
+        <v>4</v>
+      </c>
+      <c r="M317">
+        <v>3</v>
+      </c>
+      <c r="N317">
+        <v>8</v>
+      </c>
+      <c r="O317">
+        <v>1010</v>
+      </c>
+      <c r="P317">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A318" s="2">
+        <v>7.1666666666666803</v>
+      </c>
+      <c r="B318" t="s">
+        <v>648</v>
+      </c>
+      <c r="C318" t="s">
+        <v>649</v>
+      </c>
+      <c r="D318">
+        <v>123</v>
+      </c>
+      <c r="E318">
+        <v>637.20000000000005</v>
+      </c>
+      <c r="F318" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G318" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H318" t="s">
+        <v>25</v>
+      </c>
+      <c r="I318" t="s">
+        <v>26</v>
+      </c>
+      <c r="J318" t="s">
+        <v>49</v>
+      </c>
+      <c r="K318">
+        <v>5</v>
+      </c>
+      <c r="L318">
+        <v>4</v>
+      </c>
+      <c r="M318">
+        <v>3</v>
+      </c>
+      <c r="N318">
+        <v>8</v>
+      </c>
+      <c r="O318">
+        <v>1010</v>
+      </c>
+      <c r="P318">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A319" s="2">
+        <v>7.2083333333333499</v>
+      </c>
+      <c r="B319" t="s">
+        <v>650</v>
+      </c>
+      <c r="C319" t="s">
+        <v>651</v>
+      </c>
+      <c r="D319">
+        <v>145</v>
+      </c>
+      <c r="E319">
+        <v>642.79999999999995</v>
+      </c>
+      <c r="F319" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G319" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H319" t="s">
+        <v>25</v>
+      </c>
+      <c r="I319" t="s">
+        <v>26</v>
+      </c>
+      <c r="J319" t="s">
+        <v>49</v>
+      </c>
+      <c r="K319">
+        <v>5</v>
+      </c>
+      <c r="L319">
+        <v>4</v>
+      </c>
+      <c r="M319">
+        <v>2</v>
+      </c>
+      <c r="N319">
+        <v>8</v>
+      </c>
+      <c r="O319">
+        <v>1010</v>
+      </c>
+      <c r="P319">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A320" s="2">
+        <v>7.2500000000000204</v>
+      </c>
+      <c r="B320" t="s">
+        <v>652</v>
+      </c>
+      <c r="C320" t="s">
+        <v>653</v>
+      </c>
+      <c r="D320">
+        <v>146</v>
+      </c>
+      <c r="E320">
+        <v>649.6</v>
+      </c>
+      <c r="F320" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G320" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H320" t="s">
+        <v>25</v>
+      </c>
+      <c r="I320" t="s">
+        <v>26</v>
+      </c>
+      <c r="J320" t="s">
+        <v>49</v>
+      </c>
+      <c r="K320">
+        <v>5</v>
+      </c>
+      <c r="L320">
+        <v>4</v>
+      </c>
+      <c r="M320">
+        <v>2</v>
+      </c>
+      <c r="N320">
+        <v>8</v>
+      </c>
+      <c r="O320">
+        <v>1010</v>
+      </c>
+      <c r="P320">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A321" s="2">
+        <v>7.2916666666666901</v>
+      </c>
+      <c r="B321" t="s">
+        <v>654</v>
+      </c>
+      <c r="C321" t="s">
+        <v>655</v>
+      </c>
+      <c r="D321">
+        <v>147</v>
+      </c>
+      <c r="E321">
+        <v>655</v>
+      </c>
+      <c r="F321" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="G321" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H321" t="s">
+        <v>25</v>
+      </c>
+      <c r="I321" t="s">
+        <v>26</v>
+      </c>
+      <c r="J321" t="s">
+        <v>49</v>
+      </c>
+      <c r="K321">
+        <v>4</v>
+      </c>
+      <c r="L321">
+        <v>4</v>
+      </c>
+      <c r="M321">
+        <v>2</v>
+      </c>
+      <c r="N321">
+        <v>8</v>
+      </c>
+      <c r="O321">
+        <v>1010</v>
+      </c>
+      <c r="P321">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A322" s="2">
+        <v>7.3333333333333597</v>
+      </c>
+      <c r="B322" t="s">
+        <v>656</v>
+      </c>
+      <c r="C322" t="s">
+        <v>612</v>
+      </c>
+      <c r="D322">
+        <v>150</v>
+      </c>
+      <c r="E322">
+        <v>661.9</v>
+      </c>
+      <c r="F322" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="G322" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H322" t="s">
+        <v>25</v>
+      </c>
+      <c r="I322" t="s">
+        <v>26</v>
+      </c>
+      <c r="J322" t="s">
+        <v>162</v>
+      </c>
+      <c r="K322">
+        <v>5</v>
+      </c>
+      <c r="L322">
+        <v>3</v>
+      </c>
+      <c r="M322">
+        <v>0</v>
+      </c>
+      <c r="N322">
+        <v>8</v>
+      </c>
+      <c r="O322">
+        <v>1010</v>
+      </c>
+      <c r="P322">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A323" s="2">
+        <v>7.3750000000000302</v>
+      </c>
+      <c r="B323" t="s">
+        <v>657</v>
+      </c>
+      <c r="C323" t="s">
+        <v>658</v>
+      </c>
+      <c r="D323">
+        <v>150</v>
+      </c>
+      <c r="E323">
+        <v>670</v>
+      </c>
+      <c r="F323" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G323" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H323" t="s">
+        <v>25</v>
+      </c>
+      <c r="I323" t="s">
+        <v>26</v>
+      </c>
+      <c r="J323" t="s">
+        <v>162</v>
+      </c>
+      <c r="K323">
+        <v>5</v>
+      </c>
+      <c r="L323">
+        <v>3</v>
+      </c>
+      <c r="M323">
+        <v>0</v>
+      </c>
+      <c r="N323">
+        <v>8</v>
+      </c>
+      <c r="O323">
+        <v>1010</v>
+      </c>
+      <c r="P323">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A324" s="2">
+        <v>7.4166666666666998</v>
+      </c>
+      <c r="B324" t="s">
+        <v>659</v>
+      </c>
+      <c r="C324" t="s">
+        <v>605</v>
+      </c>
+      <c r="D324">
+        <v>155</v>
+      </c>
+      <c r="E324">
+        <v>677.3</v>
+      </c>
+      <c r="F324" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G324" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H324" t="s">
+        <v>25</v>
+      </c>
+      <c r="I324" t="s">
+        <v>26</v>
+      </c>
+      <c r="J324" t="s">
+        <v>162</v>
+      </c>
+      <c r="K324">
+        <v>5</v>
+      </c>
+      <c r="L324">
+        <v>2</v>
+      </c>
+      <c r="M324">
+        <v>0</v>
+      </c>
+      <c r="N324">
+        <v>8</v>
+      </c>
+      <c r="O324">
+        <v>1009</v>
+      </c>
+      <c r="P324">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A325" s="2">
+        <v>7.4583333333333703</v>
+      </c>
+      <c r="B325" t="s">
+        <v>660</v>
+      </c>
+      <c r="C325" t="s">
+        <v>661</v>
+      </c>
+      <c r="D325">
+        <v>155</v>
+      </c>
+      <c r="E325">
+        <v>685.9</v>
+      </c>
+      <c r="F325" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="G325" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H325" t="s">
+        <v>25</v>
+      </c>
+      <c r="I325" t="s">
+        <v>26</v>
+      </c>
+      <c r="J325" t="s">
+        <v>162</v>
+      </c>
+      <c r="K325">
+        <v>5</v>
+      </c>
+      <c r="L325">
+        <v>3</v>
+      </c>
+      <c r="M325">
+        <v>0</v>
+      </c>
+      <c r="N325">
+        <v>8</v>
+      </c>
+      <c r="O325">
+        <v>1009</v>
+      </c>
+      <c r="P325">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A326" s="2">
+        <v>7.50000000000004</v>
+      </c>
+      <c r="B326" t="s">
+        <v>662</v>
+      </c>
+      <c r="C326" t="s">
+        <v>664</v>
+      </c>
+      <c r="D326">
+        <v>155</v>
+      </c>
+      <c r="E326">
+        <v>693.2</v>
+      </c>
+      <c r="F326" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G326" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H326" t="s">
+        <v>25</v>
+      </c>
+      <c r="I326" t="s">
+        <v>26</v>
+      </c>
+      <c r="J326" t="s">
+        <v>162</v>
+      </c>
+      <c r="K326">
+        <v>5</v>
+      </c>
+      <c r="L326">
+        <v>3</v>
+      </c>
+      <c r="M326">
+        <v>0</v>
+      </c>
+      <c r="N326">
+        <v>8</v>
+      </c>
+      <c r="O326">
+        <v>1009</v>
+      </c>
+      <c r="P326">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A327" s="2">
+        <v>7.5416666666667096</v>
+      </c>
+      <c r="B327" t="s">
+        <v>663</v>
+      </c>
+      <c r="C327" t="s">
+        <v>665</v>
+      </c>
+      <c r="D327">
+        <v>150</v>
+      </c>
+      <c r="E327">
+        <v>700</v>
+      </c>
+      <c r="F327" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="G327" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H327" t="s">
+        <v>25</v>
+      </c>
+      <c r="I327" t="s">
+        <v>26</v>
+      </c>
+      <c r="J327" t="s">
+        <v>205</v>
+      </c>
+      <c r="K327">
+        <v>4</v>
+      </c>
+      <c r="L327">
+        <v>2</v>
+      </c>
+      <c r="M327">
+        <v>0</v>
+      </c>
+      <c r="N327">
+        <v>8</v>
+      </c>
+      <c r="O327">
+        <v>1009</v>
+      </c>
+      <c r="P327">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A328" s="2">
+        <v>7.5833333333333801</v>
+      </c>
+      <c r="B328" t="s">
+        <v>666</v>
+      </c>
+      <c r="C328" t="s">
+        <v>667</v>
+      </c>
+      <c r="D328">
+        <v>150</v>
+      </c>
+      <c r="E328">
+        <v>706.1</v>
+      </c>
+      <c r="F328" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="G328" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H328" t="s">
+        <v>25</v>
+      </c>
+      <c r="I328" t="s">
+        <v>26</v>
+      </c>
+      <c r="J328" t="s">
+        <v>205</v>
+      </c>
+      <c r="K328">
+        <v>5</v>
+      </c>
+      <c r="L328">
+        <v>2</v>
+      </c>
+      <c r="M328">
+        <v>0</v>
+      </c>
+      <c r="N328">
+        <v>8</v>
+      </c>
+      <c r="O328">
+        <v>1009</v>
+      </c>
+      <c r="P328">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Dziennik2024.xlsx
+++ b/Dziennik2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szybk\OneDrive\Pulpit\Studia\inzynierka\Inzynierka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6689546E-6037-4469-BF08-6CB0B4BB2F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4612ED6-87E3-4D9C-AAD5-F32AB3F00EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BF3D5F66-ACDF-49A3-8594-396AB682FC7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2597" uniqueCount="861">
   <si>
     <t>Godzina</t>
   </si>
@@ -2040,6 +2040,585 @@
   </si>
   <si>
     <t>14*11,8E</t>
+  </si>
+  <si>
+    <t>54*10,8N</t>
+  </si>
+  <si>
+    <t>14*03,0E</t>
+  </si>
+  <si>
+    <t>14*00,6E</t>
+  </si>
+  <si>
+    <t>54*19,7N</t>
+  </si>
+  <si>
+    <t>13*52,4E</t>
+  </si>
+  <si>
+    <t>54*22,3N</t>
+  </si>
+  <si>
+    <t>13*48,2E</t>
+  </si>
+  <si>
+    <t>54*25,8N</t>
+  </si>
+  <si>
+    <t>13*43,8E</t>
+  </si>
+  <si>
+    <t>13*42,9E</t>
+  </si>
+  <si>
+    <t>54*38,1N</t>
+  </si>
+  <si>
+    <t>13*40,1E</t>
+  </si>
+  <si>
+    <t>54*42,3N</t>
+  </si>
+  <si>
+    <t>13*37,4E</t>
+  </si>
+  <si>
+    <t>54*44,0N</t>
+  </si>
+  <si>
+    <t>13*36,0E</t>
+  </si>
+  <si>
+    <t>54*45,0N</t>
+  </si>
+  <si>
+    <t>13*34,7E</t>
+  </si>
+  <si>
+    <t>54*48,0N</t>
+  </si>
+  <si>
+    <t>13*29,7E</t>
+  </si>
+  <si>
+    <t>54*54,0N</t>
+  </si>
+  <si>
+    <t>13*16,3E</t>
+  </si>
+  <si>
+    <t>13*07,2E</t>
+  </si>
+  <si>
+    <t>55*08,8N</t>
+  </si>
+  <si>
+    <t>12*57,6E</t>
+  </si>
+  <si>
+    <t>55*13,6N</t>
+  </si>
+  <si>
+    <t>12*47,4E</t>
+  </si>
+  <si>
+    <t>55*18,8N</t>
+  </si>
+  <si>
+    <t>12*40,4E</t>
+  </si>
+  <si>
+    <t>55*25,2N</t>
+  </si>
+  <si>
+    <t>12*42,6E</t>
+  </si>
+  <si>
+    <t>55*31,1N</t>
+  </si>
+  <si>
+    <t>12*43,1E</t>
+  </si>
+  <si>
+    <t>55*37,9N</t>
+  </si>
+  <si>
+    <t>12*42,0E</t>
+  </si>
+  <si>
+    <t>55*45,2N</t>
+  </si>
+  <si>
+    <t>12*41,2E</t>
+  </si>
+  <si>
+    <t>55*50,6N</t>
+  </si>
+  <si>
+    <t>12*39,2E</t>
+  </si>
+  <si>
+    <t>55*57,2N</t>
+  </si>
+  <si>
+    <t>12*37,1E</t>
+  </si>
+  <si>
+    <t>12*36,8E</t>
+  </si>
+  <si>
+    <t>56*10,6N</t>
+  </si>
+  <si>
+    <t>12*29,5E</t>
+  </si>
+  <si>
+    <t>56*16,8N</t>
+  </si>
+  <si>
+    <t>56*21,0N</t>
+  </si>
+  <si>
+    <t>12*19,7E</t>
+  </si>
+  <si>
+    <t>12*23,7E</t>
+  </si>
+  <si>
+    <t>SWW</t>
+  </si>
+  <si>
+    <t>56*26,6N</t>
+  </si>
+  <si>
+    <t>12*16,0E</t>
+  </si>
+  <si>
+    <t>56*30,9N</t>
+  </si>
+  <si>
+    <t>12*11,1E</t>
+  </si>
+  <si>
+    <t>56*37,7N</t>
+  </si>
+  <si>
+    <t>12*05,5E</t>
+  </si>
+  <si>
+    <t>12*03,7E</t>
+  </si>
+  <si>
+    <t>56*51,0N</t>
+  </si>
+  <si>
+    <t>56*57,5N</t>
+  </si>
+  <si>
+    <t>11*53,6E</t>
+  </si>
+  <si>
+    <t>11*58,0E</t>
+  </si>
+  <si>
+    <t>57*03,5N</t>
+  </si>
+  <si>
+    <t>11*44,9E</t>
+  </si>
+  <si>
+    <t>NWW</t>
+  </si>
+  <si>
+    <t>57*10,1N</t>
+  </si>
+  <si>
+    <t>11*38,8E</t>
+  </si>
+  <si>
+    <t>57*17,1N</t>
+  </si>
+  <si>
+    <t>11*32,6E</t>
+  </si>
+  <si>
+    <t>57*24,6N</t>
+  </si>
+  <si>
+    <t>11*28,1E</t>
+  </si>
+  <si>
+    <t>11*21,9E</t>
+  </si>
+  <si>
+    <t>57*31,4N</t>
+  </si>
+  <si>
+    <t>11*24,9E</t>
+  </si>
+  <si>
+    <t>57*37,6N</t>
+  </si>
+  <si>
+    <t>57*43,4N</t>
+  </si>
+  <si>
+    <t>11*18,5E</t>
+  </si>
+  <si>
+    <t>57*48,7N</t>
+  </si>
+  <si>
+    <t>11*14,2E</t>
+  </si>
+  <si>
+    <t>57*54,6N</t>
+  </si>
+  <si>
+    <t>11*11,0E</t>
+  </si>
+  <si>
+    <t>58*00,1N</t>
+  </si>
+  <si>
+    <t>11*10,3E</t>
+  </si>
+  <si>
+    <t>58*06,0N</t>
+  </si>
+  <si>
+    <t>11*05,0E</t>
+  </si>
+  <si>
+    <t>58*11,7N</t>
+  </si>
+  <si>
+    <t>11*03,4E</t>
+  </si>
+  <si>
+    <t>58*17,0N</t>
+  </si>
+  <si>
+    <t>11*00,7E</t>
+  </si>
+  <si>
+    <t>58*22,7N</t>
+  </si>
+  <si>
+    <t>10*56,0E</t>
+  </si>
+  <si>
+    <t>58*30,6N</t>
+  </si>
+  <si>
+    <t>10*52,6E</t>
+  </si>
+  <si>
+    <t>58*38,6N</t>
+  </si>
+  <si>
+    <t>10*50,1E</t>
+  </si>
+  <si>
+    <t>58*46,5N</t>
+  </si>
+  <si>
+    <t>10*46,9E</t>
+  </si>
+  <si>
+    <t>58*54,1N</t>
+  </si>
+  <si>
+    <t>10*45,2E</t>
+  </si>
+  <si>
+    <t>59*01,6N</t>
+  </si>
+  <si>
+    <t>10*42,9E</t>
+  </si>
+  <si>
+    <t>59*08,8N</t>
+  </si>
+  <si>
+    <t>10*40,4E</t>
+  </si>
+  <si>
+    <t>59*15,4N</t>
+  </si>
+  <si>
+    <t>10*38,6E</t>
+  </si>
+  <si>
+    <t>59*21,9N</t>
+  </si>
+  <si>
+    <t>10*36,1E</t>
+  </si>
+  <si>
+    <t>59*27,6N</t>
+  </si>
+  <si>
+    <t>10*34,7E</t>
+  </si>
+  <si>
+    <t>59*32,3N</t>
+  </si>
+  <si>
+    <t>10*38,0E</t>
+  </si>
+  <si>
+    <t>10*37,0E</t>
+  </si>
+  <si>
+    <t>59*52,8N</t>
+  </si>
+  <si>
+    <t>10*39,9E</t>
+  </si>
+  <si>
+    <t>10*33,6E</t>
+  </si>
+  <si>
+    <t>59*16,5N</t>
+  </si>
+  <si>
+    <t>59*09,7N</t>
+  </si>
+  <si>
+    <t>10*39,8E</t>
+  </si>
+  <si>
+    <t>59*04,3N</t>
+  </si>
+  <si>
+    <t>10*45,4E</t>
+  </si>
+  <si>
+    <t>59*00,3N</t>
+  </si>
+  <si>
+    <t>10*56,6E</t>
+  </si>
+  <si>
+    <t>57*51,3N</t>
+  </si>
+  <si>
+    <t>11*28,6E</t>
+  </si>
+  <si>
+    <t>57*46,0N</t>
+  </si>
+  <si>
+    <t>57*41,1N</t>
+  </si>
+  <si>
+    <t>11*27,9E</t>
+  </si>
+  <si>
+    <t>57*36,4N</t>
+  </si>
+  <si>
+    <t>11*28,5E</t>
+  </si>
+  <si>
+    <t>57*30,3N</t>
+  </si>
+  <si>
+    <t>11*27,8E</t>
+  </si>
+  <si>
+    <t>57*27,7N</t>
+  </si>
+  <si>
+    <t>11*26,7E</t>
+  </si>
+  <si>
+    <t>57*24,4N</t>
+  </si>
+  <si>
+    <t>11*27,1E</t>
+  </si>
+  <si>
+    <t>57*20,5N</t>
+  </si>
+  <si>
+    <t>11*33,1E</t>
+  </si>
+  <si>
+    <t>57*15,3N</t>
+  </si>
+  <si>
+    <t>11*37,0E</t>
+  </si>
+  <si>
+    <t>57*09,6N</t>
+  </si>
+  <si>
+    <t>11*39,4E</t>
+  </si>
+  <si>
+    <t>57*05,2N</t>
+  </si>
+  <si>
+    <t>11*43,4E</t>
+  </si>
+  <si>
+    <t>57*02,0N</t>
+  </si>
+  <si>
+    <t>11*50,2E</t>
+  </si>
+  <si>
+    <t>11*58,1E</t>
+  </si>
+  <si>
+    <t>56*58,5N</t>
+  </si>
+  <si>
+    <t>56*53,8N</t>
+  </si>
+  <si>
+    <t>11*59,6E</t>
+  </si>
+  <si>
+    <t>56*50,1N</t>
+  </si>
+  <si>
+    <t>11*59,2E</t>
+  </si>
+  <si>
+    <t>56*45,8N</t>
+  </si>
+  <si>
+    <t>11*58,5E</t>
+  </si>
+  <si>
+    <t>56*40,6N</t>
+  </si>
+  <si>
+    <t>12*01,9E</t>
+  </si>
+  <si>
+    <t>12*14,0E</t>
+  </si>
+  <si>
+    <t>56*36,0N</t>
+  </si>
+  <si>
+    <t>12*07,8E</t>
+  </si>
+  <si>
+    <t>55*33,0N</t>
+  </si>
+  <si>
+    <t>12*43,2E</t>
+  </si>
+  <si>
+    <t>55*27,6N</t>
+  </si>
+  <si>
+    <t>12*43,7E</t>
+  </si>
+  <si>
+    <t>12*44,5E</t>
+  </si>
+  <si>
+    <t>55*16,2N</t>
+  </si>
+  <si>
+    <t>12*49,6E</t>
+  </si>
+  <si>
+    <t>55*12,0N</t>
+  </si>
+  <si>
+    <t>12*55,9E</t>
+  </si>
+  <si>
+    <t>13*01,2E</t>
+  </si>
+  <si>
+    <t>13*06,3E</t>
+  </si>
+  <si>
+    <t>13*12,6E</t>
+  </si>
+  <si>
+    <t>54*58,0N</t>
+  </si>
+  <si>
+    <t>13*18,1E</t>
+  </si>
+  <si>
+    <t>13*22,4E</t>
+  </si>
+  <si>
+    <t>54*49,5N</t>
+  </si>
+  <si>
+    <t>13*26,0E</t>
+  </si>
+  <si>
+    <t>54*47,8N</t>
+  </si>
+  <si>
+    <t>13*34,4E</t>
+  </si>
+  <si>
+    <t>54*42,6N</t>
+  </si>
+  <si>
+    <t>13*32,7E</t>
+  </si>
+  <si>
+    <t>54*38,6N</t>
+  </si>
+  <si>
+    <t>13*36,4E</t>
+  </si>
+  <si>
+    <t>54*40,8N</t>
+  </si>
+  <si>
+    <t>13*41,8E</t>
+  </si>
+  <si>
+    <t>54*37,0N</t>
+  </si>
+  <si>
+    <t>13*46,4E</t>
+  </si>
+  <si>
+    <t>54*31,4N</t>
+  </si>
+  <si>
+    <t>13*51,1E</t>
+  </si>
+  <si>
+    <t>54*25,6N</t>
+  </si>
+  <si>
+    <t>13*56,2E</t>
+  </si>
+  <si>
+    <t>54*20,3N</t>
+  </si>
+  <si>
+    <t>14*01,6E</t>
+  </si>
+  <si>
+    <t>14*05,8E</t>
+  </si>
+  <si>
+    <t>54*05,2N</t>
+  </si>
+  <si>
+    <t>14*10,8E</t>
+  </si>
+  <si>
+    <t>14*14,9E</t>
   </si>
 </sst>
 </file>
@@ -2430,7 +3009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2DB018-EC3F-4C8E-A36B-34F72611C81F}">
-  <dimension ref="A1:P328"/>
+  <dimension ref="A1:P432"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -18826,6 +19405,5206 @@
         <v>17</v>
       </c>
     </row>
+    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A329" s="2">
+        <v>7.041666666666667</v>
+      </c>
+      <c r="B329" t="s">
+        <v>668</v>
+      </c>
+      <c r="C329" t="s">
+        <v>669</v>
+      </c>
+      <c r="D329">
+        <v>335</v>
+      </c>
+      <c r="E329">
+        <v>55.8</v>
+      </c>
+      <c r="F329" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G329" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H329" t="s">
+        <v>135</v>
+      </c>
+      <c r="I329" t="s">
+        <v>26</v>
+      </c>
+      <c r="J329" t="s">
+        <v>299</v>
+      </c>
+      <c r="K329">
+        <v>2</v>
+      </c>
+      <c r="L329">
+        <v>3</v>
+      </c>
+      <c r="M329">
+        <v>0</v>
+      </c>
+      <c r="N329">
+        <v>8</v>
+      </c>
+      <c r="O329">
+        <v>1009</v>
+      </c>
+      <c r="P329">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A330" s="2">
+        <v>7.0833333333333304</v>
+      </c>
+      <c r="B330" t="s">
+        <v>594</v>
+      </c>
+      <c r="C330" t="s">
+        <v>670</v>
+      </c>
+      <c r="D330">
+        <v>335</v>
+      </c>
+      <c r="E330">
+        <v>60.7</v>
+      </c>
+      <c r="F330" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G330" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H330" t="s">
+        <v>135</v>
+      </c>
+      <c r="I330" t="s">
+        <v>26</v>
+      </c>
+      <c r="J330" t="s">
+        <v>118</v>
+      </c>
+      <c r="K330">
+        <v>3</v>
+      </c>
+      <c r="L330">
+        <v>3</v>
+      </c>
+      <c r="M330">
+        <v>0</v>
+      </c>
+      <c r="N330">
+        <v>8</v>
+      </c>
+      <c r="O330">
+        <v>1002</v>
+      </c>
+      <c r="P330">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A331" s="2">
+        <v>7.125</v>
+      </c>
+      <c r="B331" t="s">
+        <v>671</v>
+      </c>
+      <c r="C331" t="s">
+        <v>672</v>
+      </c>
+      <c r="D331">
+        <v>340</v>
+      </c>
+      <c r="E331">
+        <v>67.3</v>
+      </c>
+      <c r="F331" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G331" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H331" t="s">
+        <v>135</v>
+      </c>
+      <c r="I331" t="s">
+        <v>26</v>
+      </c>
+      <c r="J331" t="s">
+        <v>241</v>
+      </c>
+      <c r="K331">
+        <v>6</v>
+      </c>
+      <c r="L331">
+        <v>3</v>
+      </c>
+      <c r="M331">
+        <v>1</v>
+      </c>
+      <c r="N331">
+        <v>8</v>
+      </c>
+      <c r="O331">
+        <v>1003</v>
+      </c>
+      <c r="P331">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A332" s="2">
+        <v>7.1666666666666696</v>
+      </c>
+      <c r="B332" t="s">
+        <v>673</v>
+      </c>
+      <c r="C332" t="s">
+        <v>674</v>
+      </c>
+      <c r="D332">
+        <v>230</v>
+      </c>
+      <c r="E332">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="F332" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="G332" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H332" t="s">
+        <v>135</v>
+      </c>
+      <c r="I332" t="s">
+        <v>26</v>
+      </c>
+      <c r="J332" t="s">
+        <v>586</v>
+      </c>
+      <c r="K332">
+        <v>4</v>
+      </c>
+      <c r="L332">
+        <v>3</v>
+      </c>
+      <c r="M332">
+        <v>2</v>
+      </c>
+      <c r="N332">
+        <v>8</v>
+      </c>
+      <c r="O332">
+        <v>1004</v>
+      </c>
+      <c r="P332">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A333" s="2">
+        <v>7.2083333333333401</v>
+      </c>
+      <c r="B333" t="s">
+        <v>675</v>
+      </c>
+      <c r="C333" t="s">
+        <v>676</v>
+      </c>
+      <c r="D333">
+        <v>322</v>
+      </c>
+      <c r="E333">
+        <v>77</v>
+      </c>
+      <c r="F333" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G333" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H333" t="s">
+        <v>135</v>
+      </c>
+      <c r="I333">
+        <v>1300</v>
+      </c>
+      <c r="J333" t="s">
+        <v>49</v>
+      </c>
+      <c r="K333">
+        <v>3</v>
+      </c>
+      <c r="L333">
+        <v>3</v>
+      </c>
+      <c r="M333">
+        <v>0</v>
+      </c>
+      <c r="N333">
+        <v>8</v>
+      </c>
+      <c r="O333">
+        <v>1005</v>
+      </c>
+      <c r="P333">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A334" s="2">
+        <v>7.916666666666667</v>
+      </c>
+      <c r="B334" t="s">
+        <v>435</v>
+      </c>
+      <c r="C334" t="s">
+        <v>677</v>
+      </c>
+      <c r="D334">
+        <v>350</v>
+      </c>
+      <c r="E334">
+        <v>88.2</v>
+      </c>
+      <c r="F334" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G334" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H334" t="s">
+        <v>135</v>
+      </c>
+      <c r="I334" t="s">
+        <v>26</v>
+      </c>
+      <c r="J334" t="s">
+        <v>533</v>
+      </c>
+      <c r="K334">
+        <v>4</v>
+      </c>
+      <c r="L334">
+        <v>2</v>
+      </c>
+      <c r="M334">
+        <v>0</v>
+      </c>
+      <c r="N334">
+        <v>8</v>
+      </c>
+      <c r="O334">
+        <v>1019</v>
+      </c>
+      <c r="P334">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A335" s="2">
+        <v>7.9583333333333304</v>
+      </c>
+      <c r="B335" t="s">
+        <v>678</v>
+      </c>
+      <c r="C335" t="s">
+        <v>679</v>
+      </c>
+      <c r="D335">
+        <v>340</v>
+      </c>
+      <c r="E335">
+        <v>93.7</v>
+      </c>
+      <c r="F335" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G335" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H335" t="s">
+        <v>135</v>
+      </c>
+      <c r="I335" t="s">
+        <v>26</v>
+      </c>
+      <c r="J335" t="s">
+        <v>586</v>
+      </c>
+      <c r="K335">
+        <v>4</v>
+      </c>
+      <c r="L335">
+        <v>2</v>
+      </c>
+      <c r="M335">
+        <v>0</v>
+      </c>
+      <c r="N335">
+        <v>8</v>
+      </c>
+      <c r="O335">
+        <v>1019</v>
+      </c>
+      <c r="P335">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A336" s="2">
+        <v>8</v>
+      </c>
+      <c r="B336" t="s">
+        <v>680</v>
+      </c>
+      <c r="C336" t="s">
+        <v>681</v>
+      </c>
+      <c r="D336">
+        <v>340</v>
+      </c>
+      <c r="E336">
+        <v>98.1</v>
+      </c>
+      <c r="F336" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G336" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H336" t="s">
+        <v>135</v>
+      </c>
+      <c r="I336" t="s">
+        <v>26</v>
+      </c>
+      <c r="J336" t="s">
+        <v>586</v>
+      </c>
+      <c r="K336">
+        <v>4</v>
+      </c>
+      <c r="L336">
+        <v>2</v>
+      </c>
+      <c r="M336">
+        <v>0</v>
+      </c>
+      <c r="N336">
+        <v>8</v>
+      </c>
+      <c r="O336">
+        <v>1019</v>
+      </c>
+      <c r="P336">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A337" s="2">
+        <v>8.0416666666666696</v>
+      </c>
+      <c r="B337" t="s">
+        <v>682</v>
+      </c>
+      <c r="C337" t="s">
+        <v>683</v>
+      </c>
+      <c r="D337">
+        <v>350</v>
+      </c>
+      <c r="E337">
+        <v>100.7</v>
+      </c>
+      <c r="F337" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G337" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H337" t="s">
+        <v>135</v>
+      </c>
+      <c r="I337" t="s">
+        <v>26</v>
+      </c>
+      <c r="J337" t="s">
+        <v>586</v>
+      </c>
+      <c r="K337">
+        <v>3</v>
+      </c>
+      <c r="L337">
+        <v>2</v>
+      </c>
+      <c r="M337">
+        <v>0</v>
+      </c>
+      <c r="N337">
+        <v>8</v>
+      </c>
+      <c r="O337">
+        <v>1019</v>
+      </c>
+      <c r="P337">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A338" s="2">
+        <v>8.0833333333333393</v>
+      </c>
+      <c r="B338" t="s">
+        <v>684</v>
+      </c>
+      <c r="C338" t="s">
+        <v>685</v>
+      </c>
+      <c r="D338">
+        <v>321</v>
+      </c>
+      <c r="E338">
+        <v>102</v>
+      </c>
+      <c r="F338" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="G338" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H338" t="s">
+        <v>135</v>
+      </c>
+      <c r="I338" t="s">
+        <v>26</v>
+      </c>
+      <c r="J338" t="s">
+        <v>241</v>
+      </c>
+      <c r="K338">
+        <v>3</v>
+      </c>
+      <c r="L338">
+        <v>2</v>
+      </c>
+      <c r="M338">
+        <v>0</v>
+      </c>
+      <c r="N338">
+        <v>8</v>
+      </c>
+      <c r="O338">
+        <v>1019</v>
+      </c>
+      <c r="P338">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A339" s="2">
+        <v>8.1250000000000107</v>
+      </c>
+      <c r="B339" t="s">
+        <v>686</v>
+      </c>
+      <c r="C339" t="s">
+        <v>687</v>
+      </c>
+      <c r="D339">
+        <v>325</v>
+      </c>
+      <c r="E339">
+        <v>106.4</v>
+      </c>
+      <c r="F339" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G339" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H339" t="s">
+        <v>135</v>
+      </c>
+      <c r="I339" t="s">
+        <v>26</v>
+      </c>
+      <c r="J339" t="s">
+        <v>241</v>
+      </c>
+      <c r="K339">
+        <v>3</v>
+      </c>
+      <c r="L339">
+        <v>2</v>
+      </c>
+      <c r="M339">
+        <v>0</v>
+      </c>
+      <c r="N339">
+        <v>8</v>
+      </c>
+      <c r="O339">
+        <v>1020</v>
+      </c>
+      <c r="P339">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A340" s="2">
+        <v>8.1666666666666803</v>
+      </c>
+      <c r="B340" t="s">
+        <v>688</v>
+      </c>
+      <c r="C340" t="s">
+        <v>622</v>
+      </c>
+      <c r="D340">
+        <v>329</v>
+      </c>
+      <c r="E340">
+        <v>113.3</v>
+      </c>
+      <c r="F340" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G340" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H340" t="s">
+        <v>135</v>
+      </c>
+      <c r="I340" t="s">
+        <v>26</v>
+      </c>
+      <c r="J340" t="s">
+        <v>241</v>
+      </c>
+      <c r="K340">
+        <v>3</v>
+      </c>
+      <c r="L340">
+        <v>3</v>
+      </c>
+      <c r="M340">
+        <v>0</v>
+      </c>
+      <c r="N340">
+        <v>8</v>
+      </c>
+      <c r="O340">
+        <v>1020</v>
+      </c>
+      <c r="P340">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A341" s="2">
+        <v>8.2083333333333499</v>
+      </c>
+      <c r="B341" t="s">
+        <v>623</v>
+      </c>
+      <c r="C341" t="s">
+        <v>689</v>
+      </c>
+      <c r="D341">
+        <v>335</v>
+      </c>
+      <c r="E341">
+        <v>119.7</v>
+      </c>
+      <c r="F341" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G341" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H341" t="s">
+        <v>135</v>
+      </c>
+      <c r="I341" t="s">
+        <v>26</v>
+      </c>
+      <c r="J341" t="s">
+        <v>241</v>
+      </c>
+      <c r="K341">
+        <v>3</v>
+      </c>
+      <c r="L341">
+        <v>3</v>
+      </c>
+      <c r="M341">
+        <v>0</v>
+      </c>
+      <c r="N341">
+        <v>8</v>
+      </c>
+      <c r="O341">
+        <v>1013</v>
+      </c>
+      <c r="P341">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A342" s="2">
+        <v>8.2500000000000195</v>
+      </c>
+      <c r="B342" t="s">
+        <v>646</v>
+      </c>
+      <c r="C342" t="s">
+        <v>690</v>
+      </c>
+      <c r="D342">
+        <v>310</v>
+      </c>
+      <c r="E342">
+        <v>127.1</v>
+      </c>
+      <c r="F342" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H342" t="s">
+        <v>135</v>
+      </c>
+      <c r="I342" t="s">
+        <v>26</v>
+      </c>
+      <c r="J342" t="s">
+        <v>241</v>
+      </c>
+      <c r="K342">
+        <v>3</v>
+      </c>
+      <c r="L342">
+        <v>3</v>
+      </c>
+      <c r="M342">
+        <v>0</v>
+      </c>
+      <c r="N342">
+        <v>8</v>
+      </c>
+      <c r="O342">
+        <v>1013</v>
+      </c>
+      <c r="P342">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A343" s="2">
+        <v>8.2916666666666892</v>
+      </c>
+      <c r="B343" t="s">
+        <v>691</v>
+      </c>
+      <c r="C343" t="s">
+        <v>692</v>
+      </c>
+      <c r="D343">
+        <v>310</v>
+      </c>
+      <c r="E343">
+        <v>134.30000000000001</v>
+      </c>
+      <c r="F343" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G343" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H343" t="s">
+        <v>135</v>
+      </c>
+      <c r="I343" t="s">
+        <v>26</v>
+      </c>
+      <c r="J343" t="s">
+        <v>241</v>
+      </c>
+      <c r="K343">
+        <v>3</v>
+      </c>
+      <c r="L343">
+        <v>2</v>
+      </c>
+      <c r="M343">
+        <v>0</v>
+      </c>
+      <c r="N343">
+        <v>8</v>
+      </c>
+      <c r="O343">
+        <v>1013</v>
+      </c>
+      <c r="P343">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A344" s="2">
+        <v>8.3333333333333606</v>
+      </c>
+      <c r="B344" t="s">
+        <v>693</v>
+      </c>
+      <c r="C344" t="s">
+        <v>694</v>
+      </c>
+      <c r="D344">
+        <v>310</v>
+      </c>
+      <c r="E344">
+        <v>141.9</v>
+      </c>
+      <c r="F344" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G344" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H344" t="s">
+        <v>135</v>
+      </c>
+      <c r="I344" t="s">
+        <v>26</v>
+      </c>
+      <c r="J344" t="s">
+        <v>241</v>
+      </c>
+      <c r="K344">
+        <v>3</v>
+      </c>
+      <c r="L344">
+        <v>2</v>
+      </c>
+      <c r="M344">
+        <v>0</v>
+      </c>
+      <c r="N344">
+        <v>8</v>
+      </c>
+      <c r="O344">
+        <v>1013</v>
+      </c>
+      <c r="P344">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A345" s="2">
+        <v>8.3750000000000302</v>
+      </c>
+      <c r="B345" t="s">
+        <v>695</v>
+      </c>
+      <c r="C345" t="s">
+        <v>696</v>
+      </c>
+      <c r="D345">
+        <v>10</v>
+      </c>
+      <c r="E345">
+        <v>149.19999999999999</v>
+      </c>
+      <c r="F345" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G345" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H345" t="s">
+        <v>135</v>
+      </c>
+      <c r="I345" t="s">
+        <v>26</v>
+      </c>
+      <c r="J345" t="s">
+        <v>118</v>
+      </c>
+      <c r="K345">
+        <v>4</v>
+      </c>
+      <c r="L345">
+        <v>2</v>
+      </c>
+      <c r="M345">
+        <v>0</v>
+      </c>
+      <c r="N345">
+        <v>8</v>
+      </c>
+      <c r="O345">
+        <v>1019</v>
+      </c>
+      <c r="P345">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A346" s="2">
+        <v>8.4166666666666998</v>
+      </c>
+      <c r="B346" t="s">
+        <v>697</v>
+      </c>
+      <c r="C346" t="s">
+        <v>698</v>
+      </c>
+      <c r="D346">
+        <v>50</v>
+      </c>
+      <c r="E346">
+        <v>155.5</v>
+      </c>
+      <c r="F346" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="G346" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H346" t="s">
+        <v>135</v>
+      </c>
+      <c r="I346" t="s">
+        <v>26</v>
+      </c>
+      <c r="J346" t="s">
+        <v>118</v>
+      </c>
+      <c r="K346">
+        <v>3</v>
+      </c>
+      <c r="L346">
+        <v>2</v>
+      </c>
+      <c r="M346">
+        <v>0</v>
+      </c>
+      <c r="N346">
+        <v>8</v>
+      </c>
+      <c r="O346">
+        <v>1019</v>
+      </c>
+      <c r="P346">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A347" s="2">
+        <v>8.4583333333333695</v>
+      </c>
+      <c r="B347" t="s">
+        <v>699</v>
+      </c>
+      <c r="C347" t="s">
+        <v>700</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>161.69999999999999</v>
+      </c>
+      <c r="F347" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G347" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H347" t="s">
+        <v>135</v>
+      </c>
+      <c r="I347" t="s">
+        <v>26</v>
+      </c>
+      <c r="J347" t="s">
+        <v>118</v>
+      </c>
+      <c r="K347">
+        <v>3</v>
+      </c>
+      <c r="L347">
+        <v>2</v>
+      </c>
+      <c r="M347">
+        <v>0</v>
+      </c>
+      <c r="N347">
+        <v>8</v>
+      </c>
+      <c r="O347">
+        <v>1013</v>
+      </c>
+      <c r="P347">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A348" s="2">
+        <v>8.5000000000000409</v>
+      </c>
+      <c r="B348" t="s">
+        <v>701</v>
+      </c>
+      <c r="C348" t="s">
+        <v>702</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>168.7</v>
+      </c>
+      <c r="F348" s="1">
+        <v>7</v>
+      </c>
+      <c r="G348" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H348" t="s">
+        <v>135</v>
+      </c>
+      <c r="I348" t="s">
+        <v>26</v>
+      </c>
+      <c r="J348" t="s">
+        <v>299</v>
+      </c>
+      <c r="K348">
+        <v>4</v>
+      </c>
+      <c r="L348">
+        <v>2</v>
+      </c>
+      <c r="M348">
+        <v>1</v>
+      </c>
+      <c r="N348">
+        <v>8</v>
+      </c>
+      <c r="O348">
+        <v>1019</v>
+      </c>
+      <c r="P348">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A349" s="2">
+        <v>8.5416666666667105</v>
+      </c>
+      <c r="B349" t="s">
+        <v>703</v>
+      </c>
+      <c r="C349" t="s">
+        <v>704</v>
+      </c>
+      <c r="D349">
+        <v>350</v>
+      </c>
+      <c r="E349">
+        <v>176.4</v>
+      </c>
+      <c r="F349" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G349" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H349" t="s">
+        <v>135</v>
+      </c>
+      <c r="I349" t="s">
+        <v>26</v>
+      </c>
+      <c r="J349" t="s">
+        <v>205</v>
+      </c>
+      <c r="K349">
+        <v>4</v>
+      </c>
+      <c r="L349">
+        <v>2</v>
+      </c>
+      <c r="M349">
+        <v>1</v>
+      </c>
+      <c r="N349">
+        <v>8</v>
+      </c>
+      <c r="O349">
+        <v>1013</v>
+      </c>
+      <c r="P349">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A350" s="2">
+        <v>8.5833333333333801</v>
+      </c>
+      <c r="B350" t="s">
+        <v>705</v>
+      </c>
+      <c r="C350" t="s">
+        <v>706</v>
+      </c>
+      <c r="D350">
+        <v>350</v>
+      </c>
+      <c r="E350">
+        <v>181.7</v>
+      </c>
+      <c r="F350" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G350" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H350" t="s">
+        <v>135</v>
+      </c>
+      <c r="I350" t="s">
+        <v>26</v>
+      </c>
+      <c r="J350" t="s">
+        <v>205</v>
+      </c>
+      <c r="K350">
+        <v>4</v>
+      </c>
+      <c r="L350">
+        <v>2</v>
+      </c>
+      <c r="M350">
+        <v>1</v>
+      </c>
+      <c r="N350">
+        <v>8</v>
+      </c>
+      <c r="O350">
+        <v>1013</v>
+      </c>
+      <c r="P350">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A351" s="2">
+        <v>8.6250000000000497</v>
+      </c>
+      <c r="B351" t="s">
+        <v>707</v>
+      </c>
+      <c r="C351" t="s">
+        <v>708</v>
+      </c>
+      <c r="D351">
+        <v>350</v>
+      </c>
+      <c r="E351">
+        <v>188.2</v>
+      </c>
+      <c r="F351" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G351" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H351" t="s">
+        <v>135</v>
+      </c>
+      <c r="I351" t="s">
+        <v>26</v>
+      </c>
+      <c r="J351" t="s">
+        <v>205</v>
+      </c>
+      <c r="K351">
+        <v>4</v>
+      </c>
+      <c r="L351">
+        <v>2</v>
+      </c>
+      <c r="M351">
+        <v>1</v>
+      </c>
+      <c r="N351">
+        <v>8</v>
+      </c>
+      <c r="O351">
+        <v>1013</v>
+      </c>
+      <c r="P351">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A352" s="2">
+        <v>8.6666666666667194</v>
+      </c>
+      <c r="B352" t="s">
+        <v>502</v>
+      </c>
+      <c r="C352" t="s">
+        <v>709</v>
+      </c>
+      <c r="D352">
+        <v>325</v>
+      </c>
+      <c r="E352">
+        <v>195.5</v>
+      </c>
+      <c r="F352" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G352" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H352" t="s">
+        <v>135</v>
+      </c>
+      <c r="I352" t="s">
+        <v>26</v>
+      </c>
+      <c r="J352" t="s">
+        <v>205</v>
+      </c>
+      <c r="K352">
+        <v>4</v>
+      </c>
+      <c r="L352">
+        <v>2</v>
+      </c>
+      <c r="M352">
+        <v>1</v>
+      </c>
+      <c r="N352">
+        <v>8</v>
+      </c>
+      <c r="O352">
+        <v>1018</v>
+      </c>
+      <c r="P352">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A353" s="2">
+        <v>8.7083333333333908</v>
+      </c>
+      <c r="B353" t="s">
+        <v>710</v>
+      </c>
+      <c r="C353" t="s">
+        <v>711</v>
+      </c>
+      <c r="D353">
+        <v>325</v>
+      </c>
+      <c r="E353">
+        <v>203.1</v>
+      </c>
+      <c r="F353" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G353" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H353" t="s">
+        <v>135</v>
+      </c>
+      <c r="I353" t="s">
+        <v>26</v>
+      </c>
+      <c r="J353" t="s">
+        <v>162</v>
+      </c>
+      <c r="K353">
+        <v>5</v>
+      </c>
+      <c r="L353">
+        <v>2</v>
+      </c>
+      <c r="M353">
+        <v>1</v>
+      </c>
+      <c r="N353">
+        <v>8</v>
+      </c>
+      <c r="O353">
+        <v>1018</v>
+      </c>
+      <c r="P353">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A354" s="2">
+        <v>8.7500000000000604</v>
+      </c>
+      <c r="B354" t="s">
+        <v>712</v>
+      </c>
+      <c r="C354" t="s">
+        <v>715</v>
+      </c>
+      <c r="D354">
+        <v>335</v>
+      </c>
+      <c r="E354">
+        <v>210.3</v>
+      </c>
+      <c r="F354" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G354" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H354" t="s">
+        <v>135</v>
+      </c>
+      <c r="I354" t="s">
+        <v>26</v>
+      </c>
+      <c r="J354" t="s">
+        <v>153</v>
+      </c>
+      <c r="K354">
+        <v>6</v>
+      </c>
+      <c r="L354">
+        <v>2</v>
+      </c>
+      <c r="M354">
+        <v>1</v>
+      </c>
+      <c r="N354">
+        <v>8</v>
+      </c>
+      <c r="O354">
+        <v>1018</v>
+      </c>
+      <c r="P354">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A355" s="2">
+        <v>8.79166666666673</v>
+      </c>
+      <c r="B355" t="s">
+        <v>713</v>
+      </c>
+      <c r="C355" t="s">
+        <v>714</v>
+      </c>
+      <c r="D355">
+        <v>335</v>
+      </c>
+      <c r="E355">
+        <v>215.7</v>
+      </c>
+      <c r="F355" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="G355" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H355" t="s">
+        <v>135</v>
+      </c>
+      <c r="I355" t="s">
+        <v>26</v>
+      </c>
+      <c r="J355" t="s">
+        <v>716</v>
+      </c>
+      <c r="K355">
+        <v>5</v>
+      </c>
+      <c r="L355">
+        <v>2</v>
+      </c>
+      <c r="M355">
+        <v>2</v>
+      </c>
+      <c r="N355">
+        <v>8</v>
+      </c>
+      <c r="O355">
+        <v>1018</v>
+      </c>
+      <c r="P355">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A356" s="2">
+        <v>8.8333333333333997</v>
+      </c>
+      <c r="B356" t="s">
+        <v>717</v>
+      </c>
+      <c r="C356" t="s">
+        <v>718</v>
+      </c>
+      <c r="D356">
+        <v>335</v>
+      </c>
+      <c r="E356">
+        <v>221.2</v>
+      </c>
+      <c r="F356" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G356" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H356" t="s">
+        <v>135</v>
+      </c>
+      <c r="I356" t="s">
+        <v>26</v>
+      </c>
+      <c r="J356" t="s">
+        <v>153</v>
+      </c>
+      <c r="K356">
+        <v>6</v>
+      </c>
+      <c r="L356">
+        <v>3</v>
+      </c>
+      <c r="M356">
+        <v>0</v>
+      </c>
+      <c r="N356">
+        <v>8</v>
+      </c>
+      <c r="O356">
+        <v>1017</v>
+      </c>
+      <c r="P356">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A357" s="2">
+        <v>8.8750000000000693</v>
+      </c>
+      <c r="B357" t="s">
+        <v>719</v>
+      </c>
+      <c r="C357" t="s">
+        <v>720</v>
+      </c>
+      <c r="D357">
+        <v>335</v>
+      </c>
+      <c r="E357">
+        <v>226.6</v>
+      </c>
+      <c r="F357" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="G357" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H357" t="s">
+        <v>135</v>
+      </c>
+      <c r="I357" t="s">
+        <v>26</v>
+      </c>
+      <c r="J357" t="s">
+        <v>153</v>
+      </c>
+      <c r="K357">
+        <v>5</v>
+      </c>
+      <c r="L357">
+        <v>4</v>
+      </c>
+      <c r="M357">
+        <v>0</v>
+      </c>
+      <c r="N357">
+        <v>8</v>
+      </c>
+      <c r="O357">
+        <v>1017</v>
+      </c>
+      <c r="P357">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A358" s="2">
+        <v>8.9166666666667407</v>
+      </c>
+      <c r="B358" t="s">
+        <v>721</v>
+      </c>
+      <c r="C358" t="s">
+        <v>722</v>
+      </c>
+      <c r="D358">
+        <v>335</v>
+      </c>
+      <c r="E358">
+        <v>234.2</v>
+      </c>
+      <c r="F358" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G358" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H358" t="s">
+        <v>135</v>
+      </c>
+      <c r="I358" t="s">
+        <v>26</v>
+      </c>
+      <c r="J358" t="s">
+        <v>153</v>
+      </c>
+      <c r="K358">
+        <v>5</v>
+      </c>
+      <c r="L358">
+        <v>4</v>
+      </c>
+      <c r="M358">
+        <v>3</v>
+      </c>
+      <c r="N358">
+        <v>8</v>
+      </c>
+      <c r="O358">
+        <v>1017</v>
+      </c>
+      <c r="P358">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A359" s="2">
+        <v>8.9583333333334103</v>
+      </c>
+      <c r="B359" t="s">
+        <v>147</v>
+      </c>
+      <c r="C359" t="s">
+        <v>723</v>
+      </c>
+      <c r="D359">
+        <v>345</v>
+      </c>
+      <c r="E359">
+        <v>241.5</v>
+      </c>
+      <c r="F359" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="G359" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H359" t="s">
+        <v>135</v>
+      </c>
+      <c r="I359" t="s">
+        <v>26</v>
+      </c>
+      <c r="J359" t="s">
+        <v>153</v>
+      </c>
+      <c r="K359">
+        <v>5</v>
+      </c>
+      <c r="L359">
+        <v>4</v>
+      </c>
+      <c r="M359">
+        <v>2</v>
+      </c>
+      <c r="N359">
+        <v>8</v>
+      </c>
+      <c r="O359">
+        <v>1017</v>
+      </c>
+      <c r="P359">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A360" s="2">
+        <v>9.0000000000000799</v>
+      </c>
+      <c r="B360" t="s">
+        <v>724</v>
+      </c>
+      <c r="C360" t="s">
+        <v>727</v>
+      </c>
+      <c r="D360">
+        <v>325</v>
+      </c>
+      <c r="E360">
+        <v>248.5</v>
+      </c>
+      <c r="F360" s="1">
+        <v>7</v>
+      </c>
+      <c r="G360" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H360" t="s">
+        <v>135</v>
+      </c>
+      <c r="I360" t="s">
+        <v>26</v>
+      </c>
+      <c r="J360" t="s">
+        <v>153</v>
+      </c>
+      <c r="K360">
+        <v>5</v>
+      </c>
+      <c r="L360">
+        <v>4</v>
+      </c>
+      <c r="M360">
+        <v>0</v>
+      </c>
+      <c r="N360">
+        <v>8</v>
+      </c>
+      <c r="O360">
+        <v>1017</v>
+      </c>
+      <c r="P360">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A361" s="2">
+        <v>9.0416666666667496</v>
+      </c>
+      <c r="B361" t="s">
+        <v>725</v>
+      </c>
+      <c r="C361" t="s">
+        <v>726</v>
+      </c>
+      <c r="D361">
+        <v>335</v>
+      </c>
+      <c r="E361">
+        <v>256</v>
+      </c>
+      <c r="F361" s="1">
+        <v>7</v>
+      </c>
+      <c r="G361" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H361" t="s">
+        <v>135</v>
+      </c>
+      <c r="I361" t="s">
+        <v>26</v>
+      </c>
+      <c r="J361" t="s">
+        <v>716</v>
+      </c>
+      <c r="K361">
+        <v>5</v>
+      </c>
+      <c r="L361">
+        <v>3</v>
+      </c>
+      <c r="M361">
+        <v>2</v>
+      </c>
+      <c r="N361">
+        <v>8</v>
+      </c>
+      <c r="O361">
+        <v>1018</v>
+      </c>
+      <c r="P361">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A362" s="2">
+        <v>9.0833333333334192</v>
+      </c>
+      <c r="B362" t="s">
+        <v>728</v>
+      </c>
+      <c r="C362" t="s">
+        <v>729</v>
+      </c>
+      <c r="D362">
+        <v>325</v>
+      </c>
+      <c r="E362">
+        <v>263.60000000000002</v>
+      </c>
+      <c r="F362" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G362" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H362" t="s">
+        <v>135</v>
+      </c>
+      <c r="I362" t="s">
+        <v>26</v>
+      </c>
+      <c r="J362" t="s">
+        <v>730</v>
+      </c>
+      <c r="K362">
+        <v>5</v>
+      </c>
+      <c r="L362">
+        <v>3</v>
+      </c>
+      <c r="M362">
+        <v>2</v>
+      </c>
+      <c r="N362">
+        <v>8</v>
+      </c>
+      <c r="O362">
+        <v>1019</v>
+      </c>
+      <c r="P362">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A363" s="2">
+        <v>9.1250000000000906</v>
+      </c>
+      <c r="B363" t="s">
+        <v>731</v>
+      </c>
+      <c r="C363" t="s">
+        <v>732</v>
+      </c>
+      <c r="D363">
+        <v>335</v>
+      </c>
+      <c r="E363">
+        <v>270.7</v>
+      </c>
+      <c r="F363" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G363" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H363" t="s">
+        <v>135</v>
+      </c>
+      <c r="I363" t="s">
+        <v>26</v>
+      </c>
+      <c r="J363" t="s">
+        <v>730</v>
+      </c>
+      <c r="K363">
+        <v>5</v>
+      </c>
+      <c r="L363">
+        <v>3</v>
+      </c>
+      <c r="M363">
+        <v>1</v>
+      </c>
+      <c r="N363">
+        <v>8</v>
+      </c>
+      <c r="O363">
+        <v>1019</v>
+      </c>
+      <c r="P363">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A364" s="2">
+        <v>9.1666666666667602</v>
+      </c>
+      <c r="B364" t="s">
+        <v>733</v>
+      </c>
+      <c r="C364" t="s">
+        <v>734</v>
+      </c>
+      <c r="D364">
+        <v>330</v>
+      </c>
+      <c r="E364">
+        <v>278.3</v>
+      </c>
+      <c r="F364" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G364" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H364" t="s">
+        <v>135</v>
+      </c>
+      <c r="I364" t="s">
+        <v>26</v>
+      </c>
+      <c r="J364" t="s">
+        <v>730</v>
+      </c>
+      <c r="K364">
+        <v>5</v>
+      </c>
+      <c r="L364">
+        <v>3</v>
+      </c>
+      <c r="M364">
+        <v>2</v>
+      </c>
+      <c r="N364">
+        <v>8</v>
+      </c>
+      <c r="O364">
+        <v>1019</v>
+      </c>
+      <c r="P364">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A365" s="2">
+        <v>9.2083333333334298</v>
+      </c>
+      <c r="B365" t="s">
+        <v>735</v>
+      </c>
+      <c r="C365" t="s">
+        <v>736</v>
+      </c>
+      <c r="D365">
+        <v>340</v>
+      </c>
+      <c r="E365">
+        <v>286.8</v>
+      </c>
+      <c r="F365" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="G365" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H365" t="s">
+        <v>135</v>
+      </c>
+      <c r="I365" t="s">
+        <v>26</v>
+      </c>
+      <c r="J365" t="s">
+        <v>153</v>
+      </c>
+      <c r="K365">
+        <v>5</v>
+      </c>
+      <c r="L365">
+        <v>3</v>
+      </c>
+      <c r="M365">
+        <v>1</v>
+      </c>
+      <c r="N365">
+        <v>8</v>
+      </c>
+      <c r="O365">
+        <v>1019</v>
+      </c>
+      <c r="P365">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A366" s="2">
+        <v>9.2500000000000995</v>
+      </c>
+      <c r="B366" t="s">
+        <v>738</v>
+      </c>
+      <c r="C366" t="s">
+        <v>739</v>
+      </c>
+      <c r="D366">
+        <v>340</v>
+      </c>
+      <c r="E366">
+        <v>293.60000000000002</v>
+      </c>
+      <c r="F366" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G366" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H366" t="s">
+        <v>135</v>
+      </c>
+      <c r="I366" t="s">
+        <v>26</v>
+      </c>
+      <c r="J366" t="s">
+        <v>153</v>
+      </c>
+      <c r="K366">
+        <v>4</v>
+      </c>
+      <c r="L366">
+        <v>3</v>
+      </c>
+      <c r="M366">
+        <v>1</v>
+      </c>
+      <c r="N366">
+        <v>8</v>
+      </c>
+      <c r="O366">
+        <v>1019</v>
+      </c>
+      <c r="P366">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A367" s="2">
+        <v>9.2916666666667709</v>
+      </c>
+      <c r="B367" t="s">
+        <v>740</v>
+      </c>
+      <c r="C367" t="s">
+        <v>737</v>
+      </c>
+      <c r="D367">
+        <v>345</v>
+      </c>
+      <c r="E367">
+        <v>300.3</v>
+      </c>
+      <c r="F367" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="G367" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H367" t="s">
+        <v>135</v>
+      </c>
+      <c r="I367" t="s">
+        <v>26</v>
+      </c>
+      <c r="J367" t="s">
+        <v>153</v>
+      </c>
+      <c r="K367">
+        <v>4</v>
+      </c>
+      <c r="L367">
+        <v>3</v>
+      </c>
+      <c r="M367">
+        <v>1</v>
+      </c>
+      <c r="N367">
+        <v>8</v>
+      </c>
+      <c r="O367">
+        <v>1019</v>
+      </c>
+      <c r="P367">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A368" s="2">
+        <v>9.3333333333334405</v>
+      </c>
+      <c r="B368" t="s">
+        <v>741</v>
+      </c>
+      <c r="C368" t="s">
+        <v>742</v>
+      </c>
+      <c r="D368">
+        <v>340</v>
+      </c>
+      <c r="E368">
+        <v>306.39999999999998</v>
+      </c>
+      <c r="F368" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G368" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H368" t="s">
+        <v>135</v>
+      </c>
+      <c r="I368" t="s">
+        <v>26</v>
+      </c>
+      <c r="J368" t="s">
+        <v>153</v>
+      </c>
+      <c r="K368">
+        <v>4</v>
+      </c>
+      <c r="L368">
+        <v>3</v>
+      </c>
+      <c r="M368">
+        <v>0</v>
+      </c>
+      <c r="N368">
+        <v>8</v>
+      </c>
+      <c r="O368">
+        <v>1020</v>
+      </c>
+      <c r="P368">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A369" s="2">
+        <v>9.3750000000001101</v>
+      </c>
+      <c r="B369" t="s">
+        <v>743</v>
+      </c>
+      <c r="C369" t="s">
+        <v>744</v>
+      </c>
+      <c r="D369">
+        <v>345</v>
+      </c>
+      <c r="E369">
+        <v>312.5</v>
+      </c>
+      <c r="F369" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="G369" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H369" t="s">
+        <v>135</v>
+      </c>
+      <c r="I369" t="s">
+        <v>26</v>
+      </c>
+      <c r="J369" t="s">
+        <v>153</v>
+      </c>
+      <c r="K369">
+        <v>4</v>
+      </c>
+      <c r="L369">
+        <v>3</v>
+      </c>
+      <c r="M369">
+        <v>0</v>
+      </c>
+      <c r="N369">
+        <v>8</v>
+      </c>
+      <c r="O369">
+        <v>1020</v>
+      </c>
+      <c r="P369">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A370" s="2">
+        <v>9.4166666666667798</v>
+      </c>
+      <c r="B370" t="s">
+        <v>745</v>
+      </c>
+      <c r="C370" t="s">
+        <v>746</v>
+      </c>
+      <c r="D370">
+        <v>340</v>
+      </c>
+      <c r="E370">
+        <v>318.7</v>
+      </c>
+      <c r="F370" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G370" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H370" t="s">
+        <v>135</v>
+      </c>
+      <c r="I370" t="s">
+        <v>26</v>
+      </c>
+      <c r="J370" t="s">
+        <v>153</v>
+      </c>
+      <c r="K370">
+        <v>3</v>
+      </c>
+      <c r="L370">
+        <v>3</v>
+      </c>
+      <c r="M370">
+        <v>0</v>
+      </c>
+      <c r="N370">
+        <v>8</v>
+      </c>
+      <c r="O370">
+        <v>1020</v>
+      </c>
+      <c r="P370">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A371" s="2">
+        <v>9.4583333333334494</v>
+      </c>
+      <c r="B371" t="s">
+        <v>747</v>
+      </c>
+      <c r="C371" t="s">
+        <v>748</v>
+      </c>
+      <c r="D371">
+        <v>330</v>
+      </c>
+      <c r="E371">
+        <v>324.3</v>
+      </c>
+      <c r="F371" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G371" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H371" t="s">
+        <v>135</v>
+      </c>
+      <c r="I371" t="s">
+        <v>26</v>
+      </c>
+      <c r="J371" t="s">
+        <v>153</v>
+      </c>
+      <c r="K371">
+        <v>3</v>
+      </c>
+      <c r="L371">
+        <v>3</v>
+      </c>
+      <c r="M371">
+        <v>0</v>
+      </c>
+      <c r="N371">
+        <v>8</v>
+      </c>
+      <c r="O371">
+        <v>1020</v>
+      </c>
+      <c r="P371">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A372" s="2">
+        <v>9.5000000000001208</v>
+      </c>
+      <c r="B372" t="s">
+        <v>749</v>
+      </c>
+      <c r="C372" t="s">
+        <v>750</v>
+      </c>
+      <c r="D372">
+        <v>350</v>
+      </c>
+      <c r="E372">
+        <v>331.3</v>
+      </c>
+      <c r="F372" s="1">
+        <v>7</v>
+      </c>
+      <c r="G372" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H372" t="s">
+        <v>135</v>
+      </c>
+      <c r="I372" t="s">
+        <v>26</v>
+      </c>
+      <c r="J372" t="s">
+        <v>153</v>
+      </c>
+      <c r="K372">
+        <v>3</v>
+      </c>
+      <c r="L372">
+        <v>2</v>
+      </c>
+      <c r="M372">
+        <v>0</v>
+      </c>
+      <c r="N372">
+        <v>8</v>
+      </c>
+      <c r="O372">
+        <v>1020</v>
+      </c>
+      <c r="P372">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A373" s="2">
+        <v>9.5416666666667904</v>
+      </c>
+      <c r="B373" t="s">
+        <v>751</v>
+      </c>
+      <c r="C373" t="s">
+        <v>752</v>
+      </c>
+      <c r="D373">
+        <v>340</v>
+      </c>
+      <c r="E373">
+        <v>337.2</v>
+      </c>
+      <c r="F373" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="G373" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H373" t="s">
+        <v>135</v>
+      </c>
+      <c r="I373" t="s">
+        <v>26</v>
+      </c>
+      <c r="J373" t="s">
+        <v>205</v>
+      </c>
+      <c r="K373">
+        <v>2</v>
+      </c>
+      <c r="L373">
+        <v>2</v>
+      </c>
+      <c r="M373">
+        <v>0</v>
+      </c>
+      <c r="N373">
+        <v>8</v>
+      </c>
+      <c r="O373">
+        <v>1020</v>
+      </c>
+      <c r="P373">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A374" s="2">
+        <v>9.58333333333346</v>
+      </c>
+      <c r="B374" t="s">
+        <v>753</v>
+      </c>
+      <c r="C374" t="s">
+        <v>754</v>
+      </c>
+      <c r="D374">
+        <v>335</v>
+      </c>
+      <c r="E374">
+        <v>342.1</v>
+      </c>
+      <c r="F374" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G374" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H374" t="s">
+        <v>135</v>
+      </c>
+      <c r="I374" t="s">
+        <v>26</v>
+      </c>
+      <c r="J374" t="s">
+        <v>118</v>
+      </c>
+      <c r="K374">
+        <v>2</v>
+      </c>
+      <c r="L374">
+        <v>2</v>
+      </c>
+      <c r="M374">
+        <v>1</v>
+      </c>
+      <c r="N374">
+        <v>8</v>
+      </c>
+      <c r="O374">
+        <v>1020</v>
+      </c>
+      <c r="P374">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A375" s="2">
+        <v>9.6250000000001297</v>
+      </c>
+      <c r="B375" t="s">
+        <v>755</v>
+      </c>
+      <c r="C375" t="s">
+        <v>756</v>
+      </c>
+      <c r="D375">
+        <v>345</v>
+      </c>
+      <c r="E375">
+        <v>348.7</v>
+      </c>
+      <c r="F375" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G375" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H375" t="s">
+        <v>135</v>
+      </c>
+      <c r="I375" t="s">
+        <v>26</v>
+      </c>
+      <c r="J375" t="s">
+        <v>118</v>
+      </c>
+      <c r="K375">
+        <v>4</v>
+      </c>
+      <c r="L375">
+        <v>2</v>
+      </c>
+      <c r="M375">
+        <v>3</v>
+      </c>
+      <c r="N375">
+        <v>8</v>
+      </c>
+      <c r="O375">
+        <v>1020</v>
+      </c>
+      <c r="P375">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A376" s="2">
+        <v>9.6666666666667993</v>
+      </c>
+      <c r="B376" t="s">
+        <v>757</v>
+      </c>
+      <c r="C376" t="s">
+        <v>758</v>
+      </c>
+      <c r="D376">
+        <v>350</v>
+      </c>
+      <c r="E376">
+        <v>356.7</v>
+      </c>
+      <c r="F376" s="1">
+        <v>8</v>
+      </c>
+      <c r="G376" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H376" t="s">
+        <v>135</v>
+      </c>
+      <c r="I376" t="s">
+        <v>26</v>
+      </c>
+      <c r="J376" t="s">
+        <v>118</v>
+      </c>
+      <c r="K376">
+        <v>2</v>
+      </c>
+      <c r="L376">
+        <v>2</v>
+      </c>
+      <c r="M376">
+        <v>3</v>
+      </c>
+      <c r="N376">
+        <v>8</v>
+      </c>
+      <c r="O376">
+        <v>1020</v>
+      </c>
+      <c r="P376">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A377" s="2">
+        <v>9.7083333333334707</v>
+      </c>
+      <c r="B377" t="s">
+        <v>759</v>
+      </c>
+      <c r="C377" t="s">
+        <v>760</v>
+      </c>
+      <c r="D377">
+        <v>350</v>
+      </c>
+      <c r="E377">
+        <v>364.3</v>
+      </c>
+      <c r="F377" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="G377" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H377" t="s">
+        <v>135</v>
+      </c>
+      <c r="I377" t="s">
+        <v>26</v>
+      </c>
+      <c r="J377" t="s">
+        <v>118</v>
+      </c>
+      <c r="K377">
+        <v>2</v>
+      </c>
+      <c r="L377">
+        <v>2</v>
+      </c>
+      <c r="M377">
+        <v>3</v>
+      </c>
+      <c r="N377">
+        <v>8</v>
+      </c>
+      <c r="O377">
+        <v>1020</v>
+      </c>
+      <c r="P377">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A378" s="2">
+        <v>9.7500000000001403</v>
+      </c>
+      <c r="B378" t="s">
+        <v>761</v>
+      </c>
+      <c r="C378" t="s">
+        <v>762</v>
+      </c>
+      <c r="D378">
+        <v>350</v>
+      </c>
+      <c r="E378">
+        <v>373.1</v>
+      </c>
+      <c r="F378" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G378" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H378" t="s">
+        <v>135</v>
+      </c>
+      <c r="I378" t="s">
+        <v>26</v>
+      </c>
+      <c r="J378" t="s">
+        <v>118</v>
+      </c>
+      <c r="K378">
+        <v>2</v>
+      </c>
+      <c r="L378">
+        <v>2</v>
+      </c>
+      <c r="M378">
+        <v>0</v>
+      </c>
+      <c r="N378">
+        <v>8</v>
+      </c>
+      <c r="O378">
+        <v>1020</v>
+      </c>
+      <c r="P378">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A379" s="2">
+        <v>9.79166666666681</v>
+      </c>
+      <c r="B379" t="s">
+        <v>763</v>
+      </c>
+      <c r="C379" t="s">
+        <v>764</v>
+      </c>
+      <c r="D379">
+        <v>350</v>
+      </c>
+      <c r="E379">
+        <v>380.9</v>
+      </c>
+      <c r="F379" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G379" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H379" t="s">
+        <v>135</v>
+      </c>
+      <c r="I379" t="s">
+        <v>26</v>
+      </c>
+      <c r="J379" t="s">
+        <v>118</v>
+      </c>
+      <c r="K379">
+        <v>3</v>
+      </c>
+      <c r="L379">
+        <v>3</v>
+      </c>
+      <c r="M379">
+        <v>0</v>
+      </c>
+      <c r="N379">
+        <v>8</v>
+      </c>
+      <c r="O379">
+        <v>1018</v>
+      </c>
+      <c r="P379">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A380" s="2">
+        <v>9.8333333333334796</v>
+      </c>
+      <c r="B380" t="s">
+        <v>765</v>
+      </c>
+      <c r="C380" t="s">
+        <v>766</v>
+      </c>
+      <c r="D380">
+        <v>350</v>
+      </c>
+      <c r="E380">
+        <v>388.7</v>
+      </c>
+      <c r="F380" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="G380" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H380" t="s">
+        <v>135</v>
+      </c>
+      <c r="I380" t="s">
+        <v>26</v>
+      </c>
+      <c r="J380" t="s">
+        <v>118</v>
+      </c>
+      <c r="K380">
+        <v>3</v>
+      </c>
+      <c r="L380">
+        <v>3</v>
+      </c>
+      <c r="M380">
+        <v>0</v>
+      </c>
+      <c r="N380">
+        <v>8</v>
+      </c>
+      <c r="O380">
+        <v>1018</v>
+      </c>
+      <c r="P380">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A381" s="2">
+        <v>9.8750000000001492</v>
+      </c>
+      <c r="B381" t="s">
+        <v>767</v>
+      </c>
+      <c r="C381" t="s">
+        <v>768</v>
+      </c>
+      <c r="D381">
+        <v>350</v>
+      </c>
+      <c r="E381">
+        <v>396.1</v>
+      </c>
+      <c r="F381" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G381" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H381" t="s">
+        <v>135</v>
+      </c>
+      <c r="I381" t="s">
+        <v>26</v>
+      </c>
+      <c r="J381" t="s">
+        <v>118</v>
+      </c>
+      <c r="K381">
+        <v>2</v>
+      </c>
+      <c r="L381">
+        <v>3</v>
+      </c>
+      <c r="M381">
+        <v>3</v>
+      </c>
+      <c r="N381">
+        <v>8</v>
+      </c>
+      <c r="O381">
+        <v>1018</v>
+      </c>
+      <c r="P381">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A382" s="2">
+        <v>9.9166666666668206</v>
+      </c>
+      <c r="B382" t="s">
+        <v>769</v>
+      </c>
+      <c r="C382" t="s">
+        <v>770</v>
+      </c>
+      <c r="D382">
+        <v>345</v>
+      </c>
+      <c r="E382">
+        <v>402.8</v>
+      </c>
+      <c r="F382" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="G382" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H382" t="s">
+        <v>135</v>
+      </c>
+      <c r="I382" t="s">
+        <v>26</v>
+      </c>
+      <c r="J382" t="s">
+        <v>153</v>
+      </c>
+      <c r="K382">
+        <v>4</v>
+      </c>
+      <c r="L382">
+        <v>3</v>
+      </c>
+      <c r="M382">
+        <v>3</v>
+      </c>
+      <c r="N382">
+        <v>8</v>
+      </c>
+      <c r="O382">
+        <v>1018</v>
+      </c>
+      <c r="P382">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A383" s="2">
+        <v>9.9583333333334902</v>
+      </c>
+      <c r="B383" t="s">
+        <v>771</v>
+      </c>
+      <c r="C383" t="s">
+        <v>772</v>
+      </c>
+      <c r="D383">
+        <v>343</v>
+      </c>
+      <c r="E383">
+        <v>409.6</v>
+      </c>
+      <c r="F383" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G383" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H383" t="s">
+        <v>135</v>
+      </c>
+      <c r="I383" t="s">
+        <v>26</v>
+      </c>
+      <c r="J383" t="s">
+        <v>205</v>
+      </c>
+      <c r="K383">
+        <v>3</v>
+      </c>
+      <c r="L383">
+        <v>3</v>
+      </c>
+      <c r="M383">
+        <v>3</v>
+      </c>
+      <c r="N383">
+        <v>8</v>
+      </c>
+      <c r="O383">
+        <v>1018</v>
+      </c>
+      <c r="P383">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A384" s="2">
+        <v>10.000000000000201</v>
+      </c>
+      <c r="B384" t="s">
+        <v>773</v>
+      </c>
+      <c r="C384" t="s">
+        <v>774</v>
+      </c>
+      <c r="D384">
+        <v>14</v>
+      </c>
+      <c r="E384">
+        <v>415.4</v>
+      </c>
+      <c r="F384" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G384" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H384" t="s">
+        <v>135</v>
+      </c>
+      <c r="I384" t="s">
+        <v>26</v>
+      </c>
+      <c r="J384" t="s">
+        <v>205</v>
+      </c>
+      <c r="K384">
+        <v>3</v>
+      </c>
+      <c r="L384">
+        <v>2</v>
+      </c>
+      <c r="M384">
+        <v>3</v>
+      </c>
+      <c r="N384">
+        <v>8</v>
+      </c>
+      <c r="O384">
+        <v>1018</v>
+      </c>
+      <c r="P384">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A385" s="2">
+        <v>10.041666666666901</v>
+      </c>
+      <c r="B385" t="s">
+        <v>775</v>
+      </c>
+      <c r="C385" t="s">
+        <v>776</v>
+      </c>
+      <c r="D385">
+        <v>20</v>
+      </c>
+      <c r="E385">
+        <v>421.4</v>
+      </c>
+      <c r="F385" s="1">
+        <v>6</v>
+      </c>
+      <c r="G385" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H385" t="s">
+        <v>135</v>
+      </c>
+      <c r="I385" t="s">
+        <v>26</v>
+      </c>
+      <c r="J385" t="s">
+        <v>118</v>
+      </c>
+      <c r="K385">
+        <v>2</v>
+      </c>
+      <c r="L385">
+        <v>2</v>
+      </c>
+      <c r="M385">
+        <v>3</v>
+      </c>
+      <c r="N385">
+        <v>8</v>
+      </c>
+      <c r="O385">
+        <v>1018</v>
+      </c>
+      <c r="P385">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A386" s="2">
+        <v>10.0833333333336</v>
+      </c>
+      <c r="B386" t="s">
+        <v>242</v>
+      </c>
+      <c r="C386" t="s">
+        <v>777</v>
+      </c>
+      <c r="D386">
+        <v>350</v>
+      </c>
+      <c r="E386">
+        <v>428.2</v>
+      </c>
+      <c r="F386" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G386" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H386" t="s">
+        <v>135</v>
+      </c>
+      <c r="I386" t="s">
+        <v>26</v>
+      </c>
+      <c r="J386" t="s">
+        <v>118</v>
+      </c>
+      <c r="K386">
+        <v>2</v>
+      </c>
+      <c r="L386">
+        <v>2</v>
+      </c>
+      <c r="M386">
+        <v>3</v>
+      </c>
+      <c r="N386">
+        <v>8</v>
+      </c>
+      <c r="O386">
+        <v>1017</v>
+      </c>
+      <c r="P386">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A387" s="2">
+        <v>10.125</v>
+      </c>
+      <c r="B387" t="s">
+        <v>778</v>
+      </c>
+      <c r="C387" t="s">
+        <v>779</v>
+      </c>
+      <c r="D387">
+        <v>43</v>
+      </c>
+      <c r="E387">
+        <v>435.1</v>
+      </c>
+      <c r="F387" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G387" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H387" t="s">
+        <v>135</v>
+      </c>
+      <c r="I387" t="s">
+        <v>26</v>
+      </c>
+      <c r="J387" t="s">
+        <v>118</v>
+      </c>
+      <c r="K387">
+        <v>2</v>
+      </c>
+      <c r="L387">
+        <v>1</v>
+      </c>
+      <c r="M387">
+        <v>3</v>
+      </c>
+      <c r="N387">
+        <v>8</v>
+      </c>
+      <c r="O387">
+        <v>1018</v>
+      </c>
+      <c r="P387">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A388" s="2">
+        <v>10.541666666666666</v>
+      </c>
+      <c r="B388" t="s">
+        <v>781</v>
+      </c>
+      <c r="C388" t="s">
+        <v>780</v>
+      </c>
+      <c r="D388">
+        <v>130</v>
+      </c>
+      <c r="E388">
+        <v>488.1</v>
+      </c>
+      <c r="F388" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G388" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H388" t="s">
+        <v>25</v>
+      </c>
+      <c r="I388" t="s">
+        <v>26</v>
+      </c>
+      <c r="J388" t="s">
+        <v>205</v>
+      </c>
+      <c r="K388">
+        <v>3</v>
+      </c>
+      <c r="L388">
+        <v>1</v>
+      </c>
+      <c r="M388">
+        <v>0</v>
+      </c>
+      <c r="N388">
+        <v>8</v>
+      </c>
+      <c r="O388">
+        <v>1012</v>
+      </c>
+      <c r="P388">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A389" s="2">
+        <v>10.5833333333333</v>
+      </c>
+      <c r="B389" t="s">
+        <v>782</v>
+      </c>
+      <c r="C389" t="s">
+        <v>783</v>
+      </c>
+      <c r="D389">
+        <v>160</v>
+      </c>
+      <c r="E389">
+        <v>495.6</v>
+      </c>
+      <c r="F389" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G389" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H389" t="s">
+        <v>25</v>
+      </c>
+      <c r="I389" t="s">
+        <v>26</v>
+      </c>
+      <c r="J389" t="s">
+        <v>153</v>
+      </c>
+      <c r="K389">
+        <v>4</v>
+      </c>
+      <c r="L389">
+        <v>2</v>
+      </c>
+      <c r="M389">
+        <v>0</v>
+      </c>
+      <c r="N389">
+        <v>8</v>
+      </c>
+      <c r="O389">
+        <v>1015</v>
+      </c>
+      <c r="P389">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A390" s="2">
+        <v>10.625</v>
+      </c>
+      <c r="B390" t="s">
+        <v>784</v>
+      </c>
+      <c r="C390" t="s">
+        <v>785</v>
+      </c>
+      <c r="D390">
+        <v>140</v>
+      </c>
+      <c r="E390">
+        <v>501.5</v>
+      </c>
+      <c r="F390" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="G390" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H390" t="s">
+        <v>25</v>
+      </c>
+      <c r="I390" t="s">
+        <v>26</v>
+      </c>
+      <c r="J390" t="s">
+        <v>153</v>
+      </c>
+      <c r="K390">
+        <v>5</v>
+      </c>
+      <c r="L390">
+        <v>4</v>
+      </c>
+      <c r="M390">
+        <v>1</v>
+      </c>
+      <c r="N390">
+        <v>8</v>
+      </c>
+      <c r="O390">
+        <v>1016</v>
+      </c>
+      <c r="P390">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A391" s="2">
+        <v>10.6666666666667</v>
+      </c>
+      <c r="B391" t="s">
+        <v>786</v>
+      </c>
+      <c r="C391" t="s">
+        <v>787</v>
+      </c>
+      <c r="D391">
+        <v>115</v>
+      </c>
+      <c r="E391">
+        <v>509.2</v>
+      </c>
+      <c r="F391" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="G391" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H391" t="s">
+        <v>25</v>
+      </c>
+      <c r="I391" t="s">
+        <v>26</v>
+      </c>
+      <c r="J391" t="s">
+        <v>162</v>
+      </c>
+      <c r="K391">
+        <v>5</v>
+      </c>
+      <c r="L391">
+        <v>3</v>
+      </c>
+      <c r="M391">
+        <v>1</v>
+      </c>
+      <c r="N391">
+        <v>8</v>
+      </c>
+      <c r="O391">
+        <v>1016</v>
+      </c>
+      <c r="P391">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A392" s="2">
+        <v>10.666666666666666</v>
+      </c>
+      <c r="B392" t="s">
+        <v>788</v>
+      </c>
+      <c r="C392" t="s">
+        <v>789</v>
+      </c>
+      <c r="D392">
+        <v>180</v>
+      </c>
+      <c r="E392">
+        <v>602.79999999999995</v>
+      </c>
+      <c r="F392" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="G392" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H392" t="s">
+        <v>77</v>
+      </c>
+      <c r="I392" t="s">
+        <v>26</v>
+      </c>
+      <c r="J392" t="s">
+        <v>102</v>
+      </c>
+      <c r="K392">
+        <v>3</v>
+      </c>
+      <c r="L392">
+        <v>2</v>
+      </c>
+      <c r="M392">
+        <v>1</v>
+      </c>
+      <c r="N392">
+        <v>8</v>
+      </c>
+      <c r="O392">
+        <v>1022</v>
+      </c>
+      <c r="P392">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A393" s="2">
+        <v>10.7083333333333</v>
+      </c>
+      <c r="B393" t="s">
+        <v>790</v>
+      </c>
+      <c r="C393" t="s">
+        <v>789</v>
+      </c>
+      <c r="D393">
+        <v>180</v>
+      </c>
+      <c r="E393">
+        <v>608.20000000000005</v>
+      </c>
+      <c r="F393" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G393" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H393" t="s">
+        <v>77</v>
+      </c>
+      <c r="I393" t="s">
+        <v>26</v>
+      </c>
+      <c r="J393" t="s">
+        <v>102</v>
+      </c>
+      <c r="K393">
+        <v>2</v>
+      </c>
+      <c r="L393">
+        <v>2</v>
+      </c>
+      <c r="M393">
+        <v>1</v>
+      </c>
+      <c r="N393">
+        <v>8</v>
+      </c>
+      <c r="O393">
+        <v>1021</v>
+      </c>
+      <c r="P393">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A394" s="2">
+        <v>10.75</v>
+      </c>
+      <c r="B394" t="s">
+        <v>791</v>
+      </c>
+      <c r="C394" t="s">
+        <v>792</v>
+      </c>
+      <c r="D394">
+        <v>180</v>
+      </c>
+      <c r="E394">
+        <v>613.1</v>
+      </c>
+      <c r="F394" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G394" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H394" t="s">
+        <v>77</v>
+      </c>
+      <c r="I394" t="s">
+        <v>26</v>
+      </c>
+      <c r="J394" t="s">
+        <v>102</v>
+      </c>
+      <c r="K394">
+        <v>3</v>
+      </c>
+      <c r="L394">
+        <v>2</v>
+      </c>
+      <c r="M394">
+        <v>1</v>
+      </c>
+      <c r="N394">
+        <v>8</v>
+      </c>
+      <c r="O394">
+        <v>1021</v>
+      </c>
+      <c r="P394">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A395" s="2">
+        <v>10.7916666666667</v>
+      </c>
+      <c r="B395" t="s">
+        <v>793</v>
+      </c>
+      <c r="C395" t="s">
+        <v>794</v>
+      </c>
+      <c r="D395">
+        <v>170</v>
+      </c>
+      <c r="E395">
+        <v>617.79999999999995</v>
+      </c>
+      <c r="F395" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="G395" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H395" t="s">
+        <v>77</v>
+      </c>
+      <c r="I395" t="s">
+        <v>26</v>
+      </c>
+      <c r="J395" t="s">
+        <v>99</v>
+      </c>
+      <c r="K395">
+        <v>3</v>
+      </c>
+      <c r="L395">
+        <v>2</v>
+      </c>
+      <c r="M395">
+        <v>0</v>
+      </c>
+      <c r="N395">
+        <v>8</v>
+      </c>
+      <c r="O395">
+        <v>1021</v>
+      </c>
+      <c r="P395">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A396" s="2">
+        <v>10.8333333333334</v>
+      </c>
+      <c r="B396" t="s">
+        <v>795</v>
+      </c>
+      <c r="C396" t="s">
+        <v>796</v>
+      </c>
+      <c r="D396">
+        <v>170</v>
+      </c>
+      <c r="E396">
+        <v>624</v>
+      </c>
+      <c r="F396" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="G396" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H396" t="s">
+        <v>77</v>
+      </c>
+      <c r="I396" t="s">
+        <v>26</v>
+      </c>
+      <c r="J396" t="s">
+        <v>99</v>
+      </c>
+      <c r="K396">
+        <v>3</v>
+      </c>
+      <c r="L396">
+        <v>2</v>
+      </c>
+      <c r="M396">
+        <v>1</v>
+      </c>
+      <c r="N396">
+        <v>8</v>
+      </c>
+      <c r="O396">
+        <v>1020</v>
+      </c>
+      <c r="P396">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A397" s="2">
+        <v>10.875000000000099</v>
+      </c>
+      <c r="B397" t="s">
+        <v>797</v>
+      </c>
+      <c r="C397" t="s">
+        <v>798</v>
+      </c>
+      <c r="D397">
+        <v>195</v>
+      </c>
+      <c r="E397">
+        <v>626.79999999999995</v>
+      </c>
+      <c r="F397" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="G397" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H397" t="s">
+        <v>77</v>
+      </c>
+      <c r="I397" t="s">
+        <v>26</v>
+      </c>
+      <c r="J397" t="s">
+        <v>99</v>
+      </c>
+      <c r="K397">
+        <v>3</v>
+      </c>
+      <c r="L397">
+        <v>2</v>
+      </c>
+      <c r="M397">
+        <v>1</v>
+      </c>
+      <c r="N397">
+        <v>8</v>
+      </c>
+      <c r="O397">
+        <v>1020</v>
+      </c>
+      <c r="P397">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="398" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A398" s="2">
+        <v>10.916666666666799</v>
+      </c>
+      <c r="B398" t="s">
+        <v>799</v>
+      </c>
+      <c r="C398" t="s">
+        <v>800</v>
+      </c>
+      <c r="D398">
+        <v>130</v>
+      </c>
+      <c r="E398">
+        <v>630.79999999999995</v>
+      </c>
+      <c r="F398" s="1">
+        <v>4</v>
+      </c>
+      <c r="G398" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H398" t="s">
+        <v>77</v>
+      </c>
+      <c r="I398" t="s">
+        <v>26</v>
+      </c>
+      <c r="J398" t="s">
+        <v>99</v>
+      </c>
+      <c r="K398">
+        <v>2</v>
+      </c>
+      <c r="L398">
+        <v>2</v>
+      </c>
+      <c r="M398">
+        <v>1</v>
+      </c>
+      <c r="N398">
+        <v>8</v>
+      </c>
+      <c r="O398">
+        <v>1020</v>
+      </c>
+      <c r="P398">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A399" s="2">
+        <v>10.958333333333499</v>
+      </c>
+      <c r="B399" t="s">
+        <v>801</v>
+      </c>
+      <c r="C399" t="s">
+        <v>802</v>
+      </c>
+      <c r="D399">
+        <v>140</v>
+      </c>
+      <c r="E399">
+        <v>635.9</v>
+      </c>
+      <c r="F399" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G399" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H399" t="s">
+        <v>77</v>
+      </c>
+      <c r="I399" t="s">
+        <v>26</v>
+      </c>
+      <c r="J399" t="s">
+        <v>589</v>
+      </c>
+      <c r="K399">
+        <v>3</v>
+      </c>
+      <c r="L399">
+        <v>2</v>
+      </c>
+      <c r="M399">
+        <v>1</v>
+      </c>
+      <c r="N399">
+        <v>8</v>
+      </c>
+      <c r="O399">
+        <v>1020</v>
+      </c>
+      <c r="P399">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A400" s="2">
+        <v>11.000000000000201</v>
+      </c>
+      <c r="B400" t="s">
+        <v>803</v>
+      </c>
+      <c r="C400" t="s">
+        <v>804</v>
+      </c>
+      <c r="D400">
+        <v>165</v>
+      </c>
+      <c r="E400">
+        <v>641.6</v>
+      </c>
+      <c r="F400" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G400" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H400" t="s">
+        <v>77</v>
+      </c>
+      <c r="I400" t="s">
+        <v>26</v>
+      </c>
+      <c r="J400" t="s">
+        <v>115</v>
+      </c>
+      <c r="K400">
+        <v>3</v>
+      </c>
+      <c r="L400">
+        <v>2</v>
+      </c>
+      <c r="M400">
+        <v>1</v>
+      </c>
+      <c r="N400">
+        <v>8</v>
+      </c>
+      <c r="O400">
+        <v>1020</v>
+      </c>
+      <c r="P400">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A401" s="2">
+        <v>11.041666666666901</v>
+      </c>
+      <c r="B401" t="s">
+        <v>805</v>
+      </c>
+      <c r="C401" t="s">
+        <v>806</v>
+      </c>
+      <c r="D401">
+        <v>140</v>
+      </c>
+      <c r="E401">
+        <v>647</v>
+      </c>
+      <c r="F401" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G401" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H401" t="s">
+        <v>77</v>
+      </c>
+      <c r="I401" t="s">
+        <v>26</v>
+      </c>
+      <c r="J401" t="s">
+        <v>586</v>
+      </c>
+      <c r="K401">
+        <v>3</v>
+      </c>
+      <c r="L401">
+        <v>2</v>
+      </c>
+      <c r="M401">
+        <v>0</v>
+      </c>
+      <c r="N401">
+        <v>8</v>
+      </c>
+      <c r="O401">
+        <v>1020</v>
+      </c>
+      <c r="P401">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A402" s="2">
+        <v>11.0833333333336</v>
+      </c>
+      <c r="B402" t="s">
+        <v>807</v>
+      </c>
+      <c r="C402" t="s">
+        <v>808</v>
+      </c>
+      <c r="D402">
+        <v>130</v>
+      </c>
+      <c r="E402">
+        <v>652.6</v>
+      </c>
+      <c r="F402" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G402" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H402" t="s">
+        <v>77</v>
+      </c>
+      <c r="I402" t="s">
+        <v>26</v>
+      </c>
+      <c r="J402" t="s">
+        <v>586</v>
+      </c>
+      <c r="K402">
+        <v>3</v>
+      </c>
+      <c r="L402">
+        <v>2</v>
+      </c>
+      <c r="M402">
+        <v>0</v>
+      </c>
+      <c r="N402">
+        <v>8</v>
+      </c>
+      <c r="O402">
+        <v>1020</v>
+      </c>
+      <c r="P402">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A403" s="2">
+        <v>11.1250000000003</v>
+      </c>
+      <c r="B403" t="s">
+        <v>809</v>
+      </c>
+      <c r="C403" t="s">
+        <v>810</v>
+      </c>
+      <c r="D403">
+        <v>130</v>
+      </c>
+      <c r="E403">
+        <v>657.4</v>
+      </c>
+      <c r="F403" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="G403" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H403" t="s">
+        <v>77</v>
+      </c>
+      <c r="I403" t="s">
+        <v>26</v>
+      </c>
+      <c r="J403" t="s">
+        <v>533</v>
+      </c>
+      <c r="K403">
+        <v>3</v>
+      </c>
+      <c r="L403">
+        <v>2</v>
+      </c>
+      <c r="M403">
+        <v>0</v>
+      </c>
+      <c r="N403">
+        <v>8</v>
+      </c>
+      <c r="O403">
+        <v>1020</v>
+      </c>
+      <c r="P403">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A404" s="2">
+        <v>11.166666666667</v>
+      </c>
+      <c r="B404" t="s">
+        <v>812</v>
+      </c>
+      <c r="C404" t="s">
+        <v>811</v>
+      </c>
+      <c r="D404">
+        <v>155</v>
+      </c>
+      <c r="E404">
+        <v>663.2</v>
+      </c>
+      <c r="F404" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G404" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H404" t="s">
+        <v>77</v>
+      </c>
+      <c r="I404" t="s">
+        <v>26</v>
+      </c>
+      <c r="J404" t="s">
+        <v>586</v>
+      </c>
+      <c r="K404">
+        <v>3</v>
+      </c>
+      <c r="L404">
+        <v>2</v>
+      </c>
+      <c r="M404">
+        <v>0</v>
+      </c>
+      <c r="N404">
+        <v>8</v>
+      </c>
+      <c r="O404">
+        <v>1020</v>
+      </c>
+      <c r="P404">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A405" s="2">
+        <v>11.2083333333337</v>
+      </c>
+      <c r="B405" t="s">
+        <v>813</v>
+      </c>
+      <c r="C405" t="s">
+        <v>814</v>
+      </c>
+      <c r="D405">
+        <v>170</v>
+      </c>
+      <c r="E405">
+        <v>668</v>
+      </c>
+      <c r="F405" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="G405" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H405" t="s">
+        <v>77</v>
+      </c>
+      <c r="I405" t="s">
+        <v>26</v>
+      </c>
+      <c r="J405" t="s">
+        <v>586</v>
+      </c>
+      <c r="K405">
+        <v>3</v>
+      </c>
+      <c r="L405">
+        <v>2</v>
+      </c>
+      <c r="M405">
+        <v>1</v>
+      </c>
+      <c r="N405">
+        <v>8</v>
+      </c>
+      <c r="O405">
+        <v>1020</v>
+      </c>
+      <c r="P405">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A406" s="2">
+        <v>11.2500000000004</v>
+      </c>
+      <c r="B406" t="s">
+        <v>815</v>
+      </c>
+      <c r="C406" t="s">
+        <v>816</v>
+      </c>
+      <c r="D406">
+        <v>180</v>
+      </c>
+      <c r="E406">
+        <v>671.8</v>
+      </c>
+      <c r="F406" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="G406" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H406" t="s">
+        <v>77</v>
+      </c>
+      <c r="I406" t="s">
+        <v>26</v>
+      </c>
+      <c r="J406" t="s">
+        <v>586</v>
+      </c>
+      <c r="K406">
+        <v>3</v>
+      </c>
+      <c r="L406">
+        <v>2</v>
+      </c>
+      <c r="M406">
+        <v>2</v>
+      </c>
+      <c r="N406">
+        <v>8</v>
+      </c>
+      <c r="O406">
+        <v>1020</v>
+      </c>
+      <c r="P406">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A407" s="2">
+        <v>11.2916666666671</v>
+      </c>
+      <c r="B407" t="s">
+        <v>817</v>
+      </c>
+      <c r="C407" t="s">
+        <v>818</v>
+      </c>
+      <c r="D407">
+        <v>180</v>
+      </c>
+      <c r="E407">
+        <v>676.3</v>
+      </c>
+      <c r="F407" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G407" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H407" t="s">
+        <v>77</v>
+      </c>
+      <c r="I407" t="s">
+        <v>26</v>
+      </c>
+      <c r="J407" t="s">
+        <v>241</v>
+      </c>
+      <c r="K407">
+        <v>4</v>
+      </c>
+      <c r="L407">
+        <v>2</v>
+      </c>
+      <c r="M407">
+        <v>1</v>
+      </c>
+      <c r="N407">
+        <v>8</v>
+      </c>
+      <c r="O407">
+        <v>1020</v>
+      </c>
+      <c r="P407">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A408" s="2">
+        <v>11.333333333333799</v>
+      </c>
+      <c r="B408" t="s">
+        <v>819</v>
+      </c>
+      <c r="C408" t="s">
+        <v>820</v>
+      </c>
+      <c r="D408">
+        <v>180</v>
+      </c>
+      <c r="E408">
+        <v>681.9</v>
+      </c>
+      <c r="F408" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G408" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H408" t="s">
+        <v>77</v>
+      </c>
+      <c r="I408" t="s">
+        <v>26</v>
+      </c>
+      <c r="J408" t="s">
+        <v>241</v>
+      </c>
+      <c r="K408">
+        <v>4</v>
+      </c>
+      <c r="L408">
+        <v>2</v>
+      </c>
+      <c r="M408">
+        <v>1</v>
+      </c>
+      <c r="N408">
+        <v>8</v>
+      </c>
+      <c r="O408">
+        <v>1017</v>
+      </c>
+      <c r="P408">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A409" s="2">
+        <v>11.375000000000499</v>
+      </c>
+      <c r="B409" t="s">
+        <v>822</v>
+      </c>
+      <c r="C409" t="s">
+        <v>823</v>
+      </c>
+      <c r="D409">
+        <v>145</v>
+      </c>
+      <c r="E409">
+        <v>687.6</v>
+      </c>
+      <c r="F409" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="G409" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H409" t="s">
+        <v>77</v>
+      </c>
+      <c r="I409" t="s">
+        <v>26</v>
+      </c>
+      <c r="J409" t="s">
+        <v>241</v>
+      </c>
+      <c r="K409">
+        <v>4</v>
+      </c>
+      <c r="L409">
+        <v>2</v>
+      </c>
+      <c r="M409">
+        <v>2</v>
+      </c>
+      <c r="N409">
+        <v>8</v>
+      </c>
+      <c r="O409">
+        <v>1017</v>
+      </c>
+      <c r="P409">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A410" s="2">
+        <v>11.416666666667201</v>
+      </c>
+      <c r="B410" t="s">
+        <v>111</v>
+      </c>
+      <c r="C410" t="s">
+        <v>821</v>
+      </c>
+      <c r="D410">
+        <v>135</v>
+      </c>
+      <c r="E410">
+        <v>693.1</v>
+      </c>
+      <c r="F410" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G410" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H410" t="s">
+        <v>77</v>
+      </c>
+      <c r="I410" t="s">
+        <v>26</v>
+      </c>
+      <c r="J410" t="s">
+        <v>241</v>
+      </c>
+      <c r="K410">
+        <v>4</v>
+      </c>
+      <c r="L410">
+        <v>2</v>
+      </c>
+      <c r="M410">
+        <v>1</v>
+      </c>
+      <c r="N410">
+        <v>8</v>
+      </c>
+      <c r="O410">
+        <v>1017</v>
+      </c>
+      <c r="P410">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A411" s="2">
+        <v>11.625</v>
+      </c>
+      <c r="B411" t="s">
+        <v>824</v>
+      </c>
+      <c r="C411" t="s">
+        <v>825</v>
+      </c>
+      <c r="D411">
+        <v>170</v>
+      </c>
+      <c r="E411">
+        <v>764.7</v>
+      </c>
+      <c r="F411" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="G411" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H411" t="s">
+        <v>135</v>
+      </c>
+      <c r="I411" t="s">
+        <v>26</v>
+      </c>
+      <c r="J411" t="s">
+        <v>247</v>
+      </c>
+      <c r="K411">
+        <v>4</v>
+      </c>
+      <c r="L411">
+        <v>1</v>
+      </c>
+      <c r="M411">
+        <v>1</v>
+      </c>
+      <c r="N411">
+        <v>8</v>
+      </c>
+      <c r="O411">
+        <v>1015</v>
+      </c>
+      <c r="P411">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A412" s="2">
+        <v>11.6666666666667</v>
+      </c>
+      <c r="B412" t="s">
+        <v>826</v>
+      </c>
+      <c r="C412" t="s">
+        <v>827</v>
+      </c>
+      <c r="D412">
+        <v>180</v>
+      </c>
+      <c r="E412">
+        <v>770.3</v>
+      </c>
+      <c r="F412" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G412" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H412" t="s">
+        <v>135</v>
+      </c>
+      <c r="I412" t="s">
+        <v>26</v>
+      </c>
+      <c r="J412" t="s">
+        <v>247</v>
+      </c>
+      <c r="K412">
+        <v>5</v>
+      </c>
+      <c r="L412">
+        <v>2</v>
+      </c>
+      <c r="M412">
+        <v>0</v>
+      </c>
+      <c r="N412">
+        <v>8</v>
+      </c>
+      <c r="O412">
+        <v>1015</v>
+      </c>
+      <c r="P412">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A413" s="2">
+        <v>11.7083333333334</v>
+      </c>
+      <c r="B413" t="s">
+        <v>421</v>
+      </c>
+      <c r="C413" t="s">
+        <v>828</v>
+      </c>
+      <c r="D413">
+        <v>180</v>
+      </c>
+      <c r="E413">
+        <v>776.8</v>
+      </c>
+      <c r="F413" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="G413" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H413" t="s">
+        <v>25</v>
+      </c>
+      <c r="I413" t="s">
+        <v>26</v>
+      </c>
+      <c r="J413" t="s">
+        <v>241</v>
+      </c>
+      <c r="K413">
+        <v>6</v>
+      </c>
+      <c r="L413">
+        <v>3</v>
+      </c>
+      <c r="M413">
+        <v>0</v>
+      </c>
+      <c r="N413">
+        <v>8</v>
+      </c>
+      <c r="O413">
+        <v>1015</v>
+      </c>
+      <c r="P413">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A414" s="2">
+        <v>11.750000000000099</v>
+      </c>
+      <c r="B414" t="s">
+        <v>829</v>
+      </c>
+      <c r="C414" t="s">
+        <v>830</v>
+      </c>
+      <c r="D414">
+        <v>140</v>
+      </c>
+      <c r="E414">
+        <v>782.6</v>
+      </c>
+      <c r="F414" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="G414" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H414" t="s">
+        <v>25</v>
+      </c>
+      <c r="I414" t="s">
+        <v>26</v>
+      </c>
+      <c r="J414" t="s">
+        <v>241</v>
+      </c>
+      <c r="K414">
+        <v>6</v>
+      </c>
+      <c r="L414">
+        <v>4</v>
+      </c>
+      <c r="M414">
+        <v>0</v>
+      </c>
+      <c r="N414">
+        <v>8</v>
+      </c>
+      <c r="O414">
+        <v>1015</v>
+      </c>
+      <c r="P414">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A415" s="2">
+        <v>11.791666666666799</v>
+      </c>
+      <c r="B415" t="s">
+        <v>831</v>
+      </c>
+      <c r="C415" t="s">
+        <v>832</v>
+      </c>
+      <c r="D415">
+        <v>140</v>
+      </c>
+      <c r="E415">
+        <v>788.2</v>
+      </c>
+      <c r="F415" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G415" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H415" t="s">
+        <v>25</v>
+      </c>
+      <c r="I415" t="s">
+        <v>26</v>
+      </c>
+      <c r="J415" t="s">
+        <v>241</v>
+      </c>
+      <c r="K415">
+        <v>5</v>
+      </c>
+      <c r="L415">
+        <v>4</v>
+      </c>
+      <c r="M415">
+        <v>0</v>
+      </c>
+      <c r="N415">
+        <v>8</v>
+      </c>
+      <c r="O415">
+        <v>1015</v>
+      </c>
+      <c r="P415">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A416" s="2">
+        <v>11.833333333333499</v>
+      </c>
+      <c r="B416" t="s">
+        <v>691</v>
+      </c>
+      <c r="C416" t="s">
+        <v>833</v>
+      </c>
+      <c r="D416">
+        <v>140</v>
+      </c>
+      <c r="E416">
+        <v>792.6</v>
+      </c>
+      <c r="F416" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G416" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H416" t="s">
+        <v>25</v>
+      </c>
+      <c r="I416" t="s">
+        <v>26</v>
+      </c>
+      <c r="J416" t="s">
+        <v>241</v>
+      </c>
+      <c r="K416">
+        <v>5</v>
+      </c>
+      <c r="L416">
+        <v>4</v>
+      </c>
+      <c r="M416">
+        <v>0</v>
+      </c>
+      <c r="N416">
+        <v>8</v>
+      </c>
+      <c r="O416">
+        <v>1015</v>
+      </c>
+      <c r="P416">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A417" s="2">
+        <v>11.875000000000201</v>
+      </c>
+      <c r="B417" t="s">
+        <v>627</v>
+      </c>
+      <c r="C417" t="s">
+        <v>834</v>
+      </c>
+      <c r="D417">
+        <v>130</v>
+      </c>
+      <c r="E417">
+        <v>796.6</v>
+      </c>
+      <c r="F417" s="1">
+        <v>4</v>
+      </c>
+      <c r="G417" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H417" t="s">
+        <v>25</v>
+      </c>
+      <c r="I417" t="s">
+        <v>26</v>
+      </c>
+      <c r="J417" t="s">
+        <v>241</v>
+      </c>
+      <c r="K417">
+        <v>5</v>
+      </c>
+      <c r="L417">
+        <v>4</v>
+      </c>
+      <c r="M417">
+        <v>0</v>
+      </c>
+      <c r="N417">
+        <v>8</v>
+      </c>
+      <c r="O417">
+        <v>1015</v>
+      </c>
+      <c r="P417">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A418" s="2">
+        <v>11.916666666666901</v>
+      </c>
+      <c r="B418" t="s">
+        <v>50</v>
+      </c>
+      <c r="C418" t="s">
+        <v>835</v>
+      </c>
+      <c r="D418">
+        <v>130</v>
+      </c>
+      <c r="E418">
+        <v>801.8</v>
+      </c>
+      <c r="F418" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="G418" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H418" t="s">
+        <v>25</v>
+      </c>
+      <c r="I418" t="s">
+        <v>26</v>
+      </c>
+      <c r="J418" t="s">
+        <v>241</v>
+      </c>
+      <c r="K418">
+        <v>5</v>
+      </c>
+      <c r="L418">
+        <v>4</v>
+      </c>
+      <c r="M418">
+        <v>0</v>
+      </c>
+      <c r="N418">
+        <v>8</v>
+      </c>
+      <c r="O418">
+        <v>1015</v>
+      </c>
+      <c r="P418">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A419" s="2">
+        <v>11.9583333333336</v>
+      </c>
+      <c r="B419" t="s">
+        <v>836</v>
+      </c>
+      <c r="C419" t="s">
+        <v>837</v>
+      </c>
+      <c r="D419">
+        <v>125</v>
+      </c>
+      <c r="E419">
+        <v>807.3</v>
+      </c>
+      <c r="F419" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="G419" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H419" t="s">
+        <v>25</v>
+      </c>
+      <c r="I419" t="s">
+        <v>26</v>
+      </c>
+      <c r="J419" t="s">
+        <v>241</v>
+      </c>
+      <c r="K419">
+        <v>5</v>
+      </c>
+      <c r="L419">
+        <v>4</v>
+      </c>
+      <c r="M419">
+        <v>0</v>
+      </c>
+      <c r="N419">
+        <v>8</v>
+      </c>
+      <c r="O419">
+        <v>1015</v>
+      </c>
+      <c r="P419">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A420" s="2">
+        <v>12.0000000000003</v>
+      </c>
+      <c r="B420" t="s">
+        <v>534</v>
+      </c>
+      <c r="C420" t="s">
+        <v>838</v>
+      </c>
+      <c r="D420">
+        <v>210</v>
+      </c>
+      <c r="E420">
+        <v>813.3</v>
+      </c>
+      <c r="F420" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G420" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H420" t="s">
+        <v>25</v>
+      </c>
+      <c r="I420" t="s">
+        <v>26</v>
+      </c>
+      <c r="J420" t="s">
+        <v>533</v>
+      </c>
+      <c r="K420">
+        <v>4</v>
+      </c>
+      <c r="L420">
+        <v>4</v>
+      </c>
+      <c r="M420">
+        <v>0</v>
+      </c>
+      <c r="N420">
+        <v>8</v>
+      </c>
+      <c r="O420">
+        <v>1016</v>
+      </c>
+      <c r="P420">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A421" s="2">
+        <v>12.041666666667</v>
+      </c>
+      <c r="B421" t="s">
+        <v>839</v>
+      </c>
+      <c r="C421" t="s">
+        <v>840</v>
+      </c>
+      <c r="D421">
+        <v>135</v>
+      </c>
+      <c r="E421">
+        <v>817.8</v>
+      </c>
+      <c r="F421" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G421" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H421" t="s">
+        <v>25</v>
+      </c>
+      <c r="I421" t="s">
+        <v>26</v>
+      </c>
+      <c r="J421" t="s">
+        <v>241</v>
+      </c>
+      <c r="K421">
+        <v>4</v>
+      </c>
+      <c r="L421">
+        <v>4</v>
+      </c>
+      <c r="M421">
+        <v>0</v>
+      </c>
+      <c r="N421">
+        <v>8</v>
+      </c>
+      <c r="O421">
+        <v>1016</v>
+      </c>
+      <c r="P421">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A422" s="2">
+        <v>12.0833333333337</v>
+      </c>
+      <c r="B422" t="s">
+        <v>841</v>
+      </c>
+      <c r="C422" t="s">
+        <v>842</v>
+      </c>
+      <c r="D422">
+        <v>135</v>
+      </c>
+      <c r="E422">
+        <v>821.8</v>
+      </c>
+      <c r="F422" s="1">
+        <v>4</v>
+      </c>
+      <c r="G422" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H422" t="s">
+        <v>25</v>
+      </c>
+      <c r="I422" t="s">
+        <v>26</v>
+      </c>
+      <c r="J422" t="s">
+        <v>241</v>
+      </c>
+      <c r="K422">
+        <v>4</v>
+      </c>
+      <c r="L422">
+        <v>4</v>
+      </c>
+      <c r="M422">
+        <v>0</v>
+      </c>
+      <c r="N422">
+        <v>8</v>
+      </c>
+      <c r="O422">
+        <v>1016</v>
+      </c>
+      <c r="P422">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A423" s="2">
+        <v>12.1250000000004</v>
+      </c>
+      <c r="B423" t="s">
+        <v>843</v>
+      </c>
+      <c r="C423" t="s">
+        <v>844</v>
+      </c>
+      <c r="D423">
+        <v>140</v>
+      </c>
+      <c r="E423">
+        <v>826.3</v>
+      </c>
+      <c r="F423" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G423" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H423" t="s">
+        <v>135</v>
+      </c>
+      <c r="I423" t="s">
+        <v>26</v>
+      </c>
+      <c r="J423" t="s">
+        <v>241</v>
+      </c>
+      <c r="K423">
+        <v>5</v>
+      </c>
+      <c r="L423">
+        <v>3</v>
+      </c>
+      <c r="M423">
+        <v>0</v>
+      </c>
+      <c r="N423">
+        <v>8</v>
+      </c>
+      <c r="O423">
+        <v>1016</v>
+      </c>
+      <c r="P423">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A424" s="2">
+        <v>12.1666666666671</v>
+      </c>
+      <c r="B424" t="s">
+        <v>845</v>
+      </c>
+      <c r="C424" t="s">
+        <v>846</v>
+      </c>
+      <c r="D424">
+        <v>40</v>
+      </c>
+      <c r="E424">
+        <v>830.9</v>
+      </c>
+      <c r="F424" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G424" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H424" t="s">
+        <v>135</v>
+      </c>
+      <c r="I424" t="s">
+        <v>26</v>
+      </c>
+      <c r="J424" t="s">
+        <v>533</v>
+      </c>
+      <c r="K424">
+        <v>3</v>
+      </c>
+      <c r="L424">
+        <v>3</v>
+      </c>
+      <c r="M424">
+        <v>0</v>
+      </c>
+      <c r="N424">
+        <v>8</v>
+      </c>
+      <c r="O424">
+        <v>1016</v>
+      </c>
+      <c r="P424">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A425" s="2">
+        <v>12.208333333333799</v>
+      </c>
+      <c r="B425" t="s">
+        <v>847</v>
+      </c>
+      <c r="C425" t="s">
+        <v>848</v>
+      </c>
+      <c r="D425">
+        <v>40</v>
+      </c>
+      <c r="E425">
+        <v>835.4</v>
+      </c>
+      <c r="F425" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G425" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H425" t="s">
+        <v>135</v>
+      </c>
+      <c r="I425" t="s">
+        <v>26</v>
+      </c>
+      <c r="J425" t="s">
+        <v>241</v>
+      </c>
+      <c r="K425">
+        <v>5</v>
+      </c>
+      <c r="L425">
+        <v>3</v>
+      </c>
+      <c r="M425">
+        <v>0</v>
+      </c>
+      <c r="N425">
+        <v>8</v>
+      </c>
+      <c r="O425">
+        <v>1016</v>
+      </c>
+      <c r="P425">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A426" s="2">
+        <v>12.250000000000499</v>
+      </c>
+      <c r="B426" t="s">
+        <v>849</v>
+      </c>
+      <c r="C426" t="s">
+        <v>850</v>
+      </c>
+      <c r="D426">
+        <v>150</v>
+      </c>
+      <c r="E426">
+        <v>840.7</v>
+      </c>
+      <c r="F426" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="G426" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H426" t="s">
+        <v>135</v>
+      </c>
+      <c r="I426" t="s">
+        <v>26</v>
+      </c>
+      <c r="J426" t="s">
+        <v>241</v>
+      </c>
+      <c r="K426">
+        <v>5</v>
+      </c>
+      <c r="L426">
+        <v>3</v>
+      </c>
+      <c r="M426">
+        <v>1</v>
+      </c>
+      <c r="N426">
+        <v>8</v>
+      </c>
+      <c r="O426">
+        <v>1016</v>
+      </c>
+      <c r="P426">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A427" s="2">
+        <v>12.291666666667201</v>
+      </c>
+      <c r="B427" t="s">
+        <v>851</v>
+      </c>
+      <c r="C427" t="s">
+        <v>852</v>
+      </c>
+      <c r="D427">
+        <v>150</v>
+      </c>
+      <c r="E427">
+        <v>847</v>
+      </c>
+      <c r="F427" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="G427" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H427" t="s">
+        <v>135</v>
+      </c>
+      <c r="I427" t="s">
+        <v>26</v>
+      </c>
+      <c r="J427" t="s">
+        <v>241</v>
+      </c>
+      <c r="K427">
+        <v>5</v>
+      </c>
+      <c r="L427">
+        <v>3</v>
+      </c>
+      <c r="M427">
+        <v>1</v>
+      </c>
+      <c r="N427">
+        <v>8</v>
+      </c>
+      <c r="O427">
+        <v>1016</v>
+      </c>
+      <c r="P427">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A428" s="2">
+        <v>12.333333333333901</v>
+      </c>
+      <c r="B428" t="s">
+        <v>853</v>
+      </c>
+      <c r="C428" t="s">
+        <v>854</v>
+      </c>
+      <c r="D428">
+        <v>150</v>
+      </c>
+      <c r="E428">
+        <v>853.6</v>
+      </c>
+      <c r="F428" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="G428" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H428" t="s">
+        <v>135</v>
+      </c>
+      <c r="I428" t="s">
+        <v>26</v>
+      </c>
+      <c r="J428" t="s">
+        <v>241</v>
+      </c>
+      <c r="K428">
+        <v>5</v>
+      </c>
+      <c r="L428">
+        <v>3</v>
+      </c>
+      <c r="M428">
+        <v>1</v>
+      </c>
+      <c r="N428">
+        <v>8</v>
+      </c>
+      <c r="O428">
+        <v>1016</v>
+      </c>
+      <c r="P428">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A429" s="2">
+        <v>12.3750000000006</v>
+      </c>
+      <c r="B429" t="s">
+        <v>855</v>
+      </c>
+      <c r="C429" t="s">
+        <v>856</v>
+      </c>
+      <c r="D429">
+        <v>135</v>
+      </c>
+      <c r="E429">
+        <v>859.8</v>
+      </c>
+      <c r="F429" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G429" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H429" t="s">
+        <v>135</v>
+      </c>
+      <c r="I429" t="s">
+        <v>26</v>
+      </c>
+      <c r="J429" t="s">
+        <v>241</v>
+      </c>
+      <c r="K429">
+        <v>5</v>
+      </c>
+      <c r="L429">
+        <v>3</v>
+      </c>
+      <c r="M429">
+        <v>1</v>
+      </c>
+      <c r="N429">
+        <v>8</v>
+      </c>
+      <c r="O429">
+        <v>1016</v>
+      </c>
+      <c r="P429">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A430" s="2">
+        <v>12.4166666666673</v>
+      </c>
+      <c r="B430" t="s">
+        <v>440</v>
+      </c>
+      <c r="C430" t="s">
+        <v>857</v>
+      </c>
+      <c r="D430">
+        <v>160</v>
+      </c>
+      <c r="E430">
+        <v>868.2</v>
+      </c>
+      <c r="F430" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G430" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H430" t="s">
+        <v>135</v>
+      </c>
+      <c r="I430" t="s">
+        <v>26</v>
+      </c>
+      <c r="J430" t="s">
+        <v>241</v>
+      </c>
+      <c r="K430">
+        <v>5</v>
+      </c>
+      <c r="L430">
+        <v>3</v>
+      </c>
+      <c r="M430">
+        <v>1</v>
+      </c>
+      <c r="N430">
+        <v>8</v>
+      </c>
+      <c r="O430">
+        <v>1016</v>
+      </c>
+      <c r="P430">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A431" s="2">
+        <v>12.458333333334</v>
+      </c>
+      <c r="B431" t="s">
+        <v>858</v>
+      </c>
+      <c r="C431" t="s">
+        <v>859</v>
+      </c>
+      <c r="D431">
+        <v>150</v>
+      </c>
+      <c r="E431">
+        <v>876.2</v>
+      </c>
+      <c r="F431" s="1">
+        <v>8</v>
+      </c>
+      <c r="G431" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H431" t="s">
+        <v>135</v>
+      </c>
+      <c r="I431" t="s">
+        <v>26</v>
+      </c>
+      <c r="J431" t="s">
+        <v>533</v>
+      </c>
+      <c r="K431">
+        <v>5</v>
+      </c>
+      <c r="L431">
+        <v>3</v>
+      </c>
+      <c r="M431">
+        <v>1</v>
+      </c>
+      <c r="N431">
+        <v>8</v>
+      </c>
+      <c r="O431">
+        <v>1018</v>
+      </c>
+      <c r="P431">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A432" s="2">
+        <v>12.5000000000007</v>
+      </c>
+      <c r="B432" t="s">
+        <v>449</v>
+      </c>
+      <c r="C432" t="s">
+        <v>860</v>
+      </c>
+      <c r="D432">
+        <v>150</v>
+      </c>
+      <c r="E432">
+        <v>883.3</v>
+      </c>
+      <c r="F432" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="G432" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H432" t="s">
+        <v>135</v>
+      </c>
+      <c r="I432" t="s">
+        <v>26</v>
+      </c>
+      <c r="J432" t="s">
+        <v>533</v>
+      </c>
+      <c r="K432">
+        <v>4</v>
+      </c>
+      <c r="L432">
+        <v>3</v>
+      </c>
+      <c r="M432">
+        <v>1</v>
+      </c>
+      <c r="N432">
+        <v>8</v>
+      </c>
+      <c r="O432">
+        <v>1018</v>
+      </c>
+      <c r="P432">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:C1"/>

--- a/Dziennik2024.xlsx
+++ b/Dziennik2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szybk\OneDrive\Pulpit\Studia\inzynierka\Inzynierka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C3D542-4730-45F4-92CE-6AE8064F8D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E08EDC-8887-44D1-A629-5CACB478CCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BF3D5F66-ACDF-49A3-8594-396AB682FC7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="854">
   <si>
     <t>silnik</t>
   </si>
@@ -486,9 +486,6 @@
   </si>
   <si>
     <t>57*23,5N</t>
-  </si>
-  <si>
-    <t>G87 + F60</t>
   </si>
   <si>
     <t>57*39,7N</t>
@@ -3006,7 +3003,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -3033,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="J1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="K1" t="s">
         <v>6</v>
@@ -6227,7 +6224,7 @@
         <v>63</v>
       </c>
       <c r="H65" t="s">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="I65" t="s">
         <v>19</v>
@@ -6259,10 +6256,10 @@
         <v>1.2083333333333499</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C66" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D66">
         <v>10</v>
@@ -6277,13 +6274,13 @@
         <v>63</v>
       </c>
       <c r="H66" t="s">
+        <v>152</v>
+      </c>
+      <c r="I66" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" t="s">
         <v>153</v>
-      </c>
-      <c r="I66" t="s">
-        <v>19</v>
-      </c>
-      <c r="J66" t="s">
-        <v>154</v>
       </c>
       <c r="K66">
         <v>5</v>
@@ -6309,10 +6306,10 @@
         <v>1.25000000000002</v>
       </c>
       <c r="B67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C67" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D67">
         <v>12</v>
@@ -6359,7 +6356,7 @@
         <v>1.2916666666666901</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C68" t="s">
         <v>131</v>
@@ -6409,7 +6406,7 @@
         <v>1.3333333333333599</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C69" t="s">
         <v>122</v>
@@ -6459,10 +6456,10 @@
         <v>1.37500000000003</v>
       </c>
       <c r="B70" t="s">
+        <v>158</v>
+      </c>
+      <c r="C70" t="s">
         <v>159</v>
-      </c>
-      <c r="C70" t="s">
-        <v>160</v>
       </c>
       <c r="D70">
         <v>20</v>
@@ -6509,10 +6506,10 @@
         <v>1.4166666666667</v>
       </c>
       <c r="B71" t="s">
+        <v>160</v>
+      </c>
+      <c r="C71" t="s">
         <v>161</v>
-      </c>
-      <c r="C71" t="s">
-        <v>162</v>
       </c>
       <c r="D71">
         <v>15</v>
@@ -6559,10 +6556,10 @@
         <v>1.4583333333333699</v>
       </c>
       <c r="B72" t="s">
+        <v>162</v>
+      </c>
+      <c r="C72" t="s">
         <v>163</v>
-      </c>
-      <c r="C72" t="s">
-        <v>164</v>
       </c>
       <c r="D72">
         <v>10</v>
@@ -6609,10 +6606,10 @@
         <v>1.50000000000004</v>
       </c>
       <c r="B73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C73" t="s">
         <v>165</v>
-      </c>
-      <c r="C73" t="s">
-        <v>166</v>
       </c>
       <c r="D73">
         <v>43</v>
@@ -6659,10 +6656,10 @@
         <v>1.54166666666671</v>
       </c>
       <c r="B74" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" t="s">
         <v>167</v>
-      </c>
-      <c r="C74" t="s">
-        <v>168</v>
       </c>
       <c r="D74">
         <v>16</v>
@@ -6709,10 +6706,10 @@
         <v>1.5833333333333801</v>
       </c>
       <c r="B75" t="s">
+        <v>168</v>
+      </c>
+      <c r="C75" t="s">
         <v>169</v>
-      </c>
-      <c r="C75" t="s">
-        <v>170</v>
       </c>
       <c r="D75">
         <v>30</v>
@@ -6759,10 +6756,10 @@
         <v>1.62500000000005</v>
       </c>
       <c r="B76" t="s">
+        <v>170</v>
+      </c>
+      <c r="C76" t="s">
         <v>171</v>
-      </c>
-      <c r="C76" t="s">
-        <v>172</v>
       </c>
       <c r="D76">
         <v>30</v>
@@ -6809,10 +6806,10 @@
         <v>1.66666666666672</v>
       </c>
       <c r="B77" t="s">
+        <v>172</v>
+      </c>
+      <c r="C77" t="s">
         <v>173</v>
-      </c>
-      <c r="C77" t="s">
-        <v>174</v>
       </c>
       <c r="D77">
         <v>25</v>
@@ -6859,10 +6856,10 @@
         <v>1.7083333333333901</v>
       </c>
       <c r="B78" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" t="s">
         <v>177</v>
-      </c>
-      <c r="C78" t="s">
-        <v>178</v>
       </c>
       <c r="D78">
         <v>25</v>
@@ -6909,10 +6906,10 @@
         <v>1.75000000000006</v>
       </c>
       <c r="B79" t="s">
+        <v>174</v>
+      </c>
+      <c r="C79" t="s">
         <v>175</v>
-      </c>
-      <c r="C79" t="s">
-        <v>176</v>
       </c>
       <c r="D79">
         <v>54</v>
@@ -6959,10 +6956,10 @@
         <v>1.79166666666673</v>
       </c>
       <c r="B80" t="s">
+        <v>178</v>
+      </c>
+      <c r="C80" t="s">
         <v>179</v>
-      </c>
-      <c r="C80" t="s">
-        <v>180</v>
       </c>
       <c r="D80">
         <v>54</v>
@@ -6983,7 +6980,7 @@
         <v>19</v>
       </c>
       <c r="J80" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K80">
         <v>2</v>
@@ -7009,10 +7006,10 @@
         <v>1.8333333333334001</v>
       </c>
       <c r="B81" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" t="s">
         <v>181</v>
-      </c>
-      <c r="C81" t="s">
-        <v>182</v>
       </c>
       <c r="D81">
         <v>54</v>
@@ -7033,7 +7030,7 @@
         <v>19</v>
       </c>
       <c r="J81" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K81">
         <v>2</v>
@@ -7059,10 +7056,10 @@
         <v>1.8750000000000699</v>
       </c>
       <c r="B82" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" t="s">
         <v>183</v>
-      </c>
-      <c r="C82" t="s">
-        <v>184</v>
       </c>
       <c r="D82">
         <v>80</v>
@@ -7109,10 +7106,10 @@
         <v>1.91666666666674</v>
       </c>
       <c r="B83" t="s">
+        <v>184</v>
+      </c>
+      <c r="C83" t="s">
         <v>185</v>
-      </c>
-      <c r="C83" t="s">
-        <v>186</v>
       </c>
       <c r="D83">
         <v>80</v>
@@ -7159,10 +7156,10 @@
         <v>1.9583333333334101</v>
       </c>
       <c r="B84" t="s">
+        <v>186</v>
+      </c>
+      <c r="C84" t="s">
         <v>187</v>
-      </c>
-      <c r="C84" t="s">
-        <v>188</v>
       </c>
       <c r="D84">
         <v>80</v>
@@ -7209,10 +7206,10 @@
         <v>2.0000000000000799</v>
       </c>
       <c r="B85" t="s">
+        <v>188</v>
+      </c>
+      <c r="C85" t="s">
         <v>189</v>
-      </c>
-      <c r="C85" t="s">
-        <v>190</v>
       </c>
       <c r="D85">
         <v>73</v>
@@ -7259,10 +7256,10 @@
         <v>2.04166666666675</v>
       </c>
       <c r="B86" t="s">
+        <v>190</v>
+      </c>
+      <c r="C86" t="s">
         <v>191</v>
-      </c>
-      <c r="C86" t="s">
-        <v>192</v>
       </c>
       <c r="D86">
         <v>71</v>
@@ -7283,7 +7280,7 @@
         <v>19</v>
       </c>
       <c r="J86" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K86">
         <v>6</v>
@@ -7309,10 +7306,10 @@
         <v>2.0833333333334201</v>
       </c>
       <c r="B87" t="s">
+        <v>192</v>
+      </c>
+      <c r="C87" t="s">
         <v>193</v>
-      </c>
-      <c r="C87" t="s">
-        <v>194</v>
       </c>
       <c r="D87">
         <v>70</v>
@@ -7333,7 +7330,7 @@
         <v>19</v>
       </c>
       <c r="J87" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K87">
         <v>6</v>
@@ -7359,10 +7356,10 @@
         <v>2.1250000000000902</v>
       </c>
       <c r="B88" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" t="s">
         <v>195</v>
-      </c>
-      <c r="C88" t="s">
-        <v>196</v>
       </c>
       <c r="D88">
         <v>70</v>
@@ -7383,7 +7380,7 @@
         <v>19</v>
       </c>
       <c r="J88" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K88">
         <v>5</v>
@@ -7409,10 +7406,10 @@
         <v>2.1666666666667602</v>
       </c>
       <c r="B89" t="s">
+        <v>197</v>
+      </c>
+      <c r="C89" t="s">
         <v>198</v>
-      </c>
-      <c r="C89" t="s">
-        <v>199</v>
       </c>
       <c r="D89">
         <v>100</v>
@@ -7433,7 +7430,7 @@
         <v>19</v>
       </c>
       <c r="J89" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K89">
         <v>5</v>
@@ -7459,10 +7456,10 @@
         <v>2.2083333333334298</v>
       </c>
       <c r="B90" t="s">
+        <v>199</v>
+      </c>
+      <c r="C90" t="s">
         <v>200</v>
-      </c>
-      <c r="C90" t="s">
-        <v>201</v>
       </c>
       <c r="D90">
         <v>340</v>
@@ -7483,7 +7480,7 @@
         <v>19</v>
       </c>
       <c r="J90" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K90">
         <v>4</v>
@@ -7509,10 +7506,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="B91" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C91" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D91">
         <v>30</v>
@@ -7533,7 +7530,7 @@
         <v>19</v>
       </c>
       <c r="J91" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K91">
         <v>3</v>
@@ -7559,10 +7556,10 @@
         <v>0.875</v>
       </c>
       <c r="B92" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C92" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D92">
         <v>20</v>
@@ -7609,10 +7606,10 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="B93" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C93" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D93">
         <v>18</v>
@@ -7659,10 +7656,10 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="B94" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C94" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D94">
         <v>23</v>
@@ -7683,7 +7680,7 @@
         <v>19</v>
       </c>
       <c r="J94" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K94">
         <v>4</v>
@@ -7709,10 +7706,10 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="B95" t="s">
+        <v>209</v>
+      </c>
+      <c r="C95" t="s">
         <v>210</v>
-      </c>
-      <c r="C95" t="s">
-        <v>211</v>
       </c>
       <c r="D95">
         <v>145</v>
@@ -7759,10 +7756,10 @@
         <v>0.33333333333333298</v>
       </c>
       <c r="B96" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" t="s">
         <v>212</v>
-      </c>
-      <c r="C96" t="s">
-        <v>213</v>
       </c>
       <c r="D96">
         <v>134</v>
@@ -7809,10 +7806,10 @@
         <v>0.375</v>
       </c>
       <c r="B97" t="s">
+        <v>213</v>
+      </c>
+      <c r="C97" t="s">
         <v>214</v>
-      </c>
-      <c r="C97" t="s">
-        <v>215</v>
       </c>
       <c r="D97">
         <v>140</v>
@@ -7859,10 +7856,10 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B98" t="s">
+        <v>215</v>
+      </c>
+      <c r="C98" t="s">
         <v>216</v>
-      </c>
-      <c r="C98" t="s">
-        <v>217</v>
       </c>
       <c r="D98">
         <v>140</v>
@@ -7909,10 +7906,10 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B99" t="s">
+        <v>217</v>
+      </c>
+      <c r="C99" t="s">
         <v>218</v>
-      </c>
-      <c r="C99" t="s">
-        <v>219</v>
       </c>
       <c r="D99">
         <v>140</v>
@@ -7933,7 +7930,7 @@
         <v>19</v>
       </c>
       <c r="J99" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K99">
         <v>3</v>
@@ -7959,10 +7956,10 @@
         <v>0.500000000000001</v>
       </c>
       <c r="B100" t="s">
+        <v>219</v>
+      </c>
+      <c r="C100" t="s">
         <v>220</v>
-      </c>
-      <c r="C100" t="s">
-        <v>221</v>
       </c>
       <c r="D100">
         <v>140</v>
@@ -8009,10 +8006,10 @@
         <v>0.54166666666666796</v>
       </c>
       <c r="B101" t="s">
+        <v>221</v>
+      </c>
+      <c r="C101" t="s">
         <v>222</v>
-      </c>
-      <c r="C101" t="s">
-        <v>223</v>
       </c>
       <c r="D101">
         <v>148</v>
@@ -8059,10 +8056,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="B102" t="s">
+        <v>223</v>
+      </c>
+      <c r="C102" t="s">
         <v>224</v>
-      </c>
-      <c r="C102" t="s">
-        <v>225</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -8109,10 +8106,10 @@
         <v>0.375</v>
       </c>
       <c r="B103" t="s">
+        <v>225</v>
+      </c>
+      <c r="C103" t="s">
         <v>226</v>
-      </c>
-      <c r="C103" t="s">
-        <v>227</v>
       </c>
       <c r="D103">
         <v>270</v>
@@ -8159,10 +8156,10 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B104" t="s">
+        <v>227</v>
+      </c>
+      <c r="C104" t="s">
         <v>228</v>
-      </c>
-      <c r="C104" t="s">
-        <v>229</v>
       </c>
       <c r="D104">
         <v>185</v>
@@ -8177,7 +8174,7 @@
         <v>63</v>
       </c>
       <c r="H104" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I104">
         <v>1200</v>
@@ -8209,10 +8206,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="B105" t="s">
+        <v>230</v>
+      </c>
+      <c r="C105" t="s">
         <v>231</v>
-      </c>
-      <c r="C105" t="s">
-        <v>232</v>
       </c>
       <c r="D105">
         <v>320</v>
@@ -8227,13 +8224,13 @@
         <v>63</v>
       </c>
       <c r="H105" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I105" t="s">
         <v>19</v>
       </c>
       <c r="J105" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K105">
         <v>4</v>
@@ -8259,10 +8256,10 @@
         <v>0.875</v>
       </c>
       <c r="B106" t="s">
+        <v>233</v>
+      </c>
+      <c r="C106" t="s">
         <v>234</v>
-      </c>
-      <c r="C106" t="s">
-        <v>235</v>
       </c>
       <c r="D106">
         <v>281</v>
@@ -8277,13 +8274,13 @@
         <v>63</v>
       </c>
       <c r="H106" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I106" t="s">
         <v>19</v>
       </c>
       <c r="J106" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K106">
         <v>4</v>
@@ -8309,10 +8306,10 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="B107" t="s">
+        <v>235</v>
+      </c>
+      <c r="C107" t="s">
         <v>236</v>
-      </c>
-      <c r="C107" t="s">
-        <v>237</v>
       </c>
       <c r="D107">
         <v>267</v>
@@ -8327,13 +8324,13 @@
         <v>63</v>
       </c>
       <c r="H107" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I107" t="s">
         <v>19</v>
       </c>
       <c r="J107" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K107">
         <v>4</v>
@@ -8359,10 +8356,10 @@
         <v>0.95833333333333404</v>
       </c>
       <c r="B108" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C108" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D108">
         <v>265</v>
@@ -8377,13 +8374,13 @@
         <v>63</v>
       </c>
       <c r="H108" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I108" t="s">
         <v>19</v>
       </c>
       <c r="J108" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K108">
         <v>4</v>
@@ -8409,10 +8406,10 @@
         <v>1</v>
       </c>
       <c r="B109" t="s">
+        <v>239</v>
+      </c>
+      <c r="C109" t="s">
         <v>240</v>
-      </c>
-      <c r="C109" t="s">
-        <v>241</v>
       </c>
       <c r="D109">
         <v>250</v>
@@ -8427,13 +8424,13 @@
         <v>63</v>
       </c>
       <c r="H109" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I109" t="s">
         <v>19</v>
       </c>
       <c r="J109" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K109">
         <v>4</v>
@@ -8459,10 +8456,10 @@
         <v>1.0416666666666701</v>
       </c>
       <c r="B110" t="s">
+        <v>241</v>
+      </c>
+      <c r="C110" t="s">
         <v>242</v>
-      </c>
-      <c r="C110" t="s">
-        <v>243</v>
       </c>
       <c r="D110">
         <v>166</v>
@@ -8483,7 +8480,7 @@
         <v>19</v>
       </c>
       <c r="J110" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K110">
         <v>4</v>
@@ -8509,10 +8506,10 @@
         <v>1.0833333333333399</v>
       </c>
       <c r="B111" t="s">
+        <v>243</v>
+      </c>
+      <c r="C111" t="s">
         <v>244</v>
-      </c>
-      <c r="C111" t="s">
-        <v>245</v>
       </c>
       <c r="D111">
         <v>177</v>
@@ -8533,7 +8530,7 @@
         <v>19</v>
       </c>
       <c r="J111" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K111">
         <v>4</v>
@@ -8559,10 +8556,10 @@
         <v>1.75</v>
       </c>
       <c r="B112" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C112" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D112">
         <v>260</v>
@@ -8577,7 +8574,7 @@
         <v>63</v>
       </c>
       <c r="H112" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I112" t="s">
         <v>19</v>
@@ -8609,10 +8606,10 @@
         <v>1.7916666666666701</v>
       </c>
       <c r="B113" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C113" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D113">
         <v>220</v>
@@ -8627,7 +8624,7 @@
         <v>63</v>
       </c>
       <c r="H113" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I113" t="s">
         <v>19</v>
@@ -8659,10 +8656,10 @@
         <v>1.8333333333333399</v>
       </c>
       <c r="B114" t="s">
+        <v>248</v>
+      </c>
+      <c r="C114" t="s">
         <v>249</v>
-      </c>
-      <c r="C114" t="s">
-        <v>250</v>
       </c>
       <c r="D114">
         <v>235</v>
@@ -8677,7 +8674,7 @@
         <v>63</v>
       </c>
       <c r="H114" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I114" t="s">
         <v>19</v>
@@ -8709,10 +8706,10 @@
         <v>1.87500000000001</v>
       </c>
       <c r="B115" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C115" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D115">
         <v>235</v>
@@ -8727,7 +8724,7 @@
         <v>63</v>
       </c>
       <c r="H115" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I115" t="s">
         <v>19</v>
@@ -8759,10 +8756,10 @@
         <v>1.9166666666666801</v>
       </c>
       <c r="B116" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C116" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D116">
         <v>231</v>
@@ -8777,13 +8774,13 @@
         <v>63</v>
       </c>
       <c r="H116" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I116" t="s">
         <v>19</v>
       </c>
       <c r="J116" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K116">
         <v>1</v>
@@ -8809,10 +8806,10 @@
         <v>1.9583333333333499</v>
       </c>
       <c r="B117" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C117" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D117">
         <v>231</v>
@@ -8827,13 +8824,13 @@
         <v>63</v>
       </c>
       <c r="H117" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I117" t="s">
         <v>19</v>
       </c>
       <c r="J117" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K117">
         <v>0</v>
@@ -8859,10 +8856,10 @@
         <v>2.00000000000002</v>
       </c>
       <c r="B118" t="s">
+        <v>256</v>
+      </c>
+      <c r="C118" t="s">
         <v>257</v>
-      </c>
-      <c r="C118" t="s">
-        <v>258</v>
       </c>
       <c r="D118">
         <v>300</v>
@@ -8877,7 +8874,7 @@
         <v>63</v>
       </c>
       <c r="H118" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I118" t="s">
         <v>19</v>
@@ -8909,10 +8906,10 @@
         <v>2.0416666666666901</v>
       </c>
       <c r="B119" t="s">
+        <v>258</v>
+      </c>
+      <c r="C119" t="s">
         <v>259</v>
-      </c>
-      <c r="C119" t="s">
-        <v>260</v>
       </c>
       <c r="D119">
         <v>275</v>
@@ -8927,13 +8924,13 @@
         <v>63</v>
       </c>
       <c r="H119" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I119" t="s">
         <v>19</v>
       </c>
       <c r="J119" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K119">
         <v>4</v>
@@ -8959,10 +8956,10 @@
         <v>2.0833333333333601</v>
       </c>
       <c r="B120" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C120" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D120">
         <v>290</v>
@@ -8977,13 +8974,13 @@
         <v>63</v>
       </c>
       <c r="H120" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I120" t="s">
         <v>19</v>
       </c>
       <c r="J120" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K120">
         <v>4</v>
@@ -9009,10 +9006,10 @@
         <v>2.1250000000000302</v>
       </c>
       <c r="B121" t="s">
+        <v>261</v>
+      </c>
+      <c r="C121" t="s">
         <v>262</v>
-      </c>
-      <c r="C121" t="s">
-        <v>263</v>
       </c>
       <c r="D121">
         <v>270</v>
@@ -9033,7 +9030,7 @@
         <v>19</v>
       </c>
       <c r="J121" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K121">
         <v>5</v>
@@ -9059,10 +9056,10 @@
         <v>2.1666666666666998</v>
       </c>
       <c r="B122" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C122" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D122">
         <v>270</v>
@@ -9077,13 +9074,13 @@
         <v>63</v>
       </c>
       <c r="H122" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I122" t="s">
         <v>19</v>
       </c>
       <c r="J122" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K122">
         <v>5</v>
@@ -9109,10 +9106,10 @@
         <v>2.25</v>
       </c>
       <c r="B123" t="s">
+        <v>264</v>
+      </c>
+      <c r="C123" t="s">
         <v>265</v>
-      </c>
-      <c r="C123" t="s">
-        <v>266</v>
       </c>
       <c r="D123">
         <v>270</v>
@@ -9127,13 +9124,13 @@
         <v>63</v>
       </c>
       <c r="H123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I123" t="s">
         <v>19</v>
       </c>
       <c r="J123" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K123">
         <v>4</v>
@@ -9159,10 +9156,10 @@
         <v>2.2916666666666701</v>
       </c>
       <c r="B124" t="s">
+        <v>266</v>
+      </c>
+      <c r="C124" t="s">
         <v>267</v>
-      </c>
-      <c r="C124" t="s">
-        <v>268</v>
       </c>
       <c r="D124">
         <v>270</v>
@@ -9177,13 +9174,13 @@
         <v>63</v>
       </c>
       <c r="H124" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I124" t="s">
         <v>19</v>
       </c>
       <c r="J124" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K124">
         <v>4</v>
@@ -9209,10 +9206,10 @@
         <v>2.3333333333333401</v>
       </c>
       <c r="B125" t="s">
+        <v>268</v>
+      </c>
+      <c r="C125" t="s">
         <v>269</v>
-      </c>
-      <c r="C125" t="s">
-        <v>270</v>
       </c>
       <c r="D125">
         <v>170</v>
@@ -9227,13 +9224,13 @@
         <v>63</v>
       </c>
       <c r="H125" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I125" t="s">
         <v>19</v>
       </c>
       <c r="J125" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K125">
         <v>5</v>
@@ -9259,10 +9256,10 @@
         <v>2.3750000000000102</v>
       </c>
       <c r="B126" t="s">
+        <v>270</v>
+      </c>
+      <c r="C126" t="s">
         <v>271</v>
-      </c>
-      <c r="C126" t="s">
-        <v>272</v>
       </c>
       <c r="D126">
         <v>265</v>
@@ -9277,13 +9274,13 @@
         <v>63</v>
       </c>
       <c r="H126" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I126" t="s">
         <v>19</v>
       </c>
       <c r="J126" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K126">
         <v>5</v>
@@ -9309,10 +9306,10 @@
         <v>2.4166666666666798</v>
       </c>
       <c r="B127" t="s">
+        <v>272</v>
+      </c>
+      <c r="C127" t="s">
         <v>273</v>
-      </c>
-      <c r="C127" t="s">
-        <v>274</v>
       </c>
       <c r="D127">
         <v>270</v>
@@ -9327,13 +9324,13 @@
         <v>63</v>
       </c>
       <c r="H127" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I127" t="s">
         <v>19</v>
       </c>
       <c r="J127" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K127">
         <v>5</v>
@@ -9359,10 +9356,10 @@
         <v>2.4583333333333335</v>
       </c>
       <c r="B128" t="s">
+        <v>274</v>
+      </c>
+      <c r="C128" t="s">
         <v>275</v>
-      </c>
-      <c r="C128" t="s">
-        <v>276</v>
       </c>
       <c r="D128">
         <v>275</v>
@@ -9377,13 +9374,13 @@
         <v>63</v>
       </c>
       <c r="H128" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I128" t="s">
         <v>19</v>
       </c>
       <c r="J128" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K128">
         <v>5</v>
@@ -9409,10 +9406,10 @@
         <v>2.5</v>
       </c>
       <c r="B129" t="s">
+        <v>276</v>
+      </c>
+      <c r="C129" t="s">
         <v>277</v>
-      </c>
-      <c r="C129" t="s">
-        <v>278</v>
       </c>
       <c r="D129">
         <v>280</v>
@@ -9427,13 +9424,13 @@
         <v>63</v>
       </c>
       <c r="H129" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I129" t="s">
         <v>19</v>
       </c>
       <c r="J129" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K129">
         <v>5</v>
@@ -9459,10 +9456,10 @@
         <v>2.5416666666666701</v>
       </c>
       <c r="B130" t="s">
+        <v>278</v>
+      </c>
+      <c r="C130" t="s">
         <v>279</v>
-      </c>
-      <c r="C130" t="s">
-        <v>280</v>
       </c>
       <c r="D130">
         <v>275</v>
@@ -9477,13 +9474,13 @@
         <v>63</v>
       </c>
       <c r="H130" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I130" t="s">
         <v>19</v>
       </c>
       <c r="J130" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K130">
         <v>4</v>
@@ -9509,10 +9506,10 @@
         <v>2.5833333333333401</v>
       </c>
       <c r="B131" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C131" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D131">
         <v>265</v>
@@ -9527,13 +9524,13 @@
         <v>63</v>
       </c>
       <c r="H131" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I131" t="s">
         <v>19</v>
       </c>
       <c r="J131" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K131">
         <v>4</v>
@@ -9559,10 +9556,10 @@
         <v>2.6250000000000102</v>
       </c>
       <c r="B132" t="s">
+        <v>281</v>
+      </c>
+      <c r="C132" t="s">
         <v>282</v>
-      </c>
-      <c r="C132" t="s">
-        <v>283</v>
       </c>
       <c r="D132">
         <v>255</v>
@@ -9577,13 +9574,13 @@
         <v>63</v>
       </c>
       <c r="H132" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I132" t="s">
         <v>19</v>
       </c>
       <c r="J132" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K132">
         <v>4</v>
@@ -9609,10 +9606,10 @@
         <v>2.6666666666666798</v>
       </c>
       <c r="B133" t="s">
+        <v>283</v>
+      </c>
+      <c r="C133" t="s">
         <v>284</v>
-      </c>
-      <c r="C133" t="s">
-        <v>285</v>
       </c>
       <c r="D133">
         <v>250</v>
@@ -9627,13 +9624,13 @@
         <v>63</v>
       </c>
       <c r="H133" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I133" t="s">
         <v>19</v>
       </c>
       <c r="J133" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K133">
         <v>4</v>
@@ -9659,10 +9656,10 @@
         <v>2.7083333333333499</v>
       </c>
       <c r="B134" t="s">
+        <v>285</v>
+      </c>
+      <c r="C134" t="s">
         <v>286</v>
-      </c>
-      <c r="C134" t="s">
-        <v>287</v>
       </c>
       <c r="D134">
         <v>260</v>
@@ -9677,13 +9674,13 @@
         <v>63</v>
       </c>
       <c r="H134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I134" t="s">
         <v>19</v>
       </c>
       <c r="J134" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K134">
         <v>4</v>
@@ -9709,10 +9706,10 @@
         <v>2.75000000000002</v>
       </c>
       <c r="B135" t="s">
+        <v>287</v>
+      </c>
+      <c r="C135" t="s">
         <v>288</v>
-      </c>
-      <c r="C135" t="s">
-        <v>289</v>
       </c>
       <c r="D135">
         <v>250</v>
@@ -9727,7 +9724,7 @@
         <v>63</v>
       </c>
       <c r="H135" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I135" t="s">
         <v>19</v>
@@ -9759,10 +9756,10 @@
         <v>2.7916666666666901</v>
       </c>
       <c r="B136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C136" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D136">
         <v>248</v>
@@ -9777,13 +9774,13 @@
         <v>63</v>
       </c>
       <c r="H136" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I136" t="s">
         <v>19</v>
       </c>
       <c r="J136" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K136">
         <v>3</v>
@@ -9809,10 +9806,10 @@
         <v>2.8333333333333601</v>
       </c>
       <c r="B137" t="s">
+        <v>291</v>
+      </c>
+      <c r="C137" t="s">
         <v>292</v>
-      </c>
-      <c r="C137" t="s">
-        <v>293</v>
       </c>
       <c r="D137">
         <v>250</v>
@@ -9827,13 +9824,13 @@
         <v>63</v>
       </c>
       <c r="H137" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I137" t="s">
         <v>19</v>
       </c>
       <c r="J137" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K137">
         <v>3</v>
@@ -9859,10 +9856,10 @@
         <v>2.8750000000000302</v>
       </c>
       <c r="B138" t="s">
+        <v>293</v>
+      </c>
+      <c r="C138" t="s">
         <v>294</v>
-      </c>
-      <c r="C138" t="s">
-        <v>295</v>
       </c>
       <c r="D138">
         <v>250</v>
@@ -9877,13 +9874,13 @@
         <v>63</v>
       </c>
       <c r="H138" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I138" t="s">
         <v>19</v>
       </c>
       <c r="J138" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K138">
         <v>4</v>
@@ -9909,10 +9906,10 @@
         <v>2.9166666666666998</v>
       </c>
       <c r="B139" t="s">
+        <v>295</v>
+      </c>
+      <c r="C139" t="s">
         <v>296</v>
-      </c>
-      <c r="C139" t="s">
-        <v>297</v>
       </c>
       <c r="D139">
         <v>35</v>
@@ -9927,7 +9924,7 @@
         <v>63</v>
       </c>
       <c r="H139" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I139" t="s">
         <v>19</v>
@@ -9959,10 +9956,10 @@
         <v>2.9583333333333699</v>
       </c>
       <c r="B140" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C140" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D140">
         <v>40</v>
@@ -9983,7 +9980,7 @@
         <v>19</v>
       </c>
       <c r="J140" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K140">
         <v>3</v>
@@ -10009,10 +10006,10 @@
         <v>3.00000000000004</v>
       </c>
       <c r="B141" t="s">
+        <v>298</v>
+      </c>
+      <c r="C141" t="s">
         <v>299</v>
-      </c>
-      <c r="C141" t="s">
-        <v>300</v>
       </c>
       <c r="D141">
         <v>50</v>
@@ -10033,7 +10030,7 @@
         <v>19</v>
       </c>
       <c r="J141" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K141">
         <v>3</v>
@@ -10059,10 +10056,10 @@
         <v>3.04166666666671</v>
       </c>
       <c r="B142" t="s">
+        <v>300</v>
+      </c>
+      <c r="C142" t="s">
         <v>301</v>
-      </c>
-      <c r="C142" t="s">
-        <v>302</v>
       </c>
       <c r="D142">
         <v>53</v>
@@ -10083,7 +10080,7 @@
         <v>19</v>
       </c>
       <c r="J142" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K142">
         <v>3</v>
@@ -10109,10 +10106,10 @@
         <v>3.0833333333333801</v>
       </c>
       <c r="B143" t="s">
+        <v>302</v>
+      </c>
+      <c r="C143" t="s">
         <v>303</v>
-      </c>
-      <c r="C143" t="s">
-        <v>304</v>
       </c>
       <c r="D143">
         <v>60</v>
@@ -10133,7 +10130,7 @@
         <v>19</v>
       </c>
       <c r="J143" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K143">
         <v>1</v>
@@ -10159,10 +10156,10 @@
         <v>3.1250000000000502</v>
       </c>
       <c r="B144" t="s">
+        <v>304</v>
+      </c>
+      <c r="C144" t="s">
         <v>305</v>
-      </c>
-      <c r="C144" t="s">
-        <v>306</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -10177,13 +10174,13 @@
         <v>63</v>
       </c>
       <c r="H144" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I144" t="s">
         <v>19</v>
       </c>
       <c r="J144" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K144">
         <v>3</v>
@@ -10209,10 +10206,10 @@
         <v>3.1666666666667198</v>
       </c>
       <c r="B145" t="s">
+        <v>306</v>
+      </c>
+      <c r="C145" t="s">
         <v>307</v>
-      </c>
-      <c r="C145" t="s">
-        <v>308</v>
       </c>
       <c r="D145">
         <v>50</v>
@@ -10227,7 +10224,7 @@
         <v>63</v>
       </c>
       <c r="H145" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I145" t="s">
         <v>19</v>
@@ -10259,10 +10256,10 @@
         <v>3.2083333333333899</v>
       </c>
       <c r="B146" t="s">
+        <v>308</v>
+      </c>
+      <c r="C146" t="s">
         <v>309</v>
-      </c>
-      <c r="C146" t="s">
-        <v>310</v>
       </c>
       <c r="D146">
         <v>53</v>
@@ -10277,13 +10274,13 @@
         <v>63</v>
       </c>
       <c r="H146" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I146" t="s">
         <v>19</v>
       </c>
       <c r="J146" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K146">
         <v>4</v>
@@ -10309,10 +10306,10 @@
         <v>3.25000000000006</v>
       </c>
       <c r="B147" t="s">
+        <v>310</v>
+      </c>
+      <c r="C147" t="s">
         <v>311</v>
-      </c>
-      <c r="C147" t="s">
-        <v>312</v>
       </c>
       <c r="D147">
         <v>356</v>
@@ -10327,13 +10324,13 @@
         <v>63</v>
       </c>
       <c r="H147" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I147" t="s">
         <v>19</v>
       </c>
       <c r="J147" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K147">
         <v>4</v>
@@ -10359,10 +10356,10 @@
         <v>3.2916666666666665</v>
       </c>
       <c r="B148" t="s">
+        <v>312</v>
+      </c>
+      <c r="C148" t="s">
         <v>313</v>
-      </c>
-      <c r="C148" t="s">
-        <v>314</v>
       </c>
       <c r="D148">
         <v>29</v>
@@ -10383,7 +10380,7 @@
         <v>19</v>
       </c>
       <c r="J148" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K148">
         <v>5</v>
@@ -10409,10 +10406,10 @@
         <v>0.75</v>
       </c>
       <c r="B149" t="s">
+        <v>314</v>
+      </c>
+      <c r="C149" t="s">
         <v>315</v>
-      </c>
-      <c r="C149" t="s">
-        <v>316</v>
       </c>
       <c r="D149">
         <v>255</v>
@@ -10433,7 +10430,7 @@
         <v>19</v>
       </c>
       <c r="J149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K149">
         <v>2</v>
@@ -10459,10 +10456,10 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="B150" t="s">
+        <v>316</v>
+      </c>
+      <c r="C150" t="s">
         <v>317</v>
-      </c>
-      <c r="C150" t="s">
-        <v>318</v>
       </c>
       <c r="D150">
         <v>267</v>
@@ -10483,7 +10480,7 @@
         <v>19</v>
       </c>
       <c r="J150" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K150">
         <v>2</v>
@@ -10509,10 +10506,10 @@
         <v>0.83333333333333404</v>
       </c>
       <c r="B151" t="s">
+        <v>318</v>
+      </c>
+      <c r="C151" t="s">
         <v>319</v>
-      </c>
-      <c r="C151" t="s">
-        <v>320</v>
       </c>
       <c r="D151">
         <v>265</v>
@@ -10559,10 +10556,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="B152" t="s">
+        <v>320</v>
+      </c>
+      <c r="C152" t="s">
         <v>321</v>
-      </c>
-      <c r="C152" t="s">
-        <v>322</v>
       </c>
       <c r="D152">
         <v>225</v>
@@ -10574,7 +10571,7 @@
         <v>4.7</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H152" t="s">
         <v>127</v>
@@ -10583,7 +10580,7 @@
         <v>19</v>
       </c>
       <c r="J152" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K152">
         <v>5</v>
@@ -10609,10 +10606,10 @@
         <v>0.75</v>
       </c>
       <c r="B153" t="s">
+        <v>323</v>
+      </c>
+      <c r="C153" t="s">
         <v>324</v>
-      </c>
-      <c r="C153" t="s">
-        <v>325</v>
       </c>
       <c r="D153">
         <v>226</v>
@@ -10624,7 +10621,7 @@
         <v>5.7</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H153" t="s">
         <v>127</v>
@@ -10633,7 +10630,7 @@
         <v>19</v>
       </c>
       <c r="J153" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K153">
         <v>5</v>
@@ -10659,10 +10656,10 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="B154" t="s">
+        <v>325</v>
+      </c>
+      <c r="C154" t="s">
         <v>326</v>
-      </c>
-      <c r="C154" t="s">
-        <v>327</v>
       </c>
       <c r="D154">
         <v>241</v>
@@ -10674,7 +10671,7 @@
         <v>6.4</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H154" t="s">
         <v>127</v>
@@ -10683,7 +10680,7 @@
         <v>19</v>
       </c>
       <c r="J154" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K154">
         <v>5</v>
@@ -10709,10 +10706,10 @@
         <v>0.83333333333333404</v>
       </c>
       <c r="B155" t="s">
+        <v>327</v>
+      </c>
+      <c r="C155" t="s">
         <v>328</v>
-      </c>
-      <c r="C155" t="s">
-        <v>329</v>
       </c>
       <c r="D155">
         <v>139</v>
@@ -10724,7 +10721,7 @@
         <v>5.3</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H155" t="s">
         <v>127</v>
@@ -10759,10 +10756,10 @@
         <v>0.875000000000001</v>
       </c>
       <c r="B156" t="s">
+        <v>329</v>
+      </c>
+      <c r="C156" t="s">
         <v>330</v>
-      </c>
-      <c r="C156" t="s">
-        <v>331</v>
       </c>
       <c r="D156">
         <v>125</v>
@@ -10774,7 +10771,7 @@
         <v>6.5</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H156" t="s">
         <v>127</v>
@@ -10783,7 +10780,7 @@
         <v>19</v>
       </c>
       <c r="J156" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K156">
         <v>5</v>
@@ -10809,10 +10806,10 @@
         <v>0.91666666666666796</v>
       </c>
       <c r="B157" t="s">
+        <v>331</v>
+      </c>
+      <c r="C157" t="s">
         <v>332</v>
-      </c>
-      <c r="C157" t="s">
-        <v>333</v>
       </c>
       <c r="D157">
         <v>128</v>
@@ -10824,7 +10821,7 @@
         <v>6.6</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H157" t="s">
         <v>127</v>
@@ -10833,7 +10830,7 @@
         <v>19</v>
       </c>
       <c r="J157" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K157">
         <v>5</v>
@@ -10859,10 +10856,10 @@
         <v>0.95833333333333504</v>
       </c>
       <c r="B158" t="s">
+        <v>333</v>
+      </c>
+      <c r="C158" t="s">
         <v>334</v>
-      </c>
-      <c r="C158" t="s">
-        <v>335</v>
       </c>
       <c r="D158">
         <v>160</v>
@@ -10874,7 +10871,7 @@
         <v>5.4</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H158" t="s">
         <v>127</v>
@@ -10883,7 +10880,7 @@
         <v>19</v>
       </c>
       <c r="J158" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K158">
         <v>5</v>
@@ -10909,10 +10906,10 @@
         <v>1</v>
       </c>
       <c r="B159" t="s">
+        <v>335</v>
+      </c>
+      <c r="C159" t="s">
         <v>336</v>
-      </c>
-      <c r="C159" t="s">
-        <v>337</v>
       </c>
       <c r="D159">
         <v>160</v>
@@ -10924,7 +10921,7 @@
         <v>5.5</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H159" t="s">
         <v>127</v>
@@ -10933,7 +10930,7 @@
         <v>19</v>
       </c>
       <c r="J159" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K159">
         <v>5</v>
@@ -10959,10 +10956,10 @@
         <v>1.0833333333333333</v>
       </c>
       <c r="B160" t="s">
+        <v>337</v>
+      </c>
+      <c r="C160" t="s">
         <v>338</v>
-      </c>
-      <c r="C160" t="s">
-        <v>339</v>
       </c>
       <c r="D160">
         <v>280</v>
@@ -10974,7 +10971,7 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H160" t="s">
         <v>127</v>
@@ -11009,10 +11006,10 @@
         <v>1.125</v>
       </c>
       <c r="B161" t="s">
+        <v>339</v>
+      </c>
+      <c r="C161" t="s">
         <v>340</v>
-      </c>
-      <c r="C161" t="s">
-        <v>341</v>
       </c>
       <c r="D161">
         <v>225</v>
@@ -11024,7 +11021,7 @@
         <v>4</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H161" t="s">
         <v>127</v>
@@ -11059,10 +11056,10 @@
         <v>1.1666666666666701</v>
       </c>
       <c r="B162" t="s">
+        <v>341</v>
+      </c>
+      <c r="C162" t="s">
         <v>342</v>
-      </c>
-      <c r="C162" t="s">
-        <v>343</v>
       </c>
       <c r="D162">
         <v>220</v>
@@ -11074,7 +11071,7 @@
         <v>4.2</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H162" t="s">
         <v>127</v>
@@ -11109,10 +11106,10 @@
         <v>1.2083333333333333</v>
       </c>
       <c r="B163" t="s">
+        <v>343</v>
+      </c>
+      <c r="C163" t="s">
         <v>344</v>
-      </c>
-      <c r="C163" t="s">
-        <v>345</v>
       </c>
       <c r="D163">
         <v>150</v>
@@ -11159,10 +11156,10 @@
         <v>1.25</v>
       </c>
       <c r="B164" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C164" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D164">
         <v>175</v>
@@ -11177,7 +11174,7 @@
         <v>63</v>
       </c>
       <c r="H164" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I164" t="s">
         <v>19</v>
@@ -11209,10 +11206,10 @@
         <v>1.2916666666666701</v>
       </c>
       <c r="B165" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C165" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D165">
         <v>210</v>
@@ -11227,7 +11224,7 @@
         <v>63</v>
       </c>
       <c r="H165" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I165" t="s">
         <v>19</v>
@@ -11259,10 +11256,10 @@
         <v>1.3333333333333399</v>
       </c>
       <c r="B166" t="s">
+        <v>347</v>
+      </c>
+      <c r="C166" t="s">
         <v>348</v>
-      </c>
-      <c r="C166" t="s">
-        <v>349</v>
       </c>
       <c r="D166">
         <v>206</v>
@@ -11277,7 +11274,7 @@
         <v>63</v>
       </c>
       <c r="H166" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I166" t="s">
         <v>19</v>
@@ -11309,10 +11306,10 @@
         <v>1.375</v>
       </c>
       <c r="B167" t="s">
+        <v>349</v>
+      </c>
+      <c r="C167" t="s">
         <v>350</v>
-      </c>
-      <c r="C167" t="s">
-        <v>351</v>
       </c>
       <c r="D167">
         <v>200</v>
@@ -11327,7 +11324,7 @@
         <v>63</v>
       </c>
       <c r="H167" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I167" t="s">
         <v>19</v>
@@ -11359,10 +11356,10 @@
         <v>1.4166666666666701</v>
       </c>
       <c r="B168" t="s">
+        <v>351</v>
+      </c>
+      <c r="C168" t="s">
         <v>352</v>
-      </c>
-      <c r="C168" t="s">
-        <v>353</v>
       </c>
       <c r="D168">
         <v>200</v>
@@ -11377,7 +11374,7 @@
         <v>63</v>
       </c>
       <c r="H168" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I168" t="s">
         <v>19</v>
@@ -11409,10 +11406,10 @@
         <v>1.4583333333333399</v>
       </c>
       <c r="B169" t="s">
+        <v>353</v>
+      </c>
+      <c r="C169" t="s">
         <v>354</v>
-      </c>
-      <c r="C169" t="s">
-        <v>355</v>
       </c>
       <c r="D169">
         <v>163</v>
@@ -11427,7 +11424,7 @@
         <v>63</v>
       </c>
       <c r="H169" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I169" t="s">
         <v>19</v>
@@ -11459,10 +11456,10 @@
         <v>1.50000000000001</v>
       </c>
       <c r="B170" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C170" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D170">
         <v>190</v>
@@ -11477,7 +11474,7 @@
         <v>63</v>
       </c>
       <c r="H170" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I170" t="s">
         <v>19</v>
@@ -11509,10 +11506,10 @@
         <v>1.5416666666666801</v>
       </c>
       <c r="B171" t="s">
+        <v>355</v>
+      </c>
+      <c r="C171" t="s">
         <v>356</v>
-      </c>
-      <c r="C171" t="s">
-        <v>357</v>
       </c>
       <c r="D171">
         <v>190</v>
@@ -11527,7 +11524,7 @@
         <v>63</v>
       </c>
       <c r="H171" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I171" t="s">
         <v>19</v>
@@ -11559,10 +11556,10 @@
         <v>1.5833333333333499</v>
       </c>
       <c r="B172" t="s">
+        <v>359</v>
+      </c>
+      <c r="C172" t="s">
         <v>360</v>
-      </c>
-      <c r="C172" t="s">
-        <v>361</v>
       </c>
       <c r="D172">
         <v>210</v>
@@ -11577,7 +11574,7 @@
         <v>63</v>
       </c>
       <c r="H172" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I172" t="s">
         <v>19</v>
@@ -11609,10 +11606,10 @@
         <v>1.62500000000002</v>
       </c>
       <c r="B173" t="s">
+        <v>361</v>
+      </c>
+      <c r="C173" t="s">
         <v>362</v>
-      </c>
-      <c r="C173" t="s">
-        <v>363</v>
       </c>
       <c r="D173">
         <v>205</v>
@@ -11627,7 +11624,7 @@
         <v>63</v>
       </c>
       <c r="H173" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I173" t="s">
         <v>19</v>
@@ -11659,10 +11656,10 @@
         <v>1.6666666666666901</v>
       </c>
       <c r="B174" t="s">
+        <v>363</v>
+      </c>
+      <c r="C174" t="s">
         <v>364</v>
-      </c>
-      <c r="C174" t="s">
-        <v>365</v>
       </c>
       <c r="D174">
         <v>200</v>
@@ -11677,7 +11674,7 @@
         <v>63</v>
       </c>
       <c r="H174" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I174" t="s">
         <v>19</v>
@@ -11709,10 +11706,10 @@
         <v>1.7083333333333599</v>
       </c>
       <c r="B175" t="s">
+        <v>365</v>
+      </c>
+      <c r="C175" t="s">
         <v>366</v>
-      </c>
-      <c r="C175" t="s">
-        <v>367</v>
       </c>
       <c r="D175">
         <v>206</v>
@@ -11727,7 +11724,7 @@
         <v>63</v>
       </c>
       <c r="H175" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I175" t="s">
         <v>19</v>
@@ -11759,10 +11756,10 @@
         <v>1.75000000000003</v>
       </c>
       <c r="B176" t="s">
+        <v>367</v>
+      </c>
+      <c r="C176" t="s">
         <v>368</v>
-      </c>
-      <c r="C176" t="s">
-        <v>369</v>
       </c>
       <c r="D176">
         <v>200</v>
@@ -11777,7 +11774,7 @@
         <v>63</v>
       </c>
       <c r="H176" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I176" t="s">
         <v>19</v>
@@ -11809,10 +11806,10 @@
         <v>1.7916666666666665</v>
       </c>
       <c r="B177" t="s">
+        <v>369</v>
+      </c>
+      <c r="C177" t="s">
         <v>370</v>
-      </c>
-      <c r="C177" t="s">
-        <v>371</v>
       </c>
       <c r="D177">
         <v>212</v>
@@ -11827,7 +11824,7 @@
         <v>63</v>
       </c>
       <c r="H177" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I177" t="s">
         <v>19</v>
@@ -11859,10 +11856,10 @@
         <v>1.8333333333333299</v>
       </c>
       <c r="B178" t="s">
+        <v>371</v>
+      </c>
+      <c r="C178" t="s">
         <v>372</v>
-      </c>
-      <c r="C178" t="s">
-        <v>373</v>
       </c>
       <c r="D178">
         <v>214</v>
@@ -11877,7 +11874,7 @@
         <v>63</v>
       </c>
       <c r="H178" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I178" t="s">
         <v>19</v>
@@ -11909,10 +11906,10 @@
         <v>1.875</v>
       </c>
       <c r="B179" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C179" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D179">
         <v>202</v>
@@ -11924,7 +11921,7 @@
         <v>8.9</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H179" t="s">
         <v>127</v>
@@ -11959,10 +11956,10 @@
         <v>1.9166666666666701</v>
       </c>
       <c r="B180" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C180" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D180">
         <v>220</v>
@@ -11974,7 +11971,7 @@
         <v>9</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H180" t="s">
         <v>127</v>
@@ -12009,10 +12006,10 @@
         <v>1.9583333333333399</v>
       </c>
       <c r="B181" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C181" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D181">
         <v>220</v>
@@ -12024,7 +12021,7 @@
         <v>9</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H181" t="s">
         <v>127</v>
@@ -12059,10 +12056,10 @@
         <v>2.0000000000000102</v>
       </c>
       <c r="B182" t="s">
+        <v>379</v>
+      </c>
+      <c r="C182" t="s">
         <v>380</v>
-      </c>
-      <c r="C182" t="s">
-        <v>381</v>
       </c>
       <c r="D182">
         <v>220</v>
@@ -12109,10 +12106,10 @@
         <v>2.0416666666666798</v>
       </c>
       <c r="B183" t="s">
+        <v>381</v>
+      </c>
+      <c r="C183" t="s">
         <v>382</v>
-      </c>
-      <c r="C183" t="s">
-        <v>383</v>
       </c>
       <c r="D183">
         <v>195</v>
@@ -12159,10 +12156,10 @@
         <v>2.0833333333333499</v>
       </c>
       <c r="B184" t="s">
+        <v>383</v>
+      </c>
+      <c r="C184" t="s">
         <v>384</v>
-      </c>
-      <c r="C184" t="s">
-        <v>385</v>
       </c>
       <c r="D184">
         <v>195</v>
@@ -12209,10 +12206,10 @@
         <v>2.12500000000002</v>
       </c>
       <c r="B185" t="s">
+        <v>385</v>
+      </c>
+      <c r="C185" t="s">
         <v>386</v>
-      </c>
-      <c r="C185" t="s">
-        <v>387</v>
       </c>
       <c r="D185">
         <v>200</v>
@@ -12259,10 +12256,10 @@
         <v>2.1666666666666901</v>
       </c>
       <c r="B186" t="s">
+        <v>387</v>
+      </c>
+      <c r="C186" t="s">
         <v>388</v>
-      </c>
-      <c r="C186" t="s">
-        <v>389</v>
       </c>
       <c r="D186">
         <v>160</v>
@@ -12309,10 +12306,10 @@
         <v>2.2083333333333335</v>
       </c>
       <c r="B187" t="s">
+        <v>389</v>
+      </c>
+      <c r="C187" t="s">
         <v>390</v>
-      </c>
-      <c r="C187" t="s">
-        <v>391</v>
       </c>
       <c r="D187">
         <v>198</v>
@@ -12359,10 +12356,10 @@
         <v>2.25</v>
       </c>
       <c r="B188" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C188" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D188">
         <v>209</v>
@@ -12374,7 +12371,7 @@
         <v>9</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H188" t="s">
         <v>70</v>
@@ -12409,10 +12406,10 @@
         <v>2.2916666666666701</v>
       </c>
       <c r="B189" t="s">
+        <v>392</v>
+      </c>
+      <c r="C189" t="s">
         <v>393</v>
-      </c>
-      <c r="C189" t="s">
-        <v>394</v>
       </c>
       <c r="D189">
         <v>206</v>
@@ -12424,7 +12421,7 @@
         <v>9.1</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H189" t="s">
         <v>70</v>
@@ -12462,7 +12459,7 @@
         <v>99</v>
       </c>
       <c r="C190" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D190">
         <v>208</v>
@@ -12509,10 +12506,10 @@
         <v>2.3750000000000102</v>
       </c>
       <c r="B191" t="s">
+        <v>396</v>
+      </c>
+      <c r="C191" t="s">
         <v>397</v>
-      </c>
-      <c r="C191" t="s">
-        <v>398</v>
       </c>
       <c r="D191">
         <v>220</v>
@@ -12559,10 +12556,10 @@
         <v>2.4166666666666798</v>
       </c>
       <c r="B192" t="s">
+        <v>398</v>
+      </c>
+      <c r="C192" t="s">
         <v>399</v>
-      </c>
-      <c r="C192" t="s">
-        <v>400</v>
       </c>
       <c r="D192">
         <v>210</v>
@@ -12609,10 +12606,10 @@
         <v>2.4583333333333499</v>
       </c>
       <c r="B193" t="s">
+        <v>400</v>
+      </c>
+      <c r="C193" t="s">
         <v>401</v>
-      </c>
-      <c r="C193" t="s">
-        <v>402</v>
       </c>
       <c r="D193">
         <v>210</v>
@@ -12627,7 +12624,7 @@
         <v>63</v>
       </c>
       <c r="H193" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I193" t="s">
         <v>19</v>
@@ -12659,10 +12656,10 @@
         <v>2.50000000000002</v>
       </c>
       <c r="B194" t="s">
+        <v>402</v>
+      </c>
+      <c r="C194" t="s">
         <v>403</v>
-      </c>
-      <c r="C194" t="s">
-        <v>404</v>
       </c>
       <c r="D194">
         <v>200</v>
@@ -12677,7 +12674,7 @@
         <v>63</v>
       </c>
       <c r="H194" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I194" t="s">
         <v>19</v>
@@ -12709,10 +12706,10 @@
         <v>2.5416666666666901</v>
       </c>
       <c r="B195" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C195" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D195">
         <v>200</v>
@@ -12724,10 +12721,10 @@
         <v>8.4</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H195" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I195" t="s">
         <v>19</v>
@@ -12759,10 +12756,10 @@
         <v>2.5833333333333601</v>
       </c>
       <c r="B196" t="s">
+        <v>407</v>
+      </c>
+      <c r="C196" t="s">
         <v>408</v>
-      </c>
-      <c r="C196" t="s">
-        <v>409</v>
       </c>
       <c r="D196">
         <v>200</v>
@@ -12774,10 +12771,10 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H196" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I196" t="s">
         <v>19</v>
@@ -12809,10 +12806,10 @@
         <v>2.6250000000000302</v>
       </c>
       <c r="B197" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C197" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D197">
         <v>200</v>
@@ -12827,7 +12824,7 @@
         <v>63</v>
       </c>
       <c r="H197" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I197" t="s">
         <v>19</v>
@@ -12859,10 +12856,10 @@
         <v>2.6666666666666665</v>
       </c>
       <c r="B198" t="s">
+        <v>410</v>
+      </c>
+      <c r="C198" t="s">
         <v>411</v>
-      </c>
-      <c r="C198" t="s">
-        <v>412</v>
       </c>
       <c r="D198">
         <v>200</v>
@@ -12877,7 +12874,7 @@
         <v>63</v>
       </c>
       <c r="H198" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I198" t="s">
         <v>19</v>
@@ -12909,10 +12906,10 @@
         <v>2.7083333333333299</v>
       </c>
       <c r="B199" t="s">
+        <v>412</v>
+      </c>
+      <c r="C199" t="s">
         <v>413</v>
-      </c>
-      <c r="C199" t="s">
-        <v>414</v>
       </c>
       <c r="D199">
         <v>200</v>
@@ -12927,7 +12924,7 @@
         <v>63</v>
       </c>
       <c r="H199" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I199" t="s">
         <v>19</v>
@@ -12959,10 +12956,10 @@
         <v>2.75</v>
       </c>
       <c r="B200" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C200" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D200">
         <v>200</v>
@@ -12977,7 +12974,7 @@
         <v>63</v>
       </c>
       <c r="H200" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I200" t="s">
         <v>19</v>
@@ -13009,10 +13006,10 @@
         <v>2.7916666666666701</v>
       </c>
       <c r="B201" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C201" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D201">
         <v>200</v>
@@ -13027,7 +13024,7 @@
         <v>63</v>
       </c>
       <c r="H201" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I201" t="s">
         <v>19</v>
@@ -13059,10 +13056,10 @@
         <v>2.8333333333333401</v>
       </c>
       <c r="B202" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C202" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D202">
         <v>200</v>
@@ -13077,7 +13074,7 @@
         <v>63</v>
       </c>
       <c r="H202" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I202" t="s">
         <v>19</v>
@@ -13109,10 +13106,10 @@
         <v>2.8750000000000102</v>
       </c>
       <c r="B203" t="s">
+        <v>420</v>
+      </c>
+      <c r="C203" t="s">
         <v>421</v>
-      </c>
-      <c r="C203" t="s">
-        <v>422</v>
       </c>
       <c r="D203">
         <v>210</v>
@@ -13159,10 +13156,10 @@
         <v>2.9166666666666798</v>
       </c>
       <c r="B204" t="s">
+        <v>422</v>
+      </c>
+      <c r="C204" t="s">
         <v>423</v>
-      </c>
-      <c r="C204" t="s">
-        <v>424</v>
       </c>
       <c r="D204">
         <v>225</v>
@@ -13209,10 +13206,10 @@
         <v>2.9583333333333499</v>
       </c>
       <c r="B205" t="s">
+        <v>424</v>
+      </c>
+      <c r="C205" t="s">
         <v>425</v>
-      </c>
-      <c r="C205" t="s">
-        <v>426</v>
       </c>
       <c r="D205">
         <v>220</v>
@@ -13259,10 +13256,10 @@
         <v>3.00000000000002</v>
       </c>
       <c r="B206" t="s">
+        <v>426</v>
+      </c>
+      <c r="C206" t="s">
         <v>427</v>
-      </c>
-      <c r="C206" t="s">
-        <v>428</v>
       </c>
       <c r="D206">
         <v>215</v>
@@ -13274,7 +13271,7 @@
         <v>8</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H206" t="s">
         <v>70</v>
@@ -13309,10 +13306,10 @@
         <v>3.0416666666666901</v>
       </c>
       <c r="B207" t="s">
+        <v>428</v>
+      </c>
+      <c r="C207" t="s">
         <v>429</v>
-      </c>
-      <c r="C207" t="s">
-        <v>430</v>
       </c>
       <c r="D207">
         <v>220</v>
@@ -13359,10 +13356,10 @@
         <v>3.0833333333333601</v>
       </c>
       <c r="B208" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C208" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D208">
         <v>220</v>
@@ -13409,10 +13406,10 @@
         <v>3.1250000000000302</v>
       </c>
       <c r="B209" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C209" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D209">
         <v>217</v>
@@ -13459,10 +13456,10 @@
         <v>3.1666666666666998</v>
       </c>
       <c r="B210" t="s">
+        <v>434</v>
+      </c>
+      <c r="C210" t="s">
         <v>435</v>
-      </c>
-      <c r="C210" t="s">
-        <v>436</v>
       </c>
       <c r="D210">
         <v>232</v>
@@ -13509,10 +13506,10 @@
         <v>3.2083333333333699</v>
       </c>
       <c r="B211" t="s">
+        <v>436</v>
+      </c>
+      <c r="C211" t="s">
         <v>437</v>
-      </c>
-      <c r="C211" t="s">
-        <v>438</v>
       </c>
       <c r="D211">
         <v>233</v>
@@ -13559,10 +13556,10 @@
         <v>3.25000000000004</v>
       </c>
       <c r="B212" t="s">
+        <v>438</v>
+      </c>
+      <c r="C212" t="s">
         <v>439</v>
-      </c>
-      <c r="C212" t="s">
-        <v>440</v>
       </c>
       <c r="D212">
         <v>224</v>
@@ -13609,10 +13606,10 @@
         <v>3.875</v>
       </c>
       <c r="B213" t="s">
+        <v>440</v>
+      </c>
+      <c r="C213" t="s">
         <v>441</v>
-      </c>
-      <c r="C213" t="s">
-        <v>442</v>
       </c>
       <c r="D213">
         <v>28</v>
@@ -13659,10 +13656,10 @@
         <v>3.9166666666666701</v>
       </c>
       <c r="B214" t="s">
+        <v>442</v>
+      </c>
+      <c r="C214" t="s">
         <v>443</v>
-      </c>
-      <c r="C214" t="s">
-        <v>444</v>
       </c>
       <c r="D214">
         <v>30</v>
@@ -13709,10 +13706,10 @@
         <v>3.9583333333333401</v>
       </c>
       <c r="B215" t="s">
+        <v>444</v>
+      </c>
+      <c r="C215" t="s">
         <v>445</v>
-      </c>
-      <c r="C215" t="s">
-        <v>446</v>
       </c>
       <c r="D215">
         <v>15</v>
@@ -13759,10 +13756,10 @@
         <v>4.0000000000000098</v>
       </c>
       <c r="B216" t="s">
+        <v>446</v>
+      </c>
+      <c r="C216" t="s">
         <v>447</v>
-      </c>
-      <c r="C216" t="s">
-        <v>448</v>
       </c>
       <c r="D216">
         <v>5</v>
@@ -13809,10 +13806,10 @@
         <v>4.0416666666666803</v>
       </c>
       <c r="B217" t="s">
+        <v>448</v>
+      </c>
+      <c r="C217" t="s">
         <v>449</v>
-      </c>
-      <c r="C217" t="s">
-        <v>450</v>
       </c>
       <c r="D217">
         <v>15</v>
@@ -13859,10 +13856,10 @@
         <v>4.0833333333333499</v>
       </c>
       <c r="B218" t="s">
+        <v>450</v>
+      </c>
+      <c r="C218" t="s">
         <v>451</v>
-      </c>
-      <c r="C218" t="s">
-        <v>452</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -13909,10 +13906,10 @@
         <v>4.1250000000000204</v>
       </c>
       <c r="B219" t="s">
+        <v>452</v>
+      </c>
+      <c r="C219" t="s">
         <v>453</v>
-      </c>
-      <c r="C219" t="s">
-        <v>454</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -13959,10 +13956,10 @@
         <v>4.166666666666667</v>
       </c>
       <c r="B220" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C220" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D220">
         <v>358</v>
@@ -13983,7 +13980,7 @@
         <v>19</v>
       </c>
       <c r="J220" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K220">
         <v>2</v>
@@ -14009,10 +14006,10 @@
         <v>4.2083333333333304</v>
       </c>
       <c r="B221" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C221" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D221">
         <v>10</v>
@@ -14033,7 +14030,7 @@
         <v>19</v>
       </c>
       <c r="J221" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K221">
         <v>2</v>
@@ -14059,10 +14056,10 @@
         <v>4.25</v>
       </c>
       <c r="B222" t="s">
+        <v>456</v>
+      </c>
+      <c r="C222" t="s">
         <v>457</v>
-      </c>
-      <c r="C222" t="s">
-        <v>458</v>
       </c>
       <c r="D222">
         <v>10</v>
@@ -14083,7 +14080,7 @@
         <v>19</v>
       </c>
       <c r="J222" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K222">
         <v>2</v>
@@ -14109,10 +14106,10 @@
         <v>4.2916666666666696</v>
       </c>
       <c r="B223" t="s">
+        <v>458</v>
+      </c>
+      <c r="C223" t="s">
         <v>459</v>
-      </c>
-      <c r="C223" t="s">
-        <v>460</v>
       </c>
       <c r="D223">
         <v>10</v>
@@ -14133,7 +14130,7 @@
         <v>19</v>
       </c>
       <c r="J223" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K223">
         <v>2</v>
@@ -14159,10 +14156,10 @@
         <v>4.3333333333333401</v>
       </c>
       <c r="B224" t="s">
+        <v>460</v>
+      </c>
+      <c r="C224" t="s">
         <v>461</v>
-      </c>
-      <c r="C224" t="s">
-        <v>462</v>
       </c>
       <c r="D224">
         <v>350</v>
@@ -14183,7 +14180,7 @@
         <v>19</v>
       </c>
       <c r="J224" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K224">
         <v>3</v>
@@ -14209,10 +14206,10 @@
         <v>4.3750000000000098</v>
       </c>
       <c r="B225" t="s">
+        <v>462</v>
+      </c>
+      <c r="C225" t="s">
         <v>463</v>
-      </c>
-      <c r="C225" t="s">
-        <v>464</v>
       </c>
       <c r="D225">
         <v>356</v>
@@ -14259,10 +14256,10 @@
         <v>4.4166666666666803</v>
       </c>
       <c r="B226" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C226" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D226">
         <v>350</v>
@@ -14283,7 +14280,7 @@
         <v>19</v>
       </c>
       <c r="J226" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K226">
         <v>3</v>
@@ -14309,10 +14306,10 @@
         <v>4.4583333333333499</v>
       </c>
       <c r="B227" t="s">
+        <v>466</v>
+      </c>
+      <c r="C227" t="s">
         <v>467</v>
-      </c>
-      <c r="C227" t="s">
-        <v>468</v>
       </c>
       <c r="D227">
         <v>350</v>
@@ -14333,7 +14330,7 @@
         <v>19</v>
       </c>
       <c r="J227" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K227">
         <v>4</v>
@@ -14359,10 +14356,10 @@
         <v>4.5000000000000204</v>
       </c>
       <c r="B228" t="s">
+        <v>468</v>
+      </c>
+      <c r="C228" t="s">
         <v>469</v>
-      </c>
-      <c r="C228" t="s">
-        <v>470</v>
       </c>
       <c r="D228">
         <v>90</v>
@@ -14374,7 +14371,7 @@
         <v>7.9</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H228" t="s">
         <v>127</v>
@@ -14383,7 +14380,7 @@
         <v>19</v>
       </c>
       <c r="J228" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K228">
         <v>5</v>
@@ -14409,10 +14406,10 @@
         <v>4.5416666666666901</v>
       </c>
       <c r="B229" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C229" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D229">
         <v>85</v>
@@ -14424,7 +14421,7 @@
         <v>6.2</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H229" t="s">
         <v>127</v>
@@ -14433,7 +14430,7 @@
         <v>19</v>
       </c>
       <c r="J229" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K229">
         <v>6</v>
@@ -14459,10 +14456,10 @@
         <v>4.5833333333333597</v>
       </c>
       <c r="B230" t="s">
+        <v>472</v>
+      </c>
+      <c r="C230" t="s">
         <v>473</v>
-      </c>
-      <c r="C230" t="s">
-        <v>474</v>
       </c>
       <c r="D230">
         <v>80</v>
@@ -14474,7 +14471,7 @@
         <v>3.9</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H230" t="s">
         <v>127</v>
@@ -14483,7 +14480,7 @@
         <v>19</v>
       </c>
       <c r="J230" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K230">
         <v>6</v>
@@ -14509,10 +14506,10 @@
         <v>4.916666666666667</v>
       </c>
       <c r="B231" t="s">
+        <v>474</v>
+      </c>
+      <c r="C231" t="s">
         <v>475</v>
-      </c>
-      <c r="C231" t="s">
-        <v>476</v>
       </c>
       <c r="D231">
         <v>0</v>
@@ -14527,7 +14524,7 @@
         <v>17</v>
       </c>
       <c r="H231" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I231" t="s">
         <v>19</v>
@@ -14559,10 +14556,10 @@
         <v>4.9583333333333304</v>
       </c>
       <c r="B232" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C232" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D232">
         <v>340</v>
@@ -14577,7 +14574,7 @@
         <v>17</v>
       </c>
       <c r="H232" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I232" t="s">
         <v>19</v>
@@ -14609,10 +14606,10 @@
         <v>5</v>
       </c>
       <c r="B233" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C233" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D233">
         <v>20</v>
@@ -14627,7 +14624,7 @@
         <v>17</v>
       </c>
       <c r="H233" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I233" t="s">
         <v>19</v>
@@ -14659,10 +14656,10 @@
         <v>5.0416666666666696</v>
       </c>
       <c r="B234" t="s">
+        <v>482</v>
+      </c>
+      <c r="C234" t="s">
         <v>483</v>
-      </c>
-      <c r="C234" t="s">
-        <v>484</v>
       </c>
       <c r="D234">
         <v>26</v>
@@ -14677,7 +14674,7 @@
         <v>17</v>
       </c>
       <c r="H234" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I234" t="s">
         <v>19</v>
@@ -14709,10 +14706,10 @@
         <v>5.0833333333333401</v>
       </c>
       <c r="B235" t="s">
+        <v>484</v>
+      </c>
+      <c r="C235" t="s">
         <v>485</v>
-      </c>
-      <c r="C235" t="s">
-        <v>486</v>
       </c>
       <c r="D235">
         <v>15</v>
@@ -14727,7 +14724,7 @@
         <v>17</v>
       </c>
       <c r="H235" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I235" t="s">
         <v>19</v>
@@ -14759,10 +14756,10 @@
         <v>5.1250000000000098</v>
       </c>
       <c r="B236" t="s">
+        <v>486</v>
+      </c>
+      <c r="C236" t="s">
         <v>487</v>
-      </c>
-      <c r="C236" t="s">
-        <v>488</v>
       </c>
       <c r="D236">
         <v>20</v>
@@ -14774,10 +14771,10 @@
         <v>7.2</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H236" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I236" t="s">
         <v>19</v>
@@ -14812,7 +14809,7 @@
         <v>125</v>
       </c>
       <c r="C237" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D237">
         <v>15</v>
@@ -14824,10 +14821,10 @@
         <v>8</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H237" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I237" t="s">
         <v>19</v>
@@ -14859,10 +14856,10 @@
         <v>5.2083333333333499</v>
       </c>
       <c r="B238" t="s">
+        <v>489</v>
+      </c>
+      <c r="C238" t="s">
         <v>490</v>
-      </c>
-      <c r="C238" t="s">
-        <v>491</v>
       </c>
       <c r="D238">
         <v>15</v>
@@ -14874,10 +14871,10 @@
         <v>7.4</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H238" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I238" t="s">
         <v>19</v>
@@ -14909,10 +14906,10 @@
         <v>5.2500000000000204</v>
       </c>
       <c r="B239" t="s">
+        <v>491</v>
+      </c>
+      <c r="C239" t="s">
         <v>492</v>
-      </c>
-      <c r="C239" t="s">
-        <v>493</v>
       </c>
       <c r="D239">
         <v>7</v>
@@ -14924,10 +14921,10 @@
         <v>7.5</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H239" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I239" t="s">
         <v>19</v>
@@ -14959,10 +14956,10 @@
         <v>5.25</v>
       </c>
       <c r="B240" t="s">
+        <v>493</v>
+      </c>
+      <c r="C240" t="s">
         <v>494</v>
-      </c>
-      <c r="C240" t="s">
-        <v>495</v>
       </c>
       <c r="D240">
         <v>115</v>
@@ -15009,10 +15006,10 @@
         <v>5.2916666666666696</v>
       </c>
       <c r="B241" t="s">
+        <v>495</v>
+      </c>
+      <c r="C241" t="s">
         <v>496</v>
-      </c>
-      <c r="C241" t="s">
-        <v>497</v>
       </c>
       <c r="D241">
         <v>220</v>
@@ -15059,10 +15056,10 @@
         <v>5.3333333333333401</v>
       </c>
       <c r="B242" t="s">
+        <v>497</v>
+      </c>
+      <c r="C242" t="s">
         <v>498</v>
-      </c>
-      <c r="C242" t="s">
-        <v>499</v>
       </c>
       <c r="D242">
         <v>215</v>
@@ -15109,10 +15106,10 @@
         <v>5.3750000000000098</v>
       </c>
       <c r="B243" t="s">
+        <v>499</v>
+      </c>
+      <c r="C243" t="s">
         <v>500</v>
-      </c>
-      <c r="C243" t="s">
-        <v>501</v>
       </c>
       <c r="D243">
         <v>206</v>
@@ -15159,10 +15156,10 @@
         <v>5.4166666666666803</v>
       </c>
       <c r="B244" t="s">
+        <v>501</v>
+      </c>
+      <c r="C244" t="s">
         <v>502</v>
-      </c>
-      <c r="C244" t="s">
-        <v>503</v>
       </c>
       <c r="D244">
         <v>205</v>
@@ -15209,10 +15206,10 @@
         <v>5.4583333333333499</v>
       </c>
       <c r="B245" t="s">
+        <v>503</v>
+      </c>
+      <c r="C245" t="s">
         <v>504</v>
-      </c>
-      <c r="C245" t="s">
-        <v>505</v>
       </c>
       <c r="D245">
         <v>205</v>
@@ -15259,10 +15256,10 @@
         <v>5.5000000000000204</v>
       </c>
       <c r="B246" t="s">
+        <v>505</v>
+      </c>
+      <c r="C246" t="s">
         <v>506</v>
-      </c>
-      <c r="C246" t="s">
-        <v>507</v>
       </c>
       <c r="D246">
         <v>210</v>
@@ -15309,10 +15306,10 @@
         <v>5.5416666666666901</v>
       </c>
       <c r="B247" t="s">
+        <v>507</v>
+      </c>
+      <c r="C247" t="s">
         <v>508</v>
-      </c>
-      <c r="C247" t="s">
-        <v>509</v>
       </c>
       <c r="D247">
         <v>205</v>
@@ -15359,10 +15356,10 @@
         <v>5.5833333333333597</v>
       </c>
       <c r="B248" t="s">
+        <v>509</v>
+      </c>
+      <c r="C248" t="s">
         <v>510</v>
-      </c>
-      <c r="C248" t="s">
-        <v>511</v>
       </c>
       <c r="D248">
         <v>203</v>
@@ -15409,10 +15406,10 @@
         <v>5.6250000000000302</v>
       </c>
       <c r="B249" t="s">
+        <v>511</v>
+      </c>
+      <c r="C249" t="s">
         <v>512</v>
-      </c>
-      <c r="C249" t="s">
-        <v>513</v>
       </c>
       <c r="D249">
         <v>210</v>
@@ -15459,10 +15456,10 @@
         <v>5.5</v>
       </c>
       <c r="B250" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C250" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D250">
         <v>257</v>
@@ -15483,7 +15480,7 @@
         <v>19</v>
       </c>
       <c r="J250" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K250">
         <v>2</v>
@@ -15509,10 +15506,10 @@
         <v>5.5416666666666696</v>
       </c>
       <c r="B251" t="s">
+        <v>514</v>
+      </c>
+      <c r="C251" t="s">
         <v>515</v>
-      </c>
-      <c r="C251" t="s">
-        <v>516</v>
       </c>
       <c r="D251">
         <v>200</v>
@@ -15559,10 +15556,10 @@
         <v>5.5833333333333401</v>
       </c>
       <c r="B252" t="s">
+        <v>516</v>
+      </c>
+      <c r="C252" t="s">
         <v>517</v>
-      </c>
-      <c r="C252" t="s">
-        <v>518</v>
       </c>
       <c r="D252">
         <v>205</v>
@@ -15583,7 +15580,7 @@
         <v>19</v>
       </c>
       <c r="J252" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K252">
         <v>3</v>
@@ -15609,10 +15606,10 @@
         <v>5.6250000000000098</v>
       </c>
       <c r="B253" t="s">
+        <v>518</v>
+      </c>
+      <c r="C253" t="s">
         <v>519</v>
-      </c>
-      <c r="C253" t="s">
-        <v>520</v>
       </c>
       <c r="D253">
         <v>180</v>
@@ -15633,7 +15630,7 @@
         <v>19</v>
       </c>
       <c r="J253" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K253">
         <v>4</v>
@@ -15659,10 +15656,10 @@
         <v>5.6666666666666803</v>
       </c>
       <c r="B254" t="s">
+        <v>520</v>
+      </c>
+      <c r="C254" t="s">
         <v>521</v>
-      </c>
-      <c r="C254" t="s">
-        <v>522</v>
       </c>
       <c r="D254">
         <v>195</v>
@@ -15683,7 +15680,7 @@
         <v>19</v>
       </c>
       <c r="J254" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K254">
         <v>5</v>
@@ -15709,10 +15706,10 @@
         <v>5.7083333333333499</v>
       </c>
       <c r="B255" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C255" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D255">
         <v>195</v>
@@ -15733,7 +15730,7 @@
         <v>19</v>
       </c>
       <c r="J255" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K255">
         <v>5</v>
@@ -15759,10 +15756,10 @@
         <v>5.7500000000000204</v>
       </c>
       <c r="B256" t="s">
+        <v>525</v>
+      </c>
+      <c r="C256" t="s">
         <v>526</v>
-      </c>
-      <c r="C256" t="s">
-        <v>527</v>
       </c>
       <c r="D256">
         <v>208</v>
@@ -15783,7 +15780,7 @@
         <v>19</v>
       </c>
       <c r="J256" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K256">
         <v>5</v>
@@ -15809,10 +15806,10 @@
         <v>5.7916666666666901</v>
       </c>
       <c r="B257" t="s">
+        <v>527</v>
+      </c>
+      <c r="C257" t="s">
         <v>528</v>
-      </c>
-      <c r="C257" t="s">
-        <v>529</v>
       </c>
       <c r="D257">
         <v>214</v>
@@ -15833,7 +15830,7 @@
         <v>19</v>
       </c>
       <c r="J257" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K257">
         <v>6</v>
@@ -15859,10 +15856,10 @@
         <v>5.8333333333333597</v>
       </c>
       <c r="B258" t="s">
+        <v>529</v>
+      </c>
+      <c r="C258" t="s">
         <v>530</v>
-      </c>
-      <c r="C258" t="s">
-        <v>531</v>
       </c>
       <c r="D258">
         <v>240</v>
@@ -15883,7 +15880,7 @@
         <v>19</v>
       </c>
       <c r="J258" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K258">
         <v>6</v>
@@ -15909,10 +15906,10 @@
         <v>5.8750000000000302</v>
       </c>
       <c r="B259" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C259" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D259">
         <v>220</v>
@@ -15933,7 +15930,7 @@
         <v>19</v>
       </c>
       <c r="J259" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K259">
         <v>5</v>
@@ -15959,10 +15956,10 @@
         <v>5.9166666666666998</v>
       </c>
       <c r="B260" t="s">
+        <v>533</v>
+      </c>
+      <c r="C260" t="s">
         <v>534</v>
-      </c>
-      <c r="C260" t="s">
-        <v>535</v>
       </c>
       <c r="D260">
         <v>240</v>
@@ -15983,7 +15980,7 @@
         <v>19</v>
       </c>
       <c r="J260" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K260">
         <v>5</v>
@@ -16009,10 +16006,10 @@
         <v>5.333333333333333</v>
       </c>
       <c r="B261" t="s">
+        <v>535</v>
+      </c>
+      <c r="C261" t="s">
         <v>536</v>
-      </c>
-      <c r="C261" t="s">
-        <v>537</v>
       </c>
       <c r="D261">
         <v>100</v>
@@ -16059,10 +16056,10 @@
         <v>4.375</v>
       </c>
       <c r="B262" t="s">
+        <v>537</v>
+      </c>
+      <c r="C262" t="s">
         <v>538</v>
-      </c>
-      <c r="C262" t="s">
-        <v>539</v>
       </c>
       <c r="D262">
         <v>105</v>
@@ -16109,10 +16106,10 @@
         <v>4.416666666666667</v>
       </c>
       <c r="B263" t="s">
+        <v>539</v>
+      </c>
+      <c r="C263" t="s">
         <v>540</v>
-      </c>
-      <c r="C263" t="s">
-        <v>541</v>
       </c>
       <c r="D263">
         <v>115</v>
@@ -16159,10 +16156,10 @@
         <v>4.4583333333333304</v>
       </c>
       <c r="B264" t="s">
+        <v>541</v>
+      </c>
+      <c r="C264" t="s">
         <v>542</v>
-      </c>
-      <c r="C264" t="s">
-        <v>543</v>
       </c>
       <c r="D264">
         <v>105</v>
@@ -16183,7 +16180,7 @@
         <v>19</v>
       </c>
       <c r="J264" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K264">
         <v>2</v>
@@ -16209,10 +16206,10 @@
         <v>4.5</v>
       </c>
       <c r="B265" t="s">
+        <v>543</v>
+      </c>
+      <c r="C265" t="s">
         <v>544</v>
-      </c>
-      <c r="C265" t="s">
-        <v>545</v>
       </c>
       <c r="D265">
         <v>105</v>
@@ -16259,10 +16256,10 @@
         <v>4.5416666666666696</v>
       </c>
       <c r="B266" t="s">
+        <v>546</v>
+      </c>
+      <c r="C266" t="s">
         <v>547</v>
-      </c>
-      <c r="C266" t="s">
-        <v>548</v>
       </c>
       <c r="D266">
         <v>100</v>
@@ -16283,7 +16280,7 @@
         <v>19</v>
       </c>
       <c r="J266" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K266">
         <v>2</v>
@@ -16309,10 +16306,10 @@
         <v>4.5833333333333401</v>
       </c>
       <c r="B267" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C267" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D267">
         <v>108</v>
@@ -16333,7 +16330,7 @@
         <v>19</v>
       </c>
       <c r="J267" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K267">
         <v>2</v>
@@ -16359,10 +16356,10 @@
         <v>4.6250000000000098</v>
       </c>
       <c r="B268" t="s">
+        <v>549</v>
+      </c>
+      <c r="C268" t="s">
         <v>550</v>
-      </c>
-      <c r="C268" t="s">
-        <v>551</v>
       </c>
       <c r="D268">
         <v>100</v>
@@ -16383,7 +16380,7 @@
         <v>19</v>
       </c>
       <c r="J268" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K268">
         <v>1</v>
@@ -16409,10 +16406,10 @@
         <v>4.6666666666666803</v>
       </c>
       <c r="B269" t="s">
+        <v>551</v>
+      </c>
+      <c r="C269" t="s">
         <v>552</v>
-      </c>
-      <c r="C269" t="s">
-        <v>553</v>
       </c>
       <c r="D269">
         <v>65</v>
@@ -16433,7 +16430,7 @@
         <v>19</v>
       </c>
       <c r="J269" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K269">
         <v>1</v>
@@ -16459,10 +16456,10 @@
         <v>4.7083333333333499</v>
       </c>
       <c r="B270" t="s">
+        <v>551</v>
+      </c>
+      <c r="C270" t="s">
         <v>552</v>
-      </c>
-      <c r="C270" t="s">
-        <v>553</v>
       </c>
       <c r="D270">
         <v>65</v>
@@ -16483,7 +16480,7 @@
         <v>19</v>
       </c>
       <c r="J270" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K270">
         <v>2</v>
@@ -16509,10 +16506,10 @@
         <v>4.7500000000000204</v>
       </c>
       <c r="B271" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C271" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D271">
         <v>65</v>
@@ -16533,7 +16530,7 @@
         <v>19</v>
       </c>
       <c r="J271" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K271">
         <v>1</v>
@@ -16559,10 +16556,10 @@
         <v>4.7916666666666901</v>
       </c>
       <c r="B272" t="s">
+        <v>553</v>
+      </c>
+      <c r="C272" t="s">
         <v>554</v>
-      </c>
-      <c r="C272" t="s">
-        <v>555</v>
       </c>
       <c r="D272">
         <v>120</v>
@@ -16609,10 +16606,10 @@
         <v>4.8333333333333597</v>
       </c>
       <c r="B273" t="s">
+        <v>555</v>
+      </c>
+      <c r="C273" t="s">
         <v>556</v>
-      </c>
-      <c r="C273" t="s">
-        <v>557</v>
       </c>
       <c r="D273">
         <v>120</v>
@@ -16659,10 +16656,10 @@
         <v>4.8750000000000302</v>
       </c>
       <c r="B274" t="s">
+        <v>557</v>
+      </c>
+      <c r="C274" t="s">
         <v>558</v>
-      </c>
-      <c r="C274" t="s">
-        <v>559</v>
       </c>
       <c r="D274">
         <v>80</v>
@@ -16709,10 +16706,10 @@
         <v>4.9166666666666998</v>
       </c>
       <c r="B275" t="s">
+        <v>559</v>
+      </c>
+      <c r="C275" t="s">
         <v>560</v>
-      </c>
-      <c r="C275" t="s">
-        <v>561</v>
       </c>
       <c r="D275">
         <v>105</v>
@@ -16759,10 +16756,10 @@
         <v>4.9583333333333703</v>
       </c>
       <c r="B276" t="s">
+        <v>561</v>
+      </c>
+      <c r="C276" t="s">
         <v>562</v>
-      </c>
-      <c r="C276" t="s">
-        <v>563</v>
       </c>
       <c r="D276">
         <v>105</v>
@@ -16783,7 +16780,7 @@
         <v>19</v>
       </c>
       <c r="J276" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K276">
         <v>3</v>
@@ -16809,10 +16806,10 @@
         <v>5.00000000000004</v>
       </c>
       <c r="B277" t="s">
+        <v>563</v>
+      </c>
+      <c r="C277" t="s">
         <v>564</v>
-      </c>
-      <c r="C277" t="s">
-        <v>565</v>
       </c>
       <c r="D277">
         <v>105</v>
@@ -16833,7 +16830,7 @@
         <v>19</v>
       </c>
       <c r="J277" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K277">
         <v>3</v>
@@ -16859,10 +16856,10 @@
         <v>5.0416666666667096</v>
       </c>
       <c r="B278" t="s">
+        <v>565</v>
+      </c>
+      <c r="C278" t="s">
         <v>566</v>
-      </c>
-      <c r="C278" t="s">
-        <v>567</v>
       </c>
       <c r="D278">
         <v>105</v>
@@ -16909,10 +16906,10 @@
         <v>5.0833333333333801</v>
       </c>
       <c r="B279" t="s">
+        <v>567</v>
+      </c>
+      <c r="C279" t="s">
         <v>568</v>
-      </c>
-      <c r="C279" t="s">
-        <v>569</v>
       </c>
       <c r="D279">
         <v>105</v>
@@ -16959,10 +16956,10 @@
         <v>5.1250000000000497</v>
       </c>
       <c r="B280" t="s">
+        <v>569</v>
+      </c>
+      <c r="C280" t="s">
         <v>570</v>
-      </c>
-      <c r="C280" t="s">
-        <v>571</v>
       </c>
       <c r="D280">
         <v>105</v>
@@ -17009,10 +17006,10 @@
         <v>5.1666666666667203</v>
       </c>
       <c r="B281" t="s">
+        <v>571</v>
+      </c>
+      <c r="C281" t="s">
         <v>572</v>
-      </c>
-      <c r="C281" t="s">
-        <v>573</v>
       </c>
       <c r="D281">
         <v>105</v>
@@ -17059,10 +17056,10 @@
         <v>5.2083333333333899</v>
       </c>
       <c r="B282" t="s">
+        <v>573</v>
+      </c>
+      <c r="C282" t="s">
         <v>574</v>
-      </c>
-      <c r="C282" t="s">
-        <v>575</v>
       </c>
       <c r="D282">
         <v>105</v>
@@ -17109,10 +17106,10 @@
         <v>5.458333333333333</v>
       </c>
       <c r="B283" t="s">
+        <v>575</v>
+      </c>
+      <c r="C283" t="s">
         <v>576</v>
-      </c>
-      <c r="C283" t="s">
-        <v>577</v>
       </c>
       <c r="D283">
         <v>285</v>
@@ -17133,7 +17130,7 @@
         <v>19</v>
       </c>
       <c r="J283" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K283">
         <v>3</v>
@@ -17159,10 +17156,10 @@
         <v>5.5</v>
       </c>
       <c r="B284" t="s">
+        <v>578</v>
+      </c>
+      <c r="C284" t="s">
         <v>579</v>
-      </c>
-      <c r="C284" t="s">
-        <v>580</v>
       </c>
       <c r="D284">
         <v>285</v>
@@ -17183,7 +17180,7 @@
         <v>19</v>
       </c>
       <c r="J284" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K284">
         <v>3</v>
@@ -17209,10 +17206,10 @@
         <v>5.5416666666666696</v>
       </c>
       <c r="B285" t="s">
+        <v>581</v>
+      </c>
+      <c r="C285" t="s">
         <v>582</v>
-      </c>
-      <c r="C285" t="s">
-        <v>583</v>
       </c>
       <c r="D285">
         <v>285</v>
@@ -17233,7 +17230,7 @@
         <v>19</v>
       </c>
       <c r="J285" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K285">
         <v>3</v>
@@ -17259,10 +17256,10 @@
         <v>5.5833333333333401</v>
       </c>
       <c r="B286" t="s">
+        <v>583</v>
+      </c>
+      <c r="C286" t="s">
         <v>584</v>
-      </c>
-      <c r="C286" t="s">
-        <v>585</v>
       </c>
       <c r="D286">
         <v>285</v>
@@ -17283,7 +17280,7 @@
         <v>19</v>
       </c>
       <c r="J286" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K286">
         <v>3</v>
@@ -17309,10 +17306,10 @@
         <v>5.6250000000000098</v>
       </c>
       <c r="B287" t="s">
+        <v>585</v>
+      </c>
+      <c r="C287" t="s">
         <v>586</v>
-      </c>
-      <c r="C287" t="s">
-        <v>587</v>
       </c>
       <c r="D287">
         <v>285</v>
@@ -17359,10 +17356,10 @@
         <v>5.6666666666666803</v>
       </c>
       <c r="B288" t="s">
+        <v>587</v>
+      </c>
+      <c r="C288" t="s">
         <v>588</v>
-      </c>
-      <c r="C288" t="s">
-        <v>589</v>
       </c>
       <c r="D288">
         <v>280</v>
@@ -17409,10 +17406,10 @@
         <v>5.7083333333333499</v>
       </c>
       <c r="B289" t="s">
+        <v>589</v>
+      </c>
+      <c r="C289" t="s">
         <v>590</v>
-      </c>
-      <c r="C289" t="s">
-        <v>591</v>
       </c>
       <c r="D289">
         <v>281</v>
@@ -17459,10 +17456,10 @@
         <v>5.7500000000000204</v>
       </c>
       <c r="B290" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C290" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D290">
         <v>270</v>
@@ -17509,10 +17506,10 @@
         <v>5.7916666666666901</v>
       </c>
       <c r="B291" t="s">
+        <v>592</v>
+      </c>
+      <c r="C291" t="s">
         <v>593</v>
-      </c>
-      <c r="C291" t="s">
-        <v>594</v>
       </c>
       <c r="D291">
         <v>280</v>
@@ -17559,10 +17556,10 @@
         <v>5.8333333333333597</v>
       </c>
       <c r="B292" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C292" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D292">
         <v>285</v>
@@ -17609,10 +17606,10 @@
         <v>5.8750000000000302</v>
       </c>
       <c r="B293" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C293" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D293">
         <v>288</v>
@@ -17659,10 +17656,10 @@
         <v>5.9166666666666998</v>
       </c>
       <c r="B294" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C294" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D294">
         <v>358</v>
@@ -17709,10 +17706,10 @@
         <v>5.9583333333333703</v>
       </c>
       <c r="B295" t="s">
+        <v>597</v>
+      </c>
+      <c r="C295" t="s">
         <v>598</v>
-      </c>
-      <c r="C295" t="s">
-        <v>599</v>
       </c>
       <c r="D295">
         <v>15</v>
@@ -17759,10 +17756,10 @@
         <v>6.00000000000004</v>
       </c>
       <c r="B296" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C296" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D296">
         <v>266</v>
@@ -17809,10 +17806,10 @@
         <v>6.0416666666667096</v>
       </c>
       <c r="B297" t="s">
+        <v>600</v>
+      </c>
+      <c r="C297" t="s">
         <v>601</v>
-      </c>
-      <c r="C297" t="s">
-        <v>602</v>
       </c>
       <c r="D297">
         <v>250</v>
@@ -17859,10 +17856,10 @@
         <v>6.0833333333333801</v>
       </c>
       <c r="B298" t="s">
+        <v>602</v>
+      </c>
+      <c r="C298" t="s">
         <v>603</v>
-      </c>
-      <c r="C298" t="s">
-        <v>604</v>
       </c>
       <c r="D298">
         <v>10</v>
@@ -17909,10 +17906,10 @@
         <v>6.25</v>
       </c>
       <c r="B299" t="s">
+        <v>604</v>
+      </c>
+      <c r="C299" t="s">
         <v>605</v>
-      </c>
-      <c r="C299" t="s">
-        <v>606</v>
       </c>
       <c r="D299">
         <v>330</v>
@@ -17959,10 +17956,10 @@
         <v>6.2916666666666696</v>
       </c>
       <c r="B300" t="s">
+        <v>606</v>
+      </c>
+      <c r="C300" t="s">
         <v>607</v>
-      </c>
-      <c r="C300" t="s">
-        <v>608</v>
       </c>
       <c r="D300">
         <v>333</v>
@@ -18009,10 +18006,10 @@
         <v>6.3333333333333401</v>
       </c>
       <c r="B301" t="s">
+        <v>608</v>
+      </c>
+      <c r="C301" t="s">
         <v>609</v>
-      </c>
-      <c r="C301" t="s">
-        <v>610</v>
       </c>
       <c r="D301">
         <v>330</v>
@@ -18059,10 +18056,10 @@
         <v>6.3750000000000098</v>
       </c>
       <c r="B302" t="s">
+        <v>610</v>
+      </c>
+      <c r="C302" t="s">
         <v>611</v>
-      </c>
-      <c r="C302" t="s">
-        <v>612</v>
       </c>
       <c r="D302">
         <v>330</v>
@@ -18109,10 +18106,10 @@
         <v>6.4166666666666803</v>
       </c>
       <c r="B303" t="s">
+        <v>612</v>
+      </c>
+      <c r="C303" t="s">
         <v>613</v>
-      </c>
-      <c r="C303" t="s">
-        <v>614</v>
       </c>
       <c r="D303">
         <v>333</v>
@@ -18159,10 +18156,10 @@
         <v>6.4583333333333499</v>
       </c>
       <c r="B304" t="s">
+        <v>614</v>
+      </c>
+      <c r="C304" t="s">
         <v>615</v>
-      </c>
-      <c r="C304" t="s">
-        <v>616</v>
       </c>
       <c r="D304">
         <v>325</v>
@@ -18183,7 +18180,7 @@
         <v>19</v>
       </c>
       <c r="J304" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K304">
         <v>3</v>
@@ -18209,10 +18206,10 @@
         <v>6.5000000000000204</v>
       </c>
       <c r="B305" t="s">
+        <v>616</v>
+      </c>
+      <c r="C305" t="s">
         <v>617</v>
-      </c>
-      <c r="C305" t="s">
-        <v>618</v>
       </c>
       <c r="D305">
         <v>310</v>
@@ -18259,10 +18256,10 @@
         <v>6.5416666666666901</v>
       </c>
       <c r="B306" t="s">
+        <v>618</v>
+      </c>
+      <c r="C306" t="s">
         <v>619</v>
-      </c>
-      <c r="C306" t="s">
-        <v>620</v>
       </c>
       <c r="D306">
         <v>310</v>
@@ -18309,10 +18306,10 @@
         <v>6.5833333333333597</v>
       </c>
       <c r="B307" t="s">
+        <v>620</v>
+      </c>
+      <c r="C307" t="s">
         <v>621</v>
-      </c>
-      <c r="C307" t="s">
-        <v>622</v>
       </c>
       <c r="D307">
         <v>310</v>
@@ -18359,10 +18356,10 @@
         <v>6.6250000000000302</v>
       </c>
       <c r="B308" t="s">
+        <v>622</v>
+      </c>
+      <c r="C308" t="s">
         <v>623</v>
-      </c>
-      <c r="C308" t="s">
-        <v>624</v>
       </c>
       <c r="D308">
         <v>310</v>
@@ -18409,10 +18406,10 @@
         <v>6.6666666666666998</v>
       </c>
       <c r="B309" t="s">
+        <v>624</v>
+      </c>
+      <c r="C309" t="s">
         <v>625</v>
-      </c>
-      <c r="C309" t="s">
-        <v>626</v>
       </c>
       <c r="D309">
         <v>307</v>
@@ -18459,10 +18456,10 @@
         <v>6.7083333333333703</v>
       </c>
       <c r="B310" t="s">
+        <v>626</v>
+      </c>
+      <c r="C310" t="s">
         <v>627</v>
-      </c>
-      <c r="C310" t="s">
-        <v>628</v>
       </c>
       <c r="D310">
         <v>310</v>
@@ -18509,10 +18506,10 @@
         <v>6.75000000000004</v>
       </c>
       <c r="B311" t="s">
+        <v>628</v>
+      </c>
+      <c r="C311" t="s">
         <v>629</v>
-      </c>
-      <c r="C311" t="s">
-        <v>630</v>
       </c>
       <c r="D311">
         <v>5</v>
@@ -18559,10 +18556,10 @@
         <v>6.958333333333333</v>
       </c>
       <c r="B312" t="s">
+        <v>630</v>
+      </c>
+      <c r="C312" t="s">
         <v>631</v>
-      </c>
-      <c r="C312" t="s">
-        <v>632</v>
       </c>
       <c r="D312">
         <v>170</v>
@@ -18574,7 +18571,7 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H312" t="s">
         <v>18</v>
@@ -18609,10 +18606,10 @@
         <v>7</v>
       </c>
       <c r="B313" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C313" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D313">
         <v>180</v>
@@ -18624,7 +18621,7 @@
         <v>9.5</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H313" t="s">
         <v>18</v>
@@ -18659,10 +18656,10 @@
         <v>7.0416666666666696</v>
       </c>
       <c r="B314" t="s">
+        <v>633</v>
+      </c>
+      <c r="C314" t="s">
         <v>634</v>
-      </c>
-      <c r="C314" t="s">
-        <v>635</v>
       </c>
       <c r="D314">
         <v>134</v>
@@ -18709,10 +18706,10 @@
         <v>7.0833333333333401</v>
       </c>
       <c r="B315" t="s">
+        <v>635</v>
+      </c>
+      <c r="C315" t="s">
         <v>636</v>
-      </c>
-      <c r="C315" t="s">
-        <v>637</v>
       </c>
       <c r="D315">
         <v>130</v>
@@ -18759,10 +18756,10 @@
         <v>7.1250000000000098</v>
       </c>
       <c r="B316" t="s">
+        <v>637</v>
+      </c>
+      <c r="C316" t="s">
         <v>638</v>
-      </c>
-      <c r="C316" t="s">
-        <v>639</v>
       </c>
       <c r="D316">
         <v>123</v>
@@ -18809,10 +18806,10 @@
         <v>7.1666666666666803</v>
       </c>
       <c r="B317" t="s">
+        <v>639</v>
+      </c>
+      <c r="C317" t="s">
         <v>640</v>
-      </c>
-      <c r="C317" t="s">
-        <v>641</v>
       </c>
       <c r="D317">
         <v>123</v>
@@ -18859,10 +18856,10 @@
         <v>7.2083333333333499</v>
       </c>
       <c r="B318" t="s">
+        <v>641</v>
+      </c>
+      <c r="C318" t="s">
         <v>642</v>
-      </c>
-      <c r="C318" t="s">
-        <v>643</v>
       </c>
       <c r="D318">
         <v>145</v>
@@ -18909,10 +18906,10 @@
         <v>7.2500000000000204</v>
       </c>
       <c r="B319" t="s">
+        <v>643</v>
+      </c>
+      <c r="C319" t="s">
         <v>644</v>
-      </c>
-      <c r="C319" t="s">
-        <v>645</v>
       </c>
       <c r="D319">
         <v>146</v>
@@ -18959,10 +18956,10 @@
         <v>7.2916666666666901</v>
       </c>
       <c r="B320" t="s">
+        <v>645</v>
+      </c>
+      <c r="C320" t="s">
         <v>646</v>
-      </c>
-      <c r="C320" t="s">
-        <v>647</v>
       </c>
       <c r="D320">
         <v>147</v>
@@ -19009,10 +19006,10 @@
         <v>7.3333333333333597</v>
       </c>
       <c r="B321" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C321" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D321">
         <v>150</v>
@@ -19033,7 +19030,7 @@
         <v>19</v>
       </c>
       <c r="J321" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K321">
         <v>5</v>
@@ -19059,10 +19056,10 @@
         <v>7.3750000000000302</v>
       </c>
       <c r="B322" t="s">
+        <v>648</v>
+      </c>
+      <c r="C322" t="s">
         <v>649</v>
-      </c>
-      <c r="C322" t="s">
-        <v>650</v>
       </c>
       <c r="D322">
         <v>150</v>
@@ -19083,7 +19080,7 @@
         <v>19</v>
       </c>
       <c r="J322" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K322">
         <v>5</v>
@@ -19109,10 +19106,10 @@
         <v>7.4166666666666998</v>
       </c>
       <c r="B323" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C323" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D323">
         <v>155</v>
@@ -19133,7 +19130,7 @@
         <v>19</v>
       </c>
       <c r="J323" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K323">
         <v>5</v>
@@ -19159,10 +19156,10 @@
         <v>7.4583333333333703</v>
       </c>
       <c r="B324" t="s">
+        <v>651</v>
+      </c>
+      <c r="C324" t="s">
         <v>652</v>
-      </c>
-      <c r="C324" t="s">
-        <v>653</v>
       </c>
       <c r="D324">
         <v>155</v>
@@ -19183,7 +19180,7 @@
         <v>19</v>
       </c>
       <c r="J324" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K324">
         <v>5</v>
@@ -19209,10 +19206,10 @@
         <v>7.50000000000004</v>
       </c>
       <c r="B325" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C325" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D325">
         <v>155</v>
@@ -19233,7 +19230,7 @@
         <v>19</v>
       </c>
       <c r="J325" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K325">
         <v>5</v>
@@ -19259,10 +19256,10 @@
         <v>7.5416666666667096</v>
       </c>
       <c r="B326" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C326" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D326">
         <v>150</v>
@@ -19274,7 +19271,7 @@
         <v>6.3</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H326" t="s">
         <v>18</v>
@@ -19283,7 +19280,7 @@
         <v>19</v>
       </c>
       <c r="J326" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K326">
         <v>4</v>
@@ -19309,10 +19306,10 @@
         <v>7.5833333333333801</v>
       </c>
       <c r="B327" t="s">
+        <v>657</v>
+      </c>
+      <c r="C327" t="s">
         <v>658</v>
-      </c>
-      <c r="C327" t="s">
-        <v>659</v>
       </c>
       <c r="D327">
         <v>150</v>
@@ -19324,7 +19321,7 @@
         <v>6.3</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H327" t="s">
         <v>18</v>
@@ -19333,7 +19330,7 @@
         <v>19</v>
       </c>
       <c r="J327" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K327">
         <v>5</v>
@@ -19359,10 +19356,10 @@
         <v>7.041666666666667</v>
       </c>
       <c r="B328" t="s">
+        <v>659</v>
+      </c>
+      <c r="C328" t="s">
         <v>660</v>
-      </c>
-      <c r="C328" t="s">
-        <v>661</v>
       </c>
       <c r="D328">
         <v>335</v>
@@ -19383,7 +19380,7 @@
         <v>19</v>
       </c>
       <c r="J328" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K328">
         <v>2</v>
@@ -19409,10 +19406,10 @@
         <v>7.0833333333333304</v>
       </c>
       <c r="B329" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C329" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D329">
         <v>335</v>
@@ -19459,10 +19456,10 @@
         <v>7.125</v>
       </c>
       <c r="B330" t="s">
+        <v>662</v>
+      </c>
+      <c r="C330" t="s">
         <v>663</v>
-      </c>
-      <c r="C330" t="s">
-        <v>664</v>
       </c>
       <c r="D330">
         <v>340</v>
@@ -19483,7 +19480,7 @@
         <v>19</v>
       </c>
       <c r="J330" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K330">
         <v>6</v>
@@ -19509,10 +19506,10 @@
         <v>7.1666666666666696</v>
       </c>
       <c r="B331" t="s">
+        <v>664</v>
+      </c>
+      <c r="C331" t="s">
         <v>665</v>
-      </c>
-      <c r="C331" t="s">
-        <v>666</v>
       </c>
       <c r="D331">
         <v>230</v>
@@ -19533,7 +19530,7 @@
         <v>19</v>
       </c>
       <c r="J331" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K331">
         <v>4</v>
@@ -19559,10 +19556,10 @@
         <v>7.2083333333333401</v>
       </c>
       <c r="B332" t="s">
+        <v>666</v>
+      </c>
+      <c r="C332" t="s">
         <v>667</v>
-      </c>
-      <c r="C332" t="s">
-        <v>668</v>
       </c>
       <c r="D332">
         <v>322</v>
@@ -19609,10 +19606,10 @@
         <v>7.916666666666667</v>
       </c>
       <c r="B333" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C333" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D333">
         <v>350</v>
@@ -19633,7 +19630,7 @@
         <v>19</v>
       </c>
       <c r="J333" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K333">
         <v>4</v>
@@ -19659,10 +19656,10 @@
         <v>7.9583333333333304</v>
       </c>
       <c r="B334" t="s">
+        <v>669</v>
+      </c>
+      <c r="C334" t="s">
         <v>670</v>
-      </c>
-      <c r="C334" t="s">
-        <v>671</v>
       </c>
       <c r="D334">
         <v>340</v>
@@ -19683,7 +19680,7 @@
         <v>19</v>
       </c>
       <c r="J334" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K334">
         <v>4</v>
@@ -19709,10 +19706,10 @@
         <v>8</v>
       </c>
       <c r="B335" t="s">
+        <v>671</v>
+      </c>
+      <c r="C335" t="s">
         <v>672</v>
-      </c>
-      <c r="C335" t="s">
-        <v>673</v>
       </c>
       <c r="D335">
         <v>340</v>
@@ -19733,7 +19730,7 @@
         <v>19</v>
       </c>
       <c r="J335" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K335">
         <v>4</v>
@@ -19759,10 +19756,10 @@
         <v>8.0416666666666696</v>
       </c>
       <c r="B336" t="s">
+        <v>673</v>
+      </c>
+      <c r="C336" t="s">
         <v>674</v>
-      </c>
-      <c r="C336" t="s">
-        <v>675</v>
       </c>
       <c r="D336">
         <v>350</v>
@@ -19783,7 +19780,7 @@
         <v>19</v>
       </c>
       <c r="J336" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K336">
         <v>3</v>
@@ -19809,10 +19806,10 @@
         <v>8.0833333333333393</v>
       </c>
       <c r="B337" t="s">
+        <v>675</v>
+      </c>
+      <c r="C337" t="s">
         <v>676</v>
-      </c>
-      <c r="C337" t="s">
-        <v>677</v>
       </c>
       <c r="D337">
         <v>321</v>
@@ -19833,7 +19830,7 @@
         <v>19</v>
       </c>
       <c r="J337" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K337">
         <v>3</v>
@@ -19859,10 +19856,10 @@
         <v>8.1250000000000107</v>
       </c>
       <c r="B338" t="s">
+        <v>677</v>
+      </c>
+      <c r="C338" t="s">
         <v>678</v>
-      </c>
-      <c r="C338" t="s">
-        <v>679</v>
       </c>
       <c r="D338">
         <v>325</v>
@@ -19883,7 +19880,7 @@
         <v>19</v>
       </c>
       <c r="J338" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K338">
         <v>3</v>
@@ -19909,10 +19906,10 @@
         <v>8.1666666666666803</v>
       </c>
       <c r="B339" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C339" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D339">
         <v>329</v>
@@ -19933,7 +19930,7 @@
         <v>19</v>
       </c>
       <c r="J339" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K339">
         <v>3</v>
@@ -19959,10 +19956,10 @@
         <v>8.2083333333333499</v>
       </c>
       <c r="B340" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C340" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D340">
         <v>335</v>
@@ -19983,7 +19980,7 @@
         <v>19</v>
       </c>
       <c r="J340" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K340">
         <v>3</v>
@@ -20009,10 +20006,10 @@
         <v>8.2500000000000195</v>
       </c>
       <c r="B341" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C341" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D341">
         <v>310</v>
@@ -20033,7 +20030,7 @@
         <v>19</v>
       </c>
       <c r="J341" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K341">
         <v>3</v>
@@ -20059,10 +20056,10 @@
         <v>8.2916666666666892</v>
       </c>
       <c r="B342" t="s">
+        <v>682</v>
+      </c>
+      <c r="C342" t="s">
         <v>683</v>
-      </c>
-      <c r="C342" t="s">
-        <v>684</v>
       </c>
       <c r="D342">
         <v>310</v>
@@ -20083,7 +20080,7 @@
         <v>19</v>
       </c>
       <c r="J342" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K342">
         <v>3</v>
@@ -20109,10 +20106,10 @@
         <v>8.3333333333333606</v>
       </c>
       <c r="B343" t="s">
+        <v>684</v>
+      </c>
+      <c r="C343" t="s">
         <v>685</v>
-      </c>
-      <c r="C343" t="s">
-        <v>686</v>
       </c>
       <c r="D343">
         <v>310</v>
@@ -20133,7 +20130,7 @@
         <v>19</v>
       </c>
       <c r="J343" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K343">
         <v>3</v>
@@ -20159,10 +20156,10 @@
         <v>8.3750000000000302</v>
       </c>
       <c r="B344" t="s">
+        <v>686</v>
+      </c>
+      <c r="C344" t="s">
         <v>687</v>
-      </c>
-      <c r="C344" t="s">
-        <v>688</v>
       </c>
       <c r="D344">
         <v>10</v>
@@ -20174,7 +20171,7 @@
         <v>7.3</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H344" t="s">
         <v>127</v>
@@ -20209,10 +20206,10 @@
         <v>8.4166666666666998</v>
       </c>
       <c r="B345" t="s">
+        <v>688</v>
+      </c>
+      <c r="C345" t="s">
         <v>689</v>
-      </c>
-      <c r="C345" t="s">
-        <v>690</v>
       </c>
       <c r="D345">
         <v>50</v>
@@ -20224,7 +20221,7 @@
         <v>6.3</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H345" t="s">
         <v>127</v>
@@ -20259,10 +20256,10 @@
         <v>8.4583333333333695</v>
       </c>
       <c r="B346" t="s">
+        <v>690</v>
+      </c>
+      <c r="C346" t="s">
         <v>691</v>
-      </c>
-      <c r="C346" t="s">
-        <v>692</v>
       </c>
       <c r="D346">
         <v>0</v>
@@ -20274,7 +20271,7 @@
         <v>6.2</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H346" t="s">
         <v>127</v>
@@ -20309,10 +20306,10 @@
         <v>8.5000000000000409</v>
       </c>
       <c r="B347" t="s">
+        <v>692</v>
+      </c>
+      <c r="C347" t="s">
         <v>693</v>
-      </c>
-      <c r="C347" t="s">
-        <v>694</v>
       </c>
       <c r="D347">
         <v>0</v>
@@ -20324,7 +20321,7 @@
         <v>7</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H347" t="s">
         <v>127</v>
@@ -20333,7 +20330,7 @@
         <v>19</v>
       </c>
       <c r="J347" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K347">
         <v>4</v>
@@ -20359,10 +20356,10 @@
         <v>8.5416666666667105</v>
       </c>
       <c r="B348" t="s">
+        <v>694</v>
+      </c>
+      <c r="C348" t="s">
         <v>695</v>
-      </c>
-      <c r="C348" t="s">
-        <v>696</v>
       </c>
       <c r="D348">
         <v>350</v>
@@ -20383,7 +20380,7 @@
         <v>19</v>
       </c>
       <c r="J348" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K348">
         <v>4</v>
@@ -20409,10 +20406,10 @@
         <v>8.5833333333333801</v>
       </c>
       <c r="B349" t="s">
+        <v>696</v>
+      </c>
+      <c r="C349" t="s">
         <v>697</v>
-      </c>
-      <c r="C349" t="s">
-        <v>698</v>
       </c>
       <c r="D349">
         <v>350</v>
@@ -20433,7 +20430,7 @@
         <v>19</v>
       </c>
       <c r="J349" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K349">
         <v>4</v>
@@ -20459,10 +20456,10 @@
         <v>8.6250000000000497</v>
       </c>
       <c r="B350" t="s">
+        <v>698</v>
+      </c>
+      <c r="C350" t="s">
         <v>699</v>
-      </c>
-      <c r="C350" t="s">
-        <v>700</v>
       </c>
       <c r="D350">
         <v>350</v>
@@ -20474,7 +20471,7 @@
         <v>6.5</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H350" t="s">
         <v>127</v>
@@ -20483,7 +20480,7 @@
         <v>19</v>
       </c>
       <c r="J350" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K350">
         <v>4</v>
@@ -20509,10 +20506,10 @@
         <v>8.6666666666667194</v>
       </c>
       <c r="B351" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C351" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D351">
         <v>325</v>
@@ -20524,7 +20521,7 @@
         <v>7.3</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H351" t="s">
         <v>127</v>
@@ -20533,7 +20530,7 @@
         <v>19</v>
       </c>
       <c r="J351" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K351">
         <v>4</v>
@@ -20559,10 +20556,10 @@
         <v>8.7083333333333908</v>
       </c>
       <c r="B352" t="s">
+        <v>701</v>
+      </c>
+      <c r="C352" t="s">
         <v>702</v>
-      </c>
-      <c r="C352" t="s">
-        <v>703</v>
       </c>
       <c r="D352">
         <v>325</v>
@@ -20574,7 +20571,7 @@
         <v>7.6</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H352" t="s">
         <v>127</v>
@@ -20583,7 +20580,7 @@
         <v>19</v>
       </c>
       <c r="J352" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K352">
         <v>5</v>
@@ -20609,10 +20606,10 @@
         <v>8.7500000000000604</v>
       </c>
       <c r="B353" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C353" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D353">
         <v>335</v>
@@ -20624,7 +20621,7 @@
         <v>7.2</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H353" t="s">
         <v>127</v>
@@ -20659,10 +20656,10 @@
         <v>8.79166666666673</v>
       </c>
       <c r="B354" t="s">
+        <v>704</v>
+      </c>
+      <c r="C354" t="s">
         <v>705</v>
-      </c>
-      <c r="C354" t="s">
-        <v>706</v>
       </c>
       <c r="D354">
         <v>335</v>
@@ -20674,7 +20671,7 @@
         <v>5.4</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H354" t="s">
         <v>127</v>
@@ -20683,7 +20680,7 @@
         <v>19</v>
       </c>
       <c r="J354" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="K354">
         <v>5</v>
@@ -20709,10 +20706,10 @@
         <v>8.8333333333333997</v>
       </c>
       <c r="B355" t="s">
+        <v>708</v>
+      </c>
+      <c r="C355" t="s">
         <v>709</v>
-      </c>
-      <c r="C355" t="s">
-        <v>710</v>
       </c>
       <c r="D355">
         <v>335</v>
@@ -20759,10 +20756,10 @@
         <v>8.8750000000000693</v>
       </c>
       <c r="B356" t="s">
+        <v>710</v>
+      </c>
+      <c r="C356" t="s">
         <v>711</v>
-      </c>
-      <c r="C356" t="s">
-        <v>712</v>
       </c>
       <c r="D356">
         <v>335</v>
@@ -20809,10 +20806,10 @@
         <v>8.9166666666667407</v>
       </c>
       <c r="B357" t="s">
+        <v>712</v>
+      </c>
+      <c r="C357" t="s">
         <v>713</v>
-      </c>
-      <c r="C357" t="s">
-        <v>714</v>
       </c>
       <c r="D357">
         <v>335</v>
@@ -20862,7 +20859,7 @@
         <v>139</v>
       </c>
       <c r="C358" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D358">
         <v>345</v>
@@ -20909,10 +20906,10 @@
         <v>9.0000000000000799</v>
       </c>
       <c r="B359" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C359" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D359">
         <v>325</v>
@@ -20959,10 +20956,10 @@
         <v>9.0416666666667496</v>
       </c>
       <c r="B360" t="s">
+        <v>716</v>
+      </c>
+      <c r="C360" t="s">
         <v>717</v>
-      </c>
-      <c r="C360" t="s">
-        <v>718</v>
       </c>
       <c r="D360">
         <v>335</v>
@@ -20983,7 +20980,7 @@
         <v>19</v>
       </c>
       <c r="J360" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="K360">
         <v>5</v>
@@ -21009,10 +21006,10 @@
         <v>9.0833333333334192</v>
       </c>
       <c r="B361" t="s">
+        <v>719</v>
+      </c>
+      <c r="C361" t="s">
         <v>720</v>
-      </c>
-      <c r="C361" t="s">
-        <v>721</v>
       </c>
       <c r="D361">
         <v>325</v>
@@ -21033,7 +21030,7 @@
         <v>19</v>
       </c>
       <c r="J361" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="K361">
         <v>5</v>
@@ -21059,10 +21056,10 @@
         <v>9.1250000000000906</v>
       </c>
       <c r="B362" t="s">
+        <v>722</v>
+      </c>
+      <c r="C362" t="s">
         <v>723</v>
-      </c>
-      <c r="C362" t="s">
-        <v>724</v>
       </c>
       <c r="D362">
         <v>335</v>
@@ -21083,7 +21080,7 @@
         <v>19</v>
       </c>
       <c r="J362" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="K362">
         <v>5</v>
@@ -21109,10 +21106,10 @@
         <v>9.1666666666667602</v>
       </c>
       <c r="B363" t="s">
+        <v>724</v>
+      </c>
+      <c r="C363" t="s">
         <v>725</v>
-      </c>
-      <c r="C363" t="s">
-        <v>726</v>
       </c>
       <c r="D363">
         <v>330</v>
@@ -21133,7 +21130,7 @@
         <v>19</v>
       </c>
       <c r="J363" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="K363">
         <v>5</v>
@@ -21159,10 +21156,10 @@
         <v>9.2083333333334298</v>
       </c>
       <c r="B364" t="s">
+        <v>726</v>
+      </c>
+      <c r="C364" t="s">
         <v>727</v>
-      </c>
-      <c r="C364" t="s">
-        <v>728</v>
       </c>
       <c r="D364">
         <v>340</v>
@@ -21209,10 +21206,10 @@
         <v>9.2500000000000995</v>
       </c>
       <c r="B365" t="s">
+        <v>729</v>
+      </c>
+      <c r="C365" t="s">
         <v>730</v>
-      </c>
-      <c r="C365" t="s">
-        <v>731</v>
       </c>
       <c r="D365">
         <v>340</v>
@@ -21259,10 +21256,10 @@
         <v>9.2916666666667709</v>
       </c>
       <c r="B366" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C366" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D366">
         <v>345</v>
@@ -21309,10 +21306,10 @@
         <v>9.3333333333334405</v>
       </c>
       <c r="B367" t="s">
+        <v>732</v>
+      </c>
+      <c r="C367" t="s">
         <v>733</v>
-      </c>
-      <c r="C367" t="s">
-        <v>734</v>
       </c>
       <c r="D367">
         <v>340</v>
@@ -21359,10 +21356,10 @@
         <v>9.3750000000001101</v>
       </c>
       <c r="B368" t="s">
+        <v>734</v>
+      </c>
+      <c r="C368" t="s">
         <v>735</v>
-      </c>
-      <c r="C368" t="s">
-        <v>736</v>
       </c>
       <c r="D368">
         <v>345</v>
@@ -21409,10 +21406,10 @@
         <v>9.4166666666667798</v>
       </c>
       <c r="B369" t="s">
+        <v>736</v>
+      </c>
+      <c r="C369" t="s">
         <v>737</v>
-      </c>
-      <c r="C369" t="s">
-        <v>738</v>
       </c>
       <c r="D369">
         <v>340</v>
@@ -21459,10 +21456,10 @@
         <v>9.4583333333334494</v>
       </c>
       <c r="B370" t="s">
+        <v>738</v>
+      </c>
+      <c r="C370" t="s">
         <v>739</v>
-      </c>
-      <c r="C370" t="s">
-        <v>740</v>
       </c>
       <c r="D370">
         <v>330</v>
@@ -21509,10 +21506,10 @@
         <v>9.5000000000001208</v>
       </c>
       <c r="B371" t="s">
+        <v>740</v>
+      </c>
+      <c r="C371" t="s">
         <v>741</v>
-      </c>
-      <c r="C371" t="s">
-        <v>742</v>
       </c>
       <c r="D371">
         <v>350</v>
@@ -21559,10 +21556,10 @@
         <v>9.5416666666667904</v>
       </c>
       <c r="B372" t="s">
+        <v>742</v>
+      </c>
+      <c r="C372" t="s">
         <v>743</v>
-      </c>
-      <c r="C372" t="s">
-        <v>744</v>
       </c>
       <c r="D372">
         <v>340</v>
@@ -21583,7 +21580,7 @@
         <v>19</v>
       </c>
       <c r="J372" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K372">
         <v>2</v>
@@ -21609,10 +21606,10 @@
         <v>9.58333333333346</v>
       </c>
       <c r="B373" t="s">
+        <v>744</v>
+      </c>
+      <c r="C373" t="s">
         <v>745</v>
-      </c>
-      <c r="C373" t="s">
-        <v>746</v>
       </c>
       <c r="D373">
         <v>335</v>
@@ -21659,10 +21656,10 @@
         <v>9.6250000000001297</v>
       </c>
       <c r="B374" t="s">
+        <v>746</v>
+      </c>
+      <c r="C374" t="s">
         <v>747</v>
-      </c>
-      <c r="C374" t="s">
-        <v>748</v>
       </c>
       <c r="D374">
         <v>345</v>
@@ -21709,10 +21706,10 @@
         <v>9.6666666666667993</v>
       </c>
       <c r="B375" t="s">
+        <v>748</v>
+      </c>
+      <c r="C375" t="s">
         <v>749</v>
-      </c>
-      <c r="C375" t="s">
-        <v>750</v>
       </c>
       <c r="D375">
         <v>350</v>
@@ -21759,10 +21756,10 @@
         <v>9.7083333333334707</v>
       </c>
       <c r="B376" t="s">
+        <v>750</v>
+      </c>
+      <c r="C376" t="s">
         <v>751</v>
-      </c>
-      <c r="C376" t="s">
-        <v>752</v>
       </c>
       <c r="D376">
         <v>350</v>
@@ -21809,10 +21806,10 @@
         <v>9.7500000000001403</v>
       </c>
       <c r="B377" t="s">
+        <v>752</v>
+      </c>
+      <c r="C377" t="s">
         <v>753</v>
-      </c>
-      <c r="C377" t="s">
-        <v>754</v>
       </c>
       <c r="D377">
         <v>350</v>
@@ -21859,10 +21856,10 @@
         <v>9.79166666666681</v>
       </c>
       <c r="B378" t="s">
+        <v>754</v>
+      </c>
+      <c r="C378" t="s">
         <v>755</v>
-      </c>
-      <c r="C378" t="s">
-        <v>756</v>
       </c>
       <c r="D378">
         <v>350</v>
@@ -21909,10 +21906,10 @@
         <v>9.8333333333334796</v>
       </c>
       <c r="B379" t="s">
+        <v>756</v>
+      </c>
+      <c r="C379" t="s">
         <v>757</v>
-      </c>
-      <c r="C379" t="s">
-        <v>758</v>
       </c>
       <c r="D379">
         <v>350</v>
@@ -21959,10 +21956,10 @@
         <v>9.8750000000001492</v>
       </c>
       <c r="B380" t="s">
+        <v>758</v>
+      </c>
+      <c r="C380" t="s">
         <v>759</v>
-      </c>
-      <c r="C380" t="s">
-        <v>760</v>
       </c>
       <c r="D380">
         <v>350</v>
@@ -22009,10 +22006,10 @@
         <v>9.9166666666668206</v>
       </c>
       <c r="B381" t="s">
+        <v>760</v>
+      </c>
+      <c r="C381" t="s">
         <v>761</v>
-      </c>
-      <c r="C381" t="s">
-        <v>762</v>
       </c>
       <c r="D381">
         <v>345</v>
@@ -22059,10 +22056,10 @@
         <v>9.9583333333334902</v>
       </c>
       <c r="B382" t="s">
+        <v>762</v>
+      </c>
+      <c r="C382" t="s">
         <v>763</v>
-      </c>
-      <c r="C382" t="s">
-        <v>764</v>
       </c>
       <c r="D382">
         <v>343</v>
@@ -22083,7 +22080,7 @@
         <v>19</v>
       </c>
       <c r="J382" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K382">
         <v>3</v>
@@ -22109,10 +22106,10 @@
         <v>10.000000000000201</v>
       </c>
       <c r="B383" t="s">
+        <v>764</v>
+      </c>
+      <c r="C383" t="s">
         <v>765</v>
-      </c>
-      <c r="C383" t="s">
-        <v>766</v>
       </c>
       <c r="D383">
         <v>14</v>
@@ -22133,7 +22130,7 @@
         <v>19</v>
       </c>
       <c r="J383" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K383">
         <v>3</v>
@@ -22159,10 +22156,10 @@
         <v>10.041666666666901</v>
       </c>
       <c r="B384" t="s">
+        <v>766</v>
+      </c>
+      <c r="C384" t="s">
         <v>767</v>
-      </c>
-      <c r="C384" t="s">
-        <v>768</v>
       </c>
       <c r="D384">
         <v>20</v>
@@ -22209,10 +22206,10 @@
         <v>10.0833333333336</v>
       </c>
       <c r="B385" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C385" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D385">
         <v>350</v>
@@ -22259,10 +22256,10 @@
         <v>10.125</v>
       </c>
       <c r="B386" t="s">
+        <v>769</v>
+      </c>
+      <c r="C386" t="s">
         <v>770</v>
-      </c>
-      <c r="C386" t="s">
-        <v>771</v>
       </c>
       <c r="D386">
         <v>43</v>
@@ -22309,10 +22306,10 @@
         <v>10.541666666666666</v>
       </c>
       <c r="B387" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C387" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D387">
         <v>130</v>
@@ -22333,7 +22330,7 @@
         <v>19</v>
       </c>
       <c r="J387" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K387">
         <v>3</v>
@@ -22359,10 +22356,10 @@
         <v>10.5833333333333</v>
       </c>
       <c r="B388" t="s">
+        <v>773</v>
+      </c>
+      <c r="C388" t="s">
         <v>774</v>
-      </c>
-      <c r="C388" t="s">
-        <v>775</v>
       </c>
       <c r="D388">
         <v>160</v>
@@ -22409,10 +22406,10 @@
         <v>10.625</v>
       </c>
       <c r="B389" t="s">
+        <v>775</v>
+      </c>
+      <c r="C389" t="s">
         <v>776</v>
-      </c>
-      <c r="C389" t="s">
-        <v>777</v>
       </c>
       <c r="D389">
         <v>140</v>
@@ -22424,7 +22421,7 @@
         <v>5.9</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H389" t="s">
         <v>18</v>
@@ -22459,10 +22456,10 @@
         <v>10.6666666666667</v>
       </c>
       <c r="B390" t="s">
+        <v>777</v>
+      </c>
+      <c r="C390" t="s">
         <v>778</v>
-      </c>
-      <c r="C390" t="s">
-        <v>779</v>
       </c>
       <c r="D390">
         <v>115</v>
@@ -22474,7 +22471,7 @@
         <v>7.7</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H390" t="s">
         <v>18</v>
@@ -22483,7 +22480,7 @@
         <v>19</v>
       </c>
       <c r="J390" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K390">
         <v>5</v>
@@ -22509,10 +22506,10 @@
         <v>10.666666666666666</v>
       </c>
       <c r="B391" t="s">
+        <v>779</v>
+      </c>
+      <c r="C391" t="s">
         <v>780</v>
-      </c>
-      <c r="C391" t="s">
-        <v>781</v>
       </c>
       <c r="D391">
         <v>180</v>
@@ -22559,10 +22556,10 @@
         <v>10.7083333333333</v>
       </c>
       <c r="B392" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C392" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D392">
         <v>180</v>
@@ -22609,10 +22606,10 @@
         <v>10.75</v>
       </c>
       <c r="B393" t="s">
+        <v>782</v>
+      </c>
+      <c r="C393" t="s">
         <v>783</v>
-      </c>
-      <c r="C393" t="s">
-        <v>784</v>
       </c>
       <c r="D393">
         <v>180</v>
@@ -22659,10 +22656,10 @@
         <v>10.7916666666667</v>
       </c>
       <c r="B394" t="s">
+        <v>784</v>
+      </c>
+      <c r="C394" t="s">
         <v>785</v>
-      </c>
-      <c r="C394" t="s">
-        <v>786</v>
       </c>
       <c r="D394">
         <v>170</v>
@@ -22709,10 +22706,10 @@
         <v>10.8333333333334</v>
       </c>
       <c r="B395" t="s">
+        <v>786</v>
+      </c>
+      <c r="C395" t="s">
         <v>787</v>
-      </c>
-      <c r="C395" t="s">
-        <v>788</v>
       </c>
       <c r="D395">
         <v>170</v>
@@ -22759,10 +22756,10 @@
         <v>10.875000000000099</v>
       </c>
       <c r="B396" t="s">
+        <v>788</v>
+      </c>
+      <c r="C396" t="s">
         <v>789</v>
-      </c>
-      <c r="C396" t="s">
-        <v>790</v>
       </c>
       <c r="D396">
         <v>195</v>
@@ -22809,10 +22806,10 @@
         <v>10.916666666666799</v>
       </c>
       <c r="B397" t="s">
+        <v>790</v>
+      </c>
+      <c r="C397" t="s">
         <v>791</v>
-      </c>
-      <c r="C397" t="s">
-        <v>792</v>
       </c>
       <c r="D397">
         <v>130</v>
@@ -22859,10 +22856,10 @@
         <v>10.958333333333499</v>
       </c>
       <c r="B398" t="s">
+        <v>792</v>
+      </c>
+      <c r="C398" t="s">
         <v>793</v>
-      </c>
-      <c r="C398" t="s">
-        <v>794</v>
       </c>
       <c r="D398">
         <v>140</v>
@@ -22883,7 +22880,7 @@
         <v>19</v>
       </c>
       <c r="J398" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K398">
         <v>3</v>
@@ -22909,10 +22906,10 @@
         <v>11.000000000000201</v>
       </c>
       <c r="B399" t="s">
+        <v>794</v>
+      </c>
+      <c r="C399" t="s">
         <v>795</v>
-      </c>
-      <c r="C399" t="s">
-        <v>796</v>
       </c>
       <c r="D399">
         <v>165</v>
@@ -22959,10 +22956,10 @@
         <v>11.041666666666901</v>
       </c>
       <c r="B400" t="s">
+        <v>796</v>
+      </c>
+      <c r="C400" t="s">
         <v>797</v>
-      </c>
-      <c r="C400" t="s">
-        <v>798</v>
       </c>
       <c r="D400">
         <v>140</v>
@@ -22983,7 +22980,7 @@
         <v>19</v>
       </c>
       <c r="J400" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K400">
         <v>3</v>
@@ -23009,10 +23006,10 @@
         <v>11.0833333333336</v>
       </c>
       <c r="B401" t="s">
+        <v>798</v>
+      </c>
+      <c r="C401" t="s">
         <v>799</v>
-      </c>
-      <c r="C401" t="s">
-        <v>800</v>
       </c>
       <c r="D401">
         <v>130</v>
@@ -23033,7 +23030,7 @@
         <v>19</v>
       </c>
       <c r="J401" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K401">
         <v>3</v>
@@ -23059,10 +23056,10 @@
         <v>11.1250000000003</v>
       </c>
       <c r="B402" t="s">
+        <v>800</v>
+      </c>
+      <c r="C402" t="s">
         <v>801</v>
-      </c>
-      <c r="C402" t="s">
-        <v>802</v>
       </c>
       <c r="D402">
         <v>130</v>
@@ -23083,7 +23080,7 @@
         <v>19</v>
       </c>
       <c r="J402" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K402">
         <v>3</v>
@@ -23109,10 +23106,10 @@
         <v>11.166666666667</v>
       </c>
       <c r="B403" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C403" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D403">
         <v>155</v>
@@ -23133,7 +23130,7 @@
         <v>19</v>
       </c>
       <c r="J403" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K403">
         <v>3</v>
@@ -23159,10 +23156,10 @@
         <v>11.2083333333337</v>
       </c>
       <c r="B404" t="s">
+        <v>804</v>
+      </c>
+      <c r="C404" t="s">
         <v>805</v>
-      </c>
-      <c r="C404" t="s">
-        <v>806</v>
       </c>
       <c r="D404">
         <v>170</v>
@@ -23183,7 +23180,7 @@
         <v>19</v>
       </c>
       <c r="J404" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K404">
         <v>3</v>
@@ -23209,10 +23206,10 @@
         <v>11.2500000000004</v>
       </c>
       <c r="B405" t="s">
+        <v>806</v>
+      </c>
+      <c r="C405" t="s">
         <v>807</v>
-      </c>
-      <c r="C405" t="s">
-        <v>808</v>
       </c>
       <c r="D405">
         <v>180</v>
@@ -23233,7 +23230,7 @@
         <v>19</v>
       </c>
       <c r="J405" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K405">
         <v>3</v>
@@ -23259,10 +23256,10 @@
         <v>11.2916666666671</v>
       </c>
       <c r="B406" t="s">
+        <v>808</v>
+      </c>
+      <c r="C406" t="s">
         <v>809</v>
-      </c>
-      <c r="C406" t="s">
-        <v>810</v>
       </c>
       <c r="D406">
         <v>180</v>
@@ -23283,7 +23280,7 @@
         <v>19</v>
       </c>
       <c r="J406" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K406">
         <v>4</v>
@@ -23309,10 +23306,10 @@
         <v>11.333333333333799</v>
       </c>
       <c r="B407" t="s">
+        <v>810</v>
+      </c>
+      <c r="C407" t="s">
         <v>811</v>
-      </c>
-      <c r="C407" t="s">
-        <v>812</v>
       </c>
       <c r="D407">
         <v>180</v>
@@ -23333,7 +23330,7 @@
         <v>19</v>
       </c>
       <c r="J407" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K407">
         <v>4</v>
@@ -23359,10 +23356,10 @@
         <v>11.375000000000499</v>
       </c>
       <c r="B408" t="s">
+        <v>813</v>
+      </c>
+      <c r="C408" t="s">
         <v>814</v>
-      </c>
-      <c r="C408" t="s">
-        <v>815</v>
       </c>
       <c r="D408">
         <v>145</v>
@@ -23383,7 +23380,7 @@
         <v>19</v>
       </c>
       <c r="J408" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K408">
         <v>4</v>
@@ -23412,7 +23409,7 @@
         <v>103</v>
       </c>
       <c r="C409" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D409">
         <v>135</v>
@@ -23433,7 +23430,7 @@
         <v>19</v>
       </c>
       <c r="J409" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K409">
         <v>4</v>
@@ -23459,10 +23456,10 @@
         <v>11.625</v>
       </c>
       <c r="B410" t="s">
+        <v>815</v>
+      </c>
+      <c r="C410" t="s">
         <v>816</v>
-      </c>
-      <c r="C410" t="s">
-        <v>817</v>
       </c>
       <c r="D410">
         <v>170</v>
@@ -23483,7 +23480,7 @@
         <v>19</v>
       </c>
       <c r="J410" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K410">
         <v>4</v>
@@ -23509,10 +23506,10 @@
         <v>11.6666666666667</v>
       </c>
       <c r="B411" t="s">
+        <v>817</v>
+      </c>
+      <c r="C411" t="s">
         <v>818</v>
-      </c>
-      <c r="C411" t="s">
-        <v>819</v>
       </c>
       <c r="D411">
         <v>180</v>
@@ -23533,7 +23530,7 @@
         <v>19</v>
       </c>
       <c r="J411" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K411">
         <v>5</v>
@@ -23559,10 +23556,10 @@
         <v>11.7083333333334</v>
       </c>
       <c r="B412" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C412" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D412">
         <v>180</v>
@@ -23583,7 +23580,7 @@
         <v>19</v>
       </c>
       <c r="J412" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K412">
         <v>6</v>
@@ -23609,10 +23606,10 @@
         <v>11.750000000000099</v>
       </c>
       <c r="B413" t="s">
+        <v>820</v>
+      </c>
+      <c r="C413" t="s">
         <v>821</v>
-      </c>
-      <c r="C413" t="s">
-        <v>822</v>
       </c>
       <c r="D413">
         <v>140</v>
@@ -23624,7 +23621,7 @@
         <v>5.8</v>
       </c>
       <c r="G413" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H413" t="s">
         <v>18</v>
@@ -23633,7 +23630,7 @@
         <v>19</v>
       </c>
       <c r="J413" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K413">
         <v>6</v>
@@ -23659,10 +23656,10 @@
         <v>11.791666666666799</v>
       </c>
       <c r="B414" t="s">
+        <v>822</v>
+      </c>
+      <c r="C414" t="s">
         <v>823</v>
-      </c>
-      <c r="C414" t="s">
-        <v>824</v>
       </c>
       <c r="D414">
         <v>140</v>
@@ -23674,7 +23671,7 @@
         <v>5.6</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H414" t="s">
         <v>18</v>
@@ -23683,7 +23680,7 @@
         <v>19</v>
       </c>
       <c r="J414" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K414">
         <v>5</v>
@@ -23709,10 +23706,10 @@
         <v>11.833333333333499</v>
       </c>
       <c r="B415" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C415" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D415">
         <v>140</v>
@@ -23724,7 +23721,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H415" t="s">
         <v>18</v>
@@ -23733,7 +23730,7 @@
         <v>19</v>
       </c>
       <c r="J415" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K415">
         <v>5</v>
@@ -23759,10 +23756,10 @@
         <v>11.875000000000201</v>
       </c>
       <c r="B416" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C416" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D416">
         <v>130</v>
@@ -23774,7 +23771,7 @@
         <v>4</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H416" t="s">
         <v>18</v>
@@ -23783,7 +23780,7 @@
         <v>19</v>
       </c>
       <c r="J416" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K416">
         <v>5</v>
@@ -23812,7 +23809,7 @@
         <v>43</v>
       </c>
       <c r="C417" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D417">
         <v>130</v>
@@ -23824,7 +23821,7 @@
         <v>5.2</v>
       </c>
       <c r="G417" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H417" t="s">
         <v>18</v>
@@ -23833,7 +23830,7 @@
         <v>19</v>
       </c>
       <c r="J417" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K417">
         <v>5</v>
@@ -23859,10 +23856,10 @@
         <v>11.9583333333336</v>
       </c>
       <c r="B418" t="s">
+        <v>827</v>
+      </c>
+      <c r="C418" t="s">
         <v>828</v>
-      </c>
-      <c r="C418" t="s">
-        <v>829</v>
       </c>
       <c r="D418">
         <v>125</v>
@@ -23874,7 +23871,7 @@
         <v>4.7</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H418" t="s">
         <v>18</v>
@@ -23883,7 +23880,7 @@
         <v>19</v>
       </c>
       <c r="J418" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K418">
         <v>5</v>
@@ -23909,10 +23906,10 @@
         <v>12.0000000000003</v>
       </c>
       <c r="B419" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C419" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D419">
         <v>210</v>
@@ -23933,7 +23930,7 @@
         <v>19</v>
       </c>
       <c r="J419" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K419">
         <v>4</v>
@@ -23959,10 +23956,10 @@
         <v>12.041666666667</v>
       </c>
       <c r="B420" t="s">
+        <v>830</v>
+      </c>
+      <c r="C420" t="s">
         <v>831</v>
-      </c>
-      <c r="C420" t="s">
-        <v>832</v>
       </c>
       <c r="D420">
         <v>135</v>
@@ -23983,7 +23980,7 @@
         <v>19</v>
       </c>
       <c r="J420" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K420">
         <v>4</v>
@@ -24009,10 +24006,10 @@
         <v>12.0833333333337</v>
       </c>
       <c r="B421" t="s">
+        <v>832</v>
+      </c>
+      <c r="C421" t="s">
         <v>833</v>
-      </c>
-      <c r="C421" t="s">
-        <v>834</v>
       </c>
       <c r="D421">
         <v>135</v>
@@ -24033,7 +24030,7 @@
         <v>19</v>
       </c>
       <c r="J421" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K421">
         <v>4</v>
@@ -24059,10 +24056,10 @@
         <v>12.1250000000004</v>
       </c>
       <c r="B422" t="s">
+        <v>834</v>
+      </c>
+      <c r="C422" t="s">
         <v>835</v>
-      </c>
-      <c r="C422" t="s">
-        <v>836</v>
       </c>
       <c r="D422">
         <v>140</v>
@@ -24083,7 +24080,7 @@
         <v>19</v>
       </c>
       <c r="J422" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K422">
         <v>5</v>
@@ -24109,10 +24106,10 @@
         <v>12.1666666666671</v>
       </c>
       <c r="B423" t="s">
+        <v>836</v>
+      </c>
+      <c r="C423" t="s">
         <v>837</v>
-      </c>
-      <c r="C423" t="s">
-        <v>838</v>
       </c>
       <c r="D423">
         <v>40</v>
@@ -24133,7 +24130,7 @@
         <v>19</v>
       </c>
       <c r="J423" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K423">
         <v>3</v>
@@ -24159,10 +24156,10 @@
         <v>12.208333333333799</v>
       </c>
       <c r="B424" t="s">
+        <v>838</v>
+      </c>
+      <c r="C424" t="s">
         <v>839</v>
-      </c>
-      <c r="C424" t="s">
-        <v>840</v>
       </c>
       <c r="D424">
         <v>40</v>
@@ -24183,7 +24180,7 @@
         <v>19</v>
       </c>
       <c r="J424" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K424">
         <v>5</v>
@@ -24209,10 +24206,10 @@
         <v>12.250000000000499</v>
       </c>
       <c r="B425" t="s">
+        <v>840</v>
+      </c>
+      <c r="C425" t="s">
         <v>841</v>
-      </c>
-      <c r="C425" t="s">
-        <v>842</v>
       </c>
       <c r="D425">
         <v>150</v>
@@ -24224,7 +24221,7 @@
         <v>5.3</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H425" t="s">
         <v>127</v>
@@ -24233,7 +24230,7 @@
         <v>19</v>
       </c>
       <c r="J425" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K425">
         <v>5</v>
@@ -24259,10 +24256,10 @@
         <v>12.291666666667201</v>
       </c>
       <c r="B426" t="s">
+        <v>842</v>
+      </c>
+      <c r="C426" t="s">
         <v>843</v>
-      </c>
-      <c r="C426" t="s">
-        <v>844</v>
       </c>
       <c r="D426">
         <v>150</v>
@@ -24274,7 +24271,7 @@
         <v>6.3</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H426" t="s">
         <v>127</v>
@@ -24283,7 +24280,7 @@
         <v>19</v>
       </c>
       <c r="J426" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K426">
         <v>5</v>
@@ -24309,10 +24306,10 @@
         <v>12.333333333333901</v>
       </c>
       <c r="B427" t="s">
+        <v>844</v>
+      </c>
+      <c r="C427" t="s">
         <v>845</v>
-      </c>
-      <c r="C427" t="s">
-        <v>846</v>
       </c>
       <c r="D427">
         <v>150</v>
@@ -24324,7 +24321,7 @@
         <v>6.6</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H427" t="s">
         <v>127</v>
@@ -24333,7 +24330,7 @@
         <v>19</v>
       </c>
       <c r="J427" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K427">
         <v>5</v>
@@ -24359,10 +24356,10 @@
         <v>12.3750000000006</v>
       </c>
       <c r="B428" t="s">
+        <v>846</v>
+      </c>
+      <c r="C428" t="s">
         <v>847</v>
-      </c>
-      <c r="C428" t="s">
-        <v>848</v>
       </c>
       <c r="D428">
         <v>135</v>
@@ -24374,7 +24371,7 @@
         <v>6.2</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H428" t="s">
         <v>127</v>
@@ -24383,7 +24380,7 @@
         <v>19</v>
       </c>
       <c r="J428" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K428">
         <v>5</v>
@@ -24409,10 +24406,10 @@
         <v>12.4166666666673</v>
       </c>
       <c r="B429" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C429" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D429">
         <v>160</v>
@@ -24424,7 +24421,7 @@
         <v>7.5</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H429" t="s">
         <v>127</v>
@@ -24433,7 +24430,7 @@
         <v>19</v>
       </c>
       <c r="J429" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K429">
         <v>5</v>
@@ -24459,10 +24456,10 @@
         <v>12.458333333334</v>
       </c>
       <c r="B430" t="s">
+        <v>849</v>
+      </c>
+      <c r="C430" t="s">
         <v>850</v>
-      </c>
-      <c r="C430" t="s">
-        <v>851</v>
       </c>
       <c r="D430">
         <v>150</v>
@@ -24474,7 +24471,7 @@
         <v>8</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H430" t="s">
         <v>127</v>
@@ -24483,7 +24480,7 @@
         <v>19</v>
       </c>
       <c r="J430" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K430">
         <v>5</v>
@@ -24509,10 +24506,10 @@
         <v>12.5000000000007</v>
       </c>
       <c r="B431" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C431" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D431">
         <v>150</v>
@@ -24524,7 +24521,7 @@
         <v>6.2</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H431" t="s">
         <v>127</v>
@@ -24533,7 +24530,7 @@
         <v>19</v>
       </c>
       <c r="J431" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K431">
         <v>4</v>
